--- a/statistics_files/2026/2026_99_ga_net_borrower_lender.xlsx
+++ b/statistics_files/2026/2026_99_ga_net_borrower_lender.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{393B4ABC-61E5-418D-A5DD-2FF5F3BE7DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B0DA0F8-5904-4B6E-A65D-DDF424EA9341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="868"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="868" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <sheet name="October" sheetId="10" r:id="rId10"/>
     <sheet name="November" sheetId="11" r:id="rId11"/>
     <sheet name="December" sheetId="12" r:id="rId12"/>
-    <sheet name="Yearly Totals" sheetId="13" r:id="rId13"/>
+    <sheet name="Yearly total" sheetId="13" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">April!$A$1:$G$54</definedName>
@@ -40,10 +40,19 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">November!$A$1:$G$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">October!$A$1:$G$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">September!$A$1:$G$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Yearly Totals'!$A$1:$G$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Yearly total'!$A$1:$G$54</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -384,7 +393,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1124,7 +1133,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="104">
+  <dxfs count="89">
     <dxf>
       <font>
         <color auto="1"/>
@@ -1142,6 +1151,36 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1949,180 +1988,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2432,7 +2297,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3573,39 +3438,39 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
+  <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="E2">
-    <cfRule type="expression" dxfId="92" priority="7">
+    <cfRule type="expression" dxfId="88" priority="7">
       <formula>"D2&gt;0"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E37 E40:E54">
-    <cfRule type="containsText" dxfId="91" priority="6" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="87" priority="6" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F37 F40:F54">
-    <cfRule type="containsText" dxfId="90" priority="5" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="86" priority="5" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38">
-    <cfRule type="containsText" dxfId="89" priority="4" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="85" priority="4" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38">
-    <cfRule type="containsText" dxfId="88" priority="3" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="84" priority="3" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39">
-    <cfRule type="containsText" dxfId="87" priority="2" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="83" priority="2" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="containsText" dxfId="86" priority="1" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="82" priority="1" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F39)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3614,7 +3479,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4233,39 +4098,39 @@
       <c r="G54" s="33"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
+  <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
   <conditionalFormatting sqref="E2">
-    <cfRule type="expression" dxfId="29" priority="7">
+    <cfRule type="expression" dxfId="25" priority="7">
       <formula>"D2&gt;0"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E37 E40:E54">
-    <cfRule type="containsText" dxfId="28" priority="6" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="24" priority="6" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F37 F40:F54">
-    <cfRule type="containsText" dxfId="27" priority="5" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="23" priority="5" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38">
-    <cfRule type="containsText" dxfId="26" priority="4" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="22" priority="4" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38">
-    <cfRule type="containsText" dxfId="25" priority="3" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39">
-    <cfRule type="containsText" dxfId="24" priority="2" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="20" priority="2" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F39)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4274,7 +4139,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4893,39 +4758,39 @@
       <c r="G54" s="33"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
+  <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-00000A000000}"/>
   <conditionalFormatting sqref="E2">
-    <cfRule type="expression" dxfId="22" priority="7">
+    <cfRule type="expression" dxfId="18" priority="7">
       <formula>"D2&gt;0"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E37 E40:E54">
-    <cfRule type="containsText" dxfId="21" priority="6" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F37 F40:F54">
-    <cfRule type="containsText" dxfId="20" priority="5" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38">
-    <cfRule type="containsText" dxfId="19" priority="4" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38">
-    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39">
-    <cfRule type="containsText" dxfId="17" priority="2" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F39)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4934,7 +4799,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5553,39 +5418,39 @@
       <c r="G54" s="33"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
+  <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
   <conditionalFormatting sqref="E2">
-    <cfRule type="expression" dxfId="15" priority="7">
+    <cfRule type="expression" dxfId="11" priority="7">
       <formula>"D2&gt;0"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E37 E40:E54">
-    <cfRule type="containsText" dxfId="14" priority="6" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="10" priority="6" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F37 F40:F54">
-    <cfRule type="containsText" dxfId="13" priority="5" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38">
-    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38">
-    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39">
-    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F39)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5594,7 +5459,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7167,14 +7032,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
+  <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-00000C000000}"/>
   <conditionalFormatting sqref="F2:F37 F40:F54">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38">
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7198,7 +7063,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7817,39 +7682,39 @@
       <c r="G54" s="33"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
+  <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <conditionalFormatting sqref="E2">
-    <cfRule type="expression" dxfId="85" priority="7">
+    <cfRule type="expression" dxfId="81" priority="7">
       <formula>"D2&gt;0"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E37 E40:E54">
-    <cfRule type="containsText" dxfId="84" priority="6" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="80" priority="6" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F37 F40:F54">
-    <cfRule type="containsText" dxfId="83" priority="5" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="79" priority="5" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38">
-    <cfRule type="containsText" dxfId="82" priority="4" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="78" priority="4" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38">
-    <cfRule type="containsText" dxfId="81" priority="3" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="77" priority="3" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39">
-    <cfRule type="containsText" dxfId="80" priority="2" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="76" priority="2" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="containsText" dxfId="79" priority="1" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="75" priority="1" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F39)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7858,7 +7723,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8477,39 +8342,39 @@
       <c r="G54" s="33"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
+  <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <conditionalFormatting sqref="E2">
-    <cfRule type="expression" dxfId="78" priority="7">
+    <cfRule type="expression" dxfId="74" priority="7">
       <formula>"D2&gt;0"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E37 E40:E54">
-    <cfRule type="containsText" dxfId="77" priority="6" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="73" priority="6" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F37 F40:F54">
-    <cfRule type="containsText" dxfId="76" priority="5" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="72" priority="5" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38">
-    <cfRule type="containsText" dxfId="75" priority="4" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="71" priority="4" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38">
-    <cfRule type="containsText" dxfId="74" priority="3" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="70" priority="3" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39">
-    <cfRule type="containsText" dxfId="73" priority="2" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="69" priority="2" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="containsText" dxfId="72" priority="1" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="68" priority="1" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F39)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8518,7 +8383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9137,39 +9002,39 @@
       <c r="G54" s="33"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
+  <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <conditionalFormatting sqref="E2">
-    <cfRule type="expression" dxfId="71" priority="7">
+    <cfRule type="expression" dxfId="67" priority="7">
       <formula>"D2&gt;0"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E37 E40:E54">
-    <cfRule type="containsText" dxfId="70" priority="6" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="66" priority="6" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F37 F40:F54">
-    <cfRule type="containsText" dxfId="69" priority="5" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="65" priority="5" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38">
-    <cfRule type="containsText" dxfId="68" priority="4" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="64" priority="4" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38">
-    <cfRule type="containsText" dxfId="67" priority="3" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="63" priority="3" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39">
-    <cfRule type="containsText" dxfId="66" priority="2" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="62" priority="2" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="containsText" dxfId="65" priority="1" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="61" priority="1" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F39)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9178,7 +9043,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9797,39 +9662,39 @@
       <c r="G54" s="33"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
+  <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <conditionalFormatting sqref="E2">
-    <cfRule type="expression" dxfId="64" priority="7">
+    <cfRule type="expression" dxfId="60" priority="7">
       <formula>"D2&gt;0"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E37 E40:E54">
-    <cfRule type="containsText" dxfId="63" priority="6" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="59" priority="6" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F37 F40:F54">
-    <cfRule type="containsText" dxfId="62" priority="5" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="58" priority="5" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38">
-    <cfRule type="containsText" dxfId="61" priority="4" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="57" priority="4" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38">
-    <cfRule type="containsText" dxfId="60" priority="3" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="56" priority="3" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39">
-    <cfRule type="containsText" dxfId="59" priority="2" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="55" priority="2" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="containsText" dxfId="58" priority="1" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="54" priority="1" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F39)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9838,7 +9703,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10457,39 +10322,39 @@
       <c r="G54" s="33"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
+  <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <conditionalFormatting sqref="E2">
-    <cfRule type="expression" dxfId="57" priority="7">
+    <cfRule type="expression" dxfId="53" priority="7">
       <formula>"D2&gt;0"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E37 E40:E54">
-    <cfRule type="containsText" dxfId="56" priority="6" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="52" priority="6" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F37 F40:F54">
-    <cfRule type="containsText" dxfId="55" priority="5" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="51" priority="5" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38">
-    <cfRule type="containsText" dxfId="54" priority="4" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="50" priority="4" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38">
-    <cfRule type="containsText" dxfId="53" priority="3" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="49" priority="3" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39">
-    <cfRule type="containsText" dxfId="52" priority="2" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="48" priority="2" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="containsText" dxfId="51" priority="1" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="47" priority="1" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F39)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10498,7 +10363,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11117,39 +10982,39 @@
       <c r="G54" s="33"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
+  <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <conditionalFormatting sqref="E2">
-    <cfRule type="expression" dxfId="50" priority="7">
+    <cfRule type="expression" dxfId="46" priority="7">
       <formula>"D2&gt;0"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E37 E40:E54">
-    <cfRule type="containsText" dxfId="49" priority="6" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="45" priority="6" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F37 F40:F54">
-    <cfRule type="containsText" dxfId="48" priority="5" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="44" priority="5" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38">
-    <cfRule type="containsText" dxfId="47" priority="4" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="43" priority="4" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38">
-    <cfRule type="containsText" dxfId="46" priority="3" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="42" priority="3" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39">
-    <cfRule type="containsText" dxfId="45" priority="2" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="41" priority="2" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="containsText" dxfId="44" priority="1" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="40" priority="1" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F39)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11158,7 +11023,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11777,39 +11642,39 @@
       <c r="G54" s="33"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
+  <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <conditionalFormatting sqref="E2">
-    <cfRule type="expression" dxfId="43" priority="7">
+    <cfRule type="expression" dxfId="39" priority="7">
       <formula>"D2&gt;0"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E37 E40:E54">
-    <cfRule type="containsText" dxfId="42" priority="6" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="38" priority="6" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F37 F40:F54">
-    <cfRule type="containsText" dxfId="41" priority="5" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="37" priority="5" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38">
-    <cfRule type="containsText" dxfId="40" priority="4" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="36" priority="4" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38">
-    <cfRule type="containsText" dxfId="39" priority="3" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="35" priority="3" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39">
-    <cfRule type="containsText" dxfId="38" priority="2" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="34" priority="2" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="containsText" dxfId="37" priority="1" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F39)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11818,7 +11683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12437,39 +12302,39 @@
       <c r="G54" s="33"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
+  <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <conditionalFormatting sqref="E2">
-    <cfRule type="expression" dxfId="36" priority="7">
+    <cfRule type="expression" dxfId="32" priority="7">
       <formula>"D2&gt;0"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E37 E40:E54">
-    <cfRule type="containsText" dxfId="35" priority="6" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="31" priority="6" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F37 F40:F54">
-    <cfRule type="containsText" dxfId="34" priority="5" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="30" priority="5" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38">
-    <cfRule type="containsText" dxfId="33" priority="4" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="29" priority="4" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38">
-    <cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="28" priority="3" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39">
-    <cfRule type="containsText" dxfId="31" priority="2" operator="containsText" text="We borrowerd more than we lent">
+    <cfRule type="containsText" dxfId="27" priority="2" operator="containsText" text="We borrowerd more than we lent">
       <formula>NOT(ISERROR(SEARCH("We borrowerd more than we lent",E39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="containsText" dxfId="30" priority="1" operator="containsText" text="We lent more than we borrowed">
+    <cfRule type="containsText" dxfId="26" priority="1" operator="containsText" text="We lent more than we borrowed">
       <formula>NOT(ISERROR(SEARCH("We lent more than we borrowed",F39)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/statistics_files/2026/2026_99_ga_net_borrower_lender.xlsx
+++ b/statistics_files/2026/2026_99_ga_net_borrower_lender.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B0DA0F8-5904-4B6E-A65D-DDF424EA9341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74D5D48-BDAD-4137-AAEE-964CABA612A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="868" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="145">
   <si>
     <t>Library</t>
   </si>
@@ -388,6 +388,114 @@
   </si>
   <si>
     <t>1.45 : 1</t>
+  </si>
+  <si>
+    <t>1.20 : 1</t>
+  </si>
+  <si>
+    <t>1.87 : 1</t>
+  </si>
+  <si>
+    <t>1.13 : 1</t>
+  </si>
+  <si>
+    <t>0.16 : 1</t>
+  </si>
+  <si>
+    <t>0.84 : 1</t>
+  </si>
+  <si>
+    <t>1.15 : 1</t>
+  </si>
+  <si>
+    <t>0.59 : 1</t>
+  </si>
+  <si>
+    <t>1.37 : 1</t>
+  </si>
+  <si>
+    <t>0.45 : 1</t>
+  </si>
+  <si>
+    <t>1.73 : 1</t>
+  </si>
+  <si>
+    <t>1.41 : 1</t>
+  </si>
+  <si>
+    <t>2.13 : 1</t>
+  </si>
+  <si>
+    <t>0.07 : 1</t>
+  </si>
+  <si>
+    <t>1.16 : 1</t>
+  </si>
+  <si>
+    <t>0.47 : 1</t>
+  </si>
+  <si>
+    <t>1.08 : 1</t>
+  </si>
+  <si>
+    <t>0.57 : 1</t>
+  </si>
+  <si>
+    <t>0.88 : 1</t>
+  </si>
+  <si>
+    <t>1.80 : 1</t>
+  </si>
+  <si>
+    <t>0.36 : 1</t>
+  </si>
+  <si>
+    <t>0.49 : 1</t>
+  </si>
+  <si>
+    <t>1.19 : 1</t>
+  </si>
+  <si>
+    <t>2.15 : 1</t>
+  </si>
+  <si>
+    <t>0.64 : 1</t>
+  </si>
+  <si>
+    <t>0.38 : 1</t>
+  </si>
+  <si>
+    <t>0.15 : 1</t>
+  </si>
+  <si>
+    <t>2.14 : 1</t>
+  </si>
+  <si>
+    <t>0.39 : 1</t>
+  </si>
+  <si>
+    <t>0.76 : 1</t>
+  </si>
+  <si>
+    <t>1.02 : 1</t>
+  </si>
+  <si>
+    <t>1.72 : 1</t>
+  </si>
+  <si>
+    <t>1.53 : 1</t>
+  </si>
+  <si>
+    <t>0.53 : 1</t>
+  </si>
+  <si>
+    <t>1.35 : 1</t>
+  </si>
+  <si>
+    <t>0.12 : 1</t>
+  </si>
+  <si>
+    <t>1.84 : 1</t>
   </si>
 </sst>
 </file>
@@ -5500,15 +5608,15 @@
       </c>
       <c r="B2" s="7">
         <f>January!B2+February!B2+March!B2+April!B2+May!B2+June!B2+July!B2+August!B2+September!B2+October!B2+November!B2+December!B2</f>
-        <v>1441</v>
+        <v>2807</v>
       </c>
       <c r="C2" s="7">
         <f>January!C2+February!C2+March!C2+April!C2+May!C2+June!C2+July!C2+August!C2+September!C2+October!C2+November!C2+December!C2</f>
-        <v>1299</v>
+        <v>2440</v>
       </c>
       <c r="D2" s="7">
         <f>January!D2+February!D2+March!D2+April!D2+May!D2+June!D2+July!D2+August!D2+September!D2+October!D2+November!D2+December!D2</f>
-        <v>142</v>
+        <v>367</v>
       </c>
       <c r="E2" s="8" t="str">
         <f>IF(D2 &gt; 0, "We borrowed more than we lent this year", "")</f>
@@ -5520,7 +5628,7 @@
       </c>
       <c r="G2" s="9" t="str">
         <f>IF(ISERROR(ROUND(B2/C2,2)&amp;" : 1"), "", ROUND(B2/C2,2)&amp;" : 1")</f>
-        <v>1.11 : 1</v>
+        <v>1.15 : 1</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5529,15 +5637,15 @@
       </c>
       <c r="B3" s="11">
         <f>January!B3+February!B3+March!B3+April!B3+May!B3+June!B3+July!B3+August!B3+September!B3+October!B3+November!B3+December!B3</f>
-        <v>671</v>
+        <v>1343</v>
       </c>
       <c r="C3" s="11">
         <f>January!C3+February!C3+March!C3+April!C3+May!C3+June!C3+July!C3+August!C3+September!C3+October!C3+November!C3+December!C3</f>
-        <v>419</v>
+        <v>779</v>
       </c>
       <c r="D3" s="11">
         <f>January!D3+February!D3+March!D3+April!D3+May!D3+June!D3+July!D3+August!D3+September!D3+October!D3+November!D3+December!D3</f>
-        <v>252</v>
+        <v>564</v>
       </c>
       <c r="E3" s="12" t="str">
         <f t="shared" ref="E3:E54" si="0">IF(D3 &gt; 0, "We borrowed more than we lent this year", "")</f>
@@ -5549,7 +5657,7 @@
       </c>
       <c r="G3" s="13" t="str">
         <f t="shared" ref="G3:G54" si="2">IF(ISERROR(ROUND(B3/C3,2)&amp;" : 1"), "", ROUND(B3/C3,2)&amp;" : 1")</f>
-        <v>1.6 : 1</v>
+        <v>1.72 : 1</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5558,15 +5666,15 @@
       </c>
       <c r="B4" s="7">
         <f>January!B4+February!B4+March!B4+April!B4+May!B4+June!B4+July!B4+August!B4+September!B4+October!B4+November!B4+December!B4</f>
-        <v>1369</v>
+        <v>2509</v>
       </c>
       <c r="C4" s="7">
         <f>January!C4+February!C4+March!C4+April!C4+May!C4+June!C4+July!C4+August!C4+September!C4+October!C4+November!C4+December!C4</f>
-        <v>1352</v>
+        <v>2360</v>
       </c>
       <c r="D4" s="7">
         <f>January!D4+February!D4+March!D4+April!D4+May!D4+June!D4+July!D4+August!D4+September!D4+October!D4+November!D4+December!D4</f>
-        <v>17</v>
+        <v>149</v>
       </c>
       <c r="E4" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5578,7 +5686,7 @@
       </c>
       <c r="G4" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.01 : 1</v>
+        <v>1.06 : 1</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5587,15 +5695,15 @@
       </c>
       <c r="B5" s="11">
         <f>January!B5+February!B5+March!B5+April!B5+May!B5+June!B5+July!B5+August!B5+September!B5+October!B5+November!B5+December!B5</f>
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C5" s="11">
         <f>January!C5+February!C5+March!C5+April!C5+May!C5+June!C5+July!C5+August!C5+September!C5+October!C5+November!C5+December!C5</f>
-        <v>143</v>
+        <v>254</v>
       </c>
       <c r="D5" s="11">
         <f>January!D5+February!D5+March!D5+April!D5+May!D5+June!D5+July!D5+August!D5+September!D5+October!D5+November!D5+December!D5</f>
-        <v>-115</v>
+        <v>-208</v>
       </c>
       <c r="E5" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5607,7 +5715,7 @@
       </c>
       <c r="G5" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.2 : 1</v>
+        <v>0.18 : 1</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5616,27 +5724,27 @@
       </c>
       <c r="B6" s="7">
         <f>January!B6+February!B6+March!B6+April!B6+May!B6+June!B6+July!B6+August!B6+September!B6+October!B6+November!B6+December!B6</f>
-        <v>1162</v>
+        <v>2128</v>
       </c>
       <c r="C6" s="7">
         <f>January!C6+February!C6+March!C6+April!C6+May!C6+June!C6+July!C6+August!C6+September!C6+October!C6+November!C6+December!C6</f>
-        <v>1131</v>
+        <v>2284</v>
       </c>
       <c r="D6" s="7">
         <f>January!D6+February!D6+March!D6+April!D6+May!D6+June!D6+July!D6+August!D6+September!D6+October!D6+November!D6+December!D6</f>
-        <v>31</v>
+        <v>-156</v>
       </c>
       <c r="E6" s="8" t="str">
         <f t="shared" si="0"/>
-        <v>We borrowed more than we lent this year</v>
+        <v/>
       </c>
       <c r="F6" s="8" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>We lent more than we borrowed this year</v>
       </c>
       <c r="G6" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.03 : 1</v>
+        <v>0.93 : 1</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5645,15 +5753,15 @@
       </c>
       <c r="B7" s="11">
         <f>January!B7+February!B7+March!B7+April!B7+May!B7+June!B7+July!B7+August!B7+September!B7+October!B7+November!B7+December!B7</f>
-        <v>217</v>
+        <v>386</v>
       </c>
       <c r="C7" s="11">
         <f>January!C7+February!C7+March!C7+April!C7+May!C7+June!C7+July!C7+August!C7+September!C7+October!C7+November!C7+December!C7</f>
-        <v>180</v>
+        <v>327</v>
       </c>
       <c r="D7" s="11">
         <f>January!D7+February!D7+March!D7+April!D7+May!D7+June!D7+July!D7+August!D7+September!D7+October!D7+November!D7+December!D7</f>
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="E7" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5665,7 +5773,7 @@
       </c>
       <c r="G7" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.21 : 1</v>
+        <v>1.18 : 1</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5674,15 +5782,15 @@
       </c>
       <c r="B8" s="7">
         <f>January!B8+February!B8+March!B8+April!B8+May!B8+June!B8+July!B8+August!B8+September!B8+October!B8+November!B8+December!B8</f>
-        <v>111</v>
+        <v>218</v>
       </c>
       <c r="C8" s="7">
         <f>January!C8+February!C8+March!C8+April!C8+May!C8+June!C8+July!C8+August!C8+September!C8+October!C8+November!C8+December!C8</f>
-        <v>171</v>
+        <v>351</v>
       </c>
       <c r="D8" s="7">
         <f>January!D8+February!D8+March!D8+April!D8+May!D8+June!D8+July!D8+August!D8+September!D8+October!D8+November!D8+December!D8</f>
-        <v>-60</v>
+        <v>-133</v>
       </c>
       <c r="E8" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5694,7 +5802,7 @@
       </c>
       <c r="G8" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.65 : 1</v>
+        <v>0.62 : 1</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5703,15 +5811,15 @@
       </c>
       <c r="B9" s="11">
         <f>January!B9+February!B9+March!B9+April!B9+May!B9+June!B9+July!B9+August!B9+September!B9+October!B9+November!B9+December!B9</f>
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="C9" s="11">
         <f>January!C9+February!C9+March!C9+April!C9+May!C9+June!C9+July!C9+August!C9+September!C9+October!C9+November!C9+December!C9</f>
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="D9" s="11">
         <f>January!D9+February!D9+March!D9+April!D9+May!D9+June!D9+July!D9+August!D9+September!D9+October!D9+November!D9+December!D9</f>
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E9" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5723,7 +5831,7 @@
       </c>
       <c r="G9" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.11 : 1</v>
+        <v>1.22 : 1</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5732,15 +5840,15 @@
       </c>
       <c r="B10" s="7">
         <f>January!B10+February!B10+March!B10+April!B10+May!B10+June!B10+July!B10+August!B10+September!B10+October!B10+November!B10+December!B10</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" s="7">
         <f>January!C10+February!C10+March!C10+April!C10+May!C10+June!C10+July!C10+August!C10+September!C10+October!C10+November!C10+December!C10</f>
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D10" s="7">
         <f>January!D10+February!D10+March!D10+April!D10+May!D10+June!D10+July!D10+August!D10+September!D10+October!D10+November!D10+December!D10</f>
-        <v>-19</v>
+        <v>-47</v>
       </c>
       <c r="E10" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5752,7 +5860,7 @@
       </c>
       <c r="G10" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0 : 1</v>
+        <v>0.06 : 1</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5790,15 +5898,15 @@
       </c>
       <c r="B12" s="15">
         <f>January!B12+February!B12+March!B12+April!B12+May!B12+June!B12+July!B12+August!B12+September!B12+October!B12+November!B12+December!B12</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C12" s="15">
         <f>January!C12+February!C12+March!C12+April!C12+May!C12+June!C12+July!C12+August!C12+September!C12+October!C12+November!C12+December!C12</f>
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D12" s="15">
         <f>January!D12+February!D12+March!D12+April!D12+May!D12+June!D12+July!D12+August!D12+September!D12+October!D12+November!D12+December!D12</f>
-        <v>-15</v>
+        <v>-34</v>
       </c>
       <c r="E12" s="16" t="str">
         <f t="shared" si="0"/>
@@ -5810,7 +5918,7 @@
       </c>
       <c r="G12" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>0.32 : 1</v>
+        <v>0.21 : 1</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5819,15 +5927,15 @@
       </c>
       <c r="B13" s="19">
         <f>January!B13+February!B13+March!B13+April!B13+May!B13+June!B13+July!B13+August!B13+September!B13+October!B13+November!B13+December!B13</f>
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="C13" s="19">
         <f>January!C13+February!C13+March!C13+April!C13+May!C13+June!C13+July!C13+August!C13+September!C13+October!C13+November!C13+December!C13</f>
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="D13" s="19">
         <f>January!D13+February!D13+March!D13+April!D13+May!D13+June!D13+July!D13+August!D13+September!D13+October!D13+November!D13+December!D13</f>
-        <v>-12</v>
+        <v>-40</v>
       </c>
       <c r="E13" s="20" t="str">
         <f t="shared" si="0"/>
@@ -5839,7 +5947,7 @@
       </c>
       <c r="G13" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>0.78 : 1</v>
+        <v>0.7 : 1</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5848,15 +5956,15 @@
       </c>
       <c r="B14" s="15">
         <f>January!B14+February!B14+March!B14+April!B14+May!B14+June!B14+July!B14+August!B14+September!B14+October!B14+November!B14+December!B14</f>
-        <v>168</v>
+        <v>294</v>
       </c>
       <c r="C14" s="15">
         <f>January!C14+February!C14+March!C14+April!C14+May!C14+June!C14+July!C14+August!C14+September!C14+October!C14+November!C14+December!C14</f>
-        <v>270</v>
+        <v>550</v>
       </c>
       <c r="D14" s="15">
         <f>January!D14+February!D14+March!D14+April!D14+May!D14+June!D14+July!D14+August!D14+September!D14+October!D14+November!D14+December!D14</f>
-        <v>-102</v>
+        <v>-256</v>
       </c>
       <c r="E14" s="16" t="str">
         <f t="shared" si="0"/>
@@ -5868,7 +5976,7 @@
       </c>
       <c r="G14" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>0.62 : 1</v>
+        <v>0.53 : 1</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5877,15 +5985,15 @@
       </c>
       <c r="B15" s="19">
         <f>January!B15+February!B15+March!B15+April!B15+May!B15+June!B15+July!B15+August!B15+September!B15+October!B15+November!B15+December!B15</f>
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="C15" s="19">
         <f>January!C15+February!C15+March!C15+April!C15+May!C15+June!C15+July!C15+August!C15+September!C15+October!C15+November!C15+December!C15</f>
-        <v>160</v>
+        <v>325</v>
       </c>
       <c r="D15" s="19">
         <f>January!D15+February!D15+March!D15+April!D15+May!D15+June!D15+July!D15+August!D15+September!D15+October!D15+November!D15+December!D15</f>
-        <v>-105</v>
+        <v>-224</v>
       </c>
       <c r="E15" s="20" t="str">
         <f t="shared" si="0"/>
@@ -5897,7 +6005,7 @@
       </c>
       <c r="G15" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>0.34 : 1</v>
+        <v>0.31 : 1</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5906,15 +6014,15 @@
       </c>
       <c r="B16" s="7">
         <f>January!B16+February!B16+March!B16+April!B16+May!B16+June!B16+July!B16+August!B16+September!B16+October!B16+November!B16+December!B16</f>
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="C16" s="7">
         <f>January!C16+February!C16+March!C16+April!C16+May!C16+June!C16+July!C16+August!C16+September!C16+October!C16+November!C16+December!C16</f>
-        <v>237</v>
+        <v>423</v>
       </c>
       <c r="D16" s="7">
         <f>January!D16+February!D16+March!D16+April!D16+May!D16+June!D16+July!D16+August!D16+September!D16+October!D16+November!D16+December!D16</f>
-        <v>-163</v>
+        <v>-289</v>
       </c>
       <c r="E16" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5926,7 +6034,7 @@
       </c>
       <c r="G16" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.31 : 1</v>
+        <v>0.32 : 1</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5935,15 +6043,15 @@
       </c>
       <c r="B17" s="11">
         <f>January!B17+February!B17+March!B17+April!B17+May!B17+June!B17+July!B17+August!B17+September!B17+October!B17+November!B17+December!B17</f>
-        <v>694</v>
+        <v>1422</v>
       </c>
       <c r="C17" s="11">
         <f>January!C17+February!C17+March!C17+April!C17+May!C17+June!C17+July!C17+August!C17+September!C17+October!C17+November!C17+December!C17</f>
-        <v>435</v>
+        <v>857</v>
       </c>
       <c r="D17" s="11">
         <f>January!D17+February!D17+March!D17+April!D17+May!D17+June!D17+July!D17+August!D17+September!D17+October!D17+November!D17+December!D17</f>
-        <v>259</v>
+        <v>565</v>
       </c>
       <c r="E17" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5955,7 +6063,7 @@
       </c>
       <c r="G17" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.6 : 1</v>
+        <v>1.66 : 1</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5964,27 +6072,27 @@
       </c>
       <c r="B18" s="7">
         <f>January!B18+February!B18+March!B18+April!B18+May!B18+June!B18+July!B18+August!B18+September!B18+October!B18+November!B18+December!B18</f>
-        <v>89</v>
+        <v>203</v>
       </c>
       <c r="C18" s="7">
         <f>January!C18+February!C18+March!C18+April!C18+May!C18+June!C18+July!C18+August!C18+September!C18+October!C18+November!C18+December!C18</f>
-        <v>94</v>
+        <v>175</v>
       </c>
       <c r="D18" s="7">
         <f>January!D18+February!D18+March!D18+April!D18+May!D18+June!D18+July!D18+August!D18+September!D18+October!D18+November!D18+December!D18</f>
-        <v>-5</v>
+        <v>28</v>
       </c>
       <c r="E18" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>We borrowed more than we lent this year</v>
       </c>
       <c r="F18" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>We lent more than we borrowed this year</v>
+        <v/>
       </c>
       <c r="G18" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.95 : 1</v>
+        <v>1.16 : 1</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5993,15 +6101,15 @@
       </c>
       <c r="B19" s="11">
         <f>January!B19+February!B19+March!B19+April!B19+May!B19+June!B19+July!B19+August!B19+September!B19+October!B19+November!B19+December!B19</f>
-        <v>485</v>
+        <v>1209</v>
       </c>
       <c r="C19" s="11">
         <f>January!C19+February!C19+March!C19+April!C19+May!C19+June!C19+July!C19+August!C19+September!C19+October!C19+November!C19+December!C19</f>
-        <v>302</v>
+        <v>642</v>
       </c>
       <c r="D19" s="11">
         <f>January!D19+February!D19+March!D19+April!D19+May!D19+June!D19+July!D19+August!D19+September!D19+October!D19+November!D19+December!D19</f>
-        <v>183</v>
+        <v>567</v>
       </c>
       <c r="E19" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6013,7 +6121,7 @@
       </c>
       <c r="G19" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.61 : 1</v>
+        <v>1.88 : 1</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6022,15 +6130,15 @@
       </c>
       <c r="B20" s="7">
         <f>January!B20+February!B20+March!B20+April!B20+May!B20+June!B20+July!B20+August!B20+September!B20+October!B20+November!B20+December!B20</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C20" s="7">
         <f>January!C20+February!C20+March!C20+April!C20+May!C20+June!C20+July!C20+August!C20+September!C20+October!C20+November!C20+December!C20</f>
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="D20" s="7">
         <f>January!D20+February!D20+March!D20+April!D20+May!D20+June!D20+July!D20+August!D20+September!D20+October!D20+November!D20+December!D20</f>
-        <v>-52</v>
+        <v>-102</v>
       </c>
       <c r="E20" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6042,7 +6150,7 @@
       </c>
       <c r="G20" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.05 : 1</v>
+        <v>0.06 : 1</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6051,15 +6159,15 @@
       </c>
       <c r="B21" s="11">
         <f>January!B21+February!B21+March!B21+April!B21+May!B21+June!B21+July!B21+August!B21+September!B21+October!B21+November!B21+December!B21</f>
-        <v>501</v>
+        <v>949</v>
       </c>
       <c r="C21" s="11">
         <f>January!C21+February!C21+March!C21+April!C21+May!C21+June!C21+July!C21+August!C21+September!C21+October!C21+November!C21+December!C21</f>
-        <v>474</v>
+        <v>859</v>
       </c>
       <c r="D21" s="11">
         <f>January!D21+February!D21+March!D21+April!D21+May!D21+June!D21+July!D21+August!D21+September!D21+October!D21+November!D21+December!D21</f>
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="E21" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6071,7 +6179,7 @@
       </c>
       <c r="G21" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.06 : 1</v>
+        <v>1.1 : 1</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6080,15 +6188,15 @@
       </c>
       <c r="B22" s="7">
         <f>January!B22+February!B22+March!B22+April!B22+May!B22+June!B22+July!B22+August!B22+September!B22+October!B22+November!B22+December!B22</f>
-        <v>90</v>
+        <v>219</v>
       </c>
       <c r="C22" s="7">
         <f>January!C22+February!C22+March!C22+April!C22+May!C22+June!C22+July!C22+August!C22+September!C22+October!C22+November!C22+December!C22</f>
-        <v>225</v>
+        <v>497</v>
       </c>
       <c r="D22" s="7">
         <f>January!D22+February!D22+March!D22+April!D22+May!D22+June!D22+July!D22+August!D22+September!D22+October!D22+November!D22+December!D22</f>
-        <v>-135</v>
+        <v>-278</v>
       </c>
       <c r="E22" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6100,7 +6208,7 @@
       </c>
       <c r="G22" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.4 : 1</v>
+        <v>0.44 : 1</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6109,15 +6217,15 @@
       </c>
       <c r="B23" s="11">
         <f>January!B23+February!B23+March!B23+April!B23+May!B23+June!B23+July!B23+August!B23+September!B23+October!B23+November!B23+December!B23</f>
-        <v>613</v>
+        <v>1194</v>
       </c>
       <c r="C23" s="11">
         <f>January!C23+February!C23+March!C23+April!C23+May!C23+June!C23+July!C23+August!C23+September!C23+October!C23+November!C23+December!C23</f>
-        <v>586</v>
+        <v>1122</v>
       </c>
       <c r="D23" s="11">
         <f>January!D23+February!D23+March!D23+April!D23+May!D23+June!D23+July!D23+August!D23+September!D23+October!D23+November!D23+December!D23</f>
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="E23" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6129,7 +6237,7 @@
       </c>
       <c r="G23" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.05 : 1</v>
+        <v>1.06 : 1</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6138,15 +6246,15 @@
       </c>
       <c r="B24" s="7">
         <f>January!B24+February!B24+March!B24+April!B24+May!B24+June!B24+July!B24+August!B24+September!B24+October!B24+November!B24+December!B24</f>
-        <v>1809</v>
+        <v>3710</v>
       </c>
       <c r="C24" s="7">
         <f>January!C24+February!C24+March!C24+April!C24+May!C24+June!C24+July!C24+August!C24+September!C24+October!C24+November!C24+December!C24</f>
-        <v>1166</v>
+        <v>2787</v>
       </c>
       <c r="D24" s="7">
         <f>January!D24+February!D24+March!D24+April!D24+May!D24+June!D24+July!D24+August!D24+September!D24+October!D24+November!D24+December!D24</f>
-        <v>643</v>
+        <v>923</v>
       </c>
       <c r="E24" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6158,7 +6266,7 @@
       </c>
       <c r="G24" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.55 : 1</v>
+        <v>1.33 : 1</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6167,15 +6275,15 @@
       </c>
       <c r="B25" s="11">
         <f>January!B25+February!B25+March!B25+April!B25+May!B25+June!B25+July!B25+August!B25+September!B25+October!B25+November!B25+December!B25</f>
-        <v>172</v>
+        <v>346</v>
       </c>
       <c r="C25" s="11">
         <f>January!C25+February!C25+March!C25+April!C25+May!C25+June!C25+July!C25+August!C25+September!C25+October!C25+November!C25+December!C25</f>
-        <v>356</v>
+        <v>660</v>
       </c>
       <c r="D25" s="11">
         <f>January!D25+February!D25+March!D25+April!D25+May!D25+June!D25+July!D25+August!D25+September!D25+October!D25+November!D25+December!D25</f>
-        <v>-184</v>
+        <v>-314</v>
       </c>
       <c r="E25" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6187,7 +6295,7 @@
       </c>
       <c r="G25" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.48 : 1</v>
+        <v>0.52 : 1</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6225,15 +6333,15 @@
       </c>
       <c r="B27" s="11">
         <f>January!B27+February!B27+March!B27+April!B27+May!B27+June!B27+July!B27+August!B27+September!B27+October!B27+November!B27+December!B27</f>
-        <v>231</v>
+        <v>403</v>
       </c>
       <c r="C27" s="11">
         <f>January!C27+February!C27+March!C27+April!C27+May!C27+June!C27+July!C27+August!C27+September!C27+October!C27+November!C27+December!C27</f>
-        <v>146</v>
+        <v>296</v>
       </c>
       <c r="D27" s="11">
         <f>January!D27+February!D27+March!D27+April!D27+May!D27+June!D27+July!D27+August!D27+September!D27+October!D27+November!D27+December!D27</f>
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="E27" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6245,7 +6353,7 @@
       </c>
       <c r="G27" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.58 : 1</v>
+        <v>1.36 : 1</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6254,27 +6362,27 @@
       </c>
       <c r="B28" s="7">
         <f>January!B28+February!B28+March!B28+April!B28+May!B28+June!B28+July!B28+August!B28+September!B28+October!B28+November!B28+December!B28</f>
-        <v>132</v>
+        <v>258</v>
       </c>
       <c r="C28" s="7">
         <f>January!C28+February!C28+March!C28+April!C28+May!C28+June!C28+July!C28+August!C28+September!C28+October!C28+November!C28+December!C28</f>
-        <v>120</v>
+        <v>264</v>
       </c>
       <c r="D28" s="7">
         <f>January!D28+February!D28+March!D28+April!D28+May!D28+June!D28+July!D28+August!D28+September!D28+October!D28+November!D28+December!D28</f>
-        <v>12</v>
+        <v>-6</v>
       </c>
       <c r="E28" s="8" t="str">
         <f t="shared" si="0"/>
-        <v>We borrowed more than we lent this year</v>
+        <v/>
       </c>
       <c r="F28" s="8" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>We lent more than we borrowed this year</v>
       </c>
       <c r="G28" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.1 : 1</v>
+        <v>0.98 : 1</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6283,15 +6391,15 @@
       </c>
       <c r="B29" s="11">
         <f>January!B29+February!B29+March!B29+April!B29+May!B29+June!B29+July!B29+August!B29+September!B29+October!B29+November!B29+December!B29</f>
-        <v>891</v>
+        <v>1761</v>
       </c>
       <c r="C29" s="11">
         <f>January!C29+February!C29+March!C29+April!C29+May!C29+June!C29+July!C29+August!C29+September!C29+October!C29+November!C29+December!C29</f>
-        <v>550</v>
+        <v>1034</v>
       </c>
       <c r="D29" s="11">
         <f>January!D29+February!D29+March!D29+April!D29+May!D29+June!D29+July!D29+August!D29+September!D29+October!D29+November!D29+December!D29</f>
-        <v>341</v>
+        <v>727</v>
       </c>
       <c r="E29" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6303,7 +6411,7 @@
       </c>
       <c r="G29" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.62 : 1</v>
+        <v>1.7 : 1</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6312,15 +6420,15 @@
       </c>
       <c r="B30" s="7">
         <f>January!B30+February!B30+March!B30+April!B30+May!B30+June!B30+July!B30+August!B30+September!B30+October!B30+November!B30+December!B30</f>
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C30" s="7">
         <f>January!C30+February!C30+March!C30+April!C30+May!C30+June!C30+July!C30+August!C30+September!C30+October!C30+November!C30+December!C30</f>
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D30" s="7">
         <f>January!D30+February!D30+March!D30+April!D30+May!D30+June!D30+July!D30+August!D30+September!D30+October!D30+November!D30+December!D30</f>
-        <v>-5</v>
+        <v>-21</v>
       </c>
       <c r="E30" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6332,7 +6440,7 @@
       </c>
       <c r="G30" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.83 : 1</v>
+        <v>0.61 : 1</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6341,15 +6449,15 @@
       </c>
       <c r="B31" s="11">
         <f>January!B31+February!B31+March!B31+April!B31+May!B31+June!B31+July!B31+August!B31+September!B31+October!B31+November!B31+December!B31</f>
-        <v>119</v>
+        <v>258</v>
       </c>
       <c r="C31" s="11">
         <f>January!C31+February!C31+March!C31+April!C31+May!C31+June!C31+July!C31+August!C31+September!C31+October!C31+November!C31+December!C31</f>
-        <v>231</v>
+        <v>512</v>
       </c>
       <c r="D31" s="11">
         <f>January!D31+February!D31+March!D31+April!D31+May!D31+June!D31+July!D31+August!D31+September!D31+October!D31+November!D31+December!D31</f>
-        <v>-112</v>
+        <v>-254</v>
       </c>
       <c r="E31" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6361,7 +6469,7 @@
       </c>
       <c r="G31" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.52 : 1</v>
+        <v>0.5 : 1</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6370,27 +6478,27 @@
       </c>
       <c r="B32" s="7">
         <f>January!B32+February!B32+March!B32+April!B32+May!B32+June!B32+July!B32+August!B32+September!B32+October!B32+November!B32+December!B32</f>
-        <v>521</v>
+        <v>920</v>
       </c>
       <c r="C32" s="7">
         <f>January!C32+February!C32+March!C32+April!C32+May!C32+June!C32+July!C32+August!C32+September!C32+October!C32+November!C32+December!C32</f>
-        <v>520</v>
+        <v>993</v>
       </c>
       <c r="D32" s="7">
         <f>January!D32+February!D32+March!D32+April!D32+May!D32+June!D32+July!D32+August!D32+September!D32+October!D32+November!D32+December!D32</f>
-        <v>1</v>
+        <v>-73</v>
       </c>
       <c r="E32" s="8" t="str">
         <f t="shared" si="0"/>
-        <v>We borrowed more than we lent this year</v>
+        <v/>
       </c>
       <c r="F32" s="8" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>We lent more than we borrowed this year</v>
       </c>
       <c r="G32" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1 : 1</v>
+        <v>0.93 : 1</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6399,27 +6507,27 @@
       </c>
       <c r="B33" s="11">
         <f>January!B33+February!B33+March!B33+April!B33+May!B33+June!B33+July!B33+August!B33+September!B33+October!B33+November!B33+December!B33</f>
-        <v>373</v>
+        <v>757</v>
       </c>
       <c r="C33" s="11">
         <f>January!C33+February!C33+March!C33+April!C33+May!C33+June!C33+July!C33+August!C33+September!C33+October!C33+November!C33+December!C33</f>
-        <v>407</v>
+        <v>730</v>
       </c>
       <c r="D33" s="11">
         <f>January!D33+February!D33+March!D33+April!D33+May!D33+June!D33+July!D33+August!D33+September!D33+October!D33+November!D33+December!D33</f>
-        <v>-34</v>
+        <v>27</v>
       </c>
       <c r="E33" s="12" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>We borrowed more than we lent this year</v>
       </c>
       <c r="F33" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>We lent more than we borrowed this year</v>
+        <v/>
       </c>
       <c r="G33" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.92 : 1</v>
+        <v>1.04 : 1</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6428,15 +6536,15 @@
       </c>
       <c r="B34" s="7">
         <f>January!B34+February!B34+March!B34+April!B34+May!B34+June!B34+July!B34+August!B34+September!B34+October!B34+November!B34+December!B34</f>
-        <v>208</v>
+        <v>432</v>
       </c>
       <c r="C34" s="7">
         <f>January!C34+February!C34+March!C34+April!C34+May!C34+June!C34+July!C34+August!C34+September!C34+October!C34+November!C34+December!C34</f>
-        <v>104</v>
+        <v>208</v>
       </c>
       <c r="D34" s="7">
         <f>January!D34+February!D34+March!D34+April!D34+May!D34+June!D34+July!D34+August!D34+September!D34+October!D34+November!D34+December!D34</f>
-        <v>104</v>
+        <v>224</v>
       </c>
       <c r="E34" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6448,7 +6556,7 @@
       </c>
       <c r="G34" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>2 : 1</v>
+        <v>2.08 : 1</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6457,15 +6565,15 @@
       </c>
       <c r="B35" s="11">
         <f>January!B35+February!B35+March!B35+April!B35+May!B35+June!B35+July!B35+August!B35+September!B35+October!B35+November!B35+December!B35</f>
-        <v>925</v>
+        <v>1856</v>
       </c>
       <c r="C35" s="11">
         <f>January!C35+February!C35+March!C35+April!C35+May!C35+June!C35+July!C35+August!C35+September!C35+October!C35+November!C35+December!C35</f>
-        <v>1641</v>
+        <v>3086</v>
       </c>
       <c r="D35" s="11">
         <f>January!D35+February!D35+March!D35+April!D35+May!D35+June!D35+July!D35+August!D35+September!D35+October!D35+November!D35+December!D35</f>
-        <v>-716</v>
+        <v>-1230</v>
       </c>
       <c r="E35" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6477,7 +6585,7 @@
       </c>
       <c r="G35" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.56 : 1</v>
+        <v>0.6 : 1</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6486,15 +6594,15 @@
       </c>
       <c r="B36" s="7">
         <f>January!B36+February!B36+March!B36+April!B36+May!B36+June!B36+July!B36+August!B36+September!B36+October!B36+November!B36+December!B36</f>
-        <v>180</v>
+        <v>362</v>
       </c>
       <c r="C36" s="7">
         <f>January!C36+February!C36+March!C36+April!C36+May!C36+June!C36+July!C36+August!C36+September!C36+October!C36+November!C36+December!C36</f>
-        <v>644</v>
+        <v>1180</v>
       </c>
       <c r="D36" s="7">
         <f>January!D36+February!D36+March!D36+April!D36+May!D36+June!D36+July!D36+August!D36+September!D36+October!D36+November!D36+December!D36</f>
-        <v>-464</v>
+        <v>-818</v>
       </c>
       <c r="E36" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6506,7 +6614,7 @@
       </c>
       <c r="G36" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.28 : 1</v>
+        <v>0.31 : 1</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6515,15 +6623,15 @@
       </c>
       <c r="B37" s="11">
         <f>January!B37+February!B37+March!B37+April!B37+May!B37+June!B37+July!B37+August!B37+September!B37+October!B37+November!B37+December!B37</f>
-        <v>493</v>
+        <v>1027</v>
       </c>
       <c r="C37" s="11">
         <f>January!C37+February!C37+March!C37+April!C37+May!C37+June!C37+July!C37+August!C37+September!C37+October!C37+November!C37+December!C37</f>
-        <v>460</v>
+        <v>903</v>
       </c>
       <c r="D37" s="11">
         <f>January!D37+February!D37+March!D37+April!D37+May!D37+June!D37+July!D37+August!D37+September!D37+October!D37+November!D37+December!D37</f>
-        <v>33</v>
+        <v>124</v>
       </c>
       <c r="E37" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6535,7 +6643,7 @@
       </c>
       <c r="G37" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.07 : 1</v>
+        <v>1.14 : 1</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6544,15 +6652,15 @@
       </c>
       <c r="B38" s="7">
         <f>January!B38+February!B38+March!B38+April!B38+May!B38+June!B38+July!B38+August!B38+September!B38+October!B38+November!B38+December!B38</f>
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="C38" s="7">
         <f>January!C38+February!C38+March!C38+April!C38+May!C38+June!C38+July!C38+August!C38+September!C38+October!C38+November!C38+December!C38</f>
-        <v>219</v>
+        <v>385</v>
       </c>
       <c r="D38" s="7">
         <f>January!D38+February!D38+March!D38+April!D38+May!D38+June!D38+July!D38+August!D38+September!D38+October!D38+November!D38+December!D38</f>
-        <v>-200</v>
+        <v>-332</v>
       </c>
       <c r="E38" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6564,7 +6672,7 @@
       </c>
       <c r="G38" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.09 : 1</v>
+        <v>0.14 : 1</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6573,15 +6681,15 @@
       </c>
       <c r="B39" s="11">
         <f>January!B39+February!B39+March!B39+April!B39+May!B39+June!B39+July!B39+August!B39+September!B39+October!B39+November!B39+December!B39</f>
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C39" s="11">
         <f>January!C39+February!C39+March!C39+April!C39+May!C39+June!C39+July!C39+August!C39+September!C39+October!C39+November!C39+December!C39</f>
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="D39" s="11">
         <f>January!D39+February!D39+March!D39+April!D39+May!D39+June!D39+July!D39+August!D39+September!D39+October!D39+November!D39+December!D39</f>
-        <v>-31</v>
+        <v>-71</v>
       </c>
       <c r="E39" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6593,7 +6701,7 @@
       </c>
       <c r="G39" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.23 : 1</v>
+        <v>0.32 : 1</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6602,15 +6710,15 @@
       </c>
       <c r="B40" s="23">
         <f>January!B40+February!B40+March!B40+April!B40+May!B40+June!B40+July!B40+August!B40+September!B40+October!B40+November!B40+December!B40</f>
-        <v>87</v>
+        <v>210</v>
       </c>
       <c r="C40" s="23">
         <f>January!C40+February!C40+March!C40+April!C40+May!C40+June!C40+July!C40+August!C40+September!C40+October!C40+November!C40+December!C40</f>
-        <v>96</v>
+        <v>242</v>
       </c>
       <c r="D40" s="23">
         <f>January!D40+February!D40+March!D40+April!D40+May!D40+June!D40+July!D40+August!D40+September!D40+October!D40+November!D40+December!D40</f>
-        <v>-9</v>
+        <v>-32</v>
       </c>
       <c r="E40" s="24" t="str">
         <f t="shared" si="0"/>
@@ -6622,7 +6730,7 @@
       </c>
       <c r="G40" s="25" t="str">
         <f t="shared" si="2"/>
-        <v>0.91 : 1</v>
+        <v>0.87 : 1</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6631,27 +6739,27 @@
       </c>
       <c r="B41" s="27">
         <f>January!B41+February!B41+March!B41+April!B41+May!B41+June!B41+July!B41+August!B41+September!B41+October!B41+November!B41+December!B41</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C41" s="27">
         <f>January!C41+February!C41+March!C41+April!C41+May!C41+June!C41+July!C41+August!C41+September!C41+October!C41+November!C41+December!C41</f>
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="D41" s="27">
         <f>January!D41+February!D41+March!D41+April!D41+May!D41+June!D41+July!D41+August!D41+September!D41+October!D41+November!D41+December!D41</f>
-        <v>1</v>
+        <v>-28</v>
       </c>
       <c r="E41" s="28" t="str">
         <f t="shared" si="0"/>
-        <v>We borrowed more than we lent this year</v>
+        <v/>
       </c>
       <c r="F41" s="28" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>We lent more than we borrowed this year</v>
       </c>
       <c r="G41" s="29" t="str">
         <f t="shared" si="2"/>
-        <v>1.17 : 1</v>
+        <v>0.3 : 1</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6660,15 +6768,15 @@
       </c>
       <c r="B42" s="23">
         <f>January!B42+February!B42+March!B42+April!B42+May!B42+June!B42+July!B42+August!B42+September!B42+October!B42+November!B42+December!B42</f>
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C42" s="23">
         <f>January!C42+February!C42+March!C42+April!C42+May!C42+June!C42+July!C42+August!C42+September!C42+October!C42+November!C42+December!C42</f>
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D42" s="23">
         <f>January!D42+February!D42+March!D42+April!D42+May!D42+June!D42+July!D42+August!D42+September!D42+October!D42+November!D42+December!D42</f>
-        <v>-9</v>
+        <v>-32</v>
       </c>
       <c r="E42" s="24" t="str">
         <f t="shared" si="0"/>
@@ -6680,7 +6788,7 @@
       </c>
       <c r="G42" s="25" t="str">
         <f t="shared" si="2"/>
-        <v>0.63 : 1</v>
+        <v>0.47 : 1</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6689,15 +6797,15 @@
       </c>
       <c r="B43" s="27">
         <f>January!B43+February!B43+March!B43+April!B43+May!B43+June!B43+July!B43+August!B43+September!B43+October!B43+November!B43+December!B43</f>
-        <v>240</v>
+        <v>441</v>
       </c>
       <c r="C43" s="27">
         <f>January!C43+February!C43+March!C43+April!C43+May!C43+June!C43+July!C43+August!C43+September!C43+October!C43+November!C43+December!C43</f>
-        <v>105</v>
+        <v>199</v>
       </c>
       <c r="D43" s="27">
         <f>January!D43+February!D43+March!D43+April!D43+May!D43+June!D43+July!D43+August!D43+September!D43+October!D43+November!D43+December!D43</f>
-        <v>135</v>
+        <v>242</v>
       </c>
       <c r="E43" s="28" t="str">
         <f t="shared" si="0"/>
@@ -6709,7 +6817,7 @@
       </c>
       <c r="G43" s="29" t="str">
         <f t="shared" si="2"/>
-        <v>2.29 : 1</v>
+        <v>2.22 : 1</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6718,15 +6826,15 @@
       </c>
       <c r="B44" s="7">
         <f>January!B44+February!B44+March!B44+April!B44+May!B44+June!B44+July!B44+August!B44+September!B44+October!B44+November!B44+December!B44</f>
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="C44" s="7">
         <f>January!C44+February!C44+March!C44+April!C44+May!C44+June!C44+July!C44+August!C44+September!C44+October!C44+November!C44+December!C44</f>
-        <v>155</v>
+        <v>312</v>
       </c>
       <c r="D44" s="7">
         <f>January!D44+February!D44+March!D44+April!D44+May!D44+June!D44+July!D44+August!D44+September!D44+October!D44+November!D44+December!D44</f>
-        <v>-92</v>
+        <v>-187</v>
       </c>
       <c r="E44" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6738,7 +6846,7 @@
       </c>
       <c r="G44" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.41 : 1</v>
+        <v>0.4 : 1</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6747,27 +6855,27 @@
       </c>
       <c r="B45" s="11">
         <f>January!B45+February!B45+March!B45+April!B45+May!B45+June!B45+July!B45+August!B45+September!B45+October!B45+November!B45+December!B45</f>
-        <v>598</v>
+        <v>1095</v>
       </c>
       <c r="C45" s="11">
         <f>January!C45+February!C45+March!C45+April!C45+May!C45+June!C45+July!C45+August!C45+September!C45+October!C45+November!C45+December!C45</f>
-        <v>543</v>
+        <v>1199</v>
       </c>
       <c r="D45" s="11">
         <f>January!D45+February!D45+March!D45+April!D45+May!D45+June!D45+July!D45+August!D45+September!D45+October!D45+November!D45+December!D45</f>
-        <v>55</v>
+        <v>-104</v>
       </c>
       <c r="E45" s="12" t="str">
         <f t="shared" si="0"/>
-        <v>We borrowed more than we lent this year</v>
+        <v/>
       </c>
       <c r="F45" s="12" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>We lent more than we borrowed this year</v>
       </c>
       <c r="G45" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.1 : 1</v>
+        <v>0.91 : 1</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6776,15 +6884,15 @@
       </c>
       <c r="B46" s="7">
         <f>January!B46+February!B46+March!B46+April!B46+May!B46+June!B46+July!B46+August!B46+September!B46+October!B46+November!B46+December!B46</f>
-        <v>1116</v>
+        <v>1937</v>
       </c>
       <c r="C46" s="7">
         <f>January!C46+February!C46+March!C46+April!C46+May!C46+June!C46+July!C46+August!C46+September!C46+October!C46+November!C46+December!C46</f>
-        <v>809</v>
+        <v>1612</v>
       </c>
       <c r="D46" s="7">
         <f>January!D46+February!D46+March!D46+April!D46+May!D46+June!D46+July!D46+August!D46+September!D46+October!D46+November!D46+December!D46</f>
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="E46" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6796,7 +6904,7 @@
       </c>
       <c r="G46" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.38 : 1</v>
+        <v>1.2 : 1</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6805,15 +6913,15 @@
       </c>
       <c r="B47" s="11">
         <f>January!B47+February!B47+March!B47+April!B47+May!B47+June!B47+July!B47+August!B47+September!B47+October!B47+November!B47+December!B47</f>
-        <v>208</v>
+        <v>425</v>
       </c>
       <c r="C47" s="11">
         <f>January!C47+February!C47+March!C47+April!C47+May!C47+June!C47+July!C47+August!C47+September!C47+October!C47+November!C47+December!C47</f>
-        <v>670</v>
+        <v>1227</v>
       </c>
       <c r="D47" s="11">
         <f>January!D47+February!D47+March!D47+April!D47+May!D47+June!D47+July!D47+August!D47+September!D47+October!D47+November!D47+December!D47</f>
-        <v>-462</v>
+        <v>-802</v>
       </c>
       <c r="E47" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6825,7 +6933,7 @@
       </c>
       <c r="G47" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.31 : 1</v>
+        <v>0.35 : 1</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6834,15 +6942,15 @@
       </c>
       <c r="B48" s="7">
         <f>January!B48+February!B48+March!B48+April!B48+May!B48+June!B48+July!B48+August!B48+September!B48+October!B48+November!B48+December!B48</f>
-        <v>416</v>
+        <v>899</v>
       </c>
       <c r="C48" s="7">
         <f>January!C48+February!C48+March!C48+April!C48+May!C48+June!C48+July!C48+August!C48+September!C48+October!C48+November!C48+December!C48</f>
-        <v>324</v>
+        <v>605</v>
       </c>
       <c r="D48" s="7">
         <f>January!D48+February!D48+March!D48+April!D48+May!D48+June!D48+July!D48+August!D48+September!D48+October!D48+November!D48+December!D48</f>
-        <v>92</v>
+        <v>294</v>
       </c>
       <c r="E48" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6854,7 +6962,7 @@
       </c>
       <c r="G48" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.28 : 1</v>
+        <v>1.49 : 1</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6863,15 +6971,15 @@
       </c>
       <c r="B49" s="11">
         <f>January!B49+February!B49+March!B49+April!B49+May!B49+June!B49+July!B49+August!B49+September!B49+October!B49+November!B49+December!B49</f>
-        <v>873</v>
+        <v>1702</v>
       </c>
       <c r="C49" s="11">
         <f>January!C49+February!C49+March!C49+April!C49+May!C49+June!C49+July!C49+August!C49+September!C49+October!C49+November!C49+December!C49</f>
-        <v>533</v>
+        <v>1074</v>
       </c>
       <c r="D49" s="11">
         <f>January!D49+February!D49+March!D49+April!D49+May!D49+June!D49+July!D49+August!D49+September!D49+October!D49+November!D49+December!D49</f>
-        <v>340</v>
+        <v>628</v>
       </c>
       <c r="E49" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6883,7 +6991,7 @@
       </c>
       <c r="G49" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.64 : 1</v>
+        <v>1.58 : 1</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6892,15 +7000,15 @@
       </c>
       <c r="B50" s="7">
         <f>January!B50+February!B50+March!B50+April!B50+May!B50+June!B50+July!B50+August!B50+September!B50+October!B50+November!B50+December!B50</f>
-        <v>134</v>
+        <v>239</v>
       </c>
       <c r="C50" s="7">
         <f>January!C50+February!C50+March!C50+April!C50+May!C50+June!C50+July!C50+August!C50+September!C50+October!C50+November!C50+December!C50</f>
-        <v>166</v>
+        <v>363</v>
       </c>
       <c r="D50" s="7">
         <f>January!D50+February!D50+March!D50+April!D50+May!D50+June!D50+July!D50+August!D50+September!D50+October!D50+November!D50+December!D50</f>
-        <v>-32</v>
+        <v>-124</v>
       </c>
       <c r="E50" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6912,7 +7020,7 @@
       </c>
       <c r="G50" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.81 : 1</v>
+        <v>0.66 : 1</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6921,15 +7029,15 @@
       </c>
       <c r="B51" s="11">
         <f>January!B51+February!B51+March!B51+April!B51+May!B51+June!B51+July!B51+August!B51+September!B51+October!B51+November!B51+December!B51</f>
-        <v>695</v>
+        <v>1173</v>
       </c>
       <c r="C51" s="11">
         <f>January!C51+February!C51+March!C51+April!C51+May!C51+June!C51+July!C51+August!C51+September!C51+October!C51+November!C51+December!C51</f>
-        <v>355</v>
+        <v>710</v>
       </c>
       <c r="D51" s="11">
         <f>January!D51+February!D51+March!D51+April!D51+May!D51+June!D51+July!D51+August!D51+September!D51+October!D51+November!D51+December!D51</f>
-        <v>340</v>
+        <v>463</v>
       </c>
       <c r="E51" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6941,7 +7049,7 @@
       </c>
       <c r="G51" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.96 : 1</v>
+        <v>1.65 : 1</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6950,15 +7058,15 @@
       </c>
       <c r="B52" s="7">
         <f>January!B52+February!B52+March!B52+April!B52+May!B52+June!B52+July!B52+August!B52+September!B52+October!B52+November!B52+December!B52</f>
-        <v>64</v>
+        <v>252</v>
       </c>
       <c r="C52" s="7">
         <f>January!C52+February!C52+March!C52+April!C52+May!C52+June!C52+July!C52+August!C52+September!C52+October!C52+November!C52+December!C52</f>
-        <v>236</v>
+        <v>420</v>
       </c>
       <c r="D52" s="7">
         <f>January!D52+February!D52+March!D52+April!D52+May!D52+June!D52+July!D52+August!D52+September!D52+October!D52+November!D52+December!D52</f>
-        <v>-172</v>
+        <v>-168</v>
       </c>
       <c r="E52" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6970,7 +7078,7 @@
       </c>
       <c r="G52" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.27 : 1</v>
+        <v>0.6 : 1</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6979,15 +7087,15 @@
       </c>
       <c r="B53" s="11">
         <f>January!B53+February!B53+March!B53+April!B53+May!B53+June!B53+July!B53+August!B53+September!B53+October!B53+November!B53+December!B53</f>
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="C53" s="11">
         <f>January!C53+February!C53+March!C53+April!C53+May!C53+June!C53+July!C53+August!C53+September!C53+October!C53+November!C53+December!C53</f>
-        <v>294</v>
+        <v>568</v>
       </c>
       <c r="D53" s="11">
         <f>January!D53+February!D53+March!D53+April!D53+May!D53+June!D53+July!D53+August!D53+September!D53+October!D53+November!D53+December!D53</f>
-        <v>-265</v>
+        <v>-506</v>
       </c>
       <c r="E53" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6999,7 +7107,7 @@
       </c>
       <c r="G53" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.1 : 1</v>
+        <v>0.11 : 1</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7008,15 +7116,15 @@
       </c>
       <c r="B54" s="31">
         <f>January!B54+February!B54+March!B54+April!B54+May!B54+June!B54+July!B54+August!B54+September!B54+October!B54+November!B54+December!B54</f>
-        <v>318</v>
+        <v>756</v>
       </c>
       <c r="C54" s="31">
         <f>January!C54+February!C54+March!C54+April!C54+May!C54+June!C54+July!C54+August!C54+September!C54+October!C54+November!C54+December!C54</f>
-        <v>219</v>
+        <v>457</v>
       </c>
       <c r="D54" s="31">
         <f>January!D54+February!D54+March!D54+April!D54+May!D54+June!D54+July!D54+August!D54+September!D54+October!D54+November!D54+December!D54</f>
-        <v>99</v>
+        <v>299</v>
       </c>
       <c r="E54" s="32" t="str">
         <f t="shared" si="0"/>
@@ -7028,7 +7136,7 @@
       </c>
       <c r="G54" s="33" t="str">
         <f t="shared" si="2"/>
-        <v>1.45 : 1</v>
+        <v>1.65 : 1</v>
       </c>
     </row>
   </sheetData>
@@ -7102,108 +7210,204 @@
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8"/>
+      <c r="B2" s="7">
+        <v>1366</v>
+      </c>
+      <c r="C2" s="7">
+        <v>1141</v>
+      </c>
+      <c r="D2" s="7">
+        <v>225</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F2" s="8"/>
-      <c r="G2" s="9"/>
+      <c r="G2" s="9" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="12"/>
+      <c r="B3" s="11">
+        <v>672</v>
+      </c>
+      <c r="C3" s="11">
+        <v>360</v>
+      </c>
+      <c r="D3" s="11">
+        <v>312</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F3" s="12"/>
-      <c r="G3" s="13"/>
+      <c r="G3" s="13" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8"/>
+      <c r="B4" s="7">
+        <v>1140</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1008</v>
+      </c>
+      <c r="D4" s="7">
+        <v>132</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F4" s="8"/>
-      <c r="G4" s="9"/>
+      <c r="G4" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
+      <c r="B5" s="11">
+        <v>18</v>
+      </c>
+      <c r="C5" s="11">
+        <v>111</v>
+      </c>
+      <c r="D5" s="11">
+        <v>-93</v>
+      </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13"/>
+      <c r="F5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+      <c r="B6" s="7">
+        <v>966</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1153</v>
+      </c>
+      <c r="D6" s="7">
+        <v>-187</v>
+      </c>
       <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9"/>
+      <c r="F6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12"/>
+      <c r="B7" s="11">
+        <v>169</v>
+      </c>
+      <c r="C7" s="11">
+        <v>147</v>
+      </c>
+      <c r="D7" s="11">
+        <v>22</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="13"/>
+      <c r="G7" s="13" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+      <c r="B8" s="7">
+        <v>107</v>
+      </c>
+      <c r="C8" s="7">
+        <v>180</v>
+      </c>
+      <c r="D8" s="7">
+        <v>-73</v>
+      </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9"/>
+      <c r="F8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12"/>
+      <c r="B9" s="11">
+        <v>67</v>
+      </c>
+      <c r="C9" s="11">
+        <v>49</v>
+      </c>
+      <c r="D9" s="11">
+        <v>18</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="13"/>
+      <c r="G9" s="13" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="B10" s="7">
+        <v>3</v>
+      </c>
+      <c r="C10" s="7">
+        <v>31</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-28</v>
+      </c>
       <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9"/>
+      <c r="F10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
+      <c r="B11" s="11">
+        <v>0</v>
+      </c>
+      <c r="C11" s="11">
+        <v>0</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0</v>
+      </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
@@ -7212,163 +7416,309 @@
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
+      <c r="B12" s="15">
+        <v>2</v>
+      </c>
+      <c r="C12" s="15">
+        <v>21</v>
+      </c>
+      <c r="D12" s="15">
+        <v>-19</v>
+      </c>
       <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17"/>
+      <c r="F12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
+      <c r="B13" s="19">
+        <v>52</v>
+      </c>
+      <c r="C13" s="19">
+        <v>80</v>
+      </c>
+      <c r="D13" s="19">
+        <v>-28</v>
+      </c>
       <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="21"/>
+      <c r="F13" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
+      <c r="B14" s="15">
+        <v>126</v>
+      </c>
+      <c r="C14" s="15">
+        <v>280</v>
+      </c>
+      <c r="D14" s="15">
+        <v>-154</v>
+      </c>
       <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="17"/>
+      <c r="F14" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
+      <c r="B15" s="19">
+        <v>46</v>
+      </c>
+      <c r="C15" s="19">
+        <v>165</v>
+      </c>
+      <c r="D15" s="19">
+        <v>-119</v>
+      </c>
       <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="21"/>
+      <c r="F15" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
+      <c r="B16" s="7">
+        <v>60</v>
+      </c>
+      <c r="C16" s="7">
+        <v>186</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-126</v>
+      </c>
       <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="9"/>
+      <c r="F16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="12"/>
+      <c r="B17" s="11">
+        <v>728</v>
+      </c>
+      <c r="C17" s="11">
+        <v>422</v>
+      </c>
+      <c r="D17" s="11">
+        <v>306</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F17" s="12"/>
-      <c r="G17" s="13"/>
+      <c r="G17" s="13" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8"/>
+      <c r="B18" s="7">
+        <v>114</v>
+      </c>
+      <c r="C18" s="7">
+        <v>81</v>
+      </c>
+      <c r="D18" s="7">
+        <v>33</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F18" s="8"/>
-      <c r="G18" s="9"/>
+      <c r="G18" s="9" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="12"/>
+      <c r="B19" s="11">
+        <v>724</v>
+      </c>
+      <c r="C19" s="11">
+        <v>340</v>
+      </c>
+      <c r="D19" s="11">
+        <v>384</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="13"/>
+      <c r="G19" s="13" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
+      <c r="B20" s="7">
+        <v>4</v>
+      </c>
+      <c r="C20" s="7">
+        <v>54</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-50</v>
+      </c>
       <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="9"/>
+      <c r="F20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="12"/>
+      <c r="B21" s="11">
+        <v>448</v>
+      </c>
+      <c r="C21" s="11">
+        <v>385</v>
+      </c>
+      <c r="D21" s="11">
+        <v>63</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="13"/>
+      <c r="G21" s="13" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+      <c r="B22" s="7">
+        <v>129</v>
+      </c>
+      <c r="C22" s="7">
+        <v>272</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-143</v>
+      </c>
       <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="9"/>
+      <c r="F22" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="12"/>
+      <c r="B23" s="11">
+        <v>581</v>
+      </c>
+      <c r="C23" s="11">
+        <v>536</v>
+      </c>
+      <c r="D23" s="11">
+        <v>45</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="13"/>
+      <c r="G23" s="13" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8"/>
+      <c r="B24" s="7">
+        <v>1901</v>
+      </c>
+      <c r="C24" s="7">
+        <v>1621</v>
+      </c>
+      <c r="D24" s="7">
+        <v>280</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
+      <c r="G24" s="9" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="B25" s="11">
+        <v>174</v>
+      </c>
+      <c r="C25" s="11">
+        <v>304</v>
+      </c>
+      <c r="D25" s="11">
+        <v>-130</v>
+      </c>
       <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="13"/>
+      <c r="F25" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
+      <c r="B26" s="7">
+        <v>0</v>
+      </c>
+      <c r="C26" s="7">
+        <v>0</v>
+      </c>
+      <c r="D26" s="7">
+        <v>0</v>
+      </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
@@ -7377,309 +7727,589 @@
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="12"/>
+      <c r="B27" s="11">
+        <v>172</v>
+      </c>
+      <c r="C27" s="11">
+        <v>150</v>
+      </c>
+      <c r="D27" s="11">
+        <v>22</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F27" s="12"/>
-      <c r="G27" s="13"/>
+      <c r="G27" s="13" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
+      <c r="B28" s="7">
+        <v>126</v>
+      </c>
+      <c r="C28" s="7">
+        <v>144</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-18</v>
+      </c>
       <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="9"/>
+      <c r="F28" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="12"/>
+      <c r="B29" s="11">
+        <v>870</v>
+      </c>
+      <c r="C29" s="11">
+        <v>484</v>
+      </c>
+      <c r="D29" s="11">
+        <v>386</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F29" s="12"/>
-      <c r="G29" s="13"/>
+      <c r="G29" s="13" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
+      <c r="B30" s="7">
+        <v>9</v>
+      </c>
+      <c r="C30" s="7">
+        <v>25</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-16</v>
+      </c>
       <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="9"/>
+      <c r="F30" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
+      <c r="B31" s="11">
+        <v>139</v>
+      </c>
+      <c r="C31" s="11">
+        <v>281</v>
+      </c>
+      <c r="D31" s="11">
+        <v>-142</v>
+      </c>
       <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="13"/>
+      <c r="F31" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
+      <c r="B32" s="7">
+        <v>399</v>
+      </c>
+      <c r="C32" s="7">
+        <v>473</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-74</v>
+      </c>
       <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="9"/>
+      <c r="F32" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="12"/>
+      <c r="B33" s="11">
+        <v>384</v>
+      </c>
+      <c r="C33" s="11">
+        <v>323</v>
+      </c>
+      <c r="D33" s="11">
+        <v>61</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F33" s="12"/>
-      <c r="G33" s="13"/>
+      <c r="G33" s="13" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="8"/>
+      <c r="B34" s="7">
+        <v>224</v>
+      </c>
+      <c r="C34" s="7">
+        <v>104</v>
+      </c>
+      <c r="D34" s="7">
+        <v>120</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F34" s="8"/>
-      <c r="G34" s="9"/>
+      <c r="G34" s="9" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
+      <c r="B35" s="11">
+        <v>931</v>
+      </c>
+      <c r="C35" s="11">
+        <v>1445</v>
+      </c>
+      <c r="D35" s="11">
+        <v>-514</v>
+      </c>
       <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="13"/>
+      <c r="F35" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
+      <c r="B36" s="7">
+        <v>182</v>
+      </c>
+      <c r="C36" s="7">
+        <v>536</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-354</v>
+      </c>
       <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="9"/>
+      <c r="F36" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="12"/>
+      <c r="B37" s="11">
+        <v>534</v>
+      </c>
+      <c r="C37" s="11">
+        <v>443</v>
+      </c>
+      <c r="D37" s="11">
+        <v>91</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="13"/>
+      <c r="G37" s="13" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
+      <c r="B38" s="7">
+        <v>34</v>
+      </c>
+      <c r="C38" s="7">
+        <v>166</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-132</v>
+      </c>
       <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="9"/>
+      <c r="F38" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
+      <c r="B39" s="11">
+        <v>24</v>
+      </c>
+      <c r="C39" s="11">
+        <v>64</v>
+      </c>
+      <c r="D39" s="11">
+        <v>-40</v>
+      </c>
       <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="13"/>
+      <c r="F39" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
+      <c r="B40" s="23">
+        <v>123</v>
+      </c>
+      <c r="C40" s="23">
+        <v>146</v>
+      </c>
+      <c r="D40" s="23">
+        <v>-23</v>
+      </c>
       <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="25"/>
+      <c r="F40" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="25" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
+      <c r="B41" s="27">
+        <v>5</v>
+      </c>
+      <c r="C41" s="27">
+        <v>34</v>
+      </c>
+      <c r="D41" s="27">
+        <v>-29</v>
+      </c>
       <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="29"/>
+      <c r="F41" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
+      <c r="B42" s="23">
+        <v>13</v>
+      </c>
+      <c r="C42" s="23">
+        <v>36</v>
+      </c>
+      <c r="D42" s="23">
+        <v>-23</v>
+      </c>
       <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="25"/>
+      <c r="F42" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="25" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="28"/>
+      <c r="B43" s="27">
+        <v>201</v>
+      </c>
+      <c r="C43" s="27">
+        <v>94</v>
+      </c>
+      <c r="D43" s="27">
+        <v>107</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>8</v>
+      </c>
       <c r="F43" s="28"/>
-      <c r="G43" s="29"/>
+      <c r="G43" s="29" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
+      <c r="B44" s="7">
+        <v>62</v>
+      </c>
+      <c r="C44" s="7">
+        <v>157</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-95</v>
+      </c>
       <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="9"/>
+      <c r="F44" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
+      <c r="B45" s="11">
+        <v>497</v>
+      </c>
+      <c r="C45" s="11">
+        <v>656</v>
+      </c>
+      <c r="D45" s="11">
+        <v>-159</v>
+      </c>
       <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="13"/>
+      <c r="F45" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="8"/>
+      <c r="B46" s="7">
+        <v>821</v>
+      </c>
+      <c r="C46" s="7">
+        <v>803</v>
+      </c>
+      <c r="D46" s="7">
+        <v>18</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F46" s="8"/>
-      <c r="G46" s="9"/>
+      <c r="G46" s="9" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
+      <c r="B47" s="11">
+        <v>217</v>
+      </c>
+      <c r="C47" s="11">
+        <v>557</v>
+      </c>
+      <c r="D47" s="11">
+        <v>-340</v>
+      </c>
       <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="13"/>
+      <c r="F47" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="8"/>
+      <c r="B48" s="7">
+        <v>483</v>
+      </c>
+      <c r="C48" s="7">
+        <v>281</v>
+      </c>
+      <c r="D48" s="7">
+        <v>202</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F48" s="8"/>
-      <c r="G48" s="9"/>
+      <c r="G48" s="9" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="12"/>
+      <c r="B49" s="11">
+        <v>829</v>
+      </c>
+      <c r="C49" s="11">
+        <v>541</v>
+      </c>
+      <c r="D49" s="11">
+        <v>288</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="13"/>
+      <c r="G49" s="13" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
+      <c r="B50" s="7">
+        <v>105</v>
+      </c>
+      <c r="C50" s="7">
+        <v>197</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-92</v>
+      </c>
       <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="9"/>
+      <c r="F50" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="12"/>
+      <c r="B51" s="11">
+        <v>478</v>
+      </c>
+      <c r="C51" s="11">
+        <v>355</v>
+      </c>
+      <c r="D51" s="11">
+        <v>123</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F51" s="12"/>
-      <c r="G51" s="13"/>
+      <c r="G51" s="13" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="8"/>
+      <c r="B52" s="7">
+        <v>188</v>
+      </c>
+      <c r="C52" s="7">
+        <v>184</v>
+      </c>
+      <c r="D52" s="7">
+        <v>4</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F52" s="8"/>
-      <c r="G52" s="9"/>
+      <c r="G52" s="9" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
+      <c r="B53" s="11">
+        <v>33</v>
+      </c>
+      <c r="C53" s="11">
+        <v>274</v>
+      </c>
+      <c r="D53" s="11">
+        <v>-241</v>
+      </c>
       <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="13"/>
+      <c r="F53" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" s="13" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B54" s="31"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="32"/>
+      <c r="B54" s="31">
+        <v>438</v>
+      </c>
+      <c r="C54" s="31">
+        <v>238</v>
+      </c>
+      <c r="D54" s="31">
+        <v>200</v>
+      </c>
+      <c r="E54" s="32" t="s">
+        <v>8</v>
+      </c>
       <c r="F54" s="32"/>
-      <c r="G54" s="33"/>
+      <c r="G54" s="33" t="s">
+        <v>144</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-000001000000}"/>

--- a/statistics_files/2026/2026_99_ga_net_borrower_lender.xlsx
+++ b/statistics_files/2026/2026_99_ga_net_borrower_lender.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Staff\Documents\GitHub\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74D5D48-BDAD-4137-AAEE-964CABA612A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89664C4-59B5-4680-B517-D9E641DA1B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="868" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="868" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="170">
   <si>
     <t>Library</t>
   </si>
@@ -496,6 +496,81 @@
   </si>
   <si>
     <t>1.84 : 1</t>
+  </si>
+  <si>
+    <t>1.26 : 1</t>
+  </si>
+  <si>
+    <t>0.11 : 1</t>
+  </si>
+  <si>
+    <t>0.87 : 1</t>
+  </si>
+  <si>
+    <t>0.96 : 1</t>
+  </si>
+  <si>
+    <t>0.14 : 1</t>
+  </si>
+  <si>
+    <t>1.67 : 1</t>
+  </si>
+  <si>
+    <t>1.32 : 1</t>
+  </si>
+  <si>
+    <t>0.33 : 1</t>
+  </si>
+  <si>
+    <t>0.93 : 1</t>
+  </si>
+  <si>
+    <t>1.63 : 1</t>
+  </si>
+  <si>
+    <t>0.51 : 1</t>
+  </si>
+  <si>
+    <t>0.70 : 1</t>
+  </si>
+  <si>
+    <t>1.22 : 1</t>
+  </si>
+  <si>
+    <t>0.66 : 1</t>
+  </si>
+  <si>
+    <t>1.47 : 1</t>
+  </si>
+  <si>
+    <t>0.30 : 1</t>
+  </si>
+  <si>
+    <t>0.26 : 1</t>
+  </si>
+  <si>
+    <t>1.04 : 1</t>
+  </si>
+  <si>
+    <t>0.24 : 1</t>
+  </si>
+  <si>
+    <t>0.79 : 1</t>
+  </si>
+  <si>
+    <t>0.50 : 1</t>
+  </si>
+  <si>
+    <t>1.99 : 1</t>
+  </si>
+  <si>
+    <t>0.61 : 1</t>
+  </si>
+  <si>
+    <t>0.08 : 1</t>
+  </si>
+  <si>
+    <t>2.16 : 1</t>
   </si>
 </sst>
 </file>
@@ -2408,16 +2483,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2440,7 +2515,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -2461,7 +2536,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -2482,7 +2557,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -2503,7 +2578,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -2524,7 +2599,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -2545,7 +2620,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -2566,7 +2641,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -2587,7 +2662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -2608,7 +2683,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -2629,7 +2704,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -2646,7 +2721,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -2667,7 +2742,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -2688,7 +2763,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -2709,7 +2784,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -2730,7 +2805,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -2751,7 +2826,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -2772,7 +2847,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -2793,7 +2868,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -2814,7 +2889,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -2835,7 +2910,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -2856,7 +2931,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -2877,7 +2952,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -2898,7 +2973,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -2919,7 +2994,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -2940,7 +3015,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -2957,7 +3032,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -2978,7 +3053,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -2999,7 +3074,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -3020,7 +3095,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -3041,7 +3116,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -3062,7 +3137,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -3083,7 +3158,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -3104,7 +3179,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -3125,7 +3200,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -3146,7 +3221,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -3167,7 +3242,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -3188,7 +3263,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -3209,7 +3284,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -3230,7 +3305,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -3251,7 +3326,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -3272,7 +3347,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -3293,7 +3368,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -3314,7 +3389,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -3335,7 +3410,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -3356,7 +3431,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -3377,7 +3452,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -3398,7 +3473,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -3419,7 +3494,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -3440,7 +3515,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -3461,7 +3536,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -3482,7 +3557,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -3503,7 +3578,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -3524,7 +3599,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -3590,16 +3665,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3622,7 +3697,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -3633,7 +3708,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -3644,7 +3719,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -3655,7 +3730,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -3666,7 +3741,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -3677,7 +3752,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -3688,7 +3763,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -3699,7 +3774,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -3710,7 +3785,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -3721,7 +3796,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -3732,7 +3807,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -3743,7 +3818,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -3754,7 +3829,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -3765,7 +3840,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -3776,7 +3851,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -3787,7 +3862,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -3798,7 +3873,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -3809,7 +3884,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -3820,7 +3895,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -3831,7 +3906,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -3842,7 +3917,7 @@
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -3853,7 +3928,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -3864,7 +3939,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -3875,7 +3950,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -3886,7 +3961,7 @@
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -3897,7 +3972,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -3908,7 +3983,7 @@
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -3919,7 +3994,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -3930,7 +4005,7 @@
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -3941,7 +4016,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -3952,7 +4027,7 @@
       <c r="F31" s="12"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -3963,7 +4038,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -3974,7 +4049,7 @@
       <c r="F33" s="12"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -3985,7 +4060,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -3996,7 +4071,7 @@
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -4007,7 +4082,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -4018,7 +4093,7 @@
       <c r="F37" s="12"/>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -4029,7 +4104,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -4040,7 +4115,7 @@
       <c r="F39" s="12"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -4051,7 +4126,7 @@
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -4062,7 +4137,7 @@
       <c r="F41" s="28"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -4073,7 +4148,7 @@
       <c r="F42" s="24"/>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -4084,7 +4159,7 @@
       <c r="F43" s="28"/>
       <c r="G43" s="29"/>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -4095,7 +4170,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -4106,7 +4181,7 @@
       <c r="F45" s="12"/>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -4117,7 +4192,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -4128,7 +4203,7 @@
       <c r="F47" s="12"/>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -4139,7 +4214,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -4150,7 +4225,7 @@
       <c r="F49" s="12"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -4161,7 +4236,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -4172,7 +4247,7 @@
       <c r="F51" s="12"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -4183,7 +4258,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -4194,7 +4269,7 @@
       <c r="F53" s="12"/>
       <c r="G53" s="13"/>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -4250,16 +4325,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4282,7 +4357,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -4293,7 +4368,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -4304,7 +4379,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -4315,7 +4390,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -4326,7 +4401,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -4337,7 +4412,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -4348,7 +4423,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -4359,7 +4434,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -4370,7 +4445,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -4381,7 +4456,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -4392,7 +4467,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -4403,7 +4478,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -4414,7 +4489,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -4425,7 +4500,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -4436,7 +4511,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -4447,7 +4522,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -4458,7 +4533,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -4469,7 +4544,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -4480,7 +4555,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -4491,7 +4566,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -4502,7 +4577,7 @@
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -4513,7 +4588,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -4524,7 +4599,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -4535,7 +4610,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -4546,7 +4621,7 @@
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -4557,7 +4632,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -4568,7 +4643,7 @@
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -4579,7 +4654,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -4590,7 +4665,7 @@
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -4601,7 +4676,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -4612,7 +4687,7 @@
       <c r="F31" s="12"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -4623,7 +4698,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -4634,7 +4709,7 @@
       <c r="F33" s="12"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -4645,7 +4720,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -4656,7 +4731,7 @@
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -4667,7 +4742,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -4678,7 +4753,7 @@
       <c r="F37" s="12"/>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -4689,7 +4764,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -4700,7 +4775,7 @@
       <c r="F39" s="12"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -4711,7 +4786,7 @@
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -4722,7 +4797,7 @@
       <c r="F41" s="28"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -4733,7 +4808,7 @@
       <c r="F42" s="24"/>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -4744,7 +4819,7 @@
       <c r="F43" s="28"/>
       <c r="G43" s="29"/>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -4755,7 +4830,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -4766,7 +4841,7 @@
       <c r="F45" s="12"/>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -4777,7 +4852,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -4788,7 +4863,7 @@
       <c r="F47" s="12"/>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -4799,7 +4874,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -4810,7 +4885,7 @@
       <c r="F49" s="12"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -4821,7 +4896,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -4832,7 +4907,7 @@
       <c r="F51" s="12"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -4843,7 +4918,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -4854,7 +4929,7 @@
       <c r="F53" s="12"/>
       <c r="G53" s="13"/>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -4910,16 +4985,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4942,7 +5017,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -4953,7 +5028,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -4964,7 +5039,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -4975,7 +5050,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -4986,7 +5061,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -4997,7 +5072,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -5008,7 +5083,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -5019,7 +5094,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -5030,7 +5105,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -5041,7 +5116,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -5052,7 +5127,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -5063,7 +5138,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -5074,7 +5149,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -5085,7 +5160,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -5096,7 +5171,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -5107,7 +5182,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -5118,7 +5193,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -5129,7 +5204,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -5140,7 +5215,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -5151,7 +5226,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -5162,7 +5237,7 @@
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -5173,7 +5248,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -5184,7 +5259,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -5195,7 +5270,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -5206,7 +5281,7 @@
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -5217,7 +5292,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -5228,7 +5303,7 @@
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -5239,7 +5314,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -5250,7 +5325,7 @@
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -5261,7 +5336,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -5272,7 +5347,7 @@
       <c r="F31" s="12"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -5283,7 +5358,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -5294,7 +5369,7 @@
       <c r="F33" s="12"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -5305,7 +5380,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -5316,7 +5391,7 @@
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -5327,7 +5402,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -5338,7 +5413,7 @@
       <c r="F37" s="12"/>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -5349,7 +5424,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -5360,7 +5435,7 @@
       <c r="F39" s="12"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -5371,7 +5446,7 @@
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -5382,7 +5457,7 @@
       <c r="F41" s="28"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -5393,7 +5468,7 @@
       <c r="F42" s="24"/>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -5404,7 +5479,7 @@
       <c r="F43" s="28"/>
       <c r="G43" s="29"/>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -5415,7 +5490,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -5426,7 +5501,7 @@
       <c r="F45" s="12"/>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -5437,7 +5512,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -5448,7 +5523,7 @@
       <c r="F47" s="12"/>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -5459,7 +5534,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -5470,7 +5545,7 @@
       <c r="F49" s="12"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -5481,7 +5556,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -5492,7 +5567,7 @@
       <c r="F51" s="12"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -5503,7 +5578,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -5514,7 +5589,7 @@
       <c r="F53" s="12"/>
       <c r="G53" s="13"/>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -5570,16 +5645,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5602,21 +5677,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="7">
         <f>January!B2+February!B2+March!B2+April!B2+May!B2+June!B2+July!B2+August!B2+September!B2+October!B2+November!B2+December!B2</f>
-        <v>2807</v>
+        <v>4403</v>
       </c>
       <c r="C2" s="7">
         <f>January!C2+February!C2+March!C2+April!C2+May!C2+June!C2+July!C2+August!C2+September!C2+October!C2+November!C2+December!C2</f>
-        <v>2440</v>
+        <v>3703</v>
       </c>
       <c r="D2" s="7">
         <f>January!D2+February!D2+March!D2+April!D2+May!D2+June!D2+July!D2+August!D2+September!D2+October!D2+November!D2+December!D2</f>
-        <v>367</v>
+        <v>700</v>
       </c>
       <c r="E2" s="8" t="str">
         <f>IF(D2 &gt; 0, "We borrowed more than we lent this year", "")</f>
@@ -5628,24 +5703,24 @@
       </c>
       <c r="G2" s="9" t="str">
         <f>IF(ISERROR(ROUND(B2/C2,2)&amp;" : 1"), "", ROUND(B2/C2,2)&amp;" : 1")</f>
-        <v>1.15 : 1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.19 : 1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="11">
         <f>January!B3+February!B3+March!B3+April!B3+May!B3+June!B3+July!B3+August!B3+September!B3+October!B3+November!B3+December!B3</f>
-        <v>1343</v>
+        <v>1993</v>
       </c>
       <c r="C3" s="11">
         <f>January!C3+February!C3+March!C3+April!C3+May!C3+June!C3+July!C3+August!C3+September!C3+October!C3+November!C3+December!C3</f>
-        <v>779</v>
+        <v>1228</v>
       </c>
       <c r="D3" s="11">
         <f>January!D3+February!D3+March!D3+April!D3+May!D3+June!D3+July!D3+August!D3+September!D3+October!D3+November!D3+December!D3</f>
-        <v>564</v>
+        <v>765</v>
       </c>
       <c r="E3" s="12" t="str">
         <f t="shared" ref="E3:E54" si="0">IF(D3 &gt; 0, "We borrowed more than we lent this year", "")</f>
@@ -5657,24 +5732,24 @@
       </c>
       <c r="G3" s="13" t="str">
         <f t="shared" ref="G3:G54" si="2">IF(ISERROR(ROUND(B3/C3,2)&amp;" : 1"), "", ROUND(B3/C3,2)&amp;" : 1")</f>
-        <v>1.72 : 1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.62 : 1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="7">
         <f>January!B4+February!B4+March!B4+April!B4+May!B4+June!B4+July!B4+August!B4+September!B4+October!B4+November!B4+December!B4</f>
-        <v>2509</v>
+        <v>3822</v>
       </c>
       <c r="C4" s="7">
         <f>January!C4+February!C4+March!C4+April!C4+May!C4+June!C4+July!C4+August!C4+September!C4+October!C4+November!C4+December!C4</f>
-        <v>2360</v>
+        <v>3480</v>
       </c>
       <c r="D4" s="7">
         <f>January!D4+February!D4+March!D4+April!D4+May!D4+June!D4+July!D4+August!D4+September!D4+October!D4+November!D4+December!D4</f>
-        <v>149</v>
+        <v>342</v>
       </c>
       <c r="E4" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5686,24 +5761,24 @@
       </c>
       <c r="G4" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.06 : 1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.1 : 1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="11">
         <f>January!B5+February!B5+March!B5+April!B5+May!B5+June!B5+July!B5+August!B5+September!B5+October!B5+November!B5+December!B5</f>
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C5" s="11">
         <f>January!C5+February!C5+March!C5+April!C5+May!C5+June!C5+July!C5+August!C5+September!C5+October!C5+November!C5+December!C5</f>
-        <v>254</v>
+        <v>367</v>
       </c>
       <c r="D5" s="11">
         <f>January!D5+February!D5+March!D5+April!D5+May!D5+June!D5+July!D5+August!D5+September!D5+October!D5+November!D5+December!D5</f>
-        <v>-208</v>
+        <v>-309</v>
       </c>
       <c r="E5" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5715,24 +5790,24 @@
       </c>
       <c r="G5" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.18 : 1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.16 : 1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="7">
         <f>January!B6+February!B6+March!B6+April!B6+May!B6+June!B6+July!B6+August!B6+September!B6+October!B6+November!B6+December!B6</f>
-        <v>2128</v>
+        <v>3189</v>
       </c>
       <c r="C6" s="7">
         <f>January!C6+February!C6+March!C6+April!C6+May!C6+June!C6+July!C6+August!C6+September!C6+October!C6+November!C6+December!C6</f>
-        <v>2284</v>
+        <v>3454</v>
       </c>
       <c r="D6" s="7">
         <f>January!D6+February!D6+March!D6+April!D6+May!D6+June!D6+July!D6+August!D6+September!D6+October!D6+November!D6+December!D6</f>
-        <v>-156</v>
+        <v>-265</v>
       </c>
       <c r="E6" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5744,24 +5819,24 @@
       </c>
       <c r="G6" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.93 : 1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.92 : 1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="11">
         <f>January!B7+February!B7+March!B7+April!B7+May!B7+June!B7+July!B7+August!B7+September!B7+October!B7+November!B7+December!B7</f>
-        <v>386</v>
+        <v>614</v>
       </c>
       <c r="C7" s="11">
         <f>January!C7+February!C7+March!C7+April!C7+May!C7+June!C7+July!C7+August!C7+September!C7+October!C7+November!C7+December!C7</f>
-        <v>327</v>
+        <v>515</v>
       </c>
       <c r="D7" s="11">
         <f>January!D7+February!D7+March!D7+April!D7+May!D7+June!D7+July!D7+August!D7+September!D7+October!D7+November!D7+December!D7</f>
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="E7" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5773,24 +5848,24 @@
       </c>
       <c r="G7" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.18 : 1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.19 : 1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="7">
         <f>January!B8+February!B8+March!B8+April!B8+May!B8+June!B8+July!B8+August!B8+September!B8+October!B8+November!B8+December!B8</f>
-        <v>218</v>
+        <v>362</v>
       </c>
       <c r="C8" s="7">
         <f>January!C8+February!C8+March!C8+April!C8+May!C8+June!C8+July!C8+August!C8+September!C8+October!C8+November!C8+December!C8</f>
-        <v>351</v>
+        <v>516</v>
       </c>
       <c r="D8" s="7">
         <f>January!D8+February!D8+March!D8+April!D8+May!D8+June!D8+July!D8+August!D8+September!D8+October!D8+November!D8+December!D8</f>
-        <v>-133</v>
+        <v>-154</v>
       </c>
       <c r="E8" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5802,24 +5877,24 @@
       </c>
       <c r="G8" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.62 : 1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.7 : 1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B9" s="11">
         <f>January!B9+February!B9+March!B9+April!B9+May!B9+June!B9+July!B9+August!B9+September!B9+October!B9+November!B9+December!B9</f>
-        <v>140</v>
+        <v>185</v>
       </c>
       <c r="C9" s="11">
         <f>January!C9+February!C9+March!C9+April!C9+May!C9+June!C9+July!C9+August!C9+September!C9+October!C9+November!C9+December!C9</f>
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="D9" s="11">
         <f>January!D9+February!D9+March!D9+April!D9+May!D9+June!D9+July!D9+August!D9+September!D9+October!D9+November!D9+December!D9</f>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E9" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5831,10 +5906,10 @@
       </c>
       <c r="G9" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.22 : 1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.14 : 1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -5844,11 +5919,11 @@
       </c>
       <c r="C10" s="7">
         <f>January!C10+February!C10+March!C10+April!C10+May!C10+June!C10+July!C10+August!C10+September!C10+October!C10+November!C10+December!C10</f>
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D10" s="7">
         <f>January!D10+February!D10+March!D10+April!D10+May!D10+June!D10+July!D10+August!D10+September!D10+October!D10+November!D10+December!D10</f>
-        <v>-47</v>
+        <v>-73</v>
       </c>
       <c r="E10" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5860,10 +5935,10 @@
       </c>
       <c r="G10" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.06 : 1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.04 : 1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -5892,21 +5967,21 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="15">
         <f>January!B12+February!B12+March!B12+April!B12+May!B12+June!B12+July!B12+August!B12+September!B12+October!B12+November!B12+December!B12</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C12" s="15">
         <f>January!C12+February!C12+March!C12+April!C12+May!C12+June!C12+July!C12+August!C12+September!C12+October!C12+November!C12+December!C12</f>
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D12" s="15">
         <f>January!D12+February!D12+March!D12+April!D12+May!D12+June!D12+July!D12+August!D12+September!D12+October!D12+November!D12+December!D12</f>
-        <v>-34</v>
+        <v>-53</v>
       </c>
       <c r="E12" s="16" t="str">
         <f t="shared" si="0"/>
@@ -5918,24 +5993,24 @@
       </c>
       <c r="G12" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>0.21 : 1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.18 : 1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
       <c r="B13" s="19">
         <f>January!B13+February!B13+March!B13+April!B13+May!B13+June!B13+July!B13+August!B13+September!B13+October!B13+November!B13+December!B13</f>
-        <v>94</v>
+        <v>163</v>
       </c>
       <c r="C13" s="19">
         <f>January!C13+February!C13+March!C13+April!C13+May!C13+June!C13+July!C13+August!C13+September!C13+October!C13+November!C13+December!C13</f>
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="D13" s="19">
         <f>January!D13+February!D13+March!D13+April!D13+May!D13+June!D13+July!D13+August!D13+September!D13+October!D13+November!D13+December!D13</f>
-        <v>-40</v>
+        <v>-29</v>
       </c>
       <c r="E13" s="20" t="str">
         <f t="shared" si="0"/>
@@ -5947,24 +6022,24 @@
       </c>
       <c r="G13" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>0.7 : 1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.85 : 1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
       <c r="B14" s="15">
         <f>January!B14+February!B14+March!B14+April!B14+May!B14+June!B14+July!B14+August!B14+September!B14+October!B14+November!B14+December!B14</f>
-        <v>294</v>
+        <v>431</v>
       </c>
       <c r="C14" s="15">
         <f>January!C14+February!C14+March!C14+April!C14+May!C14+June!C14+July!C14+August!C14+September!C14+October!C14+November!C14+December!C14</f>
-        <v>550</v>
+        <v>884</v>
       </c>
       <c r="D14" s="15">
         <f>January!D14+February!D14+March!D14+April!D14+May!D14+June!D14+July!D14+August!D14+September!D14+October!D14+November!D14+December!D14</f>
-        <v>-256</v>
+        <v>-453</v>
       </c>
       <c r="E14" s="16" t="str">
         <f t="shared" si="0"/>
@@ -5976,24 +6051,24 @@
       </c>
       <c r="G14" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>0.53 : 1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.49 : 1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
       <c r="B15" s="19">
         <f>January!B15+February!B15+March!B15+April!B15+May!B15+June!B15+July!B15+August!B15+September!B15+October!B15+November!B15+December!B15</f>
-        <v>101</v>
+        <v>152</v>
       </c>
       <c r="C15" s="19">
         <f>January!C15+February!C15+March!C15+April!C15+May!C15+June!C15+July!C15+August!C15+September!C15+October!C15+November!C15+December!C15</f>
-        <v>325</v>
+        <v>460</v>
       </c>
       <c r="D15" s="19">
         <f>January!D15+February!D15+March!D15+April!D15+May!D15+June!D15+July!D15+August!D15+September!D15+October!D15+November!D15+December!D15</f>
-        <v>-224</v>
+        <v>-308</v>
       </c>
       <c r="E15" s="20" t="str">
         <f t="shared" si="0"/>
@@ -6005,24 +6080,24 @@
       </c>
       <c r="G15" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>0.31 : 1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.33 : 1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B16" s="7">
         <f>January!B16+February!B16+March!B16+April!B16+May!B16+June!B16+July!B16+August!B16+September!B16+October!B16+November!B16+December!B16</f>
-        <v>134</v>
+        <v>187</v>
       </c>
       <c r="C16" s="7">
         <f>January!C16+February!C16+March!C16+April!C16+May!C16+June!C16+July!C16+August!C16+September!C16+October!C16+November!C16+December!C16</f>
-        <v>423</v>
+        <v>652</v>
       </c>
       <c r="D16" s="7">
         <f>January!D16+February!D16+March!D16+April!D16+May!D16+June!D16+July!D16+August!D16+September!D16+October!D16+November!D16+December!D16</f>
-        <v>-289</v>
+        <v>-465</v>
       </c>
       <c r="E16" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6034,24 +6109,24 @@
       </c>
       <c r="G16" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.32 : 1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.29 : 1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
       <c r="B17" s="11">
         <f>January!B17+February!B17+March!B17+April!B17+May!B17+June!B17+July!B17+August!B17+September!B17+October!B17+November!B17+December!B17</f>
-        <v>1422</v>
+        <v>2118</v>
       </c>
       <c r="C17" s="11">
         <f>January!C17+February!C17+March!C17+April!C17+May!C17+June!C17+July!C17+August!C17+September!C17+October!C17+November!C17+December!C17</f>
-        <v>857</v>
+        <v>1286</v>
       </c>
       <c r="D17" s="11">
         <f>January!D17+February!D17+March!D17+April!D17+May!D17+June!D17+July!D17+August!D17+September!D17+October!D17+November!D17+December!D17</f>
-        <v>565</v>
+        <v>832</v>
       </c>
       <c r="E17" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6063,24 +6138,24 @@
       </c>
       <c r="G17" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.66 : 1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.65 : 1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="7">
         <f>January!B18+February!B18+March!B18+April!B18+May!B18+June!B18+July!B18+August!B18+September!B18+October!B18+November!B18+December!B18</f>
-        <v>203</v>
+        <v>276</v>
       </c>
       <c r="C18" s="7">
         <f>January!C18+February!C18+March!C18+April!C18+May!C18+June!C18+July!C18+August!C18+September!C18+October!C18+November!C18+December!C18</f>
-        <v>175</v>
+        <v>246</v>
       </c>
       <c r="D18" s="7">
         <f>January!D18+February!D18+March!D18+April!D18+May!D18+June!D18+July!D18+August!D18+September!D18+October!D18+November!D18+December!D18</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E18" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6092,24 +6167,24 @@
       </c>
       <c r="G18" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.16 : 1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.12 : 1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
       <c r="B19" s="11">
         <f>January!B19+February!B19+March!B19+April!B19+May!B19+June!B19+July!B19+August!B19+September!B19+October!B19+November!B19+December!B19</f>
-        <v>1209</v>
+        <v>1789</v>
       </c>
       <c r="C19" s="11">
         <f>January!C19+February!C19+March!C19+April!C19+May!C19+June!C19+July!C19+August!C19+September!C19+October!C19+November!C19+December!C19</f>
-        <v>642</v>
+        <v>990</v>
       </c>
       <c r="D19" s="11">
         <f>January!D19+February!D19+March!D19+April!D19+May!D19+June!D19+July!D19+August!D19+September!D19+October!D19+November!D19+December!D19</f>
-        <v>567</v>
+        <v>799</v>
       </c>
       <c r="E19" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6121,10 +6196,10 @@
       </c>
       <c r="G19" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.88 : 1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.81 : 1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -6134,11 +6209,11 @@
       </c>
       <c r="C20" s="7">
         <f>January!C20+February!C20+March!C20+April!C20+May!C20+June!C20+July!C20+August!C20+September!C20+October!C20+November!C20+December!C20</f>
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="D20" s="7">
         <f>January!D20+February!D20+March!D20+April!D20+May!D20+June!D20+July!D20+August!D20+September!D20+October!D20+November!D20+December!D20</f>
-        <v>-102</v>
+        <v>-157</v>
       </c>
       <c r="E20" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6150,24 +6225,24 @@
       </c>
       <c r="G20" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.06 : 1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.04 : 1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
       <c r="B21" s="11">
         <f>January!B21+February!B21+March!B21+April!B21+May!B21+June!B21+July!B21+August!B21+September!B21+October!B21+November!B21+December!B21</f>
-        <v>949</v>
+        <v>1512</v>
       </c>
       <c r="C21" s="11">
         <f>January!C21+February!C21+March!C21+April!C21+May!C21+June!C21+July!C21+August!C21+September!C21+October!C21+November!C21+December!C21</f>
-        <v>859</v>
+        <v>1285</v>
       </c>
       <c r="D21" s="11">
         <f>January!D21+February!D21+March!D21+April!D21+May!D21+June!D21+July!D21+August!D21+September!D21+October!D21+November!D21+December!D21</f>
-        <v>90</v>
+        <v>227</v>
       </c>
       <c r="E21" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6179,24 +6254,24 @@
       </c>
       <c r="G21" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.1 : 1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.18 : 1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B22" s="7">
         <f>January!B22+February!B22+March!B22+April!B22+May!B22+June!B22+July!B22+August!B22+September!B22+October!B22+November!B22+December!B22</f>
-        <v>219</v>
+        <v>287</v>
       </c>
       <c r="C22" s="7">
         <f>January!C22+February!C22+March!C22+April!C22+May!C22+June!C22+July!C22+August!C22+September!C22+October!C22+November!C22+December!C22</f>
-        <v>497</v>
+        <v>737</v>
       </c>
       <c r="D22" s="7">
         <f>January!D22+February!D22+March!D22+April!D22+May!D22+June!D22+July!D22+August!D22+September!D22+October!D22+November!D22+December!D22</f>
-        <v>-278</v>
+        <v>-450</v>
       </c>
       <c r="E22" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6208,24 +6283,24 @@
       </c>
       <c r="G22" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.44 : 1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.39 : 1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
       <c r="B23" s="11">
         <f>January!B23+February!B23+March!B23+April!B23+May!B23+June!B23+July!B23+August!B23+September!B23+October!B23+November!B23+December!B23</f>
-        <v>1194</v>
+        <v>2054</v>
       </c>
       <c r="C23" s="11">
         <f>January!C23+February!C23+March!C23+April!C23+May!C23+June!C23+July!C23+August!C23+September!C23+October!C23+November!C23+December!C23</f>
-        <v>1122</v>
+        <v>1747</v>
       </c>
       <c r="D23" s="11">
         <f>January!D23+February!D23+March!D23+April!D23+May!D23+June!D23+July!D23+August!D23+September!D23+October!D23+November!D23+December!D23</f>
-        <v>72</v>
+        <v>307</v>
       </c>
       <c r="E23" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6237,24 +6312,24 @@
       </c>
       <c r="G23" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.06 : 1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.18 : 1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
       <c r="B24" s="7">
         <f>January!B24+February!B24+March!B24+April!B24+May!B24+June!B24+July!B24+August!B24+September!B24+October!B24+November!B24+December!B24</f>
-        <v>3710</v>
+        <v>5484</v>
       </c>
       <c r="C24" s="7">
         <f>January!C24+February!C24+March!C24+April!C24+May!C24+June!C24+July!C24+August!C24+September!C24+October!C24+November!C24+December!C24</f>
-        <v>2787</v>
+        <v>4324</v>
       </c>
       <c r="D24" s="7">
         <f>January!D24+February!D24+March!D24+April!D24+May!D24+June!D24+July!D24+August!D24+September!D24+October!D24+November!D24+December!D24</f>
-        <v>923</v>
+        <v>1160</v>
       </c>
       <c r="E24" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6266,24 +6341,24 @@
       </c>
       <c r="G24" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.33 : 1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.27 : 1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
       <c r="B25" s="11">
         <f>January!B25+February!B25+March!B25+April!B25+May!B25+June!B25+July!B25+August!B25+September!B25+October!B25+November!B25+December!B25</f>
-        <v>346</v>
+        <v>463</v>
       </c>
       <c r="C25" s="11">
         <f>January!C25+February!C25+March!C25+April!C25+May!C25+June!C25+July!C25+August!C25+September!C25+October!C25+November!C25+December!C25</f>
-        <v>660</v>
+        <v>1014</v>
       </c>
       <c r="D25" s="11">
         <f>January!D25+February!D25+March!D25+April!D25+May!D25+June!D25+July!D25+August!D25+September!D25+October!D25+November!D25+December!D25</f>
-        <v>-314</v>
+        <v>-551</v>
       </c>
       <c r="E25" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6295,10 +6370,10 @@
       </c>
       <c r="G25" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.52 : 1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.46 : 1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -6327,21 +6402,21 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
       <c r="B27" s="11">
         <f>January!B27+February!B27+March!B27+April!B27+May!B27+June!B27+July!B27+August!B27+September!B27+October!B27+November!B27+December!B27</f>
-        <v>403</v>
+        <v>572</v>
       </c>
       <c r="C27" s="11">
         <f>January!C27+February!C27+March!C27+April!C27+May!C27+June!C27+July!C27+August!C27+September!C27+October!C27+November!C27+December!C27</f>
-        <v>296</v>
+        <v>478</v>
       </c>
       <c r="D27" s="11">
         <f>January!D27+February!D27+March!D27+April!D27+May!D27+June!D27+July!D27+August!D27+September!D27+October!D27+November!D27+December!D27</f>
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="E27" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6353,53 +6428,53 @@
       </c>
       <c r="G27" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.36 : 1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.2 : 1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B28" s="7">
         <f>January!B28+February!B28+March!B28+April!B28+May!B28+June!B28+July!B28+August!B28+September!B28+October!B28+November!B28+December!B28</f>
-        <v>258</v>
+        <v>411</v>
       </c>
       <c r="C28" s="7">
         <f>January!C28+February!C28+March!C28+April!C28+May!C28+June!C28+July!C28+August!C28+September!C28+October!C28+November!C28+December!C28</f>
-        <v>264</v>
+        <v>402</v>
       </c>
       <c r="D28" s="7">
         <f>January!D28+February!D28+March!D28+April!D28+May!D28+June!D28+July!D28+August!D28+September!D28+October!D28+November!D28+December!D28</f>
-        <v>-6</v>
+        <v>9</v>
       </c>
       <c r="E28" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>We borrowed more than we lent this year</v>
       </c>
       <c r="F28" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>We lent more than we borrowed this year</v>
+        <v/>
       </c>
       <c r="G28" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.98 : 1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.02 : 1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B29" s="11">
         <f>January!B29+February!B29+March!B29+April!B29+May!B29+June!B29+July!B29+August!B29+September!B29+October!B29+November!B29+December!B29</f>
-        <v>1761</v>
+        <v>2561</v>
       </c>
       <c r="C29" s="11">
         <f>January!C29+February!C29+March!C29+April!C29+May!C29+June!C29+July!C29+August!C29+September!C29+October!C29+November!C29+December!C29</f>
-        <v>1034</v>
+        <v>1525</v>
       </c>
       <c r="D29" s="11">
         <f>January!D29+February!D29+March!D29+April!D29+May!D29+June!D29+July!D29+August!D29+September!D29+October!D29+November!D29+December!D29</f>
-        <v>727</v>
+        <v>1036</v>
       </c>
       <c r="E29" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6411,24 +6486,24 @@
       </c>
       <c r="G29" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.7 : 1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.68 : 1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B30" s="7">
         <f>January!B30+February!B30+March!B30+April!B30+May!B30+June!B30+July!B30+August!B30+September!B30+October!B30+November!B30+December!B30</f>
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C30" s="7">
         <f>January!C30+February!C30+March!C30+April!C30+May!C30+June!C30+July!C30+August!C30+September!C30+October!C30+November!C30+December!C30</f>
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D30" s="7">
         <f>January!D30+February!D30+March!D30+April!D30+May!D30+June!D30+July!D30+August!D30+September!D30+October!D30+November!D30+December!D30</f>
-        <v>-21</v>
+        <v>-9</v>
       </c>
       <c r="E30" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6440,24 +6515,24 @@
       </c>
       <c r="G30" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.61 : 1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.87 : 1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
       <c r="B31" s="11">
         <f>January!B31+February!B31+March!B31+April!B31+May!B31+June!B31+July!B31+August!B31+September!B31+October!B31+November!B31+December!B31</f>
-        <v>258</v>
+        <v>404</v>
       </c>
       <c r="C31" s="11">
         <f>January!C31+February!C31+March!C31+April!C31+May!C31+June!C31+July!C31+August!C31+September!C31+October!C31+November!C31+December!C31</f>
-        <v>512</v>
+        <v>797</v>
       </c>
       <c r="D31" s="11">
         <f>January!D31+February!D31+March!D31+April!D31+May!D31+June!D31+July!D31+August!D31+September!D31+October!D31+November!D31+December!D31</f>
-        <v>-254</v>
+        <v>-393</v>
       </c>
       <c r="E31" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6469,24 +6544,24 @@
       </c>
       <c r="G31" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.5 : 1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.51 : 1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
       <c r="B32" s="7">
         <f>January!B32+February!B32+March!B32+April!B32+May!B32+June!B32+July!B32+August!B32+September!B32+October!B32+November!B32+December!B32</f>
-        <v>920</v>
+        <v>1349</v>
       </c>
       <c r="C32" s="7">
         <f>January!C32+February!C32+March!C32+April!C32+May!C32+June!C32+July!C32+August!C32+September!C32+October!C32+November!C32+December!C32</f>
-        <v>993</v>
+        <v>1602</v>
       </c>
       <c r="D32" s="7">
         <f>January!D32+February!D32+March!D32+April!D32+May!D32+June!D32+July!D32+August!D32+September!D32+October!D32+November!D32+December!D32</f>
-        <v>-73</v>
+        <v>-253</v>
       </c>
       <c r="E32" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6498,24 +6573,24 @@
       </c>
       <c r="G32" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.93 : 1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.84 : 1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
       <c r="B33" s="11">
         <f>January!B33+February!B33+March!B33+April!B33+May!B33+June!B33+July!B33+August!B33+September!B33+October!B33+November!B33+December!B33</f>
-        <v>757</v>
+        <v>1143</v>
       </c>
       <c r="C33" s="11">
         <f>January!C33+February!C33+March!C33+April!C33+May!C33+June!C33+July!C33+August!C33+September!C33+October!C33+November!C33+December!C33</f>
-        <v>730</v>
+        <v>1046</v>
       </c>
       <c r="D33" s="11">
         <f>January!D33+February!D33+March!D33+April!D33+May!D33+June!D33+July!D33+August!D33+September!D33+October!D33+November!D33+December!D33</f>
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="E33" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6527,24 +6602,24 @@
       </c>
       <c r="G33" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.04 : 1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.09 : 1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
       <c r="B34" s="7">
         <f>January!B34+February!B34+March!B34+April!B34+May!B34+June!B34+July!B34+August!B34+September!B34+October!B34+November!B34+December!B34</f>
-        <v>432</v>
+        <v>581</v>
       </c>
       <c r="C34" s="7">
         <f>January!C34+February!C34+March!C34+April!C34+May!C34+June!C34+July!C34+August!C34+September!C34+October!C34+November!C34+December!C34</f>
-        <v>208</v>
+        <v>365</v>
       </c>
       <c r="D34" s="7">
         <f>January!D34+February!D34+March!D34+April!D34+May!D34+June!D34+July!D34+August!D34+September!D34+October!D34+November!D34+December!D34</f>
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="E34" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6556,24 +6631,24 @@
       </c>
       <c r="G34" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>2.08 : 1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.59 : 1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B35" s="11">
         <f>January!B35+February!B35+March!B35+April!B35+May!B35+June!B35+July!B35+August!B35+September!B35+October!B35+November!B35+December!B35</f>
-        <v>1856</v>
+        <v>2915</v>
       </c>
       <c r="C35" s="11">
         <f>January!C35+February!C35+March!C35+April!C35+May!C35+June!C35+July!C35+August!C35+September!C35+October!C35+November!C35+December!C35</f>
-        <v>3086</v>
+        <v>4702</v>
       </c>
       <c r="D35" s="11">
         <f>January!D35+February!D35+March!D35+April!D35+May!D35+June!D35+July!D35+August!D35+September!D35+October!D35+November!D35+December!D35</f>
-        <v>-1230</v>
+        <v>-1787</v>
       </c>
       <c r="E35" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6585,24 +6660,24 @@
       </c>
       <c r="G35" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.6 : 1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.62 : 1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
       <c r="B36" s="7">
         <f>January!B36+February!B36+March!B36+April!B36+May!B36+June!B36+July!B36+August!B36+September!B36+October!B36+November!B36+December!B36</f>
-        <v>362</v>
+        <v>515</v>
       </c>
       <c r="C36" s="7">
         <f>January!C36+February!C36+March!C36+April!C36+May!C36+June!C36+July!C36+August!C36+September!C36+October!C36+November!C36+December!C36</f>
-        <v>1180</v>
+        <v>1750</v>
       </c>
       <c r="D36" s="7">
         <f>January!D36+February!D36+March!D36+April!D36+May!D36+June!D36+July!D36+August!D36+September!D36+October!D36+November!D36+December!D36</f>
-        <v>-818</v>
+        <v>-1235</v>
       </c>
       <c r="E36" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6614,24 +6689,24 @@
       </c>
       <c r="G36" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.31 : 1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.29 : 1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
       <c r="B37" s="11">
         <f>January!B37+February!B37+March!B37+April!B37+May!B37+June!B37+July!B37+August!B37+September!B37+October!B37+November!B37+December!B37</f>
-        <v>1027</v>
+        <v>1709</v>
       </c>
       <c r="C37" s="11">
         <f>January!C37+February!C37+March!C37+April!C37+May!C37+June!C37+July!C37+August!C37+September!C37+October!C37+November!C37+December!C37</f>
-        <v>903</v>
+        <v>1368</v>
       </c>
       <c r="D37" s="11">
         <f>January!D37+February!D37+March!D37+April!D37+May!D37+June!D37+July!D37+August!D37+September!D37+October!D37+November!D37+December!D37</f>
-        <v>124</v>
+        <v>341</v>
       </c>
       <c r="E37" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6643,24 +6718,24 @@
       </c>
       <c r="G37" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.14 : 1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.25 : 1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
       <c r="B38" s="7">
         <f>January!B38+February!B38+March!B38+April!B38+May!B38+June!B38+July!B38+August!B38+September!B38+October!B38+November!B38+December!B38</f>
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="C38" s="7">
         <f>January!C38+February!C38+March!C38+April!C38+May!C38+June!C38+July!C38+August!C38+September!C38+October!C38+November!C38+December!C38</f>
-        <v>385</v>
+        <v>611</v>
       </c>
       <c r="D38" s="7">
         <f>January!D38+February!D38+March!D38+April!D38+May!D38+June!D38+July!D38+August!D38+September!D38+October!D38+November!D38+December!D38</f>
-        <v>-332</v>
+        <v>-525</v>
       </c>
       <c r="E38" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6675,21 +6750,21 @@
         <v>0.14 : 1</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
       <c r="B39" s="11">
         <f>January!B39+February!B39+March!B39+April!B39+May!B39+June!B39+July!B39+August!B39+September!B39+October!B39+November!B39+December!B39</f>
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C39" s="11">
         <f>January!C39+February!C39+March!C39+April!C39+May!C39+June!C39+July!C39+August!C39+September!C39+October!C39+November!C39+December!C39</f>
-        <v>104</v>
+        <v>207</v>
       </c>
       <c r="D39" s="11">
         <f>January!D39+February!D39+March!D39+April!D39+May!D39+June!D39+July!D39+August!D39+September!D39+October!D39+November!D39+December!D39</f>
-        <v>-71</v>
+        <v>-143</v>
       </c>
       <c r="E39" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6701,24 +6776,24 @@
       </c>
       <c r="G39" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.32 : 1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.31 : 1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
       <c r="B40" s="23">
         <f>January!B40+February!B40+March!B40+April!B40+May!B40+June!B40+July!B40+August!B40+September!B40+October!B40+November!B40+December!B40</f>
-        <v>210</v>
+        <v>347</v>
       </c>
       <c r="C40" s="23">
         <f>January!C40+February!C40+March!C40+April!C40+May!C40+June!C40+July!C40+August!C40+September!C40+October!C40+November!C40+December!C40</f>
-        <v>242</v>
+        <v>384</v>
       </c>
       <c r="D40" s="23">
         <f>January!D40+February!D40+March!D40+April!D40+May!D40+June!D40+July!D40+August!D40+September!D40+October!D40+November!D40+December!D40</f>
-        <v>-32</v>
+        <v>-37</v>
       </c>
       <c r="E40" s="24" t="str">
         <f t="shared" si="0"/>
@@ -6730,24 +6805,24 @@
       </c>
       <c r="G40" s="25" t="str">
         <f t="shared" si="2"/>
-        <v>0.87 : 1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.9 : 1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
       <c r="B41" s="27">
         <f>January!B41+February!B41+March!B41+April!B41+May!B41+June!B41+July!B41+August!B41+September!B41+October!B41+November!B41+December!B41</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C41" s="27">
         <f>January!C41+February!C41+March!C41+April!C41+May!C41+June!C41+July!C41+August!C41+September!C41+October!C41+November!C41+December!C41</f>
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D41" s="27">
         <f>January!D41+February!D41+March!D41+April!D41+May!D41+June!D41+July!D41+August!D41+September!D41+October!D41+November!D41+December!D41</f>
-        <v>-28</v>
+        <v>-52</v>
       </c>
       <c r="E41" s="28" t="str">
         <f t="shared" si="0"/>
@@ -6759,24 +6834,24 @@
       </c>
       <c r="G41" s="29" t="str">
         <f t="shared" si="2"/>
-        <v>0.3 : 1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.26 : 1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
       <c r="B42" s="23">
         <f>January!B42+February!B42+March!B42+April!B42+May!B42+June!B42+July!B42+August!B42+September!B42+October!B42+November!B42+December!B42</f>
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C42" s="23">
         <f>January!C42+February!C42+March!C42+April!C42+May!C42+June!C42+July!C42+August!C42+September!C42+October!C42+November!C42+December!C42</f>
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="D42" s="23">
         <f>January!D42+February!D42+March!D42+April!D42+May!D42+June!D42+July!D42+August!D42+September!D42+October!D42+November!D42+December!D42</f>
-        <v>-32</v>
+        <v>-57</v>
       </c>
       <c r="E42" s="24" t="str">
         <f t="shared" si="0"/>
@@ -6788,24 +6863,24 @@
       </c>
       <c r="G42" s="25" t="str">
         <f t="shared" si="2"/>
-        <v>0.47 : 1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.39 : 1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
       <c r="B43" s="27">
         <f>January!B43+February!B43+March!B43+April!B43+May!B43+June!B43+July!B43+August!B43+September!B43+October!B43+November!B43+December!B43</f>
-        <v>441</v>
+        <v>558</v>
       </c>
       <c r="C43" s="27">
         <f>January!C43+February!C43+March!C43+April!C43+May!C43+June!C43+July!C43+August!C43+September!C43+October!C43+November!C43+December!C43</f>
-        <v>199</v>
+        <v>312</v>
       </c>
       <c r="D43" s="27">
         <f>January!D43+February!D43+March!D43+April!D43+May!D43+June!D43+July!D43+August!D43+September!D43+October!D43+November!D43+December!D43</f>
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E43" s="28" t="str">
         <f t="shared" si="0"/>
@@ -6817,24 +6892,24 @@
       </c>
       <c r="G43" s="29" t="str">
         <f t="shared" si="2"/>
-        <v>2.22 : 1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.79 : 1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
       <c r="B44" s="7">
         <f>January!B44+February!B44+March!B44+April!B44+May!B44+June!B44+July!B44+August!B44+September!B44+October!B44+November!B44+December!B44</f>
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="C44" s="7">
         <f>January!C44+February!C44+March!C44+April!C44+May!C44+June!C44+July!C44+August!C44+September!C44+October!C44+November!C44+December!C44</f>
-        <v>312</v>
+        <v>521</v>
       </c>
       <c r="D44" s="7">
         <f>January!D44+February!D44+March!D44+April!D44+May!D44+June!D44+July!D44+August!D44+September!D44+October!D44+November!D44+December!D44</f>
-        <v>-187</v>
+        <v>-345</v>
       </c>
       <c r="E44" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6846,24 +6921,24 @@
       </c>
       <c r="G44" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.4 : 1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.34 : 1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
       <c r="B45" s="11">
         <f>January!B45+February!B45+March!B45+April!B45+May!B45+June!B45+July!B45+August!B45+September!B45+October!B45+November!B45+December!B45</f>
-        <v>1095</v>
+        <v>1629</v>
       </c>
       <c r="C45" s="11">
         <f>January!C45+February!C45+March!C45+April!C45+May!C45+June!C45+July!C45+August!C45+September!C45+October!C45+November!C45+December!C45</f>
-        <v>1199</v>
+        <v>1878</v>
       </c>
       <c r="D45" s="11">
         <f>January!D45+February!D45+March!D45+April!D45+May!D45+June!D45+July!D45+August!D45+September!D45+October!D45+November!D45+December!D45</f>
-        <v>-104</v>
+        <v>-249</v>
       </c>
       <c r="E45" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6875,24 +6950,24 @@
       </c>
       <c r="G45" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.91 : 1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.87 : 1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
       <c r="B46" s="7">
         <f>January!B46+February!B46+March!B46+April!B46+May!B46+June!B46+July!B46+August!B46+September!B46+October!B46+November!B46+December!B46</f>
-        <v>1937</v>
+        <v>2910</v>
       </c>
       <c r="C46" s="7">
         <f>January!C46+February!C46+March!C46+April!C46+May!C46+June!C46+July!C46+August!C46+September!C46+October!C46+November!C46+December!C46</f>
-        <v>1612</v>
+        <v>2373</v>
       </c>
       <c r="D46" s="7">
         <f>January!D46+February!D46+March!D46+April!D46+May!D46+June!D46+July!D46+August!D46+September!D46+October!D46+November!D46+December!D46</f>
-        <v>325</v>
+        <v>537</v>
       </c>
       <c r="E46" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6904,24 +6979,24 @@
       </c>
       <c r="G46" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.2 : 1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.23 : 1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
       <c r="B47" s="11">
         <f>January!B47+February!B47+March!B47+April!B47+May!B47+June!B47+July!B47+August!B47+September!B47+October!B47+November!B47+December!B47</f>
-        <v>425</v>
+        <v>720</v>
       </c>
       <c r="C47" s="11">
         <f>January!C47+February!C47+March!C47+April!C47+May!C47+June!C47+July!C47+August!C47+September!C47+October!C47+November!C47+December!C47</f>
-        <v>1227</v>
+        <v>1820</v>
       </c>
       <c r="D47" s="11">
         <f>January!D47+February!D47+March!D47+April!D47+May!D47+June!D47+July!D47+August!D47+September!D47+October!D47+November!D47+December!D47</f>
-        <v>-802</v>
+        <v>-1100</v>
       </c>
       <c r="E47" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6933,24 +7008,24 @@
       </c>
       <c r="G47" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.35 : 1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.4 : 1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
       <c r="B48" s="7">
         <f>January!B48+February!B48+March!B48+April!B48+May!B48+June!B48+July!B48+August!B48+September!B48+October!B48+November!B48+December!B48</f>
-        <v>899</v>
+        <v>1456</v>
       </c>
       <c r="C48" s="7">
         <f>January!C48+February!C48+March!C48+April!C48+May!C48+June!C48+July!C48+August!C48+September!C48+October!C48+November!C48+December!C48</f>
-        <v>605</v>
+        <v>885</v>
       </c>
       <c r="D48" s="7">
         <f>January!D48+February!D48+March!D48+April!D48+May!D48+June!D48+July!D48+August!D48+September!D48+October!D48+November!D48+December!D48</f>
-        <v>294</v>
+        <v>571</v>
       </c>
       <c r="E48" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6962,24 +7037,24 @@
       </c>
       <c r="G48" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.49 : 1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.65 : 1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
       <c r="B49" s="11">
         <f>January!B49+February!B49+March!B49+April!B49+May!B49+June!B49+July!B49+August!B49+September!B49+October!B49+November!B49+December!B49</f>
-        <v>1702</v>
+        <v>2751</v>
       </c>
       <c r="C49" s="11">
         <f>January!C49+February!C49+March!C49+April!C49+May!C49+June!C49+July!C49+August!C49+September!C49+October!C49+November!C49+December!C49</f>
-        <v>1074</v>
+        <v>1656</v>
       </c>
       <c r="D49" s="11">
         <f>January!D49+February!D49+March!D49+April!D49+May!D49+June!D49+July!D49+August!D49+September!D49+October!D49+November!D49+December!D49</f>
-        <v>628</v>
+        <v>1095</v>
       </c>
       <c r="E49" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6991,24 +7066,24 @@
       </c>
       <c r="G49" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.58 : 1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.66 : 1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
       <c r="B50" s="7">
         <f>January!B50+February!B50+March!B50+April!B50+May!B50+June!B50+July!B50+August!B50+September!B50+October!B50+November!B50+December!B50</f>
-        <v>239</v>
+        <v>382</v>
       </c>
       <c r="C50" s="7">
         <f>January!C50+February!C50+March!C50+April!C50+May!C50+June!C50+July!C50+August!C50+September!C50+October!C50+November!C50+December!C50</f>
-        <v>363</v>
+        <v>534</v>
       </c>
       <c r="D50" s="7">
         <f>January!D50+February!D50+March!D50+April!D50+May!D50+June!D50+July!D50+August!D50+September!D50+October!D50+November!D50+December!D50</f>
-        <v>-124</v>
+        <v>-152</v>
       </c>
       <c r="E50" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7020,24 +7095,24 @@
       </c>
       <c r="G50" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.66 : 1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.72 : 1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
       <c r="B51" s="11">
         <f>January!B51+February!B51+March!B51+April!B51+May!B51+June!B51+July!B51+August!B51+September!B51+October!B51+November!B51+December!B51</f>
-        <v>1173</v>
+        <v>1672</v>
       </c>
       <c r="C51" s="11">
         <f>January!C51+February!C51+March!C51+April!C51+May!C51+June!C51+July!C51+August!C51+September!C51+October!C51+November!C51+December!C51</f>
-        <v>710</v>
+        <v>1124</v>
       </c>
       <c r="D51" s="11">
         <f>January!D51+February!D51+March!D51+April!D51+May!D51+June!D51+July!D51+August!D51+September!D51+October!D51+November!D51+December!D51</f>
-        <v>463</v>
+        <v>548</v>
       </c>
       <c r="E51" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7049,24 +7124,24 @@
       </c>
       <c r="G51" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.65 : 1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.49 : 1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B52" s="7">
         <f>January!B52+February!B52+March!B52+April!B52+May!B52+June!B52+July!B52+August!B52+September!B52+October!B52+November!B52+December!B52</f>
-        <v>252</v>
+        <v>413</v>
       </c>
       <c r="C52" s="7">
         <f>January!C52+February!C52+March!C52+April!C52+May!C52+June!C52+July!C52+August!C52+September!C52+October!C52+November!C52+December!C52</f>
-        <v>420</v>
+        <v>686</v>
       </c>
       <c r="D52" s="7">
         <f>January!D52+February!D52+March!D52+April!D52+May!D52+June!D52+July!D52+August!D52+September!D52+October!D52+November!D52+December!D52</f>
-        <v>-168</v>
+        <v>-273</v>
       </c>
       <c r="E52" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7081,21 +7156,21 @@
         <v>0.6 : 1</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
       <c r="B53" s="11">
         <f>January!B53+February!B53+March!B53+April!B53+May!B53+June!B53+July!B53+August!B53+September!B53+October!B53+November!B53+December!B53</f>
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C53" s="11">
         <f>January!C53+February!C53+March!C53+April!C53+May!C53+June!C53+July!C53+August!C53+September!C53+October!C53+November!C53+December!C53</f>
-        <v>568</v>
+        <v>819</v>
       </c>
       <c r="D53" s="11">
         <f>January!D53+February!D53+March!D53+April!D53+May!D53+June!D53+July!D53+August!D53+September!D53+October!D53+November!D53+December!D53</f>
-        <v>-506</v>
+        <v>-737</v>
       </c>
       <c r="E53" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7107,24 +7182,24 @@
       </c>
       <c r="G53" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.11 : 1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.1 : 1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
       <c r="B54" s="31">
         <f>January!B54+February!B54+March!B54+April!B54+May!B54+June!B54+July!B54+August!B54+September!B54+October!B54+November!B54+December!B54</f>
-        <v>756</v>
+        <v>1204</v>
       </c>
       <c r="C54" s="31">
         <f>January!C54+February!C54+March!C54+April!C54+May!C54+June!C54+July!C54+August!C54+September!C54+October!C54+November!C54+December!C54</f>
-        <v>457</v>
+        <v>664</v>
       </c>
       <c r="D54" s="31">
         <f>January!D54+February!D54+March!D54+April!D54+May!D54+June!D54+July!D54+August!D54+September!D54+October!D54+November!D54+December!D54</f>
-        <v>299</v>
+        <v>540</v>
       </c>
       <c r="E54" s="32" t="str">
         <f t="shared" si="0"/>
@@ -7136,7 +7211,7 @@
       </c>
       <c r="G54" s="33" t="str">
         <f t="shared" si="2"/>
-        <v>1.65 : 1</v>
+        <v>1.81 : 1</v>
       </c>
     </row>
   </sheetData>
@@ -7174,16 +7249,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7206,7 +7281,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -7227,7 +7302,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -7248,7 +7323,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -7269,7 +7344,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -7290,7 +7365,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -7311,7 +7386,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -7332,7 +7407,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -7353,7 +7428,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -7374,7 +7449,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -7395,7 +7470,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -7412,7 +7487,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -7433,7 +7508,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -7454,7 +7529,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -7475,7 +7550,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -7496,7 +7571,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -7517,7 +7592,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -7538,7 +7613,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -7559,7 +7634,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -7580,7 +7655,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -7601,7 +7676,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -7622,7 +7697,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -7643,7 +7718,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -7664,7 +7739,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -7685,7 +7760,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -7706,7 +7781,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -7723,7 +7798,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -7744,7 +7819,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -7765,7 +7840,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -7786,7 +7861,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -7807,7 +7882,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -7828,7 +7903,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -7849,7 +7924,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -7870,7 +7945,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -7891,7 +7966,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -7912,7 +7987,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -7933,7 +8008,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -7954,7 +8029,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -7975,7 +8050,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -7996,7 +8071,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -8017,7 +8092,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -8038,7 +8113,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -8059,7 +8134,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -8080,7 +8155,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -8101,7 +8176,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -8122,7 +8197,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -8143,7 +8218,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -8164,7 +8239,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -8185,7 +8260,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -8206,7 +8281,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -8227,7 +8302,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -8248,7 +8323,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -8269,7 +8344,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -8290,7 +8365,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -8356,16 +8431,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8388,588 +8463,1110 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8"/>
+      <c r="B2" s="7">
+        <v>1596</v>
+      </c>
+      <c r="C2" s="7">
+        <v>1263</v>
+      </c>
+      <c r="D2" s="7">
+        <v>333</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F2" s="8"/>
-      <c r="G2" s="9"/>
-    </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G2" s="9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="12"/>
+      <c r="B3" s="11">
+        <v>650</v>
+      </c>
+      <c r="C3" s="11">
+        <v>449</v>
+      </c>
+      <c r="D3" s="11">
+        <v>201</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F3" s="12"/>
-      <c r="G3" s="13"/>
-    </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G3" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8"/>
+      <c r="B4" s="7">
+        <v>1313</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1120</v>
+      </c>
+      <c r="D4" s="7">
+        <v>193</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F4" s="8"/>
-      <c r="G4" s="9"/>
-    </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G4" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
+      <c r="B5" s="11">
+        <v>12</v>
+      </c>
+      <c r="C5" s="11">
+        <v>113</v>
+      </c>
+      <c r="D5" s="11">
+        <v>-101</v>
+      </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13"/>
-    </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+      <c r="B6" s="7">
+        <v>1061</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1170</v>
+      </c>
+      <c r="D6" s="7">
+        <v>-109</v>
+      </c>
       <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9"/>
-    </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12"/>
+      <c r="B7" s="11">
+        <v>228</v>
+      </c>
+      <c r="C7" s="11">
+        <v>188</v>
+      </c>
+      <c r="D7" s="11">
+        <v>40</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="13"/>
-    </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G7" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+      <c r="B8" s="7">
+        <v>144</v>
+      </c>
+      <c r="C8" s="7">
+        <v>165</v>
+      </c>
+      <c r="D8" s="7">
+        <v>-21</v>
+      </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9"/>
-    </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
+      <c r="B9" s="11">
+        <v>45</v>
+      </c>
+      <c r="C9" s="11">
+        <v>47</v>
+      </c>
+      <c r="D9" s="11">
+        <v>-2</v>
+      </c>
       <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="13"/>
-    </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F9" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="B10" s="7">
+        <v>0</v>
+      </c>
+      <c r="C10" s="7">
+        <v>26</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-26</v>
+      </c>
       <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9"/>
-    </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
+      <c r="B11" s="11">
+        <v>0</v>
+      </c>
+      <c r="C11" s="11">
+        <v>0</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0</v>
+      </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
+      <c r="B12" s="15">
+        <v>3</v>
+      </c>
+      <c r="C12" s="15">
+        <v>22</v>
+      </c>
+      <c r="D12" s="15">
+        <v>-19</v>
+      </c>
       <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17"/>
-    </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="20"/>
+      <c r="B13" s="19">
+        <v>69</v>
+      </c>
+      <c r="C13" s="19">
+        <v>58</v>
+      </c>
+      <c r="D13" s="19">
+        <v>11</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>8</v>
+      </c>
       <c r="F13" s="20"/>
-      <c r="G13" s="21"/>
-    </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G13" s="21" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
+      <c r="B14" s="15">
+        <v>137</v>
+      </c>
+      <c r="C14" s="15">
+        <v>334</v>
+      </c>
+      <c r="D14" s="15">
+        <v>-197</v>
+      </c>
       <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="17"/>
-    </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F14" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
+      <c r="B15" s="19">
+        <v>51</v>
+      </c>
+      <c r="C15" s="19">
+        <v>135</v>
+      </c>
+      <c r="D15" s="19">
+        <v>-84</v>
+      </c>
       <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="21"/>
-    </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F15" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
+      <c r="B16" s="7">
+        <v>53</v>
+      </c>
+      <c r="C16" s="7">
+        <v>229</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-176</v>
+      </c>
       <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="9"/>
-    </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="12"/>
+      <c r="B17" s="11">
+        <v>696</v>
+      </c>
+      <c r="C17" s="11">
+        <v>429</v>
+      </c>
+      <c r="D17" s="11">
+        <v>267</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F17" s="12"/>
-      <c r="G17" s="13"/>
-    </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G17" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8"/>
+      <c r="B18" s="7">
+        <v>73</v>
+      </c>
+      <c r="C18" s="7">
+        <v>71</v>
+      </c>
+      <c r="D18" s="7">
+        <v>2</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F18" s="8"/>
-      <c r="G18" s="9"/>
-    </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G18" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="12"/>
+      <c r="B19" s="11">
+        <v>580</v>
+      </c>
+      <c r="C19" s="11">
+        <v>348</v>
+      </c>
+      <c r="D19" s="11">
+        <v>232</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="13"/>
-    </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G19" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
+      <c r="B20" s="7">
+        <v>0</v>
+      </c>
+      <c r="C20" s="7">
+        <v>55</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-55</v>
+      </c>
       <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="9"/>
-    </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="12"/>
+      <c r="B21" s="11">
+        <v>563</v>
+      </c>
+      <c r="C21" s="11">
+        <v>426</v>
+      </c>
+      <c r="D21" s="11">
+        <v>137</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="13"/>
-    </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G21" s="13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+      <c r="B22" s="7">
+        <v>68</v>
+      </c>
+      <c r="C22" s="7">
+        <v>240</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-172</v>
+      </c>
       <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="9"/>
-    </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F22" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="12"/>
+      <c r="B23" s="11">
+        <v>860</v>
+      </c>
+      <c r="C23" s="11">
+        <v>625</v>
+      </c>
+      <c r="D23" s="11">
+        <v>235</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="13"/>
-    </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G23" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8"/>
+      <c r="B24" s="7">
+        <v>1774</v>
+      </c>
+      <c r="C24" s="7">
+        <v>1537</v>
+      </c>
+      <c r="D24" s="7">
+        <v>237</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
-    </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G24" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="B25" s="11">
+        <v>117</v>
+      </c>
+      <c r="C25" s="11">
+        <v>354</v>
+      </c>
+      <c r="D25" s="11">
+        <v>-237</v>
+      </c>
       <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="13"/>
-    </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F25" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
+      <c r="B26" s="7">
+        <v>0</v>
+      </c>
+      <c r="C26" s="7">
+        <v>0</v>
+      </c>
+      <c r="D26" s="7">
+        <v>0</v>
+      </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
+      <c r="B27" s="11">
+        <v>169</v>
+      </c>
+      <c r="C27" s="11">
+        <v>182</v>
+      </c>
+      <c r="D27" s="11">
+        <v>-13</v>
+      </c>
       <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="13"/>
-    </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F27" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="8"/>
+      <c r="B28" s="7">
+        <v>153</v>
+      </c>
+      <c r="C28" s="7">
+        <v>138</v>
+      </c>
+      <c r="D28" s="7">
+        <v>15</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F28" s="8"/>
-      <c r="G28" s="9"/>
-    </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G28" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="12"/>
+      <c r="B29" s="11">
+        <v>800</v>
+      </c>
+      <c r="C29" s="11">
+        <v>491</v>
+      </c>
+      <c r="D29" s="11">
+        <v>309</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F29" s="12"/>
-      <c r="G29" s="13"/>
-    </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G29" s="13" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="8"/>
+      <c r="B30" s="7">
+        <v>27</v>
+      </c>
+      <c r="C30" s="7">
+        <v>15</v>
+      </c>
+      <c r="D30" s="7">
+        <v>12</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F30" s="8"/>
-      <c r="G30" s="9"/>
-    </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G30" s="9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
+      <c r="B31" s="11">
+        <v>146</v>
+      </c>
+      <c r="C31" s="11">
+        <v>285</v>
+      </c>
+      <c r="D31" s="11">
+        <v>-139</v>
+      </c>
       <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="13"/>
-    </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F31" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
+      <c r="B32" s="7">
+        <v>429</v>
+      </c>
+      <c r="C32" s="7">
+        <v>609</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-180</v>
+      </c>
       <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="9"/>
-    </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F32" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="12"/>
+      <c r="B33" s="11">
+        <v>386</v>
+      </c>
+      <c r="C33" s="11">
+        <v>316</v>
+      </c>
+      <c r="D33" s="11">
+        <v>70</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F33" s="12"/>
-      <c r="G33" s="13"/>
-    </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G33" s="13" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
+      <c r="B34" s="7">
+        <v>149</v>
+      </c>
+      <c r="C34" s="7">
+        <v>157</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-8</v>
+      </c>
       <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="9"/>
-    </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F34" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
+      <c r="B35" s="11">
+        <v>1059</v>
+      </c>
+      <c r="C35" s="11">
+        <v>1616</v>
+      </c>
+      <c r="D35" s="11">
+        <v>-557</v>
+      </c>
       <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="13"/>
-    </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F35" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
+      <c r="B36" s="7">
+        <v>153</v>
+      </c>
+      <c r="C36" s="7">
+        <v>570</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-417</v>
+      </c>
       <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="9"/>
-    </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F36" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="12"/>
+      <c r="B37" s="11">
+        <v>682</v>
+      </c>
+      <c r="C37" s="11">
+        <v>465</v>
+      </c>
+      <c r="D37" s="11">
+        <v>217</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="13"/>
-    </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G37" s="13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
+      <c r="B38" s="7">
+        <v>33</v>
+      </c>
+      <c r="C38" s="7">
+        <v>226</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-193</v>
+      </c>
       <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="9"/>
-    </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F38" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
+      <c r="B39" s="11">
+        <v>31</v>
+      </c>
+      <c r="C39" s="11">
+        <v>103</v>
+      </c>
+      <c r="D39" s="11">
+        <v>-72</v>
+      </c>
       <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="13"/>
-    </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F39" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
+      <c r="B40" s="23">
+        <v>137</v>
+      </c>
+      <c r="C40" s="23">
+        <v>142</v>
+      </c>
+      <c r="D40" s="23">
+        <v>-5</v>
+      </c>
       <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="25"/>
-    </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F40" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="25" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
+      <c r="B41" s="27">
+        <v>6</v>
+      </c>
+      <c r="C41" s="27">
+        <v>30</v>
+      </c>
+      <c r="D41" s="27">
+        <v>-24</v>
+      </c>
       <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="29"/>
-    </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F41" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
+      <c r="B42" s="23">
+        <v>9</v>
+      </c>
+      <c r="C42" s="23">
+        <v>34</v>
+      </c>
+      <c r="D42" s="23">
+        <v>-25</v>
+      </c>
       <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="25"/>
-    </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F42" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="25" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="28"/>
+      <c r="B43" s="27">
+        <v>117</v>
+      </c>
+      <c r="C43" s="27">
+        <v>113</v>
+      </c>
+      <c r="D43" s="27">
+        <v>4</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>8</v>
+      </c>
       <c r="F43" s="28"/>
-      <c r="G43" s="29"/>
-    </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G43" s="29" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
+      <c r="B44" s="7">
+        <v>51</v>
+      </c>
+      <c r="C44" s="7">
+        <v>209</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-158</v>
+      </c>
       <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="9"/>
-    </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F44" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
+      <c r="B45" s="11">
+        <v>534</v>
+      </c>
+      <c r="C45" s="11">
+        <v>679</v>
+      </c>
+      <c r="D45" s="11">
+        <v>-145</v>
+      </c>
       <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="13"/>
-    </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F45" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="8"/>
+      <c r="B46" s="7">
+        <v>973</v>
+      </c>
+      <c r="C46" s="7">
+        <v>761</v>
+      </c>
+      <c r="D46" s="7">
+        <v>212</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F46" s="8"/>
-      <c r="G46" s="9"/>
-    </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G46" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
+      <c r="B47" s="11">
+        <v>295</v>
+      </c>
+      <c r="C47" s="11">
+        <v>593</v>
+      </c>
+      <c r="D47" s="11">
+        <v>-298</v>
+      </c>
       <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="13"/>
-    </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F47" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="8"/>
+      <c r="B48" s="7">
+        <v>557</v>
+      </c>
+      <c r="C48" s="7">
+        <v>280</v>
+      </c>
+      <c r="D48" s="7">
+        <v>277</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F48" s="8"/>
-      <c r="G48" s="9"/>
-    </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G48" s="9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="12"/>
+      <c r="B49" s="11">
+        <v>1049</v>
+      </c>
+      <c r="C49" s="11">
+        <v>582</v>
+      </c>
+      <c r="D49" s="11">
+        <v>467</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="13"/>
-    </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G49" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
+      <c r="B50" s="7">
+        <v>143</v>
+      </c>
+      <c r="C50" s="7">
+        <v>171</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-28</v>
+      </c>
       <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="9"/>
-    </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F50" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="12"/>
+      <c r="B51" s="11">
+        <v>499</v>
+      </c>
+      <c r="C51" s="11">
+        <v>414</v>
+      </c>
+      <c r="D51" s="11">
+        <v>85</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F51" s="12"/>
-      <c r="G51" s="13"/>
-    </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G51" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
+      <c r="B52" s="7">
+        <v>161</v>
+      </c>
+      <c r="C52" s="7">
+        <v>266</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-105</v>
+      </c>
       <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="9"/>
-    </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F52" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
+      <c r="B53" s="11">
+        <v>20</v>
+      </c>
+      <c r="C53" s="11">
+        <v>251</v>
+      </c>
+      <c r="D53" s="11">
+        <v>-231</v>
+      </c>
       <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="13"/>
-    </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F53" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" s="13" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B54" s="31"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="32"/>
+      <c r="B54" s="31">
+        <v>448</v>
+      </c>
+      <c r="C54" s="31">
+        <v>207</v>
+      </c>
+      <c r="D54" s="31">
+        <v>241</v>
+      </c>
+      <c r="E54" s="32" t="s">
+        <v>8</v>
+      </c>
       <c r="F54" s="32"/>
-      <c r="G54" s="33"/>
+      <c r="G54" s="33" t="s">
+        <v>169</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
@@ -9016,16 +9613,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9048,7 +9645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -9059,7 +9656,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -9070,7 +9667,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -9081,7 +9678,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -9092,7 +9689,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -9103,7 +9700,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -9114,7 +9711,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -9125,7 +9722,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -9136,7 +9733,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -9147,7 +9744,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -9158,7 +9755,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -9169,7 +9766,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -9180,7 +9777,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -9191,7 +9788,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -9202,7 +9799,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -9213,7 +9810,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -9224,7 +9821,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -9235,7 +9832,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -9246,7 +9843,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -9257,7 +9854,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -9268,7 +9865,7 @@
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -9279,7 +9876,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -9290,7 +9887,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -9301,7 +9898,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -9312,7 +9909,7 @@
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -9323,7 +9920,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -9334,7 +9931,7 @@
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -9345,7 +9942,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -9356,7 +9953,7 @@
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -9367,7 +9964,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -9378,7 +9975,7 @@
       <c r="F31" s="12"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -9389,7 +9986,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -9400,7 +9997,7 @@
       <c r="F33" s="12"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -9411,7 +10008,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -9422,7 +10019,7 @@
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -9433,7 +10030,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -9444,7 +10041,7 @@
       <c r="F37" s="12"/>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -9455,7 +10052,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -9466,7 +10063,7 @@
       <c r="F39" s="12"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -9477,7 +10074,7 @@
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -9488,7 +10085,7 @@
       <c r="F41" s="28"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -9499,7 +10096,7 @@
       <c r="F42" s="24"/>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -9510,7 +10107,7 @@
       <c r="F43" s="28"/>
       <c r="G43" s="29"/>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -9521,7 +10118,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -9532,7 +10129,7 @@
       <c r="F45" s="12"/>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -9543,7 +10140,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -9554,7 +10151,7 @@
       <c r="F47" s="12"/>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -9565,7 +10162,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -9576,7 +10173,7 @@
       <c r="F49" s="12"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -9587,7 +10184,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -9598,7 +10195,7 @@
       <c r="F51" s="12"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -9609,7 +10206,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -9620,7 +10217,7 @@
       <c r="F53" s="12"/>
       <c r="G53" s="13"/>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -9676,16 +10273,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9708,7 +10305,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -9719,7 +10316,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -9730,7 +10327,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -9741,7 +10338,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -9752,7 +10349,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -9763,7 +10360,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -9774,7 +10371,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -9785,7 +10382,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -9796,7 +10393,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -9807,7 +10404,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -9818,7 +10415,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -9829,7 +10426,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -9840,7 +10437,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -9851,7 +10448,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -9862,7 +10459,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -9873,7 +10470,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -9884,7 +10481,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -9895,7 +10492,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -9906,7 +10503,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -9917,7 +10514,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -9928,7 +10525,7 @@
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -9939,7 +10536,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -9950,7 +10547,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -9961,7 +10558,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -9972,7 +10569,7 @@
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -9983,7 +10580,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -9994,7 +10591,7 @@
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -10005,7 +10602,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -10016,7 +10613,7 @@
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -10027,7 +10624,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -10038,7 +10635,7 @@
       <c r="F31" s="12"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -10049,7 +10646,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -10060,7 +10657,7 @@
       <c r="F33" s="12"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -10071,7 +10668,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -10082,7 +10679,7 @@
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -10093,7 +10690,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -10104,7 +10701,7 @@
       <c r="F37" s="12"/>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -10115,7 +10712,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -10126,7 +10723,7 @@
       <c r="F39" s="12"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -10137,7 +10734,7 @@
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -10148,7 +10745,7 @@
       <c r="F41" s="28"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -10159,7 +10756,7 @@
       <c r="F42" s="24"/>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -10170,7 +10767,7 @@
       <c r="F43" s="28"/>
       <c r="G43" s="29"/>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -10181,7 +10778,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -10192,7 +10789,7 @@
       <c r="F45" s="12"/>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -10203,7 +10800,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -10214,7 +10811,7 @@
       <c r="F47" s="12"/>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -10225,7 +10822,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -10236,7 +10833,7 @@
       <c r="F49" s="12"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -10247,7 +10844,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -10258,7 +10855,7 @@
       <c r="F51" s="12"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -10269,7 +10866,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -10280,7 +10877,7 @@
       <c r="F53" s="12"/>
       <c r="G53" s="13"/>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -10336,16 +10933,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10368,7 +10965,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -10379,7 +10976,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -10390,7 +10987,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -10401,7 +10998,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -10412,7 +11009,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -10423,7 +11020,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -10434,7 +11031,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -10445,7 +11042,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -10456,7 +11053,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -10467,7 +11064,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -10478,7 +11075,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -10489,7 +11086,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -10500,7 +11097,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -10511,7 +11108,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -10522,7 +11119,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -10533,7 +11130,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -10544,7 +11141,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -10555,7 +11152,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -10566,7 +11163,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -10577,7 +11174,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -10588,7 +11185,7 @@
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -10599,7 +11196,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -10610,7 +11207,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -10621,7 +11218,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -10632,7 +11229,7 @@
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -10643,7 +11240,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -10654,7 +11251,7 @@
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -10665,7 +11262,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -10676,7 +11273,7 @@
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -10687,7 +11284,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -10698,7 +11295,7 @@
       <c r="F31" s="12"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -10709,7 +11306,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -10720,7 +11317,7 @@
       <c r="F33" s="12"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -10731,7 +11328,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -10742,7 +11339,7 @@
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -10753,7 +11350,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -10764,7 +11361,7 @@
       <c r="F37" s="12"/>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -10775,7 +11372,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -10786,7 +11383,7 @@
       <c r="F39" s="12"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -10797,7 +11394,7 @@
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -10808,7 +11405,7 @@
       <c r="F41" s="28"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -10819,7 +11416,7 @@
       <c r="F42" s="24"/>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -10830,7 +11427,7 @@
       <c r="F43" s="28"/>
       <c r="G43" s="29"/>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -10841,7 +11438,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -10852,7 +11449,7 @@
       <c r="F45" s="12"/>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -10863,7 +11460,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -10874,7 +11471,7 @@
       <c r="F47" s="12"/>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -10885,7 +11482,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -10896,7 +11493,7 @@
       <c r="F49" s="12"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -10907,7 +11504,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -10918,7 +11515,7 @@
       <c r="F51" s="12"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -10929,7 +11526,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -10940,7 +11537,7 @@
       <c r="F53" s="12"/>
       <c r="G53" s="13"/>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -10996,16 +11593,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11028,7 +11625,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -11039,7 +11636,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -11050,7 +11647,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -11061,7 +11658,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -11072,7 +11669,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -11083,7 +11680,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -11094,7 +11691,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -11105,7 +11702,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -11116,7 +11713,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -11127,7 +11724,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -11138,7 +11735,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -11149,7 +11746,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -11160,7 +11757,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -11171,7 +11768,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -11182,7 +11779,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -11193,7 +11790,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -11204,7 +11801,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -11215,7 +11812,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -11226,7 +11823,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -11237,7 +11834,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -11248,7 +11845,7 @@
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -11259,7 +11856,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -11270,7 +11867,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -11281,7 +11878,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -11292,7 +11889,7 @@
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -11303,7 +11900,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -11314,7 +11911,7 @@
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -11325,7 +11922,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -11336,7 +11933,7 @@
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -11347,7 +11944,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -11358,7 +11955,7 @@
       <c r="F31" s="12"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -11369,7 +11966,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -11380,7 +11977,7 @@
       <c r="F33" s="12"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -11391,7 +11988,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -11402,7 +11999,7 @@
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -11413,7 +12010,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -11424,7 +12021,7 @@
       <c r="F37" s="12"/>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -11435,7 +12032,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -11446,7 +12043,7 @@
       <c r="F39" s="12"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -11457,7 +12054,7 @@
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -11468,7 +12065,7 @@
       <c r="F41" s="28"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -11479,7 +12076,7 @@
       <c r="F42" s="24"/>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -11490,7 +12087,7 @@
       <c r="F43" s="28"/>
       <c r="G43" s="29"/>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -11501,7 +12098,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -11512,7 +12109,7 @@
       <c r="F45" s="12"/>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -11523,7 +12120,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -11534,7 +12131,7 @@
       <c r="F47" s="12"/>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -11545,7 +12142,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -11556,7 +12153,7 @@
       <c r="F49" s="12"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -11567,7 +12164,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -11578,7 +12175,7 @@
       <c r="F51" s="12"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -11589,7 +12186,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -11600,7 +12197,7 @@
       <c r="F53" s="12"/>
       <c r="G53" s="13"/>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -11656,16 +12253,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11688,7 +12285,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -11699,7 +12296,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -11710,7 +12307,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -11721,7 +12318,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -11732,7 +12329,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -11743,7 +12340,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -11754,7 +12351,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -11765,7 +12362,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -11776,7 +12373,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -11787,7 +12384,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -11798,7 +12395,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -11809,7 +12406,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -11820,7 +12417,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -11831,7 +12428,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -11842,7 +12439,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -11853,7 +12450,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -11864,7 +12461,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -11875,7 +12472,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -11886,7 +12483,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -11897,7 +12494,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -11908,7 +12505,7 @@
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -11919,7 +12516,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -11930,7 +12527,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -11941,7 +12538,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -11952,7 +12549,7 @@
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -11963,7 +12560,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -11974,7 +12571,7 @@
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -11985,7 +12582,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -11996,7 +12593,7 @@
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -12007,7 +12604,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -12018,7 +12615,7 @@
       <c r="F31" s="12"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -12029,7 +12626,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -12040,7 +12637,7 @@
       <c r="F33" s="12"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -12051,7 +12648,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -12062,7 +12659,7 @@
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -12073,7 +12670,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -12084,7 +12681,7 @@
       <c r="F37" s="12"/>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -12095,7 +12692,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -12106,7 +12703,7 @@
       <c r="F39" s="12"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -12117,7 +12714,7 @@
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -12128,7 +12725,7 @@
       <c r="F41" s="28"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -12139,7 +12736,7 @@
       <c r="F42" s="24"/>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -12150,7 +12747,7 @@
       <c r="F43" s="28"/>
       <c r="G43" s="29"/>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -12161,7 +12758,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -12172,7 +12769,7 @@
       <c r="F45" s="12"/>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -12183,7 +12780,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -12194,7 +12791,7 @@
       <c r="F47" s="12"/>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -12205,7 +12802,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -12216,7 +12813,7 @@
       <c r="F49" s="12"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -12227,7 +12824,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -12238,7 +12835,7 @@
       <c r="F51" s="12"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -12249,7 +12846,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -12260,7 +12857,7 @@
       <c r="F53" s="12"/>
       <c r="G53" s="13"/>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -12316,16 +12913,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12348,7 +12945,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -12359,7 +12956,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -12370,7 +12967,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -12381,7 +12978,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -12392,7 +12989,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -12403,7 +13000,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -12414,7 +13011,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -12425,7 +13022,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -12436,7 +13033,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -12447,7 +13044,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -12458,7 +13055,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -12469,7 +13066,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -12480,7 +13077,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -12491,7 +13088,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -12502,7 +13099,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -12513,7 +13110,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -12524,7 +13121,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -12535,7 +13132,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -12546,7 +13143,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -12557,7 +13154,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -12568,7 +13165,7 @@
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -12579,7 +13176,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -12590,7 +13187,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -12601,7 +13198,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -12612,7 +13209,7 @@
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -12623,7 +13220,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -12634,7 +13231,7 @@
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -12645,7 +13242,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -12656,7 +13253,7 @@
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -12667,7 +13264,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -12678,7 +13275,7 @@
       <c r="F31" s="12"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -12689,7 +13286,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -12700,7 +13297,7 @@
       <c r="F33" s="12"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -12711,7 +13308,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -12722,7 +13319,7 @@
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -12733,7 +13330,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -12744,7 +13341,7 @@
       <c r="F37" s="12"/>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -12755,7 +13352,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -12766,7 +13363,7 @@
       <c r="F39" s="12"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -12777,7 +13374,7 @@
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -12788,7 +13385,7 @@
       <c r="F41" s="28"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -12799,7 +13396,7 @@
       <c r="F42" s="24"/>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -12810,7 +13407,7 @@
       <c r="F43" s="28"/>
       <c r="G43" s="29"/>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -12821,7 +13418,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -12832,7 +13429,7 @@
       <c r="F45" s="12"/>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -12843,7 +13440,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -12854,7 +13451,7 @@
       <c r="F47" s="12"/>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -12865,7 +13462,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -12876,7 +13473,7 @@
       <c r="F49" s="12"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -12887,7 +13484,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -12898,7 +13495,7 @@
       <c r="F51" s="12"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -12909,7 +13506,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -12920,7 +13517,7 @@
       <c r="F53" s="12"/>
       <c r="G53" s="13"/>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>

--- a/statistics_files/2026/2026_99_ga_net_borrower_lender.xlsx
+++ b/statistics_files/2026/2026_99_ga_net_borrower_lender.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Staff\Documents\GitHub\next_statistics\statistics_files\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89664C4-59B5-4680-B517-D9E641DA1B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8F3741-B17E-4A00-AB99-C6B409AD2B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="868" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="868" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="193">
   <si>
     <t>Library</t>
   </si>
@@ -571,6 +571,75 @@
   </si>
   <si>
     <t>2.16 : 1</t>
+  </si>
+  <si>
+    <t>1.18 : 1</t>
+  </si>
+  <si>
+    <t>0.19 : 1</t>
+  </si>
+  <si>
+    <t>0.86 : 1</t>
+  </si>
+  <si>
+    <t>1.40 : 1</t>
+  </si>
+  <si>
+    <t>1.23 : 1</t>
+  </si>
+  <si>
+    <t>1.46 : 1</t>
+  </si>
+  <si>
+    <t>0.06 : 1</t>
+  </si>
+  <si>
+    <t>0.44 : 1</t>
+  </si>
+  <si>
+    <t>0.98 : 1</t>
+  </si>
+  <si>
+    <t>1.36 : 1</t>
+  </si>
+  <si>
+    <t>1.78 : 1</t>
+  </si>
+  <si>
+    <t>3.89 : 1</t>
+  </si>
+  <si>
+    <t>0.80 : 1</t>
+  </si>
+  <si>
+    <t>1.12 : 1</t>
+  </si>
+  <si>
+    <t>1.57 : 1</t>
+  </si>
+  <si>
+    <t>0.37 : 1</t>
+  </si>
+  <si>
+    <t>2.03 : 1</t>
+  </si>
+  <si>
+    <t>0.25 : 1</t>
+  </si>
+  <si>
+    <t>0.77 : 1</t>
+  </si>
+  <si>
+    <t>1.09 : 1</t>
+  </si>
+  <si>
+    <t>1.68 : 1</t>
+  </si>
+  <si>
+    <t>0.85 : 1</t>
+  </si>
+  <si>
+    <t>2.65 : 1</t>
   </si>
 </sst>
 </file>
@@ -2483,16 +2552,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2515,7 +2584,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -2536,7 +2605,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -2557,7 +2626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -2578,7 +2647,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -2599,7 +2668,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -2620,7 +2689,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -2641,7 +2710,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -2662,7 +2731,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -2683,7 +2752,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -2704,7 +2773,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -2721,7 +2790,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -2742,7 +2811,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -2763,7 +2832,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -2784,7 +2853,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -2805,7 +2874,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -2826,7 +2895,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -2847,7 +2916,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -2868,7 +2937,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -2889,7 +2958,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -2910,7 +2979,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -2931,7 +3000,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -2952,7 +3021,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -2973,7 +3042,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -2994,7 +3063,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -3015,7 +3084,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -3032,7 +3101,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -3053,7 +3122,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -3074,7 +3143,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -3095,7 +3164,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -3116,7 +3185,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -3137,7 +3206,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -3158,7 +3227,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -3179,7 +3248,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -3200,7 +3269,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -3221,7 +3290,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -3242,7 +3311,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -3263,7 +3332,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -3284,7 +3353,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -3305,7 +3374,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -3326,7 +3395,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -3347,7 +3416,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -3368,7 +3437,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -3389,7 +3458,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -3410,7 +3479,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -3431,7 +3500,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -3452,7 +3521,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -3473,7 +3542,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -3494,7 +3563,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -3515,7 +3584,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -3536,7 +3605,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -3557,7 +3626,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -3578,7 +3647,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -3599,7 +3668,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -3665,16 +3734,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3697,7 +3766,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -3708,7 +3777,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -3719,7 +3788,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -3730,7 +3799,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -3741,7 +3810,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -3752,7 +3821,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -3763,7 +3832,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -3774,7 +3843,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -3785,7 +3854,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -3796,7 +3865,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -3807,7 +3876,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -3818,7 +3887,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -3829,7 +3898,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -3840,7 +3909,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -3851,7 +3920,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -3862,7 +3931,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -3873,7 +3942,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -3884,7 +3953,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -3895,7 +3964,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -3906,7 +3975,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -3917,7 +3986,7 @@
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -3928,7 +3997,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -3939,7 +4008,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -3950,7 +4019,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -3961,7 +4030,7 @@
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -3972,7 +4041,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -3983,7 +4052,7 @@
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -3994,7 +4063,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -4005,7 +4074,7 @@
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -4016,7 +4085,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -4027,7 +4096,7 @@
       <c r="F31" s="12"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -4038,7 +4107,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -4049,7 +4118,7 @@
       <c r="F33" s="12"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -4060,7 +4129,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -4071,7 +4140,7 @@
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -4082,7 +4151,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -4093,7 +4162,7 @@
       <c r="F37" s="12"/>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -4104,7 +4173,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -4115,7 +4184,7 @@
       <c r="F39" s="12"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -4126,7 +4195,7 @@
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -4137,7 +4206,7 @@
       <c r="F41" s="28"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -4148,7 +4217,7 @@
       <c r="F42" s="24"/>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -4159,7 +4228,7 @@
       <c r="F43" s="28"/>
       <c r="G43" s="29"/>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -4170,7 +4239,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -4181,7 +4250,7 @@
       <c r="F45" s="12"/>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -4192,7 +4261,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -4203,7 +4272,7 @@
       <c r="F47" s="12"/>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -4214,7 +4283,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -4225,7 +4294,7 @@
       <c r="F49" s="12"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -4236,7 +4305,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -4247,7 +4316,7 @@
       <c r="F51" s="12"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -4258,7 +4327,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -4269,7 +4338,7 @@
       <c r="F53" s="12"/>
       <c r="G53" s="13"/>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -4325,16 +4394,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4357,7 +4426,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -4368,7 +4437,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -4379,7 +4448,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -4390,7 +4459,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -4401,7 +4470,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -4412,7 +4481,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -4423,7 +4492,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -4434,7 +4503,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -4445,7 +4514,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -4456,7 +4525,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -4467,7 +4536,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -4478,7 +4547,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -4489,7 +4558,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -4500,7 +4569,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -4511,7 +4580,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -4522,7 +4591,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -4533,7 +4602,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -4544,7 +4613,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -4555,7 +4624,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -4566,7 +4635,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -4577,7 +4646,7 @@
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -4588,7 +4657,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -4599,7 +4668,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -4610,7 +4679,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -4621,7 +4690,7 @@
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -4632,7 +4701,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -4643,7 +4712,7 @@
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -4654,7 +4723,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -4665,7 +4734,7 @@
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -4676,7 +4745,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -4687,7 +4756,7 @@
       <c r="F31" s="12"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -4698,7 +4767,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -4709,7 +4778,7 @@
       <c r="F33" s="12"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -4720,7 +4789,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -4731,7 +4800,7 @@
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -4742,7 +4811,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -4753,7 +4822,7 @@
       <c r="F37" s="12"/>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -4764,7 +4833,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -4775,7 +4844,7 @@
       <c r="F39" s="12"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -4786,7 +4855,7 @@
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -4797,7 +4866,7 @@
       <c r="F41" s="28"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -4808,7 +4877,7 @@
       <c r="F42" s="24"/>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -4819,7 +4888,7 @@
       <c r="F43" s="28"/>
       <c r="G43" s="29"/>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -4830,7 +4899,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -4841,7 +4910,7 @@
       <c r="F45" s="12"/>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -4852,7 +4921,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -4863,7 +4932,7 @@
       <c r="F47" s="12"/>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -4874,7 +4943,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -4885,7 +4954,7 @@
       <c r="F49" s="12"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -4896,7 +4965,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -4907,7 +4976,7 @@
       <c r="F51" s="12"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -4918,7 +4987,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -4929,7 +4998,7 @@
       <c r="F53" s="12"/>
       <c r="G53" s="13"/>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -4985,16 +5054,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5017,7 +5086,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -5028,7 +5097,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -5039,7 +5108,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -5050,7 +5119,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -5061,7 +5130,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -5072,7 +5141,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -5083,7 +5152,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -5094,7 +5163,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -5105,7 +5174,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -5116,7 +5185,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -5127,7 +5196,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -5138,7 +5207,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -5149,7 +5218,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -5160,7 +5229,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -5171,7 +5240,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -5182,7 +5251,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -5193,7 +5262,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -5204,7 +5273,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -5215,7 +5284,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -5226,7 +5295,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -5237,7 +5306,7 @@
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -5248,7 +5317,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -5259,7 +5328,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -5270,7 +5339,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -5281,7 +5350,7 @@
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -5292,7 +5361,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -5303,7 +5372,7 @@
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -5314,7 +5383,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -5325,7 +5394,7 @@
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -5336,7 +5405,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -5347,7 +5416,7 @@
       <c r="F31" s="12"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -5358,7 +5427,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -5369,7 +5438,7 @@
       <c r="F33" s="12"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -5380,7 +5449,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -5391,7 +5460,7 @@
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -5402,7 +5471,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -5413,7 +5482,7 @@
       <c r="F37" s="12"/>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -5424,7 +5493,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -5435,7 +5504,7 @@
       <c r="F39" s="12"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -5446,7 +5515,7 @@
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -5457,7 +5526,7 @@
       <c r="F41" s="28"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -5468,7 +5537,7 @@
       <c r="F42" s="24"/>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -5479,7 +5548,7 @@
       <c r="F43" s="28"/>
       <c r="G43" s="29"/>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -5490,7 +5559,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -5501,7 +5570,7 @@
       <c r="F45" s="12"/>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -5512,7 +5581,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -5523,7 +5592,7 @@
       <c r="F47" s="12"/>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -5534,7 +5603,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -5545,7 +5614,7 @@
       <c r="F49" s="12"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -5556,7 +5625,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -5567,7 +5636,7 @@
       <c r="F51" s="12"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -5578,7 +5647,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -5589,7 +5658,7 @@
       <c r="F53" s="12"/>
       <c r="G53" s="13"/>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -5645,16 +5714,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5677,21 +5746,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="7">
         <f>January!B2+February!B2+March!B2+April!B2+May!B2+June!B2+July!B2+August!B2+September!B2+October!B2+November!B2+December!B2</f>
-        <v>4403</v>
+        <v>5856</v>
       </c>
       <c r="C2" s="7">
         <f>January!C2+February!C2+March!C2+April!C2+May!C2+June!C2+July!C2+August!C2+September!C2+October!C2+November!C2+December!C2</f>
-        <v>3703</v>
+        <v>4936</v>
       </c>
       <c r="D2" s="7">
         <f>January!D2+February!D2+March!D2+April!D2+May!D2+June!D2+July!D2+August!D2+September!D2+October!D2+November!D2+December!D2</f>
-        <v>700</v>
+        <v>920</v>
       </c>
       <c r="E2" s="8" t="str">
         <f>IF(D2 &gt; 0, "We borrowed more than we lent this year", "")</f>
@@ -5706,21 +5775,21 @@
         <v>1.19 : 1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="11">
         <f>January!B3+February!B3+March!B3+April!B3+May!B3+June!B3+July!B3+August!B3+September!B3+October!B3+November!B3+December!B3</f>
-        <v>1993</v>
+        <v>2499</v>
       </c>
       <c r="C3" s="11">
         <f>January!C3+February!C3+March!C3+April!C3+May!C3+June!C3+July!C3+August!C3+September!C3+October!C3+November!C3+December!C3</f>
-        <v>1228</v>
+        <v>1685</v>
       </c>
       <c r="D3" s="11">
         <f>January!D3+February!D3+March!D3+April!D3+May!D3+June!D3+July!D3+August!D3+September!D3+October!D3+November!D3+December!D3</f>
-        <v>765</v>
+        <v>814</v>
       </c>
       <c r="E3" s="12" t="str">
         <f t="shared" ref="E3:E54" si="0">IF(D3 &gt; 0, "We borrowed more than we lent this year", "")</f>
@@ -5732,24 +5801,24 @@
       </c>
       <c r="G3" s="13" t="str">
         <f t="shared" ref="G3:G54" si="2">IF(ISERROR(ROUND(B3/C3,2)&amp;" : 1"), "", ROUND(B3/C3,2)&amp;" : 1")</f>
-        <v>1.62 : 1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.48 : 1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="7">
         <f>January!B4+February!B4+March!B4+April!B4+May!B4+June!B4+July!B4+August!B4+September!B4+October!B4+November!B4+December!B4</f>
-        <v>3822</v>
+        <v>4858</v>
       </c>
       <c r="C4" s="7">
         <f>January!C4+February!C4+March!C4+April!C4+May!C4+June!C4+July!C4+August!C4+September!C4+October!C4+November!C4+December!C4</f>
-        <v>3480</v>
+        <v>4598</v>
       </c>
       <c r="D4" s="7">
         <f>January!D4+February!D4+March!D4+April!D4+May!D4+June!D4+July!D4+August!D4+September!D4+October!D4+November!D4+December!D4</f>
-        <v>342</v>
+        <v>260</v>
       </c>
       <c r="E4" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5761,24 +5830,24 @@
       </c>
       <c r="G4" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.1 : 1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.06 : 1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="11">
         <f>January!B5+February!B5+March!B5+April!B5+May!B5+June!B5+July!B5+August!B5+September!B5+October!B5+November!B5+December!B5</f>
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="C5" s="11">
         <f>January!C5+February!C5+March!C5+April!C5+May!C5+June!C5+July!C5+August!C5+September!C5+October!C5+November!C5+December!C5</f>
-        <v>367</v>
+        <v>472</v>
       </c>
       <c r="D5" s="11">
         <f>January!D5+February!D5+March!D5+April!D5+May!D5+June!D5+July!D5+August!D5+September!D5+October!D5+November!D5+December!D5</f>
-        <v>-309</v>
+        <v>-394</v>
       </c>
       <c r="E5" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5790,24 +5859,24 @@
       </c>
       <c r="G5" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.16 : 1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.17 : 1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="7">
         <f>January!B6+February!B6+March!B6+April!B6+May!B6+June!B6+July!B6+August!B6+September!B6+October!B6+November!B6+December!B6</f>
-        <v>3189</v>
+        <v>4094</v>
       </c>
       <c r="C6" s="7">
         <f>January!C6+February!C6+March!C6+April!C6+May!C6+June!C6+July!C6+August!C6+September!C6+October!C6+November!C6+December!C6</f>
-        <v>3454</v>
+        <v>4504</v>
       </c>
       <c r="D6" s="7">
         <f>January!D6+February!D6+March!D6+April!D6+May!D6+June!D6+July!D6+August!D6+September!D6+October!D6+November!D6+December!D6</f>
-        <v>-265</v>
+        <v>-410</v>
       </c>
       <c r="E6" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5819,24 +5888,24 @@
       </c>
       <c r="G6" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.92 : 1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.91 : 1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="11">
         <f>January!B7+February!B7+March!B7+April!B7+May!B7+June!B7+July!B7+August!B7+September!B7+October!B7+November!B7+December!B7</f>
-        <v>614</v>
+        <v>850</v>
       </c>
       <c r="C7" s="11">
         <f>January!C7+February!C7+March!C7+April!C7+May!C7+June!C7+July!C7+August!C7+September!C7+October!C7+November!C7+December!C7</f>
-        <v>515</v>
+        <v>683</v>
       </c>
       <c r="D7" s="11">
         <f>January!D7+February!D7+March!D7+April!D7+May!D7+June!D7+July!D7+August!D7+September!D7+October!D7+November!D7+December!D7</f>
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="E7" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5848,24 +5917,24 @@
       </c>
       <c r="G7" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.19 : 1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.24 : 1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="7">
         <f>January!B8+February!B8+March!B8+April!B8+May!B8+June!B8+July!B8+August!B8+September!B8+October!B8+November!B8+December!B8</f>
-        <v>362</v>
+        <v>446</v>
       </c>
       <c r="C8" s="7">
         <f>January!C8+February!C8+March!C8+April!C8+May!C8+June!C8+July!C8+August!C8+September!C8+October!C8+November!C8+December!C8</f>
-        <v>516</v>
+        <v>678</v>
       </c>
       <c r="D8" s="7">
         <f>January!D8+February!D8+March!D8+April!D8+May!D8+June!D8+July!D8+August!D8+September!D8+October!D8+November!D8+December!D8</f>
-        <v>-154</v>
+        <v>-232</v>
       </c>
       <c r="E8" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5877,24 +5946,24 @@
       </c>
       <c r="G8" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.7 : 1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.66 : 1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B9" s="11">
         <f>January!B9+February!B9+March!B9+April!B9+May!B9+June!B9+July!B9+August!B9+September!B9+October!B9+November!B9+December!B9</f>
-        <v>185</v>
+        <v>229</v>
       </c>
       <c r="C9" s="11">
         <f>January!C9+February!C9+March!C9+April!C9+May!C9+June!C9+July!C9+August!C9+September!C9+October!C9+November!C9+December!C9</f>
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="D9" s="11">
         <f>January!D9+February!D9+March!D9+April!D9+May!D9+June!D9+July!D9+August!D9+September!D9+October!D9+November!D9+December!D9</f>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E9" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5906,10 +5975,10 @@
       </c>
       <c r="G9" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.14 : 1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.1 : 1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -5919,11 +5988,11 @@
       </c>
       <c r="C10" s="7">
         <f>January!C10+February!C10+March!C10+April!C10+May!C10+June!C10+July!C10+August!C10+September!C10+October!C10+November!C10+December!C10</f>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="D10" s="7">
         <f>January!D10+February!D10+March!D10+April!D10+May!D10+June!D10+July!D10+August!D10+September!D10+October!D10+November!D10+December!D10</f>
-        <v>-73</v>
+        <v>-94</v>
       </c>
       <c r="E10" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5935,10 +6004,10 @@
       </c>
       <c r="G10" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.04 : 1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.03 : 1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -5967,21 +6036,21 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="15">
         <f>January!B12+February!B12+March!B12+April!B12+May!B12+June!B12+July!B12+August!B12+September!B12+October!B12+November!B12+December!B12</f>
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C12" s="15">
         <f>January!C12+February!C12+March!C12+April!C12+May!C12+June!C12+July!C12+August!C12+September!C12+October!C12+November!C12+December!C12</f>
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D12" s="15">
         <f>January!D12+February!D12+March!D12+April!D12+May!D12+June!D12+July!D12+August!D12+September!D12+October!D12+November!D12+December!D12</f>
-        <v>-53</v>
+        <v>-60</v>
       </c>
       <c r="E12" s="16" t="str">
         <f t="shared" si="0"/>
@@ -5993,24 +6062,24 @@
       </c>
       <c r="G12" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>0.18 : 1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.28 : 1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
       <c r="B13" s="19">
         <f>January!B13+February!B13+March!B13+April!B13+May!B13+June!B13+July!B13+August!B13+September!B13+October!B13+November!B13+December!B13</f>
-        <v>163</v>
+        <v>218</v>
       </c>
       <c r="C13" s="19">
         <f>January!C13+February!C13+March!C13+April!C13+May!C13+June!C13+July!C13+August!C13+September!C13+October!C13+November!C13+December!C13</f>
-        <v>192</v>
+        <v>240</v>
       </c>
       <c r="D13" s="19">
         <f>January!D13+February!D13+March!D13+April!D13+May!D13+June!D13+July!D13+August!D13+September!D13+October!D13+November!D13+December!D13</f>
-        <v>-29</v>
+        <v>-22</v>
       </c>
       <c r="E13" s="20" t="str">
         <f t="shared" si="0"/>
@@ -6022,24 +6091,24 @@
       </c>
       <c r="G13" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>0.85 : 1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.91 : 1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
       <c r="B14" s="15">
         <f>January!B14+February!B14+March!B14+April!B14+May!B14+June!B14+July!B14+August!B14+September!B14+October!B14+November!B14+December!B14</f>
-        <v>431</v>
+        <v>547</v>
       </c>
       <c r="C14" s="15">
         <f>January!C14+February!C14+March!C14+April!C14+May!C14+June!C14+July!C14+August!C14+September!C14+October!C14+November!C14+December!C14</f>
-        <v>884</v>
+        <v>1177</v>
       </c>
       <c r="D14" s="15">
         <f>January!D14+February!D14+March!D14+April!D14+May!D14+June!D14+July!D14+August!D14+September!D14+October!D14+November!D14+December!D14</f>
-        <v>-453</v>
+        <v>-630</v>
       </c>
       <c r="E14" s="16" t="str">
         <f t="shared" si="0"/>
@@ -6051,24 +6120,24 @@
       </c>
       <c r="G14" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>0.49 : 1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.46 : 1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
       <c r="B15" s="19">
         <f>January!B15+February!B15+March!B15+April!B15+May!B15+June!B15+July!B15+August!B15+September!B15+October!B15+November!B15+December!B15</f>
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="C15" s="19">
         <f>January!C15+February!C15+March!C15+April!C15+May!C15+June!C15+July!C15+August!C15+September!C15+October!C15+November!C15+December!C15</f>
-        <v>460</v>
+        <v>585</v>
       </c>
       <c r="D15" s="19">
         <f>January!D15+February!D15+March!D15+April!D15+May!D15+June!D15+July!D15+August!D15+September!D15+October!D15+November!D15+December!D15</f>
-        <v>-308</v>
+        <v>-396</v>
       </c>
       <c r="E15" s="20" t="str">
         <f t="shared" si="0"/>
@@ -6080,24 +6149,24 @@
       </c>
       <c r="G15" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>0.33 : 1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.32 : 1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B16" s="7">
         <f>January!B16+February!B16+March!B16+April!B16+May!B16+June!B16+July!B16+August!B16+September!B16+October!B16+November!B16+December!B16</f>
-        <v>187</v>
+        <v>259</v>
       </c>
       <c r="C16" s="7">
         <f>January!C16+February!C16+March!C16+April!C16+May!C16+June!C16+July!C16+August!C16+September!C16+October!C16+November!C16+December!C16</f>
-        <v>652</v>
+        <v>789</v>
       </c>
       <c r="D16" s="7">
         <f>January!D16+February!D16+March!D16+April!D16+May!D16+June!D16+July!D16+August!D16+September!D16+October!D16+November!D16+December!D16</f>
-        <v>-465</v>
+        <v>-530</v>
       </c>
       <c r="E16" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6109,24 +6178,24 @@
       </c>
       <c r="G16" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.29 : 1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.33 : 1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
       <c r="B17" s="11">
         <f>January!B17+February!B17+March!B17+April!B17+May!B17+June!B17+July!B17+August!B17+September!B17+October!B17+November!B17+December!B17</f>
-        <v>2118</v>
+        <v>2686</v>
       </c>
       <c r="C17" s="11">
         <f>January!C17+February!C17+March!C17+April!C17+May!C17+June!C17+July!C17+August!C17+September!C17+October!C17+November!C17+December!C17</f>
-        <v>1286</v>
+        <v>1746</v>
       </c>
       <c r="D17" s="11">
         <f>January!D17+February!D17+March!D17+April!D17+May!D17+June!D17+July!D17+August!D17+September!D17+October!D17+November!D17+December!D17</f>
-        <v>832</v>
+        <v>940</v>
       </c>
       <c r="E17" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6138,24 +6207,24 @@
       </c>
       <c r="G17" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.65 : 1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.54 : 1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="7">
         <f>January!B18+February!B18+March!B18+April!B18+May!B18+June!B18+July!B18+August!B18+September!B18+October!B18+November!B18+December!B18</f>
-        <v>276</v>
+        <v>399</v>
       </c>
       <c r="C18" s="7">
         <f>January!C18+February!C18+March!C18+April!C18+May!C18+June!C18+July!C18+August!C18+September!C18+October!C18+November!C18+December!C18</f>
-        <v>246</v>
+        <v>330</v>
       </c>
       <c r="D18" s="7">
         <f>January!D18+February!D18+March!D18+April!D18+May!D18+June!D18+July!D18+August!D18+September!D18+October!D18+November!D18+December!D18</f>
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="E18" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6167,24 +6236,24 @@
       </c>
       <c r="G18" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.12 : 1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.21 : 1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
       <c r="B19" s="11">
         <f>January!B19+February!B19+March!B19+April!B19+May!B19+June!B19+July!B19+August!B19+September!B19+October!B19+November!B19+December!B19</f>
-        <v>1789</v>
+        <v>2207</v>
       </c>
       <c r="C19" s="11">
         <f>January!C19+February!C19+March!C19+April!C19+May!C19+June!C19+July!C19+August!C19+September!C19+October!C19+November!C19+December!C19</f>
-        <v>990</v>
+        <v>1293</v>
       </c>
       <c r="D19" s="11">
         <f>January!D19+February!D19+March!D19+April!D19+May!D19+June!D19+July!D19+August!D19+September!D19+October!D19+November!D19+December!D19</f>
-        <v>799</v>
+        <v>914</v>
       </c>
       <c r="E19" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6196,24 +6265,24 @@
       </c>
       <c r="G19" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.81 : 1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.71 : 1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
       <c r="B20" s="7">
         <f>January!B20+February!B20+March!B20+April!B20+May!B20+June!B20+July!B20+August!B20+September!B20+October!B20+November!B20+December!B20</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C20" s="7">
         <f>January!C20+February!C20+March!C20+April!C20+May!C20+June!C20+July!C20+August!C20+September!C20+October!C20+November!C20+December!C20</f>
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="D20" s="7">
         <f>January!D20+February!D20+March!D20+April!D20+May!D20+June!D20+July!D20+August!D20+September!D20+October!D20+November!D20+December!D20</f>
-        <v>-157</v>
+        <v>-188</v>
       </c>
       <c r="E20" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6225,24 +6294,24 @@
       </c>
       <c r="G20" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.04 : 1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.05 : 1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
       <c r="B21" s="11">
         <f>January!B21+February!B21+March!B21+April!B21+May!B21+June!B21+July!B21+August!B21+September!B21+October!B21+November!B21+December!B21</f>
-        <v>1512</v>
+        <v>1958</v>
       </c>
       <c r="C21" s="11">
         <f>January!C21+February!C21+March!C21+April!C21+May!C21+June!C21+July!C21+August!C21+September!C21+October!C21+November!C21+December!C21</f>
-        <v>1285</v>
+        <v>1678</v>
       </c>
       <c r="D21" s="11">
         <f>January!D21+February!D21+March!D21+April!D21+May!D21+June!D21+July!D21+August!D21+September!D21+October!D21+November!D21+December!D21</f>
-        <v>227</v>
+        <v>280</v>
       </c>
       <c r="E21" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6254,24 +6323,24 @@
       </c>
       <c r="G21" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.18 : 1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.17 : 1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B22" s="7">
         <f>January!B22+February!B22+March!B22+April!B22+May!B22+June!B22+July!B22+August!B22+September!B22+October!B22+November!B22+December!B22</f>
-        <v>287</v>
+        <v>377</v>
       </c>
       <c r="C22" s="7">
         <f>January!C22+February!C22+March!C22+April!C22+May!C22+June!C22+July!C22+August!C22+September!C22+October!C22+November!C22+December!C22</f>
-        <v>737</v>
+        <v>942</v>
       </c>
       <c r="D22" s="7">
         <f>January!D22+February!D22+March!D22+April!D22+May!D22+June!D22+July!D22+August!D22+September!D22+October!D22+November!D22+December!D22</f>
-        <v>-450</v>
+        <v>-565</v>
       </c>
       <c r="E22" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6283,24 +6352,24 @@
       </c>
       <c r="G22" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.39 : 1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.4 : 1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
       <c r="B23" s="11">
         <f>January!B23+February!B23+March!B23+April!B23+May!B23+June!B23+July!B23+August!B23+September!B23+October!B23+November!B23+December!B23</f>
-        <v>2054</v>
+        <v>2688</v>
       </c>
       <c r="C23" s="11">
         <f>January!C23+February!C23+March!C23+April!C23+May!C23+June!C23+July!C23+August!C23+September!C23+October!C23+November!C23+December!C23</f>
-        <v>1747</v>
+        <v>2394</v>
       </c>
       <c r="D23" s="11">
         <f>January!D23+February!D23+March!D23+April!D23+May!D23+June!D23+July!D23+August!D23+September!D23+October!D23+November!D23+December!D23</f>
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="E23" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6312,24 +6381,24 @@
       </c>
       <c r="G23" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.18 : 1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.12 : 1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
       <c r="B24" s="7">
         <f>January!B24+February!B24+March!B24+April!B24+May!B24+June!B24+July!B24+August!B24+September!B24+October!B24+November!B24+December!B24</f>
-        <v>5484</v>
+        <v>7303</v>
       </c>
       <c r="C24" s="7">
         <f>January!C24+February!C24+March!C24+April!C24+May!C24+June!C24+July!C24+August!C24+September!C24+October!C24+November!C24+December!C24</f>
-        <v>4324</v>
+        <v>5642</v>
       </c>
       <c r="D24" s="7">
         <f>January!D24+February!D24+March!D24+April!D24+May!D24+June!D24+July!D24+August!D24+September!D24+October!D24+November!D24+December!D24</f>
-        <v>1160</v>
+        <v>1661</v>
       </c>
       <c r="E24" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6341,24 +6410,24 @@
       </c>
       <c r="G24" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.27 : 1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.29 : 1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
       <c r="B25" s="11">
         <f>January!B25+February!B25+March!B25+April!B25+May!B25+June!B25+July!B25+August!B25+September!B25+October!B25+November!B25+December!B25</f>
-        <v>463</v>
+        <v>678</v>
       </c>
       <c r="C25" s="11">
         <f>January!C25+February!C25+March!C25+April!C25+May!C25+June!C25+July!C25+August!C25+September!C25+October!C25+November!C25+December!C25</f>
-        <v>1014</v>
+        <v>1338</v>
       </c>
       <c r="D25" s="11">
         <f>January!D25+February!D25+March!D25+April!D25+May!D25+June!D25+July!D25+August!D25+September!D25+October!D25+November!D25+December!D25</f>
-        <v>-551</v>
+        <v>-660</v>
       </c>
       <c r="E25" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6370,10 +6439,10 @@
       </c>
       <c r="G25" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.46 : 1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.51 : 1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -6402,21 +6471,21 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
       <c r="B27" s="11">
         <f>January!B27+February!B27+March!B27+April!B27+May!B27+June!B27+July!B27+August!B27+September!B27+October!B27+November!B27+December!B27</f>
-        <v>572</v>
+        <v>763</v>
       </c>
       <c r="C27" s="11">
         <f>January!C27+February!C27+March!C27+April!C27+May!C27+June!C27+July!C27+August!C27+September!C27+October!C27+November!C27+December!C27</f>
-        <v>478</v>
+        <v>597</v>
       </c>
       <c r="D27" s="11">
         <f>January!D27+February!D27+March!D27+April!D27+May!D27+June!D27+July!D27+August!D27+September!D27+October!D27+November!D27+December!D27</f>
-        <v>94</v>
+        <v>166</v>
       </c>
       <c r="E27" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6428,24 +6497,24 @@
       </c>
       <c r="G27" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.2 : 1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.28 : 1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B28" s="7">
         <f>January!B28+February!B28+March!B28+April!B28+May!B28+June!B28+July!B28+August!B28+September!B28+October!B28+November!B28+December!B28</f>
-        <v>411</v>
+        <v>539</v>
       </c>
       <c r="C28" s="7">
         <f>January!C28+February!C28+March!C28+April!C28+May!C28+June!C28+July!C28+August!C28+September!C28+October!C28+November!C28+December!C28</f>
-        <v>402</v>
+        <v>496</v>
       </c>
       <c r="D28" s="7">
         <f>January!D28+February!D28+March!D28+April!D28+May!D28+June!D28+July!D28+August!D28+September!D28+October!D28+November!D28+December!D28</f>
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="E28" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6457,24 +6526,24 @@
       </c>
       <c r="G28" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.02 : 1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.09 : 1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B29" s="11">
         <f>January!B29+February!B29+March!B29+April!B29+May!B29+June!B29+July!B29+August!B29+September!B29+October!B29+November!B29+December!B29</f>
-        <v>2561</v>
+        <v>3337</v>
       </c>
       <c r="C29" s="11">
         <f>January!C29+February!C29+March!C29+April!C29+May!C29+June!C29+July!C29+August!C29+September!C29+October!C29+November!C29+December!C29</f>
-        <v>1525</v>
+        <v>1960</v>
       </c>
       <c r="D29" s="11">
         <f>January!D29+February!D29+March!D29+April!D29+May!D29+June!D29+July!D29+August!D29+September!D29+October!D29+November!D29+December!D29</f>
-        <v>1036</v>
+        <v>1377</v>
       </c>
       <c r="E29" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6486,53 +6555,53 @@
       </c>
       <c r="G29" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.68 : 1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.7 : 1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B30" s="7">
         <f>January!B30+February!B30+March!B30+April!B30+May!B30+June!B30+July!B30+August!B30+September!B30+October!B30+November!B30+December!B30</f>
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="C30" s="7">
         <f>January!C30+February!C30+March!C30+April!C30+May!C30+June!C30+July!C30+August!C30+September!C30+October!C30+November!C30+December!C30</f>
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="D30" s="7">
         <f>January!D30+February!D30+March!D30+April!D30+May!D30+June!D30+July!D30+August!D30+September!D30+October!D30+November!D30+December!D30</f>
-        <v>-9</v>
+        <v>43</v>
       </c>
       <c r="E30" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>We borrowed more than we lent this year</v>
       </c>
       <c r="F30" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>We lent more than we borrowed this year</v>
+        <v/>
       </c>
       <c r="G30" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.87 : 1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.49 : 1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
       <c r="B31" s="11">
         <f>January!B31+February!B31+March!B31+April!B31+May!B31+June!B31+July!B31+August!B31+September!B31+October!B31+November!B31+December!B31</f>
-        <v>404</v>
+        <v>505</v>
       </c>
       <c r="C31" s="11">
         <f>January!C31+February!C31+March!C31+April!C31+May!C31+June!C31+July!C31+August!C31+September!C31+October!C31+November!C31+December!C31</f>
-        <v>797</v>
+        <v>1052</v>
       </c>
       <c r="D31" s="11">
         <f>January!D31+February!D31+March!D31+April!D31+May!D31+June!D31+July!D31+August!D31+September!D31+October!D31+November!D31+December!D31</f>
-        <v>-393</v>
+        <v>-547</v>
       </c>
       <c r="E31" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6544,24 +6613,24 @@
       </c>
       <c r="G31" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.51 : 1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.48 : 1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
       <c r="B32" s="7">
         <f>January!B32+February!B32+March!B32+April!B32+May!B32+June!B32+July!B32+August!B32+September!B32+October!B32+November!B32+December!B32</f>
-        <v>1349</v>
+        <v>1730</v>
       </c>
       <c r="C32" s="7">
         <f>January!C32+February!C32+March!C32+April!C32+May!C32+June!C32+July!C32+August!C32+September!C32+October!C32+November!C32+December!C32</f>
-        <v>1602</v>
+        <v>2077</v>
       </c>
       <c r="D32" s="7">
         <f>January!D32+February!D32+March!D32+April!D32+May!D32+June!D32+July!D32+August!D32+September!D32+October!D32+November!D32+December!D32</f>
-        <v>-253</v>
+        <v>-347</v>
       </c>
       <c r="E32" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6573,24 +6642,24 @@
       </c>
       <c r="G32" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.84 : 1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.83 : 1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
       <c r="B33" s="11">
         <f>January!B33+February!B33+March!B33+April!B33+May!B33+June!B33+July!B33+August!B33+September!B33+October!B33+November!B33+December!B33</f>
-        <v>1143</v>
+        <v>1453</v>
       </c>
       <c r="C33" s="11">
         <f>January!C33+February!C33+March!C33+April!C33+May!C33+June!C33+July!C33+August!C33+September!C33+October!C33+November!C33+December!C33</f>
-        <v>1046</v>
+        <v>1323</v>
       </c>
       <c r="D33" s="11">
         <f>January!D33+February!D33+March!D33+April!D33+May!D33+June!D33+July!D33+August!D33+September!D33+October!D33+November!D33+December!D33</f>
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="E33" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6602,24 +6671,24 @@
       </c>
       <c r="G33" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.09 : 1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.1 : 1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
       <c r="B34" s="7">
         <f>January!B34+February!B34+March!B34+April!B34+May!B34+June!B34+July!B34+August!B34+September!B34+October!B34+November!B34+December!B34</f>
-        <v>581</v>
+        <v>724</v>
       </c>
       <c r="C34" s="7">
         <f>January!C34+February!C34+March!C34+April!C34+May!C34+June!C34+July!C34+August!C34+September!C34+October!C34+November!C34+December!C34</f>
-        <v>365</v>
+        <v>456</v>
       </c>
       <c r="D34" s="7">
         <f>January!D34+February!D34+March!D34+April!D34+May!D34+June!D34+July!D34+August!D34+September!D34+October!D34+November!D34+December!D34</f>
-        <v>216</v>
+        <v>268</v>
       </c>
       <c r="E34" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6634,21 +6703,21 @@
         <v>1.59 : 1</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B35" s="11">
         <f>January!B35+February!B35+March!B35+April!B35+May!B35+June!B35+July!B35+August!B35+September!B35+October!B35+November!B35+December!B35</f>
-        <v>2915</v>
+        <v>3958</v>
       </c>
       <c r="C35" s="11">
         <f>January!C35+February!C35+March!C35+April!C35+May!C35+June!C35+July!C35+August!C35+September!C35+October!C35+November!C35+December!C35</f>
-        <v>4702</v>
+        <v>6023</v>
       </c>
       <c r="D35" s="11">
         <f>January!D35+February!D35+March!D35+April!D35+May!D35+June!D35+July!D35+August!D35+September!D35+October!D35+November!D35+December!D35</f>
-        <v>-1787</v>
+        <v>-2065</v>
       </c>
       <c r="E35" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6660,24 +6729,24 @@
       </c>
       <c r="G35" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.62 : 1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.66 : 1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
       <c r="B36" s="7">
         <f>January!B36+February!B36+March!B36+April!B36+May!B36+June!B36+July!B36+August!B36+September!B36+October!B36+November!B36+December!B36</f>
-        <v>515</v>
+        <v>690</v>
       </c>
       <c r="C36" s="7">
         <f>January!C36+February!C36+March!C36+April!C36+May!C36+June!C36+July!C36+August!C36+September!C36+October!C36+November!C36+December!C36</f>
-        <v>1750</v>
+        <v>2224</v>
       </c>
       <c r="D36" s="7">
         <f>January!D36+February!D36+March!D36+April!D36+May!D36+June!D36+July!D36+August!D36+September!D36+October!D36+November!D36+December!D36</f>
-        <v>-1235</v>
+        <v>-1534</v>
       </c>
       <c r="E36" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6689,24 +6758,24 @@
       </c>
       <c r="G36" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.29 : 1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.31 : 1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
       <c r="B37" s="11">
         <f>January!B37+February!B37+March!B37+April!B37+May!B37+June!B37+July!B37+August!B37+September!B37+October!B37+November!B37+December!B37</f>
-        <v>1709</v>
+        <v>2337</v>
       </c>
       <c r="C37" s="11">
         <f>January!C37+February!C37+March!C37+April!C37+May!C37+June!C37+July!C37+August!C37+September!C37+October!C37+November!C37+December!C37</f>
-        <v>1368</v>
+        <v>1678</v>
       </c>
       <c r="D37" s="11">
         <f>January!D37+February!D37+March!D37+April!D37+May!D37+June!D37+July!D37+August!D37+September!D37+October!D37+November!D37+December!D37</f>
-        <v>341</v>
+        <v>659</v>
       </c>
       <c r="E37" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6718,24 +6787,24 @@
       </c>
       <c r="G37" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.25 : 1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.39 : 1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
       <c r="B38" s="7">
         <f>January!B38+February!B38+March!B38+April!B38+May!B38+June!B38+July!B38+August!B38+September!B38+October!B38+November!B38+December!B38</f>
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="C38" s="7">
         <f>January!C38+February!C38+March!C38+April!C38+May!C38+June!C38+July!C38+August!C38+September!C38+October!C38+November!C38+December!C38</f>
-        <v>611</v>
+        <v>803</v>
       </c>
       <c r="D38" s="7">
         <f>January!D38+February!D38+March!D38+April!D38+May!D38+June!D38+July!D38+August!D38+September!D38+October!D38+November!D38+December!D38</f>
-        <v>-525</v>
+        <v>-669</v>
       </c>
       <c r="E38" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6747,24 +6816,24 @@
       </c>
       <c r="G38" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.14 : 1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.17 : 1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
       <c r="B39" s="11">
         <f>January!B39+February!B39+March!B39+April!B39+May!B39+June!B39+July!B39+August!B39+September!B39+October!B39+November!B39+December!B39</f>
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C39" s="11">
         <f>January!C39+February!C39+March!C39+April!C39+May!C39+June!C39+July!C39+August!C39+September!C39+October!C39+November!C39+December!C39</f>
-        <v>207</v>
+        <v>282</v>
       </c>
       <c r="D39" s="11">
         <f>January!D39+February!D39+March!D39+April!D39+May!D39+June!D39+July!D39+August!D39+September!D39+October!D39+November!D39+December!D39</f>
-        <v>-143</v>
+        <v>-207</v>
       </c>
       <c r="E39" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6776,24 +6845,24 @@
       </c>
       <c r="G39" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.31 : 1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.27 : 1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
       <c r="B40" s="23">
         <f>January!B40+February!B40+March!B40+April!B40+May!B40+June!B40+July!B40+August!B40+September!B40+October!B40+November!B40+December!B40</f>
-        <v>347</v>
+        <v>444</v>
       </c>
       <c r="C40" s="23">
         <f>January!C40+February!C40+March!C40+April!C40+May!C40+June!C40+July!C40+August!C40+September!C40+October!C40+November!C40+December!C40</f>
-        <v>384</v>
+        <v>506</v>
       </c>
       <c r="D40" s="23">
         <f>January!D40+February!D40+March!D40+April!D40+May!D40+June!D40+July!D40+August!D40+September!D40+October!D40+November!D40+December!D40</f>
-        <v>-37</v>
+        <v>-62</v>
       </c>
       <c r="E40" s="24" t="str">
         <f t="shared" si="0"/>
@@ -6805,24 +6874,24 @@
       </c>
       <c r="G40" s="25" t="str">
         <f t="shared" si="2"/>
-        <v>0.9 : 1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.88 : 1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
       <c r="B41" s="27">
         <f>January!B41+February!B41+March!B41+April!B41+May!B41+June!B41+July!B41+August!B41+September!B41+October!B41+November!B41+December!B41</f>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C41" s="27">
         <f>January!C41+February!C41+March!C41+April!C41+May!C41+June!C41+July!C41+August!C41+September!C41+October!C41+November!C41+December!C41</f>
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D41" s="27">
         <f>January!D41+February!D41+March!D41+April!D41+May!D41+June!D41+July!D41+August!D41+September!D41+October!D41+November!D41+December!D41</f>
-        <v>-52</v>
+        <v>-66</v>
       </c>
       <c r="E41" s="28" t="str">
         <f t="shared" si="0"/>
@@ -6837,21 +6906,21 @@
         <v>0.26 : 1</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
       <c r="B42" s="23">
         <f>January!B42+February!B42+March!B42+April!B42+May!B42+June!B42+July!B42+August!B42+September!B42+October!B42+November!B42+December!B42</f>
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C42" s="23">
         <f>January!C42+February!C42+March!C42+April!C42+May!C42+June!C42+July!C42+August!C42+September!C42+October!C42+November!C42+December!C42</f>
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="D42" s="23">
         <f>January!D42+February!D42+March!D42+April!D42+May!D42+June!D42+July!D42+August!D42+September!D42+October!D42+November!D42+December!D42</f>
-        <v>-57</v>
+        <v>-72</v>
       </c>
       <c r="E42" s="24" t="str">
         <f t="shared" si="0"/>
@@ -6863,24 +6932,24 @@
       </c>
       <c r="G42" s="25" t="str">
         <f t="shared" si="2"/>
-        <v>0.39 : 1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.41 : 1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
       <c r="B43" s="27">
         <f>January!B43+February!B43+March!B43+April!B43+May!B43+June!B43+July!B43+August!B43+September!B43+October!B43+November!B43+December!B43</f>
-        <v>558</v>
+        <v>628</v>
       </c>
       <c r="C43" s="27">
         <f>January!C43+February!C43+March!C43+April!C43+May!C43+June!C43+July!C43+August!C43+September!C43+October!C43+November!C43+December!C43</f>
-        <v>312</v>
+        <v>403</v>
       </c>
       <c r="D43" s="27">
         <f>January!D43+February!D43+March!D43+April!D43+May!D43+June!D43+July!D43+August!D43+September!D43+October!D43+November!D43+December!D43</f>
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="E43" s="28" t="str">
         <f t="shared" si="0"/>
@@ -6892,24 +6961,24 @@
       </c>
       <c r="G43" s="29" t="str">
         <f t="shared" si="2"/>
-        <v>1.79 : 1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.56 : 1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
       <c r="B44" s="7">
         <f>January!B44+February!B44+March!B44+April!B44+May!B44+June!B44+July!B44+August!B44+September!B44+October!B44+November!B44+December!B44</f>
-        <v>176</v>
+        <v>243</v>
       </c>
       <c r="C44" s="7">
         <f>January!C44+February!C44+March!C44+April!C44+May!C44+June!C44+July!C44+August!C44+September!C44+October!C44+November!C44+December!C44</f>
-        <v>521</v>
+        <v>695</v>
       </c>
       <c r="D44" s="7">
         <f>January!D44+February!D44+March!D44+April!D44+May!D44+June!D44+July!D44+August!D44+September!D44+October!D44+November!D44+December!D44</f>
-        <v>-345</v>
+        <v>-452</v>
       </c>
       <c r="E44" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6921,24 +6990,24 @@
       </c>
       <c r="G44" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.34 : 1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.35 : 1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
       <c r="B45" s="11">
         <f>January!B45+February!B45+March!B45+April!B45+May!B45+June!B45+July!B45+August!B45+September!B45+October!B45+November!B45+December!B45</f>
-        <v>1629</v>
+        <v>2179</v>
       </c>
       <c r="C45" s="11">
         <f>January!C45+February!C45+March!C45+April!C45+May!C45+June!C45+July!C45+August!C45+September!C45+October!C45+November!C45+December!C45</f>
-        <v>1878</v>
+        <v>2425</v>
       </c>
       <c r="D45" s="11">
         <f>January!D45+February!D45+March!D45+April!D45+May!D45+June!D45+July!D45+August!D45+September!D45+October!D45+November!D45+December!D45</f>
-        <v>-249</v>
+        <v>-246</v>
       </c>
       <c r="E45" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6950,24 +7019,24 @@
       </c>
       <c r="G45" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.87 : 1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.9 : 1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
       <c r="B46" s="7">
         <f>January!B46+February!B46+March!B46+April!B46+May!B46+June!B46+July!B46+August!B46+September!B46+October!B46+November!B46+December!B46</f>
-        <v>2910</v>
+        <v>3642</v>
       </c>
       <c r="C46" s="7">
         <f>January!C46+February!C46+March!C46+April!C46+May!C46+June!C46+July!C46+August!C46+September!C46+October!C46+November!C46+December!C46</f>
-        <v>2373</v>
+        <v>3047</v>
       </c>
       <c r="D46" s="7">
         <f>January!D46+February!D46+March!D46+April!D46+May!D46+June!D46+July!D46+August!D46+September!D46+October!D46+November!D46+December!D46</f>
-        <v>537</v>
+        <v>595</v>
       </c>
       <c r="E46" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6979,24 +7048,24 @@
       </c>
       <c r="G46" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.23 : 1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.2 : 1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
       <c r="B47" s="11">
         <f>January!B47+February!B47+March!B47+April!B47+May!B47+June!B47+July!B47+August!B47+September!B47+October!B47+November!B47+December!B47</f>
-        <v>720</v>
+        <v>960</v>
       </c>
       <c r="C47" s="11">
         <f>January!C47+February!C47+March!C47+April!C47+May!C47+June!C47+July!C47+August!C47+September!C47+October!C47+November!C47+December!C47</f>
-        <v>1820</v>
+        <v>2456</v>
       </c>
       <c r="D47" s="11">
         <f>January!D47+February!D47+March!D47+April!D47+May!D47+June!D47+July!D47+August!D47+September!D47+October!D47+November!D47+December!D47</f>
-        <v>-1100</v>
+        <v>-1496</v>
       </c>
       <c r="E47" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7008,24 +7077,24 @@
       </c>
       <c r="G47" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.4 : 1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.39 : 1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
       <c r="B48" s="7">
         <f>January!B48+February!B48+March!B48+April!B48+May!B48+June!B48+July!B48+August!B48+September!B48+October!B48+November!B48+December!B48</f>
-        <v>1456</v>
+        <v>1850</v>
       </c>
       <c r="C48" s="7">
         <f>January!C48+February!C48+March!C48+April!C48+May!C48+June!C48+July!C48+August!C48+September!C48+October!C48+November!C48+December!C48</f>
-        <v>885</v>
+        <v>1120</v>
       </c>
       <c r="D48" s="7">
         <f>January!D48+February!D48+March!D48+April!D48+May!D48+June!D48+July!D48+August!D48+September!D48+October!D48+November!D48+December!D48</f>
-        <v>571</v>
+        <v>730</v>
       </c>
       <c r="E48" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7040,21 +7109,21 @@
         <v>1.65 : 1</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
       <c r="B49" s="11">
         <f>January!B49+February!B49+March!B49+April!B49+May!B49+June!B49+July!B49+August!B49+September!B49+October!B49+November!B49+December!B49</f>
-        <v>2751</v>
+        <v>3735</v>
       </c>
       <c r="C49" s="11">
         <f>January!C49+February!C49+March!C49+April!C49+May!C49+June!C49+July!C49+August!C49+September!C49+October!C49+November!C49+December!C49</f>
-        <v>1656</v>
+        <v>2300</v>
       </c>
       <c r="D49" s="11">
         <f>January!D49+February!D49+March!D49+April!D49+May!D49+June!D49+July!D49+August!D49+September!D49+October!D49+November!D49+December!D49</f>
-        <v>1095</v>
+        <v>1435</v>
       </c>
       <c r="E49" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7066,24 +7135,24 @@
       </c>
       <c r="G49" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.66 : 1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.62 : 1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
       <c r="B50" s="7">
         <f>January!B50+February!B50+March!B50+April!B50+May!B50+June!B50+July!B50+August!B50+September!B50+October!B50+November!B50+December!B50</f>
-        <v>382</v>
+        <v>513</v>
       </c>
       <c r="C50" s="7">
         <f>January!C50+February!C50+March!C50+April!C50+May!C50+June!C50+July!C50+August!C50+September!C50+October!C50+November!C50+December!C50</f>
-        <v>534</v>
+        <v>689</v>
       </c>
       <c r="D50" s="7">
         <f>January!D50+February!D50+March!D50+April!D50+May!D50+June!D50+July!D50+August!D50+September!D50+October!D50+November!D50+December!D50</f>
-        <v>-152</v>
+        <v>-176</v>
       </c>
       <c r="E50" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7095,24 +7164,24 @@
       </c>
       <c r="G50" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.72 : 1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.74 : 1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
       <c r="B51" s="11">
         <f>January!B51+February!B51+March!B51+April!B51+May!B51+June!B51+July!B51+August!B51+September!B51+October!B51+November!B51+December!B51</f>
-        <v>1672</v>
+        <v>2021</v>
       </c>
       <c r="C51" s="11">
         <f>January!C51+February!C51+March!C51+April!C51+May!C51+June!C51+July!C51+August!C51+September!C51+October!C51+November!C51+December!C51</f>
-        <v>1124</v>
+        <v>1487</v>
       </c>
       <c r="D51" s="11">
         <f>January!D51+February!D51+March!D51+April!D51+May!D51+June!D51+July!D51+August!D51+September!D51+October!D51+November!D51+December!D51</f>
-        <v>548</v>
+        <v>534</v>
       </c>
       <c r="E51" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7124,24 +7193,24 @@
       </c>
       <c r="G51" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.49 : 1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.36 : 1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B52" s="7">
         <f>January!B52+February!B52+March!B52+April!B52+May!B52+June!B52+July!B52+August!B52+September!B52+October!B52+November!B52+December!B52</f>
-        <v>413</v>
+        <v>543</v>
       </c>
       <c r="C52" s="7">
         <f>January!C52+February!C52+March!C52+April!C52+May!C52+June!C52+July!C52+August!C52+September!C52+October!C52+November!C52+December!C52</f>
-        <v>686</v>
+        <v>891</v>
       </c>
       <c r="D52" s="7">
         <f>January!D52+February!D52+March!D52+April!D52+May!D52+June!D52+July!D52+August!D52+September!D52+October!D52+November!D52+December!D52</f>
-        <v>-273</v>
+        <v>-348</v>
       </c>
       <c r="E52" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7153,24 +7222,24 @@
       </c>
       <c r="G52" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.6 : 1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.61 : 1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
       <c r="B53" s="11">
         <f>January!B53+February!B53+March!B53+April!B53+May!B53+June!B53+July!B53+August!B53+September!B53+October!B53+November!B53+December!B53</f>
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="C53" s="11">
         <f>January!C53+February!C53+March!C53+April!C53+May!C53+June!C53+July!C53+August!C53+September!C53+October!C53+November!C53+December!C53</f>
-        <v>819</v>
+        <v>1026</v>
       </c>
       <c r="D53" s="11">
         <f>January!D53+February!D53+March!D53+April!D53+May!D53+June!D53+July!D53+August!D53+September!D53+October!D53+November!D53+December!D53</f>
-        <v>-737</v>
+        <v>-915</v>
       </c>
       <c r="E53" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7182,24 +7251,24 @@
       </c>
       <c r="G53" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.1 : 1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.11 : 1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
       <c r="B54" s="31">
         <f>January!B54+February!B54+March!B54+April!B54+May!B54+June!B54+July!B54+August!B54+September!B54+October!B54+November!B54+December!B54</f>
-        <v>1204</v>
+        <v>1683</v>
       </c>
       <c r="C54" s="31">
         <f>January!C54+February!C54+March!C54+April!C54+May!C54+June!C54+July!C54+August!C54+September!C54+October!C54+November!C54+December!C54</f>
-        <v>664</v>
+        <v>845</v>
       </c>
       <c r="D54" s="31">
         <f>January!D54+February!D54+March!D54+April!D54+May!D54+June!D54+July!D54+August!D54+September!D54+October!D54+November!D54+December!D54</f>
-        <v>540</v>
+        <v>838</v>
       </c>
       <c r="E54" s="32" t="str">
         <f t="shared" si="0"/>
@@ -7211,7 +7280,7 @@
       </c>
       <c r="G54" s="33" t="str">
         <f t="shared" si="2"/>
-        <v>1.81 : 1</v>
+        <v>1.99 : 1</v>
       </c>
     </row>
   </sheetData>
@@ -7249,16 +7318,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7281,7 +7350,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -7302,7 +7371,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -7323,7 +7392,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -7344,7 +7413,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -7365,7 +7434,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -7386,7 +7455,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -7407,7 +7476,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -7428,7 +7497,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -7449,7 +7518,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -7470,7 +7539,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -7487,7 +7556,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -7508,7 +7577,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -7529,7 +7598,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -7550,7 +7619,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -7571,7 +7640,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -7592,7 +7661,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -7613,7 +7682,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -7634,7 +7703,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -7655,7 +7724,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -7676,7 +7745,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -7697,7 +7766,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -7718,7 +7787,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -7739,7 +7808,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -7760,7 +7829,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -7781,7 +7850,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -7798,7 +7867,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -7819,7 +7888,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -7840,7 +7909,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -7861,7 +7930,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -7882,7 +7951,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -7903,7 +7972,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -7924,7 +7993,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -7945,7 +8014,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -7966,7 +8035,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -7987,7 +8056,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -8008,7 +8077,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -8029,7 +8098,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -8050,7 +8119,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -8071,7 +8140,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -8092,7 +8161,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -8113,7 +8182,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -8134,7 +8203,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -8155,7 +8224,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -8176,7 +8245,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -8197,7 +8266,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -8218,7 +8287,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -8239,7 +8308,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -8260,7 +8329,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -8281,7 +8350,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -8302,7 +8371,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -8323,7 +8392,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -8344,7 +8413,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -8365,7 +8434,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -8431,16 +8500,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8463,7 +8532,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -8484,7 +8553,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -8505,7 +8574,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -8526,7 +8595,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -8547,7 +8616,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -8568,7 +8637,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -8589,7 +8658,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -8610,7 +8679,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -8631,7 +8700,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -8652,7 +8721,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -8669,7 +8738,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -8690,7 +8759,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -8711,7 +8780,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -8732,7 +8801,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -8753,7 +8822,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -8774,7 +8843,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -8795,7 +8864,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -8816,7 +8885,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -8837,7 +8906,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -8858,7 +8927,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -8879,7 +8948,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -8900,7 +8969,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -8921,7 +8990,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -8942,7 +9011,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -8963,7 +9032,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -8980,7 +9049,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -9001,7 +9070,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -9022,7 +9091,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -9043,7 +9112,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -9064,7 +9133,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -9085,7 +9154,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -9106,7 +9175,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -9127,7 +9196,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -9148,7 +9217,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -9169,7 +9238,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -9190,7 +9259,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -9211,7 +9280,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -9232,7 +9301,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -9253,7 +9322,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -9274,7 +9343,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -9295,7 +9364,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -9316,7 +9385,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -9337,7 +9406,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -9358,7 +9427,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -9379,7 +9448,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -9400,7 +9469,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -9421,7 +9490,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -9442,7 +9511,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -9463,7 +9532,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -9484,7 +9553,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -9505,7 +9574,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -9526,7 +9595,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -9547,7 +9616,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -9613,16 +9682,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9645,588 +9714,1110 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8"/>
+      <c r="B2" s="7">
+        <v>1453</v>
+      </c>
+      <c r="C2" s="7">
+        <v>1233</v>
+      </c>
+      <c r="D2" s="7">
+        <v>220</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F2" s="8"/>
-      <c r="G2" s="9"/>
-    </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="12"/>
+      <c r="B3" s="11">
+        <v>506</v>
+      </c>
+      <c r="C3" s="11">
+        <v>457</v>
+      </c>
+      <c r="D3" s="11">
+        <v>49</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F3" s="12"/>
-      <c r="G3" s="13"/>
-    </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G3" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
+      <c r="B4" s="7">
+        <v>1036</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1118</v>
+      </c>
+      <c r="D4" s="7">
+        <v>-82</v>
+      </c>
       <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="9"/>
-    </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
+      <c r="B5" s="11">
+        <v>20</v>
+      </c>
+      <c r="C5" s="11">
+        <v>105</v>
+      </c>
+      <c r="D5" s="11">
+        <v>-85</v>
+      </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13"/>
-    </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+      <c r="B6" s="7">
+        <v>905</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1050</v>
+      </c>
+      <c r="D6" s="7">
+        <v>-145</v>
+      </c>
       <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9"/>
-    </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12"/>
+      <c r="B7" s="11">
+        <v>236</v>
+      </c>
+      <c r="C7" s="11">
+        <v>168</v>
+      </c>
+      <c r="D7" s="11">
+        <v>68</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="13"/>
-    </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G7" s="13" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+      <c r="B8" s="7">
+        <v>84</v>
+      </c>
+      <c r="C8" s="7">
+        <v>162</v>
+      </c>
+      <c r="D8" s="7">
+        <v>-78</v>
+      </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9"/>
-    </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
+      <c r="B9" s="11">
+        <v>44</v>
+      </c>
+      <c r="C9" s="11">
+        <v>46</v>
+      </c>
+      <c r="D9" s="11">
+        <v>-2</v>
+      </c>
       <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="13"/>
-    </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F9" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="B10" s="7">
+        <v>0</v>
+      </c>
+      <c r="C10" s="7">
+        <v>21</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-21</v>
+      </c>
       <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9"/>
-    </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
+      <c r="B11" s="11">
+        <v>0</v>
+      </c>
+      <c r="C11" s="11">
+        <v>0</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0</v>
+      </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
+      <c r="B12" s="15">
+        <v>11</v>
+      </c>
+      <c r="C12" s="15">
+        <v>18</v>
+      </c>
+      <c r="D12" s="15">
+        <v>-7</v>
+      </c>
       <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17"/>
-    </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="20"/>
+      <c r="B13" s="19">
+        <v>55</v>
+      </c>
+      <c r="C13" s="19">
+        <v>48</v>
+      </c>
+      <c r="D13" s="19">
+        <v>7</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>8</v>
+      </c>
       <c r="F13" s="20"/>
-      <c r="G13" s="21"/>
-    </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G13" s="21" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
+      <c r="B14" s="15">
+        <v>116</v>
+      </c>
+      <c r="C14" s="15">
+        <v>293</v>
+      </c>
+      <c r="D14" s="15">
+        <v>-177</v>
+      </c>
       <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="17"/>
-    </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F14" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
+      <c r="B15" s="19">
+        <v>37</v>
+      </c>
+      <c r="C15" s="19">
+        <v>125</v>
+      </c>
+      <c r="D15" s="19">
+        <v>-88</v>
+      </c>
       <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="21"/>
-    </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F15" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
+      <c r="B16" s="7">
+        <v>72</v>
+      </c>
+      <c r="C16" s="7">
+        <v>137</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-65</v>
+      </c>
       <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="9"/>
-    </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="12"/>
+      <c r="B17" s="11">
+        <v>568</v>
+      </c>
+      <c r="C17" s="11">
+        <v>460</v>
+      </c>
+      <c r="D17" s="11">
+        <v>108</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F17" s="12"/>
-      <c r="G17" s="13"/>
-    </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G17" s="13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8"/>
+      <c r="B18" s="7">
+        <v>123</v>
+      </c>
+      <c r="C18" s="7">
+        <v>84</v>
+      </c>
+      <c r="D18" s="7">
+        <v>39</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F18" s="8"/>
-      <c r="G18" s="9"/>
-    </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G18" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="12"/>
+      <c r="B19" s="11">
+        <v>418</v>
+      </c>
+      <c r="C19" s="11">
+        <v>303</v>
+      </c>
+      <c r="D19" s="11">
+        <v>115</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="13"/>
-    </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G19" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
+      <c r="B20" s="7">
+        <v>2</v>
+      </c>
+      <c r="C20" s="7">
+        <v>33</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-31</v>
+      </c>
       <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="9"/>
-    </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="12"/>
+      <c r="B21" s="11">
+        <v>446</v>
+      </c>
+      <c r="C21" s="11">
+        <v>393</v>
+      </c>
+      <c r="D21" s="11">
+        <v>53</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="13"/>
-    </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G21" s="13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+      <c r="B22" s="7">
+        <v>90</v>
+      </c>
+      <c r="C22" s="7">
+        <v>205</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-115</v>
+      </c>
       <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="9"/>
-    </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F22" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
+      <c r="B23" s="11">
+        <v>634</v>
+      </c>
+      <c r="C23" s="11">
+        <v>647</v>
+      </c>
+      <c r="D23" s="11">
+        <v>-13</v>
+      </c>
       <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="13"/>
-    </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F23" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8"/>
+      <c r="B24" s="7">
+        <v>1819</v>
+      </c>
+      <c r="C24" s="7">
+        <v>1318</v>
+      </c>
+      <c r="D24" s="7">
+        <v>501</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
-    </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G24" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="B25" s="11">
+        <v>215</v>
+      </c>
+      <c r="C25" s="11">
+        <v>324</v>
+      </c>
+      <c r="D25" s="11">
+        <v>-109</v>
+      </c>
       <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="13"/>
-    </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F25" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
+      <c r="B26" s="7">
+        <v>0</v>
+      </c>
+      <c r="C26" s="7">
+        <v>0</v>
+      </c>
+      <c r="D26" s="7">
+        <v>0</v>
+      </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="12"/>
+      <c r="B27" s="11">
+        <v>191</v>
+      </c>
+      <c r="C27" s="11">
+        <v>119</v>
+      </c>
+      <c r="D27" s="11">
+        <v>72</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F27" s="12"/>
-      <c r="G27" s="13"/>
-    </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G27" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="8"/>
+      <c r="B28" s="7">
+        <v>128</v>
+      </c>
+      <c r="C28" s="7">
+        <v>94</v>
+      </c>
+      <c r="D28" s="7">
+        <v>34</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F28" s="8"/>
-      <c r="G28" s="9"/>
-    </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G28" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="12"/>
+      <c r="B29" s="11">
+        <v>776</v>
+      </c>
+      <c r="C29" s="11">
+        <v>435</v>
+      </c>
+      <c r="D29" s="11">
+        <v>341</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F29" s="12"/>
-      <c r="G29" s="13"/>
-    </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G29" s="13" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="8"/>
+      <c r="B30" s="7">
+        <v>70</v>
+      </c>
+      <c r="C30" s="7">
+        <v>18</v>
+      </c>
+      <c r="D30" s="7">
+        <v>52</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F30" s="8"/>
-      <c r="G30" s="9"/>
-    </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G30" s="9" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
+      <c r="B31" s="11">
+        <v>101</v>
+      </c>
+      <c r="C31" s="11">
+        <v>255</v>
+      </c>
+      <c r="D31" s="11">
+        <v>-154</v>
+      </c>
       <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="13"/>
-    </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F31" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
+      <c r="B32" s="7">
+        <v>381</v>
+      </c>
+      <c r="C32" s="7">
+        <v>475</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-94</v>
+      </c>
       <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="9"/>
-    </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F32" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="12"/>
+      <c r="B33" s="11">
+        <v>310</v>
+      </c>
+      <c r="C33" s="11">
+        <v>277</v>
+      </c>
+      <c r="D33" s="11">
+        <v>33</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F33" s="12"/>
-      <c r="G33" s="13"/>
-    </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G33" s="13" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="8"/>
+      <c r="B34" s="7">
+        <v>143</v>
+      </c>
+      <c r="C34" s="7">
+        <v>91</v>
+      </c>
+      <c r="D34" s="7">
+        <v>52</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F34" s="8"/>
-      <c r="G34" s="9"/>
-    </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G34" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
+      <c r="B35" s="11">
+        <v>1043</v>
+      </c>
+      <c r="C35" s="11">
+        <v>1321</v>
+      </c>
+      <c r="D35" s="11">
+        <v>-278</v>
+      </c>
       <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="13"/>
-    </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F35" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
+      <c r="B36" s="7">
+        <v>175</v>
+      </c>
+      <c r="C36" s="7">
+        <v>474</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-299</v>
+      </c>
       <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="9"/>
-    </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F36" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="12"/>
+      <c r="B37" s="11">
+        <v>628</v>
+      </c>
+      <c r="C37" s="11">
+        <v>310</v>
+      </c>
+      <c r="D37" s="11">
+        <v>318</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="13"/>
-    </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G37" s="13" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
+      <c r="B38" s="7">
+        <v>48</v>
+      </c>
+      <c r="C38" s="7">
+        <v>192</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-144</v>
+      </c>
       <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="9"/>
-    </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F38" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
+      <c r="B39" s="11">
+        <v>11</v>
+      </c>
+      <c r="C39" s="11">
+        <v>75</v>
+      </c>
+      <c r="D39" s="11">
+        <v>-64</v>
+      </c>
       <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="13"/>
-    </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F39" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
+      <c r="B40" s="23">
+        <v>97</v>
+      </c>
+      <c r="C40" s="23">
+        <v>122</v>
+      </c>
+      <c r="D40" s="23">
+        <v>-25</v>
+      </c>
       <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="25"/>
-    </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F40" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="25" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
+      <c r="B41" s="27">
+        <v>5</v>
+      </c>
+      <c r="C41" s="27">
+        <v>19</v>
+      </c>
+      <c r="D41" s="27">
+        <v>-14</v>
+      </c>
       <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="29"/>
-    </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F41" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
+      <c r="B42" s="23">
+        <v>14</v>
+      </c>
+      <c r="C42" s="23">
+        <v>29</v>
+      </c>
+      <c r="D42" s="23">
+        <v>-15</v>
+      </c>
       <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="25"/>
-    </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F42" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
+      <c r="B43" s="27">
+        <v>70</v>
+      </c>
+      <c r="C43" s="27">
+        <v>91</v>
+      </c>
+      <c r="D43" s="27">
+        <v>-21</v>
+      </c>
       <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="29"/>
-    </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F43" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" s="29" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
+      <c r="B44" s="7">
+        <v>67</v>
+      </c>
+      <c r="C44" s="7">
+        <v>174</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-107</v>
+      </c>
       <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="9"/>
-    </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F44" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="12"/>
+      <c r="B45" s="11">
+        <v>550</v>
+      </c>
+      <c r="C45" s="11">
+        <v>547</v>
+      </c>
+      <c r="D45" s="11">
+        <v>3</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F45" s="12"/>
-      <c r="G45" s="13"/>
-    </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G45" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="8"/>
+      <c r="B46" s="7">
+        <v>732</v>
+      </c>
+      <c r="C46" s="7">
+        <v>674</v>
+      </c>
+      <c r="D46" s="7">
+        <v>58</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F46" s="8"/>
-      <c r="G46" s="9"/>
-    </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G46" s="9" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
+      <c r="B47" s="11">
+        <v>240</v>
+      </c>
+      <c r="C47" s="11">
+        <v>636</v>
+      </c>
+      <c r="D47" s="11">
+        <v>-396</v>
+      </c>
       <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="13"/>
-    </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F47" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="8"/>
+      <c r="B48" s="7">
+        <v>394</v>
+      </c>
+      <c r="C48" s="7">
+        <v>235</v>
+      </c>
+      <c r="D48" s="7">
+        <v>159</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F48" s="8"/>
-      <c r="G48" s="9"/>
-    </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G48" s="9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="12"/>
+      <c r="B49" s="11">
+        <v>984</v>
+      </c>
+      <c r="C49" s="11">
+        <v>644</v>
+      </c>
+      <c r="D49" s="11">
+        <v>340</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="13"/>
-    </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G49" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
+      <c r="B50" s="7">
+        <v>131</v>
+      </c>
+      <c r="C50" s="7">
+        <v>155</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-24</v>
+      </c>
       <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="9"/>
-    </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F50" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
+      <c r="B51" s="11">
+        <v>349</v>
+      </c>
+      <c r="C51" s="11">
+        <v>363</v>
+      </c>
+      <c r="D51" s="11">
+        <v>-14</v>
+      </c>
       <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="13"/>
-    </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F51" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
+      <c r="B52" s="7">
+        <v>130</v>
+      </c>
+      <c r="C52" s="7">
+        <v>205</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-75</v>
+      </c>
       <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="9"/>
-    </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F52" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
+      <c r="B53" s="11">
+        <v>29</v>
+      </c>
+      <c r="C53" s="11">
+        <v>207</v>
+      </c>
+      <c r="D53" s="11">
+        <v>-178</v>
+      </c>
       <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="13"/>
-    </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F53" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B54" s="31"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="32"/>
+      <c r="B54" s="31">
+        <v>479</v>
+      </c>
+      <c r="C54" s="31">
+        <v>181</v>
+      </c>
+      <c r="D54" s="31">
+        <v>298</v>
+      </c>
+      <c r="E54" s="32" t="s">
+        <v>8</v>
+      </c>
       <c r="F54" s="32"/>
-      <c r="G54" s="33"/>
+      <c r="G54" s="33" t="s">
+        <v>192</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
@@ -10273,16 +10864,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10305,7 +10896,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -10316,7 +10907,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -10327,7 +10918,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -10338,7 +10929,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -10349,7 +10940,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -10360,7 +10951,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -10371,7 +10962,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -10382,7 +10973,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -10393,7 +10984,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -10404,7 +10995,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -10415,7 +11006,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -10426,7 +11017,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -10437,7 +11028,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -10448,7 +11039,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -10459,7 +11050,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -10470,7 +11061,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -10481,7 +11072,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -10492,7 +11083,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -10503,7 +11094,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -10514,7 +11105,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -10525,7 +11116,7 @@
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -10536,7 +11127,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -10547,7 +11138,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -10558,7 +11149,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -10569,7 +11160,7 @@
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -10580,7 +11171,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -10591,7 +11182,7 @@
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -10602,7 +11193,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -10613,7 +11204,7 @@
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -10624,7 +11215,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -10635,7 +11226,7 @@
       <c r="F31" s="12"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -10646,7 +11237,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -10657,7 +11248,7 @@
       <c r="F33" s="12"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -10668,7 +11259,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -10679,7 +11270,7 @@
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -10690,7 +11281,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -10701,7 +11292,7 @@
       <c r="F37" s="12"/>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -10712,7 +11303,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -10723,7 +11314,7 @@
       <c r="F39" s="12"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -10734,7 +11325,7 @@
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -10745,7 +11336,7 @@
       <c r="F41" s="28"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -10756,7 +11347,7 @@
       <c r="F42" s="24"/>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -10767,7 +11358,7 @@
       <c r="F43" s="28"/>
       <c r="G43" s="29"/>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -10778,7 +11369,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -10789,7 +11380,7 @@
       <c r="F45" s="12"/>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -10800,7 +11391,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -10811,7 +11402,7 @@
       <c r="F47" s="12"/>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -10822,7 +11413,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -10833,7 +11424,7 @@
       <c r="F49" s="12"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -10844,7 +11435,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -10855,7 +11446,7 @@
       <c r="F51" s="12"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -10866,7 +11457,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -10877,7 +11468,7 @@
       <c r="F53" s="12"/>
       <c r="G53" s="13"/>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -10933,16 +11524,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10965,7 +11556,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -10976,7 +11567,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -10987,7 +11578,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -10998,7 +11589,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -11009,7 +11600,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -11020,7 +11611,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -11031,7 +11622,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -11042,7 +11633,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -11053,7 +11644,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -11064,7 +11655,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -11075,7 +11666,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -11086,7 +11677,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -11097,7 +11688,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -11108,7 +11699,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -11119,7 +11710,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -11130,7 +11721,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -11141,7 +11732,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -11152,7 +11743,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -11163,7 +11754,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -11174,7 +11765,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -11185,7 +11776,7 @@
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -11196,7 +11787,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -11207,7 +11798,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -11218,7 +11809,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -11229,7 +11820,7 @@
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -11240,7 +11831,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -11251,7 +11842,7 @@
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -11262,7 +11853,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -11273,7 +11864,7 @@
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -11284,7 +11875,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -11295,7 +11886,7 @@
       <c r="F31" s="12"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -11306,7 +11897,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -11317,7 +11908,7 @@
       <c r="F33" s="12"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -11328,7 +11919,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -11339,7 +11930,7 @@
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -11350,7 +11941,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -11361,7 +11952,7 @@
       <c r="F37" s="12"/>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -11372,7 +11963,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -11383,7 +11974,7 @@
       <c r="F39" s="12"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -11394,7 +11985,7 @@
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -11405,7 +11996,7 @@
       <c r="F41" s="28"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -11416,7 +12007,7 @@
       <c r="F42" s="24"/>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -11427,7 +12018,7 @@
       <c r="F43" s="28"/>
       <c r="G43" s="29"/>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -11438,7 +12029,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -11449,7 +12040,7 @@
       <c r="F45" s="12"/>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -11460,7 +12051,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -11471,7 +12062,7 @@
       <c r="F47" s="12"/>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -11482,7 +12073,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -11493,7 +12084,7 @@
       <c r="F49" s="12"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -11504,7 +12095,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -11515,7 +12106,7 @@
       <c r="F51" s="12"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -11526,7 +12117,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -11537,7 +12128,7 @@
       <c r="F53" s="12"/>
       <c r="G53" s="13"/>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -11593,16 +12184,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11625,7 +12216,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -11636,7 +12227,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -11647,7 +12238,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -11658,7 +12249,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -11669,7 +12260,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -11680,7 +12271,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -11691,7 +12282,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -11702,7 +12293,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -11713,7 +12304,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -11724,7 +12315,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -11735,7 +12326,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -11746,7 +12337,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -11757,7 +12348,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -11768,7 +12359,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -11779,7 +12370,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -11790,7 +12381,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -11801,7 +12392,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -11812,7 +12403,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -11823,7 +12414,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -11834,7 +12425,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -11845,7 +12436,7 @@
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -11856,7 +12447,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -11867,7 +12458,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -11878,7 +12469,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -11889,7 +12480,7 @@
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -11900,7 +12491,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -11911,7 +12502,7 @@
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -11922,7 +12513,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -11933,7 +12524,7 @@
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -11944,7 +12535,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -11955,7 +12546,7 @@
       <c r="F31" s="12"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -11966,7 +12557,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -11977,7 +12568,7 @@
       <c r="F33" s="12"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -11988,7 +12579,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -11999,7 +12590,7 @@
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -12010,7 +12601,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -12021,7 +12612,7 @@
       <c r="F37" s="12"/>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -12032,7 +12623,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -12043,7 +12634,7 @@
       <c r="F39" s="12"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -12054,7 +12645,7 @@
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -12065,7 +12656,7 @@
       <c r="F41" s="28"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -12076,7 +12667,7 @@
       <c r="F42" s="24"/>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -12087,7 +12678,7 @@
       <c r="F43" s="28"/>
       <c r="G43" s="29"/>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -12098,7 +12689,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -12109,7 +12700,7 @@
       <c r="F45" s="12"/>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -12120,7 +12711,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -12131,7 +12722,7 @@
       <c r="F47" s="12"/>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -12142,7 +12733,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -12153,7 +12744,7 @@
       <c r="F49" s="12"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -12164,7 +12755,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -12175,7 +12766,7 @@
       <c r="F51" s="12"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -12186,7 +12777,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -12197,7 +12788,7 @@
       <c r="F53" s="12"/>
       <c r="G53" s="13"/>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -12253,16 +12844,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12285,7 +12876,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -12296,7 +12887,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -12307,7 +12898,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -12318,7 +12909,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -12329,7 +12920,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -12340,7 +12931,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -12351,7 +12942,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -12362,7 +12953,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -12373,7 +12964,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -12384,7 +12975,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -12395,7 +12986,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -12406,7 +12997,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -12417,7 +13008,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -12428,7 +13019,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -12439,7 +13030,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -12450,7 +13041,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -12461,7 +13052,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -12472,7 +13063,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -12483,7 +13074,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -12494,7 +13085,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -12505,7 +13096,7 @@
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -12516,7 +13107,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -12527,7 +13118,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -12538,7 +13129,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -12549,7 +13140,7 @@
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -12560,7 +13151,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -12571,7 +13162,7 @@
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -12582,7 +13173,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -12593,7 +13184,7 @@
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -12604,7 +13195,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -12615,7 +13206,7 @@
       <c r="F31" s="12"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -12626,7 +13217,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -12637,7 +13228,7 @@
       <c r="F33" s="12"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -12648,7 +13239,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -12659,7 +13250,7 @@
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -12670,7 +13261,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -12681,7 +13272,7 @@
       <c r="F37" s="12"/>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -12692,7 +13283,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -12703,7 +13294,7 @@
       <c r="F39" s="12"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -12714,7 +13305,7 @@
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -12725,7 +13316,7 @@
       <c r="F41" s="28"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -12736,7 +13327,7 @@
       <c r="F42" s="24"/>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -12747,7 +13338,7 @@
       <c r="F43" s="28"/>
       <c r="G43" s="29"/>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -12758,7 +13349,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -12769,7 +13360,7 @@
       <c r="F45" s="12"/>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -12780,7 +13371,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -12791,7 +13382,7 @@
       <c r="F47" s="12"/>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -12802,7 +13393,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -12813,7 +13404,7 @@
       <c r="F49" s="12"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -12824,7 +13415,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -12835,7 +13426,7 @@
       <c r="F51" s="12"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -12846,7 +13437,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -12857,7 +13448,7 @@
       <c r="F53" s="12"/>
       <c r="G53" s="13"/>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
@@ -12913,16 +13504,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="6" width="25.6640625" style="34" customWidth="1"/>
-    <col min="7" max="7" width="28.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="6" width="25.7109375" style="34" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12945,7 +13536,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -12956,7 +13547,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
@@ -12967,7 +13558,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -12978,7 +13569,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -12989,7 +13580,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -13000,7 +13591,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -13011,7 +13602,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -13022,7 +13613,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -13033,7 +13624,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -13044,7 +13635,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
@@ -13055,7 +13646,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -13066,7 +13657,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -13077,7 +13668,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -13088,7 +13679,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
@@ -13099,7 +13690,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -13110,7 +13701,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
@@ -13121,7 +13712,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -13132,7 +13723,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
@@ -13143,7 +13734,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
@@ -13154,7 +13745,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
@@ -13165,7 +13756,7 @@
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
@@ -13176,7 +13767,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -13187,7 +13778,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -13198,7 +13789,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -13209,7 +13800,7 @@
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -13220,7 +13811,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -13231,7 +13822,7 @@
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -13242,7 +13833,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -13253,7 +13844,7 @@
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -13264,7 +13855,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
@@ -13275,7 +13866,7 @@
       <c r="F31" s="12"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
@@ -13286,7 +13877,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -13297,7 +13888,7 @@
       <c r="F33" s="12"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
@@ -13308,7 +13899,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
@@ -13319,7 +13910,7 @@
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
@@ -13330,7 +13921,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
@@ -13341,7 +13932,7 @@
       <c r="F37" s="12"/>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -13352,7 +13943,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
@@ -13363,7 +13954,7 @@
       <c r="F39" s="12"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
@@ -13374,7 +13965,7 @@
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
@@ -13385,7 +13976,7 @@
       <c r="F41" s="28"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
@@ -13396,7 +13987,7 @@
       <c r="F42" s="24"/>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
@@ -13407,7 +13998,7 @@
       <c r="F43" s="28"/>
       <c r="G43" s="29"/>
     </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
@@ -13418,7 +14009,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
@@ -13429,7 +14020,7 @@
       <c r="F45" s="12"/>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
@@ -13440,7 +14031,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -13451,7 +14042,7 @@
       <c r="F47" s="12"/>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
@@ -13462,7 +14053,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
@@ -13473,7 +14064,7 @@
       <c r="F49" s="12"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
@@ -13484,7 +14075,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
@@ -13495,7 +14086,7 @@
       <c r="F51" s="12"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
@@ -13506,7 +14097,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -13517,7 +14108,7 @@
       <c r="F53" s="12"/>
       <c r="G53" s="13"/>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>

--- a/statistics_files/2026/2026_99_ga_net_borrower_lender.xlsx
+++ b/statistics_files/2026/2026_99_ga_net_borrower_lender.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8F3741-B17E-4A00-AB99-C6B409AD2B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FDE46F-14C4-45D6-BAB6-832827452B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="868" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="210">
   <si>
     <t>Library</t>
   </si>
@@ -640,6 +640,57 @@
   </si>
   <si>
     <t>2.65 : 1</t>
+  </si>
+  <si>
+    <t>1.29 : 1</t>
+  </si>
+  <si>
+    <t>1.25 : 1</t>
+  </si>
+  <si>
+    <t>0.18 : 1</t>
+  </si>
+  <si>
+    <t>2.57 : 1</t>
+  </si>
+  <si>
+    <t>0.03 : 1</t>
+  </si>
+  <si>
+    <t>0.46 : 1</t>
+  </si>
+  <si>
+    <t>1.56 : 1</t>
+  </si>
+  <si>
+    <t>2.42 : 1</t>
+  </si>
+  <si>
+    <t>0.68 : 1</t>
+  </si>
+  <si>
+    <t>0.99 : 1</t>
+  </si>
+  <si>
+    <t>1.14 : 1</t>
+  </si>
+  <si>
+    <t>2.07 : 1</t>
+  </si>
+  <si>
+    <t>1.81 : 1</t>
+  </si>
+  <si>
+    <t>0.35 : 1</t>
+  </si>
+  <si>
+    <t>1.44 : 1</t>
+  </si>
+  <si>
+    <t>2.02 : 1</t>
+  </si>
+  <si>
+    <t>1.75 : 1</t>
   </si>
 </sst>
 </file>
@@ -5752,15 +5803,15 @@
       </c>
       <c r="B2" s="7">
         <f>January!B2+February!B2+March!B2+April!B2+May!B2+June!B2+July!B2+August!B2+September!B2+October!B2+November!B2+December!B2</f>
-        <v>5856</v>
+        <v>7107</v>
       </c>
       <c r="C2" s="7">
         <f>January!C2+February!C2+March!C2+April!C2+May!C2+June!C2+July!C2+August!C2+September!C2+October!C2+November!C2+December!C2</f>
-        <v>4936</v>
+        <v>5906</v>
       </c>
       <c r="D2" s="7">
         <f>January!D2+February!D2+March!D2+April!D2+May!D2+June!D2+July!D2+August!D2+September!D2+October!D2+November!D2+December!D2</f>
-        <v>920</v>
+        <v>1201</v>
       </c>
       <c r="E2" s="8" t="str">
         <f>IF(D2 &gt; 0, "We borrowed more than we lent this year", "")</f>
@@ -5772,7 +5823,7 @@
       </c>
       <c r="G2" s="9" t="str">
         <f>IF(ISERROR(ROUND(B2/C2,2)&amp;" : 1"), "", ROUND(B2/C2,2)&amp;" : 1")</f>
-        <v>1.19 : 1</v>
+        <v>1.2 : 1</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5781,15 +5832,15 @@
       </c>
       <c r="B3" s="11">
         <f>January!B3+February!B3+March!B3+April!B3+May!B3+June!B3+July!B3+August!B3+September!B3+October!B3+November!B3+December!B3</f>
-        <v>2499</v>
+        <v>3000</v>
       </c>
       <c r="C3" s="11">
         <f>January!C3+February!C3+March!C3+April!C3+May!C3+June!C3+July!C3+August!C3+September!C3+October!C3+November!C3+December!C3</f>
-        <v>1685</v>
+        <v>2086</v>
       </c>
       <c r="D3" s="11">
         <f>January!D3+February!D3+March!D3+April!D3+May!D3+June!D3+July!D3+August!D3+September!D3+October!D3+November!D3+December!D3</f>
-        <v>814</v>
+        <v>914</v>
       </c>
       <c r="E3" s="12" t="str">
         <f t="shared" ref="E3:E54" si="0">IF(D3 &gt; 0, "We borrowed more than we lent this year", "")</f>
@@ -5801,7 +5852,7 @@
       </c>
       <c r="G3" s="13" t="str">
         <f t="shared" ref="G3:G54" si="2">IF(ISERROR(ROUND(B3/C3,2)&amp;" : 1"), "", ROUND(B3/C3,2)&amp;" : 1")</f>
-        <v>1.48 : 1</v>
+        <v>1.44 : 1</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5810,15 +5861,15 @@
       </c>
       <c r="B4" s="7">
         <f>January!B4+February!B4+March!B4+April!B4+May!B4+June!B4+July!B4+August!B4+September!B4+October!B4+November!B4+December!B4</f>
-        <v>4858</v>
+        <v>5813</v>
       </c>
       <c r="C4" s="7">
         <f>January!C4+February!C4+March!C4+April!C4+May!C4+June!C4+July!C4+August!C4+September!C4+October!C4+November!C4+December!C4</f>
-        <v>4598</v>
+        <v>5707</v>
       </c>
       <c r="D4" s="7">
         <f>January!D4+February!D4+March!D4+April!D4+May!D4+June!D4+July!D4+August!D4+September!D4+October!D4+November!D4+December!D4</f>
-        <v>260</v>
+        <v>106</v>
       </c>
       <c r="E4" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5830,7 +5881,7 @@
       </c>
       <c r="G4" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.06 : 1</v>
+        <v>1.02 : 1</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5839,15 +5890,15 @@
       </c>
       <c r="B5" s="11">
         <f>January!B5+February!B5+March!B5+April!B5+May!B5+June!B5+July!B5+August!B5+September!B5+October!B5+November!B5+December!B5</f>
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="C5" s="11">
         <f>January!C5+February!C5+March!C5+April!C5+May!C5+June!C5+July!C5+August!C5+September!C5+October!C5+November!C5+December!C5</f>
-        <v>472</v>
+        <v>580</v>
       </c>
       <c r="D5" s="11">
         <f>January!D5+February!D5+March!D5+April!D5+May!D5+June!D5+July!D5+August!D5+September!D5+October!D5+November!D5+December!D5</f>
-        <v>-394</v>
+        <v>-483</v>
       </c>
       <c r="E5" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5868,15 +5919,15 @@
       </c>
       <c r="B6" s="7">
         <f>January!B6+February!B6+March!B6+April!B6+May!B6+June!B6+July!B6+August!B6+September!B6+October!B6+November!B6+December!B6</f>
-        <v>4094</v>
+        <v>4985</v>
       </c>
       <c r="C6" s="7">
         <f>January!C6+February!C6+March!C6+April!C6+May!C6+June!C6+July!C6+August!C6+September!C6+October!C6+November!C6+December!C6</f>
-        <v>4504</v>
+        <v>5614</v>
       </c>
       <c r="D6" s="7">
         <f>January!D6+February!D6+March!D6+April!D6+May!D6+June!D6+July!D6+August!D6+September!D6+October!D6+November!D6+December!D6</f>
-        <v>-410</v>
+        <v>-629</v>
       </c>
       <c r="E6" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5888,7 +5939,7 @@
       </c>
       <c r="G6" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.91 : 1</v>
+        <v>0.89 : 1</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5897,15 +5948,15 @@
       </c>
       <c r="B7" s="11">
         <f>January!B7+February!B7+March!B7+April!B7+May!B7+June!B7+July!B7+August!B7+September!B7+October!B7+November!B7+December!B7</f>
-        <v>850</v>
+        <v>1259</v>
       </c>
       <c r="C7" s="11">
         <f>January!C7+February!C7+March!C7+April!C7+May!C7+June!C7+July!C7+August!C7+September!C7+October!C7+November!C7+December!C7</f>
-        <v>683</v>
+        <v>842</v>
       </c>
       <c r="D7" s="11">
         <f>January!D7+February!D7+March!D7+April!D7+May!D7+June!D7+July!D7+August!D7+September!D7+October!D7+November!D7+December!D7</f>
-        <v>167</v>
+        <v>417</v>
       </c>
       <c r="E7" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5917,7 +5968,7 @@
       </c>
       <c r="G7" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.24 : 1</v>
+        <v>1.5 : 1</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5926,15 +5977,15 @@
       </c>
       <c r="B8" s="7">
         <f>January!B8+February!B8+March!B8+April!B8+May!B8+June!B8+July!B8+August!B8+September!B8+October!B8+November!B8+December!B8</f>
-        <v>446</v>
+        <v>533</v>
       </c>
       <c r="C8" s="7">
         <f>January!C8+February!C8+March!C8+April!C8+May!C8+June!C8+July!C8+August!C8+September!C8+October!C8+November!C8+December!C8</f>
-        <v>678</v>
+        <v>803</v>
       </c>
       <c r="D8" s="7">
         <f>January!D8+February!D8+March!D8+April!D8+May!D8+June!D8+July!D8+August!D8+September!D8+October!D8+November!D8+December!D8</f>
-        <v>-232</v>
+        <v>-270</v>
       </c>
       <c r="E8" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5955,15 +6006,15 @@
       </c>
       <c r="B9" s="11">
         <f>January!B9+February!B9+March!B9+April!B9+May!B9+June!B9+July!B9+August!B9+September!B9+October!B9+November!B9+December!B9</f>
-        <v>229</v>
+        <v>276</v>
       </c>
       <c r="C9" s="11">
         <f>January!C9+February!C9+March!C9+April!C9+May!C9+June!C9+July!C9+August!C9+September!C9+October!C9+November!C9+December!C9</f>
-        <v>208</v>
+        <v>248</v>
       </c>
       <c r="D9" s="11">
         <f>January!D9+February!D9+March!D9+April!D9+May!D9+June!D9+July!D9+August!D9+September!D9+October!D9+November!D9+December!D9</f>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E9" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5975,7 +6026,7 @@
       </c>
       <c r="G9" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.1 : 1</v>
+        <v>1.11 : 1</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5988,11 +6039,11 @@
       </c>
       <c r="C10" s="7">
         <f>January!C10+February!C10+March!C10+April!C10+May!C10+June!C10+July!C10+August!C10+September!C10+October!C10+November!C10+December!C10</f>
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D10" s="7">
         <f>January!D10+February!D10+March!D10+April!D10+May!D10+June!D10+July!D10+August!D10+September!D10+October!D10+November!D10+December!D10</f>
-        <v>-94</v>
+        <v>-104</v>
       </c>
       <c r="E10" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6042,15 +6093,15 @@
       </c>
       <c r="B12" s="15">
         <f>January!B12+February!B12+March!B12+April!B12+May!B12+June!B12+July!B12+August!B12+September!B12+October!B12+November!B12+December!B12</f>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C12" s="15">
         <f>January!C12+February!C12+March!C12+April!C12+May!C12+June!C12+July!C12+August!C12+September!C12+October!C12+November!C12+December!C12</f>
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D12" s="15">
         <f>January!D12+February!D12+March!D12+April!D12+May!D12+June!D12+July!D12+August!D12+September!D12+October!D12+November!D12+December!D12</f>
-        <v>-60</v>
+        <v>-64</v>
       </c>
       <c r="E12" s="16" t="str">
         <f t="shared" si="0"/>
@@ -6062,7 +6113,7 @@
       </c>
       <c r="G12" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>0.28 : 1</v>
+        <v>0.3 : 1</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6071,11 +6122,11 @@
       </c>
       <c r="B13" s="19">
         <f>January!B13+February!B13+March!B13+April!B13+May!B13+June!B13+July!B13+August!B13+September!B13+October!B13+November!B13+December!B13</f>
-        <v>218</v>
+        <v>262</v>
       </c>
       <c r="C13" s="19">
         <f>January!C13+February!C13+March!C13+April!C13+May!C13+June!C13+July!C13+August!C13+September!C13+October!C13+November!C13+December!C13</f>
-        <v>240</v>
+        <v>284</v>
       </c>
       <c r="D13" s="19">
         <f>January!D13+February!D13+March!D13+April!D13+May!D13+June!D13+July!D13+August!D13+September!D13+October!D13+November!D13+December!D13</f>
@@ -6091,7 +6142,7 @@
       </c>
       <c r="G13" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>0.91 : 1</v>
+        <v>0.92 : 1</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6100,15 +6151,15 @@
       </c>
       <c r="B14" s="15">
         <f>January!B14+February!B14+March!B14+April!B14+May!B14+June!B14+July!B14+August!B14+September!B14+October!B14+November!B14+December!B14</f>
-        <v>547</v>
+        <v>644</v>
       </c>
       <c r="C14" s="15">
         <f>January!C14+February!C14+March!C14+April!C14+May!C14+June!C14+July!C14+August!C14+September!C14+October!C14+November!C14+December!C14</f>
-        <v>1177</v>
+        <v>1421</v>
       </c>
       <c r="D14" s="15">
         <f>January!D14+February!D14+March!D14+April!D14+May!D14+June!D14+July!D14+August!D14+September!D14+October!D14+November!D14+December!D14</f>
-        <v>-630</v>
+        <v>-777</v>
       </c>
       <c r="E14" s="16" t="str">
         <f t="shared" si="0"/>
@@ -6120,7 +6171,7 @@
       </c>
       <c r="G14" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>0.46 : 1</v>
+        <v>0.45 : 1</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6129,15 +6180,15 @@
       </c>
       <c r="B15" s="19">
         <f>January!B15+February!B15+March!B15+April!B15+May!B15+June!B15+July!B15+August!B15+September!B15+October!B15+November!B15+December!B15</f>
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="C15" s="19">
         <f>January!C15+February!C15+March!C15+April!C15+May!C15+June!C15+July!C15+August!C15+September!C15+October!C15+November!C15+December!C15</f>
-        <v>585</v>
+        <v>693</v>
       </c>
       <c r="D15" s="19">
         <f>January!D15+February!D15+March!D15+April!D15+May!D15+June!D15+July!D15+August!D15+September!D15+October!D15+November!D15+December!D15</f>
-        <v>-396</v>
+        <v>-474</v>
       </c>
       <c r="E15" s="20" t="str">
         <f t="shared" si="0"/>
@@ -6158,15 +6209,15 @@
       </c>
       <c r="B16" s="7">
         <f>January!B16+February!B16+March!B16+April!B16+May!B16+June!B16+July!B16+August!B16+September!B16+October!B16+November!B16+December!B16</f>
-        <v>259</v>
+        <v>311</v>
       </c>
       <c r="C16" s="7">
         <f>January!C16+February!C16+March!C16+April!C16+May!C16+June!C16+July!C16+August!C16+September!C16+October!C16+November!C16+December!C16</f>
-        <v>789</v>
+        <v>895</v>
       </c>
       <c r="D16" s="7">
         <f>January!D16+February!D16+March!D16+April!D16+May!D16+June!D16+July!D16+August!D16+September!D16+October!D16+November!D16+December!D16</f>
-        <v>-530</v>
+        <v>-584</v>
       </c>
       <c r="E16" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6178,7 +6229,7 @@
       </c>
       <c r="G16" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.33 : 1</v>
+        <v>0.35 : 1</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6187,15 +6238,15 @@
       </c>
       <c r="B17" s="11">
         <f>January!B17+February!B17+March!B17+April!B17+May!B17+June!B17+July!B17+August!B17+September!B17+October!B17+November!B17+December!B17</f>
-        <v>2686</v>
+        <v>3243</v>
       </c>
       <c r="C17" s="11">
         <f>January!C17+February!C17+March!C17+April!C17+May!C17+June!C17+July!C17+August!C17+September!C17+October!C17+November!C17+December!C17</f>
-        <v>1746</v>
+        <v>2094</v>
       </c>
       <c r="D17" s="11">
         <f>January!D17+February!D17+March!D17+April!D17+May!D17+June!D17+July!D17+August!D17+September!D17+October!D17+November!D17+December!D17</f>
-        <v>940</v>
+        <v>1149</v>
       </c>
       <c r="E17" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6207,7 +6258,7 @@
       </c>
       <c r="G17" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.54 : 1</v>
+        <v>1.55 : 1</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6216,15 +6267,15 @@
       </c>
       <c r="B18" s="7">
         <f>January!B18+February!B18+March!B18+April!B18+May!B18+June!B18+July!B18+August!B18+September!B18+October!B18+November!B18+December!B18</f>
-        <v>399</v>
+        <v>466</v>
       </c>
       <c r="C18" s="7">
         <f>January!C18+February!C18+March!C18+April!C18+May!C18+June!C18+July!C18+August!C18+September!C18+October!C18+November!C18+December!C18</f>
-        <v>330</v>
+        <v>402</v>
       </c>
       <c r="D18" s="7">
         <f>January!D18+February!D18+March!D18+April!D18+May!D18+June!D18+July!D18+August!D18+September!D18+October!D18+November!D18+December!D18</f>
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E18" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6236,7 +6287,7 @@
       </c>
       <c r="G18" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.21 : 1</v>
+        <v>1.16 : 1</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6245,15 +6296,15 @@
       </c>
       <c r="B19" s="11">
         <f>January!B19+February!B19+March!B19+April!B19+May!B19+June!B19+July!B19+August!B19+September!B19+October!B19+November!B19+December!B19</f>
-        <v>2207</v>
+        <v>2587</v>
       </c>
       <c r="C19" s="11">
         <f>January!C19+February!C19+March!C19+April!C19+May!C19+June!C19+July!C19+August!C19+September!C19+October!C19+November!C19+December!C19</f>
-        <v>1293</v>
+        <v>1641</v>
       </c>
       <c r="D19" s="11">
         <f>January!D19+February!D19+March!D19+April!D19+May!D19+June!D19+July!D19+August!D19+September!D19+October!D19+November!D19+December!D19</f>
-        <v>914</v>
+        <v>946</v>
       </c>
       <c r="E19" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6265,7 +6316,7 @@
       </c>
       <c r="G19" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.71 : 1</v>
+        <v>1.58 : 1</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6274,15 +6325,15 @@
       </c>
       <c r="B20" s="7">
         <f>January!B20+February!B20+March!B20+April!B20+May!B20+June!B20+July!B20+August!B20+September!B20+October!B20+November!B20+December!B20</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C20" s="7">
         <f>January!C20+February!C20+March!C20+April!C20+May!C20+June!C20+July!C20+August!C20+September!C20+October!C20+November!C20+December!C20</f>
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="D20" s="7">
         <f>January!D20+February!D20+March!D20+April!D20+May!D20+June!D20+July!D20+August!D20+September!D20+October!D20+November!D20+December!D20</f>
-        <v>-188</v>
+        <v>-221</v>
       </c>
       <c r="E20" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6294,7 +6345,7 @@
       </c>
       <c r="G20" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.05 : 1</v>
+        <v>0.04 : 1</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6303,15 +6354,15 @@
       </c>
       <c r="B21" s="11">
         <f>January!B21+February!B21+March!B21+April!B21+May!B21+June!B21+July!B21+August!B21+September!B21+October!B21+November!B21+December!B21</f>
-        <v>1958</v>
+        <v>2468</v>
       </c>
       <c r="C21" s="11">
         <f>January!C21+February!C21+March!C21+April!C21+May!C21+June!C21+July!C21+August!C21+September!C21+October!C21+November!C21+December!C21</f>
-        <v>1678</v>
+        <v>2039</v>
       </c>
       <c r="D21" s="11">
         <f>January!D21+February!D21+March!D21+April!D21+May!D21+June!D21+July!D21+August!D21+September!D21+October!D21+November!D21+December!D21</f>
-        <v>280</v>
+        <v>429</v>
       </c>
       <c r="E21" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6323,7 +6374,7 @@
       </c>
       <c r="G21" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.17 : 1</v>
+        <v>1.21 : 1</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6332,15 +6383,15 @@
       </c>
       <c r="B22" s="7">
         <f>January!B22+February!B22+March!B22+April!B22+May!B22+June!B22+July!B22+August!B22+September!B22+October!B22+November!B22+December!B22</f>
-        <v>377</v>
+        <v>445</v>
       </c>
       <c r="C22" s="7">
         <f>January!C22+February!C22+March!C22+April!C22+May!C22+June!C22+July!C22+August!C22+September!C22+October!C22+November!C22+December!C22</f>
-        <v>942</v>
+        <v>1126</v>
       </c>
       <c r="D22" s="7">
         <f>January!D22+February!D22+March!D22+April!D22+May!D22+June!D22+July!D22+August!D22+September!D22+October!D22+November!D22+December!D22</f>
-        <v>-565</v>
+        <v>-681</v>
       </c>
       <c r="E22" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6361,15 +6412,15 @@
       </c>
       <c r="B23" s="11">
         <f>January!B23+February!B23+March!B23+April!B23+May!B23+June!B23+July!B23+August!B23+September!B23+October!B23+November!B23+December!B23</f>
-        <v>2688</v>
+        <v>3167</v>
       </c>
       <c r="C23" s="11">
         <f>January!C23+February!C23+March!C23+April!C23+May!C23+June!C23+July!C23+August!C23+September!C23+October!C23+November!C23+December!C23</f>
-        <v>2394</v>
+        <v>2872</v>
       </c>
       <c r="D23" s="11">
         <f>January!D23+February!D23+March!D23+April!D23+May!D23+June!D23+July!D23+August!D23+September!D23+October!D23+November!D23+December!D23</f>
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E23" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6381,7 +6432,7 @@
       </c>
       <c r="G23" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.12 : 1</v>
+        <v>1.1 : 1</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6390,15 +6441,15 @@
       </c>
       <c r="B24" s="7">
         <f>January!B24+February!B24+March!B24+April!B24+May!B24+June!B24+July!B24+August!B24+September!B24+October!B24+November!B24+December!B24</f>
-        <v>7303</v>
+        <v>9023</v>
       </c>
       <c r="C24" s="7">
         <f>January!C24+February!C24+March!C24+April!C24+May!C24+June!C24+July!C24+August!C24+September!C24+October!C24+November!C24+December!C24</f>
-        <v>5642</v>
+        <v>6889</v>
       </c>
       <c r="D24" s="7">
         <f>January!D24+February!D24+March!D24+April!D24+May!D24+June!D24+July!D24+August!D24+September!D24+October!D24+November!D24+December!D24</f>
-        <v>1661</v>
+        <v>2134</v>
       </c>
       <c r="E24" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6410,7 +6461,7 @@
       </c>
       <c r="G24" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.29 : 1</v>
+        <v>1.31 : 1</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6419,15 +6470,15 @@
       </c>
       <c r="B25" s="11">
         <f>January!B25+February!B25+March!B25+April!B25+May!B25+June!B25+July!B25+August!B25+September!B25+October!B25+November!B25+December!B25</f>
-        <v>678</v>
+        <v>801</v>
       </c>
       <c r="C25" s="11">
         <f>January!C25+February!C25+March!C25+April!C25+May!C25+June!C25+July!C25+August!C25+September!C25+October!C25+November!C25+December!C25</f>
-        <v>1338</v>
+        <v>1607</v>
       </c>
       <c r="D25" s="11">
         <f>January!D25+February!D25+March!D25+April!D25+May!D25+June!D25+July!D25+August!D25+September!D25+October!D25+November!D25+December!D25</f>
-        <v>-660</v>
+        <v>-806</v>
       </c>
       <c r="E25" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6439,7 +6490,7 @@
       </c>
       <c r="G25" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.51 : 1</v>
+        <v>0.5 : 1</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6477,15 +6528,15 @@
       </c>
       <c r="B27" s="11">
         <f>January!B27+February!B27+March!B27+April!B27+May!B27+June!B27+July!B27+August!B27+September!B27+October!B27+November!B27+December!B27</f>
-        <v>763</v>
+        <v>988</v>
       </c>
       <c r="C27" s="11">
         <f>January!C27+February!C27+March!C27+April!C27+May!C27+June!C27+July!C27+August!C27+September!C27+October!C27+November!C27+December!C27</f>
-        <v>597</v>
+        <v>763</v>
       </c>
       <c r="D27" s="11">
         <f>January!D27+February!D27+March!D27+April!D27+May!D27+June!D27+July!D27+August!D27+September!D27+October!D27+November!D27+December!D27</f>
-        <v>166</v>
+        <v>225</v>
       </c>
       <c r="E27" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6497,7 +6548,7 @@
       </c>
       <c r="G27" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.28 : 1</v>
+        <v>1.29 : 1</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6506,15 +6557,15 @@
       </c>
       <c r="B28" s="7">
         <f>January!B28+February!B28+March!B28+April!B28+May!B28+June!B28+July!B28+August!B28+September!B28+October!B28+November!B28+December!B28</f>
-        <v>539</v>
+        <v>709</v>
       </c>
       <c r="C28" s="7">
         <f>January!C28+February!C28+March!C28+April!C28+May!C28+June!C28+July!C28+August!C28+September!C28+October!C28+November!C28+December!C28</f>
-        <v>496</v>
+        <v>605</v>
       </c>
       <c r="D28" s="7">
         <f>January!D28+February!D28+March!D28+April!D28+May!D28+June!D28+July!D28+August!D28+September!D28+October!D28+November!D28+December!D28</f>
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="E28" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6526,7 +6577,7 @@
       </c>
       <c r="G28" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.09 : 1</v>
+        <v>1.17 : 1</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6535,15 +6586,15 @@
       </c>
       <c r="B29" s="11">
         <f>January!B29+February!B29+March!B29+April!B29+May!B29+June!B29+July!B29+August!B29+September!B29+October!B29+November!B29+December!B29</f>
-        <v>3337</v>
+        <v>4127</v>
       </c>
       <c r="C29" s="11">
         <f>January!C29+February!C29+March!C29+April!C29+May!C29+June!C29+July!C29+August!C29+September!C29+October!C29+November!C29+December!C29</f>
-        <v>1960</v>
+        <v>2287</v>
       </c>
       <c r="D29" s="11">
         <f>January!D29+February!D29+March!D29+April!D29+May!D29+June!D29+July!D29+August!D29+September!D29+October!D29+November!D29+December!D29</f>
-        <v>1377</v>
+        <v>1840</v>
       </c>
       <c r="E29" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6555,7 +6606,7 @@
       </c>
       <c r="G29" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.7 : 1</v>
+        <v>1.8 : 1</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6564,15 +6615,15 @@
       </c>
       <c r="B30" s="7">
         <f>January!B30+February!B30+March!B30+April!B30+May!B30+June!B30+July!B30+August!B30+September!B30+October!B30+November!B30+December!B30</f>
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="C30" s="7">
         <f>January!C30+February!C30+March!C30+April!C30+May!C30+June!C30+July!C30+August!C30+September!C30+October!C30+November!C30+December!C30</f>
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="D30" s="7">
         <f>January!D30+February!D30+March!D30+April!D30+May!D30+June!D30+July!D30+August!D30+September!D30+October!D30+November!D30+December!D30</f>
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E30" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6584,7 +6635,7 @@
       </c>
       <c r="G30" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.49 : 1</v>
+        <v>1.13 : 1</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6593,15 +6644,15 @@
       </c>
       <c r="B31" s="11">
         <f>January!B31+February!B31+March!B31+April!B31+May!B31+June!B31+July!B31+August!B31+September!B31+October!B31+November!B31+December!B31</f>
-        <v>505</v>
+        <v>597</v>
       </c>
       <c r="C31" s="11">
         <f>January!C31+February!C31+March!C31+April!C31+May!C31+June!C31+July!C31+August!C31+September!C31+October!C31+November!C31+December!C31</f>
-        <v>1052</v>
+        <v>1299</v>
       </c>
       <c r="D31" s="11">
         <f>January!D31+February!D31+March!D31+April!D31+May!D31+June!D31+July!D31+August!D31+September!D31+October!D31+November!D31+December!D31</f>
-        <v>-547</v>
+        <v>-702</v>
       </c>
       <c r="E31" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6613,7 +6664,7 @@
       </c>
       <c r="G31" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.48 : 1</v>
+        <v>0.46 : 1</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6622,15 +6673,15 @@
       </c>
       <c r="B32" s="7">
         <f>January!B32+February!B32+March!B32+April!B32+May!B32+June!B32+July!B32+August!B32+September!B32+October!B32+November!B32+December!B32</f>
-        <v>1730</v>
+        <v>2041</v>
       </c>
       <c r="C32" s="7">
         <f>January!C32+February!C32+March!C32+April!C32+May!C32+June!C32+July!C32+August!C32+September!C32+October!C32+November!C32+December!C32</f>
-        <v>2077</v>
+        <v>2534</v>
       </c>
       <c r="D32" s="7">
         <f>January!D32+February!D32+March!D32+April!D32+May!D32+June!D32+July!D32+August!D32+September!D32+October!D32+November!D32+December!D32</f>
-        <v>-347</v>
+        <v>-493</v>
       </c>
       <c r="E32" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6642,7 +6693,7 @@
       </c>
       <c r="G32" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.83 : 1</v>
+        <v>0.81 : 1</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6651,15 +6702,15 @@
       </c>
       <c r="B33" s="11">
         <f>January!B33+February!B33+March!B33+April!B33+May!B33+June!B33+July!B33+August!B33+September!B33+October!B33+November!B33+December!B33</f>
-        <v>1453</v>
+        <v>1748</v>
       </c>
       <c r="C33" s="11">
         <f>January!C33+February!C33+March!C33+April!C33+May!C33+June!C33+July!C33+August!C33+September!C33+October!C33+November!C33+December!C33</f>
-        <v>1323</v>
+        <v>1622</v>
       </c>
       <c r="D33" s="11">
         <f>January!D33+February!D33+March!D33+April!D33+May!D33+June!D33+July!D33+August!D33+September!D33+October!D33+November!D33+December!D33</f>
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E33" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6671,7 +6722,7 @@
       </c>
       <c r="G33" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.1 : 1</v>
+        <v>1.08 : 1</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6680,15 +6731,15 @@
       </c>
       <c r="B34" s="7">
         <f>January!B34+February!B34+March!B34+April!B34+May!B34+June!B34+July!B34+August!B34+September!B34+October!B34+November!B34+December!B34</f>
-        <v>724</v>
+        <v>867</v>
       </c>
       <c r="C34" s="7">
         <f>January!C34+February!C34+March!C34+April!C34+May!C34+June!C34+July!C34+August!C34+September!C34+October!C34+November!C34+December!C34</f>
-        <v>456</v>
+        <v>581</v>
       </c>
       <c r="D34" s="7">
         <f>January!D34+February!D34+March!D34+April!D34+May!D34+June!D34+July!D34+August!D34+September!D34+October!D34+November!D34+December!D34</f>
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="E34" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6700,7 +6751,7 @@
       </c>
       <c r="G34" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.59 : 1</v>
+        <v>1.49 : 1</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6709,15 +6760,15 @@
       </c>
       <c r="B35" s="11">
         <f>January!B35+February!B35+March!B35+April!B35+May!B35+June!B35+July!B35+August!B35+September!B35+October!B35+November!B35+December!B35</f>
-        <v>3958</v>
+        <v>4883</v>
       </c>
       <c r="C35" s="11">
         <f>January!C35+February!C35+March!C35+April!C35+May!C35+June!C35+July!C35+August!C35+September!C35+October!C35+November!C35+December!C35</f>
-        <v>6023</v>
+        <v>7460</v>
       </c>
       <c r="D35" s="11">
         <f>January!D35+February!D35+March!D35+April!D35+May!D35+June!D35+July!D35+August!D35+September!D35+October!D35+November!D35+December!D35</f>
-        <v>-2065</v>
+        <v>-2577</v>
       </c>
       <c r="E35" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6729,7 +6780,7 @@
       </c>
       <c r="G35" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.66 : 1</v>
+        <v>0.65 : 1</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6738,15 +6789,15 @@
       </c>
       <c r="B36" s="7">
         <f>January!B36+February!B36+March!B36+April!B36+May!B36+June!B36+July!B36+August!B36+September!B36+October!B36+November!B36+December!B36</f>
-        <v>690</v>
+        <v>850</v>
       </c>
       <c r="C36" s="7">
         <f>January!C36+February!C36+March!C36+April!C36+May!C36+June!C36+July!C36+August!C36+September!C36+October!C36+November!C36+December!C36</f>
-        <v>2224</v>
+        <v>2733</v>
       </c>
       <c r="D36" s="7">
         <f>January!D36+February!D36+March!D36+April!D36+May!D36+June!D36+July!D36+August!D36+September!D36+October!D36+November!D36+December!D36</f>
-        <v>-1534</v>
+        <v>-1883</v>
       </c>
       <c r="E36" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6767,15 +6818,15 @@
       </c>
       <c r="B37" s="11">
         <f>January!B37+February!B37+March!B37+April!B37+May!B37+June!B37+July!B37+August!B37+September!B37+October!B37+November!B37+December!B37</f>
-        <v>2337</v>
+        <v>2858</v>
       </c>
       <c r="C37" s="11">
         <f>January!C37+February!C37+March!C37+April!C37+May!C37+June!C37+July!C37+August!C37+September!C37+October!C37+November!C37+December!C37</f>
-        <v>1678</v>
+        <v>1930</v>
       </c>
       <c r="D37" s="11">
         <f>January!D37+February!D37+March!D37+April!D37+May!D37+June!D37+July!D37+August!D37+September!D37+October!D37+November!D37+December!D37</f>
-        <v>659</v>
+        <v>928</v>
       </c>
       <c r="E37" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6787,7 +6838,7 @@
       </c>
       <c r="G37" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.39 : 1</v>
+        <v>1.48 : 1</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6796,15 +6847,15 @@
       </c>
       <c r="B38" s="7">
         <f>January!B38+February!B38+March!B38+April!B38+May!B38+June!B38+July!B38+August!B38+September!B38+October!B38+November!B38+December!B38</f>
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="C38" s="7">
         <f>January!C38+February!C38+March!C38+April!C38+May!C38+June!C38+July!C38+August!C38+September!C38+October!C38+November!C38+December!C38</f>
-        <v>803</v>
+        <v>1026</v>
       </c>
       <c r="D38" s="7">
         <f>January!D38+February!D38+March!D38+April!D38+May!D38+June!D38+July!D38+August!D38+September!D38+October!D38+November!D38+December!D38</f>
-        <v>-669</v>
+        <v>-859</v>
       </c>
       <c r="E38" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6816,7 +6867,7 @@
       </c>
       <c r="G38" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.17 : 1</v>
+        <v>0.16 : 1</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6829,11 +6880,11 @@
       </c>
       <c r="C39" s="11">
         <f>January!C39+February!C39+March!C39+April!C39+May!C39+June!C39+July!C39+August!C39+September!C39+October!C39+November!C39+December!C39</f>
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="D39" s="11">
         <f>January!D39+February!D39+March!D39+April!D39+May!D39+June!D39+July!D39+August!D39+September!D39+October!D39+November!D39+December!D39</f>
-        <v>-207</v>
+        <v>-243</v>
       </c>
       <c r="E39" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6845,7 +6896,7 @@
       </c>
       <c r="G39" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.27 : 1</v>
+        <v>0.24 : 1</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6854,15 +6905,15 @@
       </c>
       <c r="B40" s="23">
         <f>January!B40+February!B40+March!B40+April!B40+May!B40+June!B40+July!B40+August!B40+September!B40+October!B40+November!B40+December!B40</f>
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C40" s="23">
         <f>January!C40+February!C40+March!C40+April!C40+May!C40+June!C40+July!C40+August!C40+September!C40+October!C40+November!C40+December!C40</f>
-        <v>506</v>
+        <v>563</v>
       </c>
       <c r="D40" s="23">
         <f>January!D40+February!D40+March!D40+April!D40+May!D40+June!D40+July!D40+August!D40+September!D40+October!D40+November!D40+December!D40</f>
-        <v>-62</v>
+        <v>-115</v>
       </c>
       <c r="E40" s="24" t="str">
         <f t="shared" si="0"/>
@@ -6874,7 +6925,7 @@
       </c>
       <c r="G40" s="25" t="str">
         <f t="shared" si="2"/>
-        <v>0.88 : 1</v>
+        <v>0.8 : 1</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6887,11 +6938,11 @@
       </c>
       <c r="C41" s="27">
         <f>January!C41+February!C41+March!C41+April!C41+May!C41+June!C41+July!C41+August!C41+September!C41+October!C41+November!C41+December!C41</f>
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D41" s="27">
         <f>January!D41+February!D41+March!D41+April!D41+May!D41+June!D41+July!D41+August!D41+September!D41+October!D41+November!D41+December!D41</f>
-        <v>-66</v>
+        <v>-76</v>
       </c>
       <c r="E41" s="28" t="str">
         <f t="shared" si="0"/>
@@ -6903,7 +6954,7 @@
       </c>
       <c r="G41" s="29" t="str">
         <f t="shared" si="2"/>
-        <v>0.26 : 1</v>
+        <v>0.23 : 1</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6916,11 +6967,11 @@
       </c>
       <c r="C42" s="23">
         <f>January!C42+February!C42+March!C42+April!C42+May!C42+June!C42+July!C42+August!C42+September!C42+October!C42+November!C42+December!C42</f>
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D42" s="23">
         <f>January!D42+February!D42+March!D42+April!D42+May!D42+June!D42+July!D42+August!D42+September!D42+October!D42+November!D42+December!D42</f>
-        <v>-72</v>
+        <v>-75</v>
       </c>
       <c r="E42" s="24" t="str">
         <f t="shared" si="0"/>
@@ -6932,7 +6983,7 @@
       </c>
       <c r="G42" s="25" t="str">
         <f t="shared" si="2"/>
-        <v>0.41 : 1</v>
+        <v>0.4 : 1</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6941,15 +6992,15 @@
       </c>
       <c r="B43" s="27">
         <f>January!B43+February!B43+March!B43+April!B43+May!B43+June!B43+July!B43+August!B43+September!B43+October!B43+November!B43+December!B43</f>
-        <v>628</v>
+        <v>767</v>
       </c>
       <c r="C43" s="27">
         <f>January!C43+February!C43+March!C43+April!C43+May!C43+June!C43+July!C43+August!C43+September!C43+October!C43+November!C43+December!C43</f>
-        <v>403</v>
+        <v>480</v>
       </c>
       <c r="D43" s="27">
         <f>January!D43+February!D43+March!D43+April!D43+May!D43+June!D43+July!D43+August!D43+September!D43+October!D43+November!D43+December!D43</f>
-        <v>225</v>
+        <v>287</v>
       </c>
       <c r="E43" s="28" t="str">
         <f t="shared" si="0"/>
@@ -6961,7 +7012,7 @@
       </c>
       <c r="G43" s="29" t="str">
         <f t="shared" si="2"/>
-        <v>1.56 : 1</v>
+        <v>1.6 : 1</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6970,15 +7021,15 @@
       </c>
       <c r="B44" s="7">
         <f>January!B44+February!B44+March!B44+April!B44+May!B44+June!B44+July!B44+August!B44+September!B44+October!B44+November!B44+December!B44</f>
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="C44" s="7">
         <f>January!C44+February!C44+March!C44+April!C44+May!C44+June!C44+July!C44+August!C44+September!C44+October!C44+November!C44+December!C44</f>
-        <v>695</v>
+        <v>888</v>
       </c>
       <c r="D44" s="7">
         <f>January!D44+February!D44+March!D44+April!D44+May!D44+June!D44+July!D44+August!D44+September!D44+October!D44+November!D44+December!D44</f>
-        <v>-452</v>
+        <v>-577</v>
       </c>
       <c r="E44" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6999,15 +7050,15 @@
       </c>
       <c r="B45" s="11">
         <f>January!B45+February!B45+March!B45+April!B45+May!B45+June!B45+July!B45+August!B45+September!B45+October!B45+November!B45+December!B45</f>
-        <v>2179</v>
+        <v>2649</v>
       </c>
       <c r="C45" s="11">
         <f>January!C45+February!C45+March!C45+April!C45+May!C45+June!C45+July!C45+August!C45+September!C45+October!C45+November!C45+December!C45</f>
-        <v>2425</v>
+        <v>2905</v>
       </c>
       <c r="D45" s="11">
         <f>January!D45+February!D45+March!D45+April!D45+May!D45+June!D45+July!D45+August!D45+September!D45+October!D45+November!D45+December!D45</f>
-        <v>-246</v>
+        <v>-256</v>
       </c>
       <c r="E45" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7019,7 +7070,7 @@
       </c>
       <c r="G45" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.9 : 1</v>
+        <v>0.91 : 1</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7028,15 +7079,15 @@
       </c>
       <c r="B46" s="7">
         <f>January!B46+February!B46+March!B46+April!B46+May!B46+June!B46+July!B46+August!B46+September!B46+October!B46+November!B46+December!B46</f>
-        <v>3642</v>
+        <v>4368</v>
       </c>
       <c r="C46" s="7">
         <f>January!C46+February!C46+March!C46+April!C46+May!C46+June!C46+July!C46+August!C46+September!C46+October!C46+November!C46+December!C46</f>
-        <v>3047</v>
+        <v>3550</v>
       </c>
       <c r="D46" s="7">
         <f>January!D46+February!D46+March!D46+April!D46+May!D46+June!D46+July!D46+August!D46+September!D46+October!D46+November!D46+December!D46</f>
-        <v>595</v>
+        <v>818</v>
       </c>
       <c r="E46" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7048,7 +7099,7 @@
       </c>
       <c r="G46" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.2 : 1</v>
+        <v>1.23 : 1</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7057,15 +7108,15 @@
       </c>
       <c r="B47" s="11">
         <f>January!B47+February!B47+March!B47+April!B47+May!B47+June!B47+July!B47+August!B47+September!B47+October!B47+November!B47+December!B47</f>
-        <v>960</v>
+        <v>1124</v>
       </c>
       <c r="C47" s="11">
         <f>January!C47+February!C47+March!C47+April!C47+May!C47+June!C47+July!C47+August!C47+September!C47+October!C47+November!C47+December!C47</f>
-        <v>2456</v>
+        <v>2947</v>
       </c>
       <c r="D47" s="11">
         <f>January!D47+February!D47+March!D47+April!D47+May!D47+June!D47+July!D47+August!D47+September!D47+October!D47+November!D47+December!D47</f>
-        <v>-1496</v>
+        <v>-1823</v>
       </c>
       <c r="E47" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7077,7 +7128,7 @@
       </c>
       <c r="G47" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.39 : 1</v>
+        <v>0.38 : 1</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7086,15 +7137,15 @@
       </c>
       <c r="B48" s="7">
         <f>January!B48+February!B48+March!B48+April!B48+May!B48+June!B48+July!B48+August!B48+September!B48+October!B48+November!B48+December!B48</f>
-        <v>1850</v>
+        <v>2129</v>
       </c>
       <c r="C48" s="7">
         <f>January!C48+February!C48+March!C48+April!C48+May!C48+June!C48+July!C48+August!C48+September!C48+October!C48+November!C48+December!C48</f>
-        <v>1120</v>
+        <v>1300</v>
       </c>
       <c r="D48" s="7">
         <f>January!D48+February!D48+March!D48+April!D48+May!D48+June!D48+July!D48+August!D48+September!D48+October!D48+November!D48+December!D48</f>
-        <v>730</v>
+        <v>829</v>
       </c>
       <c r="E48" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7106,7 +7157,7 @@
       </c>
       <c r="G48" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.65 : 1</v>
+        <v>1.64 : 1</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7115,15 +7166,15 @@
       </c>
       <c r="B49" s="11">
         <f>January!B49+February!B49+March!B49+April!B49+May!B49+June!B49+July!B49+August!B49+September!B49+October!B49+November!B49+December!B49</f>
-        <v>3735</v>
+        <v>4772</v>
       </c>
       <c r="C49" s="11">
         <f>January!C49+February!C49+March!C49+April!C49+May!C49+June!C49+July!C49+August!C49+September!C49+October!C49+November!C49+December!C49</f>
-        <v>2300</v>
+        <v>2814</v>
       </c>
       <c r="D49" s="11">
         <f>January!D49+February!D49+March!D49+April!D49+May!D49+June!D49+July!D49+August!D49+September!D49+October!D49+November!D49+December!D49</f>
-        <v>1435</v>
+        <v>1958</v>
       </c>
       <c r="E49" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7135,7 +7186,7 @@
       </c>
       <c r="G49" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.62 : 1</v>
+        <v>1.7 : 1</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7144,15 +7195,15 @@
       </c>
       <c r="B50" s="7">
         <f>January!B50+February!B50+March!B50+April!B50+May!B50+June!B50+July!B50+August!B50+September!B50+October!B50+November!B50+December!B50</f>
-        <v>513</v>
+        <v>610</v>
       </c>
       <c r="C50" s="7">
         <f>January!C50+February!C50+March!C50+April!C50+May!C50+June!C50+July!C50+August!C50+September!C50+October!C50+November!C50+December!C50</f>
-        <v>689</v>
+        <v>835</v>
       </c>
       <c r="D50" s="7">
         <f>January!D50+February!D50+March!D50+April!D50+May!D50+June!D50+July!D50+August!D50+September!D50+October!D50+November!D50+December!D50</f>
-        <v>-176</v>
+        <v>-225</v>
       </c>
       <c r="E50" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7164,7 +7215,7 @@
       </c>
       <c r="G50" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.74 : 1</v>
+        <v>0.73 : 1</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7173,15 +7224,15 @@
       </c>
       <c r="B51" s="11">
         <f>January!B51+February!B51+March!B51+April!B51+May!B51+June!B51+July!B51+August!B51+September!B51+October!B51+November!B51+December!B51</f>
-        <v>2021</v>
+        <v>2334</v>
       </c>
       <c r="C51" s="11">
         <f>January!C51+February!C51+March!C51+April!C51+May!C51+June!C51+July!C51+August!C51+September!C51+October!C51+November!C51+December!C51</f>
-        <v>1487</v>
+        <v>1802</v>
       </c>
       <c r="D51" s="11">
         <f>January!D51+February!D51+March!D51+April!D51+May!D51+June!D51+July!D51+August!D51+September!D51+October!D51+November!D51+December!D51</f>
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E51" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7193,7 +7244,7 @@
       </c>
       <c r="G51" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.36 : 1</v>
+        <v>1.3 : 1</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7202,15 +7253,15 @@
       </c>
       <c r="B52" s="7">
         <f>January!B52+February!B52+March!B52+April!B52+May!B52+June!B52+July!B52+August!B52+September!B52+October!B52+November!B52+December!B52</f>
-        <v>543</v>
+        <v>616</v>
       </c>
       <c r="C52" s="7">
         <f>January!C52+February!C52+March!C52+April!C52+May!C52+June!C52+July!C52+August!C52+September!C52+October!C52+November!C52+December!C52</f>
-        <v>891</v>
+        <v>1105</v>
       </c>
       <c r="D52" s="7">
         <f>January!D52+February!D52+March!D52+April!D52+May!D52+June!D52+July!D52+August!D52+September!D52+October!D52+November!D52+December!D52</f>
-        <v>-348</v>
+        <v>-489</v>
       </c>
       <c r="E52" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7222,7 +7273,7 @@
       </c>
       <c r="G52" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.61 : 1</v>
+        <v>0.56 : 1</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7231,15 +7282,15 @@
       </c>
       <c r="B53" s="11">
         <f>January!B53+February!B53+March!B53+April!B53+May!B53+June!B53+July!B53+August!B53+September!B53+October!B53+November!B53+December!B53</f>
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="C53" s="11">
         <f>January!C53+February!C53+March!C53+April!C53+May!C53+June!C53+July!C53+August!C53+September!C53+October!C53+November!C53+December!C53</f>
-        <v>1026</v>
+        <v>1223</v>
       </c>
       <c r="D53" s="11">
         <f>January!D53+February!D53+March!D53+April!D53+May!D53+June!D53+July!D53+August!D53+September!D53+October!D53+November!D53+December!D53</f>
-        <v>-915</v>
+        <v>-1093</v>
       </c>
       <c r="E53" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7260,15 +7311,15 @@
       </c>
       <c r="B54" s="31">
         <f>January!B54+February!B54+March!B54+April!B54+May!B54+June!B54+July!B54+August!B54+September!B54+October!B54+November!B54+December!B54</f>
-        <v>1683</v>
+        <v>1985</v>
       </c>
       <c r="C54" s="31">
         <f>January!C54+February!C54+March!C54+April!C54+May!C54+June!C54+July!C54+August!C54+September!C54+October!C54+November!C54+December!C54</f>
-        <v>845</v>
+        <v>1018</v>
       </c>
       <c r="D54" s="31">
         <f>January!D54+February!D54+March!D54+April!D54+May!D54+June!D54+July!D54+August!D54+September!D54+October!D54+November!D54+December!D54</f>
-        <v>838</v>
+        <v>967</v>
       </c>
       <c r="E54" s="32" t="str">
         <f t="shared" si="0"/>
@@ -7280,7 +7331,7 @@
       </c>
       <c r="G54" s="33" t="str">
         <f t="shared" si="2"/>
-        <v>1.99 : 1</v>
+        <v>1.95 : 1</v>
       </c>
     </row>
   </sheetData>
@@ -10900,108 +10951,204 @@
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8"/>
+      <c r="B2" s="7">
+        <v>1251</v>
+      </c>
+      <c r="C2" s="7">
+        <v>970</v>
+      </c>
+      <c r="D2" s="7">
+        <v>281</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F2" s="8"/>
-      <c r="G2" s="9"/>
+      <c r="G2" s="9" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="12"/>
+      <c r="B3" s="11">
+        <v>501</v>
+      </c>
+      <c r="C3" s="11">
+        <v>401</v>
+      </c>
+      <c r="D3" s="11">
+        <v>100</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F3" s="12"/>
-      <c r="G3" s="13"/>
+      <c r="G3" s="13" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
+      <c r="B4" s="7">
+        <v>955</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1109</v>
+      </c>
+      <c r="D4" s="7">
+        <v>-154</v>
+      </c>
       <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="9"/>
+      <c r="F4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
+      <c r="B5" s="11">
+        <v>19</v>
+      </c>
+      <c r="C5" s="11">
+        <v>108</v>
+      </c>
+      <c r="D5" s="11">
+        <v>-89</v>
+      </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13"/>
+      <c r="F5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+      <c r="B6" s="7">
+        <v>891</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1110</v>
+      </c>
+      <c r="D6" s="7">
+        <v>-219</v>
+      </c>
       <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9"/>
+      <c r="F6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12"/>
+      <c r="B7" s="11">
+        <v>409</v>
+      </c>
+      <c r="C7" s="11">
+        <v>159</v>
+      </c>
+      <c r="D7" s="11">
+        <v>250</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="13"/>
+      <c r="G7" s="13" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+      <c r="B8" s="7">
+        <v>87</v>
+      </c>
+      <c r="C8" s="7">
+        <v>125</v>
+      </c>
+      <c r="D8" s="7">
+        <v>-38</v>
+      </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9"/>
+      <c r="F8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12"/>
+      <c r="B9" s="11">
+        <v>47</v>
+      </c>
+      <c r="C9" s="11">
+        <v>40</v>
+      </c>
+      <c r="D9" s="11">
+        <v>7</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="13"/>
+      <c r="G9" s="13" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="B10" s="7">
+        <v>0</v>
+      </c>
+      <c r="C10" s="7">
+        <v>10</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-10</v>
+      </c>
       <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9"/>
+      <c r="F10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
+      <c r="B11" s="11">
+        <v>0</v>
+      </c>
+      <c r="C11" s="11">
+        <v>0</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0</v>
+      </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
@@ -11010,163 +11157,307 @@
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
+      <c r="B12" s="15">
+        <v>4</v>
+      </c>
+      <c r="C12" s="15">
+        <v>8</v>
+      </c>
+      <c r="D12" s="15">
+        <v>-4</v>
+      </c>
       <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17"/>
+      <c r="F12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
+      <c r="B13" s="19">
+        <v>44</v>
+      </c>
+      <c r="C13" s="19">
+        <v>44</v>
+      </c>
+      <c r="D13" s="19">
+        <v>0</v>
+      </c>
       <c r="E13" s="20"/>
       <c r="F13" s="20"/>
-      <c r="G13" s="21"/>
+      <c r="G13" s="21" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
+      <c r="B14" s="15">
+        <v>97</v>
+      </c>
+      <c r="C14" s="15">
+        <v>244</v>
+      </c>
+      <c r="D14" s="15">
+        <v>-147</v>
+      </c>
       <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="17"/>
+      <c r="F14" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
+      <c r="B15" s="19">
+        <v>30</v>
+      </c>
+      <c r="C15" s="19">
+        <v>108</v>
+      </c>
+      <c r="D15" s="19">
+        <v>-78</v>
+      </c>
       <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="21"/>
+      <c r="F15" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
+      <c r="B16" s="7">
+        <v>52</v>
+      </c>
+      <c r="C16" s="7">
+        <v>106</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-54</v>
+      </c>
       <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="9"/>
+      <c r="F16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="12"/>
+      <c r="B17" s="11">
+        <v>557</v>
+      </c>
+      <c r="C17" s="11">
+        <v>348</v>
+      </c>
+      <c r="D17" s="11">
+        <v>209</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F17" s="12"/>
-      <c r="G17" s="13"/>
+      <c r="G17" s="13" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
+      <c r="B18" s="7">
+        <v>67</v>
+      </c>
+      <c r="C18" s="7">
+        <v>72</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-5</v>
+      </c>
       <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="9"/>
+      <c r="F18" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="12"/>
+      <c r="B19" s="11">
+        <v>380</v>
+      </c>
+      <c r="C19" s="11">
+        <v>348</v>
+      </c>
+      <c r="D19" s="11">
+        <v>32</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="13"/>
+      <c r="G19" s="13" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
+      <c r="B20" s="7">
+        <v>1</v>
+      </c>
+      <c r="C20" s="7">
+        <v>34</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-33</v>
+      </c>
       <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="9"/>
+      <c r="F20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="12"/>
+      <c r="B21" s="11">
+        <v>510</v>
+      </c>
+      <c r="C21" s="11">
+        <v>361</v>
+      </c>
+      <c r="D21" s="11">
+        <v>149</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="13"/>
+      <c r="G21" s="13" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+      <c r="B22" s="7">
+        <v>68</v>
+      </c>
+      <c r="C22" s="7">
+        <v>184</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-116</v>
+      </c>
       <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="9"/>
+      <c r="F22" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="12"/>
+      <c r="B23" s="11">
+        <v>479</v>
+      </c>
+      <c r="C23" s="11">
+        <v>478</v>
+      </c>
+      <c r="D23" s="11">
+        <v>1</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="13"/>
+      <c r="G23" s="13" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8"/>
+      <c r="B24" s="7">
+        <v>1720</v>
+      </c>
+      <c r="C24" s="7">
+        <v>1247</v>
+      </c>
+      <c r="D24" s="7">
+        <v>473</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
+      <c r="G24" s="9" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="B25" s="11">
+        <v>123</v>
+      </c>
+      <c r="C25" s="11">
+        <v>269</v>
+      </c>
+      <c r="D25" s="11">
+        <v>-146</v>
+      </c>
       <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="13"/>
+      <c r="F25" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
+      <c r="B26" s="7">
+        <v>0</v>
+      </c>
+      <c r="C26" s="7">
+        <v>0</v>
+      </c>
+      <c r="D26" s="7">
+        <v>0</v>
+      </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
@@ -11175,309 +11466,589 @@
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="12"/>
+      <c r="B27" s="11">
+        <v>225</v>
+      </c>
+      <c r="C27" s="11">
+        <v>166</v>
+      </c>
+      <c r="D27" s="11">
+        <v>59</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F27" s="12"/>
-      <c r="G27" s="13"/>
+      <c r="G27" s="13" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="8"/>
+      <c r="B28" s="7">
+        <v>170</v>
+      </c>
+      <c r="C28" s="7">
+        <v>109</v>
+      </c>
+      <c r="D28" s="7">
+        <v>61</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F28" s="8"/>
-      <c r="G28" s="9"/>
+      <c r="G28" s="9" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="12"/>
+      <c r="B29" s="11">
+        <v>790</v>
+      </c>
+      <c r="C29" s="11">
+        <v>327</v>
+      </c>
+      <c r="D29" s="11">
+        <v>463</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F29" s="12"/>
-      <c r="G29" s="13"/>
+      <c r="G29" s="13" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
+      <c r="B30" s="7">
+        <v>25</v>
+      </c>
+      <c r="C30" s="7">
+        <v>50</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-25</v>
+      </c>
       <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="9"/>
+      <c r="F30" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
+      <c r="B31" s="11">
+        <v>92</v>
+      </c>
+      <c r="C31" s="11">
+        <v>247</v>
+      </c>
+      <c r="D31" s="11">
+        <v>-155</v>
+      </c>
       <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="13"/>
+      <c r="F31" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
+      <c r="B32" s="7">
+        <v>311</v>
+      </c>
+      <c r="C32" s="7">
+        <v>457</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-146</v>
+      </c>
       <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="9"/>
+      <c r="F32" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
+      <c r="B33" s="11">
+        <v>295</v>
+      </c>
+      <c r="C33" s="11">
+        <v>299</v>
+      </c>
+      <c r="D33" s="11">
+        <v>-4</v>
+      </c>
       <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="13"/>
+      <c r="F33" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="8"/>
+      <c r="B34" s="7">
+        <v>143</v>
+      </c>
+      <c r="C34" s="7">
+        <v>125</v>
+      </c>
+      <c r="D34" s="7">
+        <v>18</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F34" s="8"/>
-      <c r="G34" s="9"/>
+      <c r="G34" s="9" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
+      <c r="B35" s="11">
+        <v>925</v>
+      </c>
+      <c r="C35" s="11">
+        <v>1437</v>
+      </c>
+      <c r="D35" s="11">
+        <v>-512</v>
+      </c>
       <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="13"/>
+      <c r="F35" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
+      <c r="B36" s="7">
+        <v>160</v>
+      </c>
+      <c r="C36" s="7">
+        <v>509</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-349</v>
+      </c>
       <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="9"/>
+      <c r="F36" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="12"/>
+      <c r="B37" s="11">
+        <v>521</v>
+      </c>
+      <c r="C37" s="11">
+        <v>252</v>
+      </c>
+      <c r="D37" s="11">
+        <v>269</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="13"/>
+      <c r="G37" s="13" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
+      <c r="B38" s="7">
+        <v>33</v>
+      </c>
+      <c r="C38" s="7">
+        <v>223</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-190</v>
+      </c>
       <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="9"/>
+      <c r="F38" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
+      <c r="B39" s="11">
+        <v>0</v>
+      </c>
+      <c r="C39" s="11">
+        <v>36</v>
+      </c>
+      <c r="D39" s="11">
+        <v>-36</v>
+      </c>
       <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="13"/>
+      <c r="F39" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
+      <c r="B40" s="23">
+        <v>4</v>
+      </c>
+      <c r="C40" s="23">
+        <v>57</v>
+      </c>
+      <c r="D40" s="23">
+        <v>-53</v>
+      </c>
       <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="25"/>
+      <c r="F40" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="25" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
+      <c r="B41" s="27">
+        <v>0</v>
+      </c>
+      <c r="C41" s="27">
+        <v>10</v>
+      </c>
+      <c r="D41" s="27">
+        <v>-10</v>
+      </c>
       <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="29"/>
+      <c r="F41" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
+      <c r="B42" s="23">
+        <v>0</v>
+      </c>
+      <c r="C42" s="23">
+        <v>3</v>
+      </c>
+      <c r="D42" s="23">
+        <v>-3</v>
+      </c>
       <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="25"/>
+      <c r="F42" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="25" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="28"/>
+      <c r="B43" s="27">
+        <v>139</v>
+      </c>
+      <c r="C43" s="27">
+        <v>77</v>
+      </c>
+      <c r="D43" s="27">
+        <v>62</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>8</v>
+      </c>
       <c r="F43" s="28"/>
-      <c r="G43" s="29"/>
+      <c r="G43" s="29" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
+      <c r="B44" s="7">
+        <v>68</v>
+      </c>
+      <c r="C44" s="7">
+        <v>193</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-125</v>
+      </c>
       <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="9"/>
+      <c r="F44" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
+      <c r="B45" s="11">
+        <v>470</v>
+      </c>
+      <c r="C45" s="11">
+        <v>480</v>
+      </c>
+      <c r="D45" s="11">
+        <v>-10</v>
+      </c>
       <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="13"/>
+      <c r="F45" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="8"/>
+      <c r="B46" s="7">
+        <v>726</v>
+      </c>
+      <c r="C46" s="7">
+        <v>503</v>
+      </c>
+      <c r="D46" s="7">
+        <v>223</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F46" s="8"/>
-      <c r="G46" s="9"/>
+      <c r="G46" s="9" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
+      <c r="B47" s="11">
+        <v>164</v>
+      </c>
+      <c r="C47" s="11">
+        <v>491</v>
+      </c>
+      <c r="D47" s="11">
+        <v>-327</v>
+      </c>
       <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="13"/>
+      <c r="F47" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="8"/>
+      <c r="B48" s="7">
+        <v>279</v>
+      </c>
+      <c r="C48" s="7">
+        <v>180</v>
+      </c>
+      <c r="D48" s="7">
+        <v>99</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F48" s="8"/>
-      <c r="G48" s="9"/>
+      <c r="G48" s="9" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="12"/>
+      <c r="B49" s="11">
+        <v>1037</v>
+      </c>
+      <c r="C49" s="11">
+        <v>514</v>
+      </c>
+      <c r="D49" s="11">
+        <v>523</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="13"/>
+      <c r="G49" s="13" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
+      <c r="B50" s="7">
+        <v>97</v>
+      </c>
+      <c r="C50" s="7">
+        <v>146</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-49</v>
+      </c>
       <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="9"/>
+      <c r="F50" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
+      <c r="B51" s="11">
+        <v>313</v>
+      </c>
+      <c r="C51" s="11">
+        <v>315</v>
+      </c>
+      <c r="D51" s="11">
+        <v>-2</v>
+      </c>
       <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="13"/>
+      <c r="F51" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
+      <c r="B52" s="7">
+        <v>73</v>
+      </c>
+      <c r="C52" s="7">
+        <v>214</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-141</v>
+      </c>
       <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="9"/>
+      <c r="F52" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
+      <c r="B53" s="11">
+        <v>19</v>
+      </c>
+      <c r="C53" s="11">
+        <v>197</v>
+      </c>
+      <c r="D53" s="11">
+        <v>-178</v>
+      </c>
       <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="13"/>
+      <c r="F53" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" s="13" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B54" s="31"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="32"/>
+      <c r="B54" s="31">
+        <v>302</v>
+      </c>
+      <c r="C54" s="31">
+        <v>173</v>
+      </c>
+      <c r="D54" s="31">
+        <v>129</v>
+      </c>
+      <c r="E54" s="32" t="s">
+        <v>8</v>
+      </c>
       <c r="F54" s="32"/>
-      <c r="G54" s="33"/>
+      <c r="G54" s="33" t="s">
+        <v>209</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-000004000000}"/>

--- a/statistics_files/2026/2026_99_ga_net_borrower_lender.xlsx
+++ b/statistics_files/2026/2026_99_ga_net_borrower_lender.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FDE46F-14C4-45D6-BAB6-832827452B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C143CEFD-28F2-4A59-98ED-2C6EEF1CAB1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="868" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="221">
   <si>
     <t>Library</t>
   </si>
@@ -691,6 +691,39 @@
   </si>
   <si>
     <t>1.75 : 1</t>
+  </si>
+  <si>
+    <t>1.74 : 1</t>
+  </si>
+  <si>
+    <t>0.17 : 1</t>
+  </si>
+  <si>
+    <t>0.89 : 1</t>
+  </si>
+  <si>
+    <t>0.43 : 1</t>
+  </si>
+  <si>
+    <t>1.24 : 1</t>
+  </si>
+  <si>
+    <t>1.97 : 1</t>
+  </si>
+  <si>
+    <t>0.67 : 1</t>
+  </si>
+  <si>
+    <t>1.59 : 1</t>
+  </si>
+  <si>
+    <t>1.34 : 1</t>
+  </si>
+  <si>
+    <t>0.90 : 1</t>
+  </si>
+  <si>
+    <t>1.79 : 1</t>
   </si>
 </sst>
 </file>
@@ -5803,15 +5836,15 @@
       </c>
       <c r="B2" s="7">
         <f>January!B2+February!B2+March!B2+April!B2+May!B2+June!B2+July!B2+August!B2+September!B2+October!B2+November!B2+December!B2</f>
-        <v>7107</v>
+        <v>8466</v>
       </c>
       <c r="C2" s="7">
         <f>January!C2+February!C2+March!C2+April!C2+May!C2+June!C2+July!C2+August!C2+September!C2+October!C2+November!C2+December!C2</f>
-        <v>5906</v>
+        <v>6879</v>
       </c>
       <c r="D2" s="7">
         <f>January!D2+February!D2+March!D2+April!D2+May!D2+June!D2+July!D2+August!D2+September!D2+October!D2+November!D2+December!D2</f>
-        <v>1201</v>
+        <v>1587</v>
       </c>
       <c r="E2" s="8" t="str">
         <f>IF(D2 &gt; 0, "We borrowed more than we lent this year", "")</f>
@@ -5823,7 +5856,7 @@
       </c>
       <c r="G2" s="9" t="str">
         <f>IF(ISERROR(ROUND(B2/C2,2)&amp;" : 1"), "", ROUND(B2/C2,2)&amp;" : 1")</f>
-        <v>1.2 : 1</v>
+        <v>1.23 : 1</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5832,15 +5865,15 @@
       </c>
       <c r="B3" s="11">
         <f>January!B3+February!B3+March!B3+April!B3+May!B3+June!B3+July!B3+August!B3+September!B3+October!B3+November!B3+December!B3</f>
-        <v>3000</v>
+        <v>3719</v>
       </c>
       <c r="C3" s="11">
         <f>January!C3+February!C3+March!C3+April!C3+May!C3+June!C3+July!C3+August!C3+September!C3+October!C3+November!C3+December!C3</f>
-        <v>2086</v>
+        <v>2447</v>
       </c>
       <c r="D3" s="11">
         <f>January!D3+February!D3+March!D3+April!D3+May!D3+June!D3+July!D3+August!D3+September!D3+October!D3+November!D3+December!D3</f>
-        <v>914</v>
+        <v>1272</v>
       </c>
       <c r="E3" s="12" t="str">
         <f t="shared" ref="E3:E54" si="0">IF(D3 &gt; 0, "We borrowed more than we lent this year", "")</f>
@@ -5852,7 +5885,7 @@
       </c>
       <c r="G3" s="13" t="str">
         <f t="shared" ref="G3:G54" si="2">IF(ISERROR(ROUND(B3/C3,2)&amp;" : 1"), "", ROUND(B3/C3,2)&amp;" : 1")</f>
-        <v>1.44 : 1</v>
+        <v>1.52 : 1</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5861,15 +5894,15 @@
       </c>
       <c r="B4" s="7">
         <f>January!B4+February!B4+March!B4+April!B4+May!B4+June!B4+July!B4+August!B4+September!B4+October!B4+November!B4+December!B4</f>
-        <v>5813</v>
+        <v>7067</v>
       </c>
       <c r="C4" s="7">
         <f>January!C4+February!C4+March!C4+April!C4+May!C4+June!C4+July!C4+August!C4+September!C4+October!C4+November!C4+December!C4</f>
-        <v>5707</v>
+        <v>6754</v>
       </c>
       <c r="D4" s="7">
         <f>January!D4+February!D4+March!D4+April!D4+May!D4+June!D4+July!D4+August!D4+September!D4+October!D4+November!D4+December!D4</f>
-        <v>106</v>
+        <v>313</v>
       </c>
       <c r="E4" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5881,7 +5914,7 @@
       </c>
       <c r="G4" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.02 : 1</v>
+        <v>1.05 : 1</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5890,15 +5923,15 @@
       </c>
       <c r="B5" s="11">
         <f>January!B5+February!B5+March!B5+April!B5+May!B5+June!B5+July!B5+August!B5+September!B5+October!B5+November!B5+December!B5</f>
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="C5" s="11">
         <f>January!C5+February!C5+March!C5+April!C5+May!C5+June!C5+July!C5+August!C5+September!C5+October!C5+November!C5+December!C5</f>
-        <v>580</v>
+        <v>701</v>
       </c>
       <c r="D5" s="11">
         <f>January!D5+February!D5+March!D5+April!D5+May!D5+June!D5+July!D5+August!D5+September!D5+October!D5+November!D5+December!D5</f>
-        <v>-483</v>
+        <v>-568</v>
       </c>
       <c r="E5" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5910,7 +5943,7 @@
       </c>
       <c r="G5" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.17 : 1</v>
+        <v>0.19 : 1</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5919,15 +5952,15 @@
       </c>
       <c r="B6" s="7">
         <f>January!B6+February!B6+March!B6+April!B6+May!B6+June!B6+July!B6+August!B6+September!B6+October!B6+November!B6+December!B6</f>
-        <v>4985</v>
+        <v>5941</v>
       </c>
       <c r="C6" s="7">
         <f>January!C6+February!C6+March!C6+April!C6+May!C6+June!C6+July!C6+August!C6+September!C6+October!C6+November!C6+December!C6</f>
-        <v>5614</v>
+        <v>6613</v>
       </c>
       <c r="D6" s="7">
         <f>January!D6+February!D6+March!D6+April!D6+May!D6+June!D6+July!D6+August!D6+September!D6+October!D6+November!D6+December!D6</f>
-        <v>-629</v>
+        <v>-672</v>
       </c>
       <c r="E6" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5939,7 +5972,7 @@
       </c>
       <c r="G6" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.89 : 1</v>
+        <v>0.9 : 1</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5948,15 +5981,15 @@
       </c>
       <c r="B7" s="11">
         <f>January!B7+February!B7+March!B7+April!B7+May!B7+June!B7+July!B7+August!B7+September!B7+October!B7+November!B7+December!B7</f>
-        <v>1259</v>
+        <v>1499</v>
       </c>
       <c r="C7" s="11">
         <f>January!C7+February!C7+March!C7+April!C7+May!C7+June!C7+July!C7+August!C7+September!C7+October!C7+November!C7+December!C7</f>
-        <v>842</v>
+        <v>1032</v>
       </c>
       <c r="D7" s="11">
         <f>January!D7+February!D7+March!D7+April!D7+May!D7+June!D7+July!D7+August!D7+September!D7+October!D7+November!D7+December!D7</f>
-        <v>417</v>
+        <v>467</v>
       </c>
       <c r="E7" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5968,7 +6001,7 @@
       </c>
       <c r="G7" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.5 : 1</v>
+        <v>1.45 : 1</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5977,15 +6010,15 @@
       </c>
       <c r="B8" s="7">
         <f>January!B8+February!B8+March!B8+April!B8+May!B8+June!B8+July!B8+August!B8+September!B8+October!B8+November!B8+December!B8</f>
-        <v>533</v>
+        <v>636</v>
       </c>
       <c r="C8" s="7">
         <f>January!C8+February!C8+March!C8+April!C8+May!C8+June!C8+July!C8+August!C8+September!C8+October!C8+November!C8+December!C8</f>
-        <v>803</v>
+        <v>962</v>
       </c>
       <c r="D8" s="7">
         <f>January!D8+February!D8+March!D8+April!D8+May!D8+June!D8+July!D8+August!D8+September!D8+October!D8+November!D8+December!D8</f>
-        <v>-270</v>
+        <v>-326</v>
       </c>
       <c r="E8" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6006,15 +6039,15 @@
       </c>
       <c r="B9" s="11">
         <f>January!B9+February!B9+March!B9+April!B9+May!B9+June!B9+July!B9+August!B9+September!B9+October!B9+November!B9+December!B9</f>
-        <v>276</v>
+        <v>344</v>
       </c>
       <c r="C9" s="11">
         <f>January!C9+February!C9+March!C9+April!C9+May!C9+June!C9+July!C9+August!C9+September!C9+October!C9+November!C9+December!C9</f>
-        <v>248</v>
+        <v>287</v>
       </c>
       <c r="D9" s="11">
         <f>January!D9+February!D9+March!D9+April!D9+May!D9+June!D9+July!D9+August!D9+September!D9+October!D9+November!D9+December!D9</f>
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="E9" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6026,7 +6059,7 @@
       </c>
       <c r="G9" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.11 : 1</v>
+        <v>1.2 : 1</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6039,11 +6072,11 @@
       </c>
       <c r="C10" s="7">
         <f>January!C10+February!C10+March!C10+April!C10+May!C10+June!C10+July!C10+August!C10+September!C10+October!C10+November!C10+December!C10</f>
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="D10" s="7">
         <f>January!D10+February!D10+March!D10+April!D10+May!D10+June!D10+July!D10+August!D10+September!D10+October!D10+November!D10+December!D10</f>
-        <v>-104</v>
+        <v>-118</v>
       </c>
       <c r="E10" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6055,7 +6088,7 @@
       </c>
       <c r="G10" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.03 : 1</v>
+        <v>0.02 : 1</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6093,15 +6126,15 @@
       </c>
       <c r="B12" s="15">
         <f>January!B12+February!B12+March!B12+April!B12+May!B12+June!B12+July!B12+August!B12+September!B12+October!B12+November!B12+December!B12</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C12" s="15">
         <f>January!C12+February!C12+March!C12+April!C12+May!C12+June!C12+July!C12+August!C12+September!C12+October!C12+November!C12+December!C12</f>
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="D12" s="15">
         <f>January!D12+February!D12+March!D12+April!D12+May!D12+June!D12+July!D12+August!D12+September!D12+October!D12+November!D12+December!D12</f>
-        <v>-64</v>
+        <v>-84</v>
       </c>
       <c r="E12" s="16" t="str">
         <f t="shared" si="0"/>
@@ -6113,7 +6146,7 @@
       </c>
       <c r="G12" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>0.3 : 1</v>
+        <v>0.27 : 1</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6122,15 +6155,15 @@
       </c>
       <c r="B13" s="19">
         <f>January!B13+February!B13+March!B13+April!B13+May!B13+June!B13+July!B13+August!B13+September!B13+October!B13+November!B13+December!B13</f>
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="C13" s="19">
         <f>January!C13+February!C13+March!C13+April!C13+May!C13+June!C13+July!C13+August!C13+September!C13+October!C13+November!C13+December!C13</f>
-        <v>284</v>
+        <v>337</v>
       </c>
       <c r="D13" s="19">
         <f>January!D13+February!D13+March!D13+April!D13+May!D13+June!D13+July!D13+August!D13+September!D13+October!D13+November!D13+December!D13</f>
-        <v>-22</v>
+        <v>-48</v>
       </c>
       <c r="E13" s="20" t="str">
         <f t="shared" si="0"/>
@@ -6142,7 +6175,7 @@
       </c>
       <c r="G13" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>0.92 : 1</v>
+        <v>0.86 : 1</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6151,15 +6184,15 @@
       </c>
       <c r="B14" s="15">
         <f>January!B14+February!B14+March!B14+April!B14+May!B14+June!B14+July!B14+August!B14+September!B14+October!B14+November!B14+December!B14</f>
-        <v>644</v>
+        <v>751</v>
       </c>
       <c r="C14" s="15">
         <f>January!C14+February!C14+March!C14+April!C14+May!C14+June!C14+July!C14+August!C14+September!C14+October!C14+November!C14+December!C14</f>
-        <v>1421</v>
+        <v>1716</v>
       </c>
       <c r="D14" s="15">
         <f>January!D14+February!D14+March!D14+April!D14+May!D14+June!D14+July!D14+August!D14+September!D14+October!D14+November!D14+December!D14</f>
-        <v>-777</v>
+        <v>-965</v>
       </c>
       <c r="E14" s="16" t="str">
         <f t="shared" si="0"/>
@@ -6171,7 +6204,7 @@
       </c>
       <c r="G14" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>0.45 : 1</v>
+        <v>0.44 : 1</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6180,15 +6213,15 @@
       </c>
       <c r="B15" s="19">
         <f>January!B15+February!B15+March!B15+April!B15+May!B15+June!B15+July!B15+August!B15+September!B15+October!B15+November!B15+December!B15</f>
-        <v>219</v>
+        <v>275</v>
       </c>
       <c r="C15" s="19">
         <f>January!C15+February!C15+March!C15+April!C15+May!C15+June!C15+July!C15+August!C15+September!C15+October!C15+November!C15+December!C15</f>
-        <v>693</v>
+        <v>828</v>
       </c>
       <c r="D15" s="19">
         <f>January!D15+February!D15+March!D15+April!D15+May!D15+June!D15+July!D15+August!D15+September!D15+October!D15+November!D15+December!D15</f>
-        <v>-474</v>
+        <v>-553</v>
       </c>
       <c r="E15" s="20" t="str">
         <f t="shared" si="0"/>
@@ -6200,7 +6233,7 @@
       </c>
       <c r="G15" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>0.32 : 1</v>
+        <v>0.33 : 1</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6209,15 +6242,15 @@
       </c>
       <c r="B16" s="7">
         <f>January!B16+February!B16+March!B16+April!B16+May!B16+June!B16+July!B16+August!B16+September!B16+October!B16+November!B16+December!B16</f>
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="C16" s="7">
         <f>January!C16+February!C16+March!C16+April!C16+May!C16+June!C16+July!C16+August!C16+September!C16+October!C16+November!C16+December!C16</f>
-        <v>895</v>
+        <v>1038</v>
       </c>
       <c r="D16" s="7">
         <f>January!D16+February!D16+March!D16+April!D16+May!D16+June!D16+July!D16+August!D16+September!D16+October!D16+November!D16+December!D16</f>
-        <v>-584</v>
+        <v>-674</v>
       </c>
       <c r="E16" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6238,15 +6271,15 @@
       </c>
       <c r="B17" s="11">
         <f>January!B17+February!B17+March!B17+April!B17+May!B17+June!B17+July!B17+August!B17+September!B17+October!B17+November!B17+December!B17</f>
-        <v>3243</v>
+        <v>3913</v>
       </c>
       <c r="C17" s="11">
         <f>January!C17+February!C17+March!C17+April!C17+May!C17+June!C17+July!C17+August!C17+September!C17+October!C17+November!C17+December!C17</f>
-        <v>2094</v>
+        <v>2510</v>
       </c>
       <c r="D17" s="11">
         <f>January!D17+February!D17+March!D17+April!D17+May!D17+June!D17+July!D17+August!D17+September!D17+October!D17+November!D17+December!D17</f>
-        <v>1149</v>
+        <v>1403</v>
       </c>
       <c r="E17" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6258,7 +6291,7 @@
       </c>
       <c r="G17" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.55 : 1</v>
+        <v>1.56 : 1</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6267,15 +6300,15 @@
       </c>
       <c r="B18" s="7">
         <f>January!B18+February!B18+March!B18+April!B18+May!B18+June!B18+July!B18+August!B18+September!B18+October!B18+November!B18+December!B18</f>
-        <v>466</v>
+        <v>543</v>
       </c>
       <c r="C18" s="7">
         <f>January!C18+February!C18+March!C18+April!C18+May!C18+June!C18+July!C18+August!C18+September!C18+October!C18+November!C18+December!C18</f>
-        <v>402</v>
+        <v>482</v>
       </c>
       <c r="D18" s="7">
         <f>January!D18+February!D18+March!D18+April!D18+May!D18+June!D18+July!D18+August!D18+September!D18+October!D18+November!D18+December!D18</f>
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E18" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6287,7 +6320,7 @@
       </c>
       <c r="G18" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.16 : 1</v>
+        <v>1.13 : 1</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6296,15 +6329,15 @@
       </c>
       <c r="B19" s="11">
         <f>January!B19+February!B19+March!B19+April!B19+May!B19+June!B19+July!B19+August!B19+September!B19+October!B19+November!B19+December!B19</f>
-        <v>2587</v>
+        <v>2987</v>
       </c>
       <c r="C19" s="11">
         <f>January!C19+February!C19+March!C19+April!C19+May!C19+June!C19+July!C19+August!C19+September!C19+October!C19+November!C19+December!C19</f>
-        <v>1641</v>
+        <v>1959</v>
       </c>
       <c r="D19" s="11">
         <f>January!D19+February!D19+March!D19+April!D19+May!D19+June!D19+July!D19+August!D19+September!D19+October!D19+November!D19+December!D19</f>
-        <v>946</v>
+        <v>1028</v>
       </c>
       <c r="E19" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6316,7 +6349,7 @@
       </c>
       <c r="G19" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.58 : 1</v>
+        <v>1.52 : 1</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6325,15 +6358,15 @@
       </c>
       <c r="B20" s="7">
         <f>January!B20+February!B20+March!B20+April!B20+May!B20+June!B20+July!B20+August!B20+September!B20+October!B20+November!B20+December!B20</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20" s="7">
         <f>January!C20+February!C20+March!C20+April!C20+May!C20+June!C20+July!C20+August!C20+September!C20+October!C20+November!C20+December!C20</f>
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="D20" s="7">
         <f>January!D20+February!D20+March!D20+April!D20+May!D20+June!D20+July!D20+August!D20+September!D20+October!D20+November!D20+December!D20</f>
-        <v>-221</v>
+        <v>-250</v>
       </c>
       <c r="E20" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6354,15 +6387,15 @@
       </c>
       <c r="B21" s="11">
         <f>January!B21+February!B21+March!B21+April!B21+May!B21+June!B21+July!B21+August!B21+September!B21+October!B21+November!B21+December!B21</f>
-        <v>2468</v>
+        <v>2932</v>
       </c>
       <c r="C21" s="11">
         <f>January!C21+February!C21+March!C21+April!C21+May!C21+June!C21+July!C21+August!C21+September!C21+October!C21+November!C21+December!C21</f>
-        <v>2039</v>
+        <v>2378</v>
       </c>
       <c r="D21" s="11">
         <f>January!D21+February!D21+March!D21+April!D21+May!D21+June!D21+July!D21+August!D21+September!D21+October!D21+November!D21+December!D21</f>
-        <v>429</v>
+        <v>554</v>
       </c>
       <c r="E21" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6374,7 +6407,7 @@
       </c>
       <c r="G21" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.21 : 1</v>
+        <v>1.23 : 1</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6383,15 +6416,15 @@
       </c>
       <c r="B22" s="7">
         <f>January!B22+February!B22+March!B22+April!B22+May!B22+June!B22+July!B22+August!B22+September!B22+October!B22+November!B22+December!B22</f>
-        <v>445</v>
+        <v>524</v>
       </c>
       <c r="C22" s="7">
         <f>January!C22+February!C22+March!C22+April!C22+May!C22+June!C22+July!C22+August!C22+September!C22+October!C22+November!C22+December!C22</f>
-        <v>1126</v>
+        <v>1341</v>
       </c>
       <c r="D22" s="7">
         <f>January!D22+February!D22+March!D22+April!D22+May!D22+June!D22+July!D22+August!D22+September!D22+October!D22+November!D22+December!D22</f>
-        <v>-681</v>
+        <v>-817</v>
       </c>
       <c r="E22" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6403,7 +6436,7 @@
       </c>
       <c r="G22" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.4 : 1</v>
+        <v>0.39 : 1</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6412,15 +6445,15 @@
       </c>
       <c r="B23" s="11">
         <f>January!B23+February!B23+March!B23+April!B23+May!B23+June!B23+July!B23+August!B23+September!B23+October!B23+November!B23+December!B23</f>
-        <v>3167</v>
+        <v>3751</v>
       </c>
       <c r="C23" s="11">
         <f>January!C23+February!C23+March!C23+April!C23+May!C23+June!C23+July!C23+August!C23+September!C23+October!C23+November!C23+December!C23</f>
-        <v>2872</v>
+        <v>3527</v>
       </c>
       <c r="D23" s="11">
         <f>January!D23+February!D23+March!D23+April!D23+May!D23+June!D23+July!D23+August!D23+September!D23+October!D23+November!D23+December!D23</f>
-        <v>295</v>
+        <v>224</v>
       </c>
       <c r="E23" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6432,7 +6465,7 @@
       </c>
       <c r="G23" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.1 : 1</v>
+        <v>1.06 : 1</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6441,15 +6474,15 @@
       </c>
       <c r="B24" s="7">
         <f>January!B24+February!B24+March!B24+April!B24+May!B24+June!B24+July!B24+August!B24+September!B24+October!B24+November!B24+December!B24</f>
-        <v>9023</v>
+        <v>10595</v>
       </c>
       <c r="C24" s="7">
         <f>January!C24+February!C24+March!C24+April!C24+May!C24+June!C24+July!C24+August!C24+September!C24+October!C24+November!C24+December!C24</f>
-        <v>6889</v>
+        <v>8302</v>
       </c>
       <c r="D24" s="7">
         <f>January!D24+February!D24+March!D24+April!D24+May!D24+June!D24+July!D24+August!D24+September!D24+October!D24+November!D24+December!D24</f>
-        <v>2134</v>
+        <v>2293</v>
       </c>
       <c r="E24" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6461,7 +6494,7 @@
       </c>
       <c r="G24" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.31 : 1</v>
+        <v>1.28 : 1</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6470,15 +6503,15 @@
       </c>
       <c r="B25" s="11">
         <f>January!B25+February!B25+March!B25+April!B25+May!B25+June!B25+July!B25+August!B25+September!B25+October!B25+November!B25+December!B25</f>
-        <v>801</v>
+        <v>952</v>
       </c>
       <c r="C25" s="11">
         <f>January!C25+February!C25+March!C25+April!C25+May!C25+June!C25+July!C25+August!C25+September!C25+October!C25+November!C25+December!C25</f>
-        <v>1607</v>
+        <v>1962</v>
       </c>
       <c r="D25" s="11">
         <f>January!D25+February!D25+March!D25+April!D25+May!D25+June!D25+July!D25+August!D25+September!D25+October!D25+November!D25+December!D25</f>
-        <v>-806</v>
+        <v>-1010</v>
       </c>
       <c r="E25" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6490,7 +6523,7 @@
       </c>
       <c r="G25" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.5 : 1</v>
+        <v>0.49 : 1</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6528,15 +6561,15 @@
       </c>
       <c r="B27" s="11">
         <f>January!B27+February!B27+March!B27+April!B27+May!B27+June!B27+July!B27+August!B27+September!B27+October!B27+November!B27+December!B27</f>
-        <v>988</v>
+        <v>1213</v>
       </c>
       <c r="C27" s="11">
         <f>January!C27+February!C27+March!C27+April!C27+May!C27+June!C27+July!C27+August!C27+September!C27+October!C27+November!C27+December!C27</f>
-        <v>763</v>
+        <v>944</v>
       </c>
       <c r="D27" s="11">
         <f>January!D27+February!D27+March!D27+April!D27+May!D27+June!D27+July!D27+August!D27+September!D27+October!D27+November!D27+December!D27</f>
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="E27" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6548,7 +6581,7 @@
       </c>
       <c r="G27" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.29 : 1</v>
+        <v>1.28 : 1</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6557,15 +6590,15 @@
       </c>
       <c r="B28" s="7">
         <f>January!B28+February!B28+March!B28+April!B28+May!B28+June!B28+July!B28+August!B28+September!B28+October!B28+November!B28+December!B28</f>
-        <v>709</v>
+        <v>869</v>
       </c>
       <c r="C28" s="7">
         <f>January!C28+February!C28+March!C28+April!C28+May!C28+June!C28+July!C28+August!C28+September!C28+October!C28+November!C28+December!C28</f>
-        <v>605</v>
+        <v>698</v>
       </c>
       <c r="D28" s="7">
         <f>January!D28+February!D28+March!D28+April!D28+May!D28+June!D28+July!D28+August!D28+September!D28+October!D28+November!D28+December!D28</f>
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="E28" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6577,7 +6610,7 @@
       </c>
       <c r="G28" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.17 : 1</v>
+        <v>1.24 : 1</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6586,15 +6619,15 @@
       </c>
       <c r="B29" s="11">
         <f>January!B29+February!B29+March!B29+April!B29+May!B29+June!B29+July!B29+August!B29+September!B29+October!B29+November!B29+December!B29</f>
-        <v>4127</v>
+        <v>5009</v>
       </c>
       <c r="C29" s="11">
         <f>January!C29+February!C29+March!C29+April!C29+May!C29+June!C29+July!C29+August!C29+September!C29+October!C29+November!C29+December!C29</f>
-        <v>2287</v>
+        <v>2734</v>
       </c>
       <c r="D29" s="11">
         <f>January!D29+February!D29+March!D29+April!D29+May!D29+June!D29+July!D29+August!D29+September!D29+October!D29+November!D29+December!D29</f>
-        <v>1840</v>
+        <v>2275</v>
       </c>
       <c r="E29" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6606,7 +6639,7 @@
       </c>
       <c r="G29" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.8 : 1</v>
+        <v>1.83 : 1</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6615,15 +6648,15 @@
       </c>
       <c r="B30" s="7">
         <f>January!B30+February!B30+March!B30+April!B30+May!B30+June!B30+July!B30+August!B30+September!B30+October!B30+November!B30+December!B30</f>
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="C30" s="7">
         <f>January!C30+February!C30+March!C30+April!C30+May!C30+June!C30+July!C30+August!C30+September!C30+October!C30+November!C30+December!C30</f>
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="D30" s="7">
         <f>January!D30+February!D30+March!D30+April!D30+May!D30+June!D30+July!D30+August!D30+September!D30+October!D30+November!D30+December!D30</f>
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E30" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6635,7 +6668,7 @@
       </c>
       <c r="G30" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.13 : 1</v>
+        <v>1.02 : 1</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6644,15 +6677,15 @@
       </c>
       <c r="B31" s="11">
         <f>January!B31+February!B31+March!B31+April!B31+May!B31+June!B31+July!B31+August!B31+September!B31+October!B31+November!B31+December!B31</f>
-        <v>597</v>
+        <v>691</v>
       </c>
       <c r="C31" s="11">
         <f>January!C31+February!C31+March!C31+April!C31+May!C31+June!C31+July!C31+August!C31+September!C31+October!C31+November!C31+December!C31</f>
-        <v>1299</v>
+        <v>1562</v>
       </c>
       <c r="D31" s="11">
         <f>January!D31+February!D31+March!D31+April!D31+May!D31+June!D31+July!D31+August!D31+September!D31+October!D31+November!D31+December!D31</f>
-        <v>-702</v>
+        <v>-871</v>
       </c>
       <c r="E31" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6664,7 +6697,7 @@
       </c>
       <c r="G31" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.46 : 1</v>
+        <v>0.44 : 1</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6673,15 +6706,15 @@
       </c>
       <c r="B32" s="7">
         <f>January!B32+February!B32+March!B32+April!B32+May!B32+June!B32+July!B32+August!B32+September!B32+October!B32+November!B32+December!B32</f>
-        <v>2041</v>
+        <v>2376</v>
       </c>
       <c r="C32" s="7">
         <f>January!C32+February!C32+March!C32+April!C32+May!C32+June!C32+July!C32+August!C32+September!C32+October!C32+November!C32+December!C32</f>
-        <v>2534</v>
+        <v>3031</v>
       </c>
       <c r="D32" s="7">
         <f>January!D32+February!D32+March!D32+April!D32+May!D32+June!D32+July!D32+August!D32+September!D32+October!D32+November!D32+December!D32</f>
-        <v>-493</v>
+        <v>-655</v>
       </c>
       <c r="E32" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6693,7 +6726,7 @@
       </c>
       <c r="G32" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.81 : 1</v>
+        <v>0.78 : 1</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6702,15 +6735,15 @@
       </c>
       <c r="B33" s="11">
         <f>January!B33+February!B33+March!B33+April!B33+May!B33+June!B33+July!B33+August!B33+September!B33+October!B33+November!B33+December!B33</f>
-        <v>1748</v>
+        <v>2096</v>
       </c>
       <c r="C33" s="11">
         <f>January!C33+February!C33+March!C33+April!C33+May!C33+June!C33+July!C33+August!C33+September!C33+October!C33+November!C33+December!C33</f>
-        <v>1622</v>
+        <v>1893</v>
       </c>
       <c r="D33" s="11">
         <f>January!D33+February!D33+March!D33+April!D33+May!D33+June!D33+July!D33+August!D33+September!D33+October!D33+November!D33+December!D33</f>
-        <v>126</v>
+        <v>203</v>
       </c>
       <c r="E33" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6722,7 +6755,7 @@
       </c>
       <c r="G33" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.08 : 1</v>
+        <v>1.11 : 1</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6731,15 +6764,15 @@
       </c>
       <c r="B34" s="7">
         <f>January!B34+February!B34+March!B34+April!B34+May!B34+June!B34+July!B34+August!B34+September!B34+October!B34+November!B34+December!B34</f>
-        <v>867</v>
+        <v>1014</v>
       </c>
       <c r="C34" s="7">
         <f>January!C34+February!C34+March!C34+April!C34+May!C34+June!C34+July!C34+August!C34+September!C34+October!C34+November!C34+December!C34</f>
-        <v>581</v>
+        <v>702</v>
       </c>
       <c r="D34" s="7">
         <f>January!D34+February!D34+March!D34+April!D34+May!D34+June!D34+July!D34+August!D34+September!D34+October!D34+November!D34+December!D34</f>
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="E34" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6751,7 +6784,7 @@
       </c>
       <c r="G34" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.49 : 1</v>
+        <v>1.44 : 1</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6760,15 +6793,15 @@
       </c>
       <c r="B35" s="11">
         <f>January!B35+February!B35+March!B35+April!B35+May!B35+June!B35+July!B35+August!B35+September!B35+October!B35+November!B35+December!B35</f>
-        <v>4883</v>
+        <v>5914</v>
       </c>
       <c r="C35" s="11">
         <f>January!C35+February!C35+March!C35+April!C35+May!C35+June!C35+July!C35+August!C35+September!C35+October!C35+November!C35+December!C35</f>
-        <v>7460</v>
+        <v>9026</v>
       </c>
       <c r="D35" s="11">
         <f>January!D35+February!D35+March!D35+April!D35+May!D35+June!D35+July!D35+August!D35+September!D35+October!D35+November!D35+December!D35</f>
-        <v>-2577</v>
+        <v>-3112</v>
       </c>
       <c r="E35" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6780,7 +6813,7 @@
       </c>
       <c r="G35" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.65 : 1</v>
+        <v>0.66 : 1</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6789,15 +6822,15 @@
       </c>
       <c r="B36" s="7">
         <f>January!B36+February!B36+March!B36+April!B36+May!B36+June!B36+July!B36+August!B36+September!B36+October!B36+November!B36+December!B36</f>
-        <v>850</v>
+        <v>1026</v>
       </c>
       <c r="C36" s="7">
         <f>January!C36+February!C36+March!C36+April!C36+May!C36+June!C36+July!C36+August!C36+September!C36+October!C36+November!C36+December!C36</f>
-        <v>2733</v>
+        <v>3300</v>
       </c>
       <c r="D36" s="7">
         <f>January!D36+February!D36+March!D36+April!D36+May!D36+June!D36+July!D36+August!D36+September!D36+October!D36+November!D36+December!D36</f>
-        <v>-1883</v>
+        <v>-2274</v>
       </c>
       <c r="E36" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6818,15 +6851,15 @@
       </c>
       <c r="B37" s="11">
         <f>January!B37+February!B37+March!B37+April!B37+May!B37+June!B37+July!B37+August!B37+September!B37+October!B37+November!B37+December!B37</f>
-        <v>2858</v>
+        <v>3408</v>
       </c>
       <c r="C37" s="11">
         <f>January!C37+February!C37+March!C37+April!C37+May!C37+June!C37+July!C37+August!C37+September!C37+October!C37+November!C37+December!C37</f>
-        <v>1930</v>
+        <v>2312</v>
       </c>
       <c r="D37" s="11">
         <f>January!D37+February!D37+March!D37+April!D37+May!D37+June!D37+July!D37+August!D37+September!D37+October!D37+November!D37+December!D37</f>
-        <v>928</v>
+        <v>1096</v>
       </c>
       <c r="E37" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6838,7 +6871,7 @@
       </c>
       <c r="G37" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.48 : 1</v>
+        <v>1.47 : 1</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6847,15 +6880,15 @@
       </c>
       <c r="B38" s="7">
         <f>January!B38+February!B38+March!B38+April!B38+May!B38+June!B38+July!B38+August!B38+September!B38+October!B38+November!B38+December!B38</f>
-        <v>167</v>
+        <v>245</v>
       </c>
       <c r="C38" s="7">
         <f>January!C38+February!C38+March!C38+April!C38+May!C38+June!C38+July!C38+August!C38+September!C38+October!C38+November!C38+December!C38</f>
-        <v>1026</v>
+        <v>1254</v>
       </c>
       <c r="D38" s="7">
         <f>January!D38+February!D38+March!D38+April!D38+May!D38+June!D38+July!D38+August!D38+September!D38+October!D38+November!D38+December!D38</f>
-        <v>-859</v>
+        <v>-1009</v>
       </c>
       <c r="E38" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6867,7 +6900,7 @@
       </c>
       <c r="G38" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.16 : 1</v>
+        <v>0.2 : 1</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6880,11 +6913,11 @@
       </c>
       <c r="C39" s="11">
         <f>January!C39+February!C39+March!C39+April!C39+May!C39+June!C39+July!C39+August!C39+September!C39+October!C39+November!C39+December!C39</f>
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="D39" s="11">
         <f>January!D39+February!D39+March!D39+April!D39+May!D39+June!D39+July!D39+August!D39+September!D39+October!D39+November!D39+December!D39</f>
-        <v>-243</v>
+        <v>-253</v>
       </c>
       <c r="E39" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6896,7 +6929,7 @@
       </c>
       <c r="G39" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.24 : 1</v>
+        <v>0.23 : 1</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6909,11 +6942,11 @@
       </c>
       <c r="C40" s="23">
         <f>January!C40+February!C40+March!C40+April!C40+May!C40+June!C40+July!C40+August!C40+September!C40+October!C40+November!C40+December!C40</f>
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D40" s="23">
         <f>January!D40+February!D40+March!D40+April!D40+May!D40+June!D40+July!D40+August!D40+September!D40+October!D40+November!D40+December!D40</f>
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="E40" s="24" t="str">
         <f t="shared" si="0"/>
@@ -6925,7 +6958,7 @@
       </c>
       <c r="G40" s="25" t="str">
         <f t="shared" si="2"/>
-        <v>0.8 : 1</v>
+        <v>0.79 : 1</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6934,15 +6967,15 @@
       </c>
       <c r="B41" s="27">
         <f>January!B41+February!B41+March!B41+April!B41+May!B41+June!B41+July!B41+August!B41+September!B41+October!B41+November!B41+December!B41</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C41" s="27">
         <f>January!C41+February!C41+March!C41+April!C41+May!C41+June!C41+July!C41+August!C41+September!C41+October!C41+November!C41+December!C41</f>
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D41" s="27">
         <f>January!D41+February!D41+March!D41+April!D41+May!D41+June!D41+July!D41+August!D41+September!D41+October!D41+November!D41+December!D41</f>
-        <v>-76</v>
+        <v>-81</v>
       </c>
       <c r="E41" s="28" t="str">
         <f t="shared" si="0"/>
@@ -6967,11 +7000,11 @@
       </c>
       <c r="C42" s="23">
         <f>January!C42+February!C42+March!C42+April!C42+May!C42+June!C42+July!C42+August!C42+September!C42+October!C42+November!C42+December!C42</f>
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D42" s="23">
         <f>January!D42+February!D42+March!D42+April!D42+May!D42+June!D42+July!D42+August!D42+September!D42+October!D42+November!D42+December!D42</f>
-        <v>-75</v>
+        <v>-79</v>
       </c>
       <c r="E42" s="24" t="str">
         <f t="shared" si="0"/>
@@ -6983,7 +7016,7 @@
       </c>
       <c r="G42" s="25" t="str">
         <f t="shared" si="2"/>
-        <v>0.4 : 1</v>
+        <v>0.39 : 1</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6992,15 +7025,15 @@
       </c>
       <c r="B43" s="27">
         <f>January!B43+February!B43+March!B43+April!B43+May!B43+June!B43+July!B43+August!B43+September!B43+October!B43+November!B43+December!B43</f>
-        <v>767</v>
+        <v>807</v>
       </c>
       <c r="C43" s="27">
         <f>January!C43+February!C43+March!C43+April!C43+May!C43+June!C43+July!C43+August!C43+September!C43+October!C43+November!C43+December!C43</f>
-        <v>480</v>
+        <v>593</v>
       </c>
       <c r="D43" s="27">
         <f>January!D43+February!D43+March!D43+April!D43+May!D43+June!D43+July!D43+August!D43+September!D43+October!D43+November!D43+December!D43</f>
-        <v>287</v>
+        <v>214</v>
       </c>
       <c r="E43" s="28" t="str">
         <f t="shared" si="0"/>
@@ -7012,7 +7045,7 @@
       </c>
       <c r="G43" s="29" t="str">
         <f t="shared" si="2"/>
-        <v>1.6 : 1</v>
+        <v>1.36 : 1</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7021,15 +7054,15 @@
       </c>
       <c r="B44" s="7">
         <f>January!B44+February!B44+March!B44+April!B44+May!B44+June!B44+July!B44+August!B44+September!B44+October!B44+November!B44+December!B44</f>
-        <v>311</v>
+        <v>381</v>
       </c>
       <c r="C44" s="7">
         <f>January!C44+February!C44+March!C44+April!C44+May!C44+June!C44+July!C44+August!C44+September!C44+October!C44+November!C44+December!C44</f>
-        <v>888</v>
+        <v>1064</v>
       </c>
       <c r="D44" s="7">
         <f>January!D44+February!D44+March!D44+April!D44+May!D44+June!D44+July!D44+August!D44+September!D44+October!D44+November!D44+December!D44</f>
-        <v>-577</v>
+        <v>-683</v>
       </c>
       <c r="E44" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7041,7 +7074,7 @@
       </c>
       <c r="G44" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.35 : 1</v>
+        <v>0.36 : 1</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7050,15 +7083,15 @@
       </c>
       <c r="B45" s="11">
         <f>January!B45+February!B45+March!B45+April!B45+May!B45+June!B45+July!B45+August!B45+September!B45+October!B45+November!B45+December!B45</f>
-        <v>2649</v>
+        <v>3093</v>
       </c>
       <c r="C45" s="11">
         <f>January!C45+February!C45+March!C45+April!C45+May!C45+June!C45+July!C45+August!C45+September!C45+October!C45+November!C45+December!C45</f>
-        <v>2905</v>
+        <v>3457</v>
       </c>
       <c r="D45" s="11">
         <f>January!D45+February!D45+March!D45+April!D45+May!D45+June!D45+July!D45+August!D45+September!D45+October!D45+November!D45+December!D45</f>
-        <v>-256</v>
+        <v>-364</v>
       </c>
       <c r="E45" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7070,7 +7103,7 @@
       </c>
       <c r="G45" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.91 : 1</v>
+        <v>0.89 : 1</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7079,15 +7112,15 @@
       </c>
       <c r="B46" s="7">
         <f>January!B46+February!B46+March!B46+April!B46+May!B46+June!B46+July!B46+August!B46+September!B46+October!B46+November!B46+December!B46</f>
-        <v>4368</v>
+        <v>5150</v>
       </c>
       <c r="C46" s="7">
         <f>January!C46+February!C46+March!C46+April!C46+May!C46+June!C46+July!C46+August!C46+September!C46+October!C46+November!C46+December!C46</f>
-        <v>3550</v>
+        <v>4041</v>
       </c>
       <c r="D46" s="7">
         <f>January!D46+February!D46+March!D46+April!D46+May!D46+June!D46+July!D46+August!D46+September!D46+October!D46+November!D46+December!D46</f>
-        <v>818</v>
+        <v>1109</v>
       </c>
       <c r="E46" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7099,7 +7132,7 @@
       </c>
       <c r="G46" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.23 : 1</v>
+        <v>1.27 : 1</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7108,15 +7141,15 @@
       </c>
       <c r="B47" s="11">
         <f>January!B47+February!B47+March!B47+April!B47+May!B47+June!B47+July!B47+August!B47+September!B47+October!B47+November!B47+December!B47</f>
-        <v>1124</v>
+        <v>1357</v>
       </c>
       <c r="C47" s="11">
         <f>January!C47+February!C47+March!C47+April!C47+May!C47+June!C47+July!C47+August!C47+September!C47+October!C47+November!C47+December!C47</f>
-        <v>2947</v>
+        <v>3441</v>
       </c>
       <c r="D47" s="11">
         <f>January!D47+February!D47+March!D47+April!D47+May!D47+June!D47+July!D47+August!D47+September!D47+October!D47+November!D47+December!D47</f>
-        <v>-1823</v>
+        <v>-2084</v>
       </c>
       <c r="E47" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7128,7 +7161,7 @@
       </c>
       <c r="G47" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.38 : 1</v>
+        <v>0.39 : 1</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7137,15 +7170,15 @@
       </c>
       <c r="B48" s="7">
         <f>January!B48+February!B48+March!B48+April!B48+May!B48+June!B48+July!B48+August!B48+September!B48+October!B48+November!B48+December!B48</f>
-        <v>2129</v>
+        <v>2380</v>
       </c>
       <c r="C48" s="7">
         <f>January!C48+February!C48+March!C48+April!C48+May!C48+June!C48+July!C48+August!C48+September!C48+October!C48+November!C48+December!C48</f>
-        <v>1300</v>
+        <v>1487</v>
       </c>
       <c r="D48" s="7">
         <f>January!D48+February!D48+March!D48+April!D48+May!D48+June!D48+July!D48+August!D48+September!D48+October!D48+November!D48+December!D48</f>
-        <v>829</v>
+        <v>893</v>
       </c>
       <c r="E48" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7157,7 +7190,7 @@
       </c>
       <c r="G48" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.64 : 1</v>
+        <v>1.6 : 1</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7166,15 +7199,15 @@
       </c>
       <c r="B49" s="11">
         <f>January!B49+February!B49+March!B49+April!B49+May!B49+June!B49+July!B49+August!B49+September!B49+October!B49+November!B49+December!B49</f>
-        <v>4772</v>
+        <v>5757</v>
       </c>
       <c r="C49" s="11">
         <f>January!C49+February!C49+March!C49+April!C49+May!C49+June!C49+July!C49+August!C49+September!C49+October!C49+November!C49+December!C49</f>
-        <v>2814</v>
+        <v>3276</v>
       </c>
       <c r="D49" s="11">
         <f>January!D49+February!D49+March!D49+April!D49+May!D49+June!D49+July!D49+August!D49+September!D49+October!D49+November!D49+December!D49</f>
-        <v>1958</v>
+        <v>2481</v>
       </c>
       <c r="E49" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7186,7 +7219,7 @@
       </c>
       <c r="G49" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.7 : 1</v>
+        <v>1.76 : 1</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7195,15 +7228,15 @@
       </c>
       <c r="B50" s="7">
         <f>January!B50+February!B50+March!B50+April!B50+May!B50+June!B50+July!B50+August!B50+September!B50+October!B50+November!B50+December!B50</f>
-        <v>610</v>
+        <v>717</v>
       </c>
       <c r="C50" s="7">
         <f>January!C50+February!C50+March!C50+April!C50+May!C50+June!C50+July!C50+August!C50+September!C50+October!C50+November!C50+December!C50</f>
-        <v>835</v>
+        <v>987</v>
       </c>
       <c r="D50" s="7">
         <f>January!D50+February!D50+March!D50+April!D50+May!D50+June!D50+July!D50+August!D50+September!D50+October!D50+November!D50+December!D50</f>
-        <v>-225</v>
+        <v>-270</v>
       </c>
       <c r="E50" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7224,15 +7257,15 @@
       </c>
       <c r="B51" s="11">
         <f>January!B51+February!B51+March!B51+April!B51+May!B51+June!B51+July!B51+August!B51+September!B51+October!B51+November!B51+December!B51</f>
-        <v>2334</v>
+        <v>2675</v>
       </c>
       <c r="C51" s="11">
         <f>January!C51+February!C51+March!C51+April!C51+May!C51+June!C51+July!C51+August!C51+September!C51+October!C51+November!C51+December!C51</f>
-        <v>1802</v>
+        <v>2183</v>
       </c>
       <c r="D51" s="11">
         <f>January!D51+February!D51+March!D51+April!D51+May!D51+June!D51+July!D51+August!D51+September!D51+October!D51+November!D51+December!D51</f>
-        <v>532</v>
+        <v>492</v>
       </c>
       <c r="E51" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7244,7 +7277,7 @@
       </c>
       <c r="G51" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.3 : 1</v>
+        <v>1.23 : 1</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7253,15 +7286,15 @@
       </c>
       <c r="B52" s="7">
         <f>January!B52+February!B52+March!B52+April!B52+May!B52+June!B52+July!B52+August!B52+September!B52+October!B52+November!B52+December!B52</f>
-        <v>616</v>
+        <v>671</v>
       </c>
       <c r="C52" s="7">
         <f>January!C52+February!C52+March!C52+April!C52+May!C52+June!C52+July!C52+August!C52+September!C52+October!C52+November!C52+December!C52</f>
-        <v>1105</v>
+        <v>1327</v>
       </c>
       <c r="D52" s="7">
         <f>January!D52+February!D52+March!D52+April!D52+May!D52+June!D52+July!D52+August!D52+September!D52+October!D52+November!D52+December!D52</f>
-        <v>-489</v>
+        <v>-656</v>
       </c>
       <c r="E52" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7273,7 +7306,7 @@
       </c>
       <c r="G52" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.56 : 1</v>
+        <v>0.51 : 1</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7282,15 +7315,15 @@
       </c>
       <c r="B53" s="11">
         <f>January!B53+February!B53+March!B53+April!B53+May!B53+June!B53+July!B53+August!B53+September!B53+October!B53+November!B53+December!B53</f>
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="C53" s="11">
         <f>January!C53+February!C53+March!C53+April!C53+May!C53+June!C53+July!C53+August!C53+September!C53+October!C53+November!C53+December!C53</f>
-        <v>1223</v>
+        <v>1486</v>
       </c>
       <c r="D53" s="11">
         <f>January!D53+February!D53+March!D53+April!D53+May!D53+June!D53+July!D53+August!D53+September!D53+October!D53+November!D53+December!D53</f>
-        <v>-1093</v>
+        <v>-1329</v>
       </c>
       <c r="E53" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7311,15 +7344,15 @@
       </c>
       <c r="B54" s="31">
         <f>January!B54+February!B54+March!B54+April!B54+May!B54+June!B54+July!B54+August!B54+September!B54+October!B54+November!B54+December!B54</f>
-        <v>1985</v>
+        <v>2384</v>
       </c>
       <c r="C54" s="31">
         <f>January!C54+February!C54+March!C54+April!C54+May!C54+June!C54+July!C54+August!C54+September!C54+October!C54+November!C54+December!C54</f>
-        <v>1018</v>
+        <v>1241</v>
       </c>
       <c r="D54" s="31">
         <f>January!D54+February!D54+March!D54+April!D54+May!D54+June!D54+July!D54+August!D54+September!D54+October!D54+November!D54+December!D54</f>
-        <v>967</v>
+        <v>1143</v>
       </c>
       <c r="E54" s="32" t="str">
         <f t="shared" si="0"/>
@@ -7331,7 +7364,7 @@
       </c>
       <c r="G54" s="33" t="str">
         <f t="shared" si="2"/>
-        <v>1.95 : 1</v>
+        <v>1.92 : 1</v>
       </c>
     </row>
   </sheetData>
@@ -12131,108 +12164,204 @@
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8"/>
+      <c r="B2" s="7">
+        <v>1359</v>
+      </c>
+      <c r="C2" s="7">
+        <v>973</v>
+      </c>
+      <c r="D2" s="7">
+        <v>386</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F2" s="8"/>
-      <c r="G2" s="9"/>
+      <c r="G2" s="9" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="12"/>
+      <c r="B3" s="11">
+        <v>719</v>
+      </c>
+      <c r="C3" s="11">
+        <v>361</v>
+      </c>
+      <c r="D3" s="11">
+        <v>358</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F3" s="12"/>
-      <c r="G3" s="13"/>
+      <c r="G3" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8"/>
+      <c r="B4" s="7">
+        <v>1254</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1047</v>
+      </c>
+      <c r="D4" s="7">
+        <v>207</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F4" s="8"/>
-      <c r="G4" s="9"/>
+      <c r="G4" s="9" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
+      <c r="B5" s="11">
+        <v>36</v>
+      </c>
+      <c r="C5" s="11">
+        <v>121</v>
+      </c>
+      <c r="D5" s="11">
+        <v>-85</v>
+      </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13"/>
+      <c r="F5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+      <c r="B6" s="7">
+        <v>956</v>
+      </c>
+      <c r="C6" s="7">
+        <v>999</v>
+      </c>
+      <c r="D6" s="7">
+        <v>-43</v>
+      </c>
       <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9"/>
+      <c r="F6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12"/>
+      <c r="B7" s="11">
+        <v>240</v>
+      </c>
+      <c r="C7" s="11">
+        <v>190</v>
+      </c>
+      <c r="D7" s="11">
+        <v>50</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="13"/>
+      <c r="G7" s="13" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+      <c r="B8" s="7">
+        <v>103</v>
+      </c>
+      <c r="C8" s="7">
+        <v>159</v>
+      </c>
+      <c r="D8" s="7">
+        <v>-56</v>
+      </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9"/>
+      <c r="F8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12"/>
+      <c r="B9" s="11">
+        <v>68</v>
+      </c>
+      <c r="C9" s="11">
+        <v>39</v>
+      </c>
+      <c r="D9" s="11">
+        <v>29</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="13"/>
+      <c r="G9" s="13" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="B10" s="7">
+        <v>0</v>
+      </c>
+      <c r="C10" s="7">
+        <v>14</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-14</v>
+      </c>
       <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9"/>
+      <c r="F10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
+      <c r="B11" s="11">
+        <v>0</v>
+      </c>
+      <c r="C11" s="11">
+        <v>0</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0</v>
+      </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
@@ -12241,163 +12370,309 @@
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
+      <c r="B12" s="15">
+        <v>4</v>
+      </c>
+      <c r="C12" s="15">
+        <v>24</v>
+      </c>
+      <c r="D12" s="15">
+        <v>-20</v>
+      </c>
       <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17"/>
+      <c r="F12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
+      <c r="B13" s="19">
+        <v>27</v>
+      </c>
+      <c r="C13" s="19">
+        <v>53</v>
+      </c>
+      <c r="D13" s="19">
+        <v>-26</v>
+      </c>
       <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="21"/>
+      <c r="F13" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
+      <c r="B14" s="15">
+        <v>107</v>
+      </c>
+      <c r="C14" s="15">
+        <v>295</v>
+      </c>
+      <c r="D14" s="15">
+        <v>-188</v>
+      </c>
       <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="17"/>
+      <c r="F14" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
+      <c r="B15" s="19">
+        <v>56</v>
+      </c>
+      <c r="C15" s="19">
+        <v>135</v>
+      </c>
+      <c r="D15" s="19">
+        <v>-79</v>
+      </c>
       <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="21"/>
+      <c r="F15" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
+      <c r="B16" s="7">
+        <v>53</v>
+      </c>
+      <c r="C16" s="7">
+        <v>143</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-90</v>
+      </c>
       <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="9"/>
+      <c r="F16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="12"/>
+      <c r="B17" s="11">
+        <v>670</v>
+      </c>
+      <c r="C17" s="11">
+        <v>416</v>
+      </c>
+      <c r="D17" s="11">
+        <v>254</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F17" s="12"/>
-      <c r="G17" s="13"/>
+      <c r="G17" s="13" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
+      <c r="B18" s="7">
+        <v>77</v>
+      </c>
+      <c r="C18" s="7">
+        <v>80</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-3</v>
+      </c>
       <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="9"/>
+      <c r="F18" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="12"/>
+      <c r="B19" s="11">
+        <v>400</v>
+      </c>
+      <c r="C19" s="11">
+        <v>318</v>
+      </c>
+      <c r="D19" s="11">
+        <v>82</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="13"/>
+      <c r="G19" s="13" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
+      <c r="B20" s="7">
+        <v>1</v>
+      </c>
+      <c r="C20" s="7">
+        <v>30</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-29</v>
+      </c>
       <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="9"/>
+      <c r="F20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="12"/>
+      <c r="B21" s="11">
+        <v>464</v>
+      </c>
+      <c r="C21" s="11">
+        <v>339</v>
+      </c>
+      <c r="D21" s="11">
+        <v>125</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="13"/>
+      <c r="G21" s="13" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+      <c r="B22" s="7">
+        <v>79</v>
+      </c>
+      <c r="C22" s="7">
+        <v>215</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-136</v>
+      </c>
       <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="9"/>
+      <c r="F22" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
+      <c r="B23" s="11">
+        <v>584</v>
+      </c>
+      <c r="C23" s="11">
+        <v>655</v>
+      </c>
+      <c r="D23" s="11">
+        <v>-71</v>
+      </c>
       <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="13"/>
+      <c r="F23" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8"/>
+      <c r="B24" s="7">
+        <v>1572</v>
+      </c>
+      <c r="C24" s="7">
+        <v>1413</v>
+      </c>
+      <c r="D24" s="7">
+        <v>159</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
+      <c r="G24" s="9" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="B25" s="11">
+        <v>151</v>
+      </c>
+      <c r="C25" s="11">
+        <v>355</v>
+      </c>
+      <c r="D25" s="11">
+        <v>-204</v>
+      </c>
       <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="13"/>
+      <c r="F25" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
+      <c r="B26" s="7">
+        <v>0</v>
+      </c>
+      <c r="C26" s="7">
+        <v>0</v>
+      </c>
+      <c r="D26" s="7">
+        <v>0</v>
+      </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
@@ -12406,309 +12681,589 @@
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="12"/>
+      <c r="B27" s="11">
+        <v>225</v>
+      </c>
+      <c r="C27" s="11">
+        <v>181</v>
+      </c>
+      <c r="D27" s="11">
+        <v>44</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F27" s="12"/>
-      <c r="G27" s="13"/>
+      <c r="G27" s="13" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="8"/>
+      <c r="B28" s="7">
+        <v>160</v>
+      </c>
+      <c r="C28" s="7">
+        <v>93</v>
+      </c>
+      <c r="D28" s="7">
+        <v>67</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F28" s="8"/>
-      <c r="G28" s="9"/>
+      <c r="G28" s="9" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="12"/>
+      <c r="B29" s="11">
+        <v>882</v>
+      </c>
+      <c r="C29" s="11">
+        <v>447</v>
+      </c>
+      <c r="D29" s="11">
+        <v>435</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F29" s="12"/>
-      <c r="G29" s="13"/>
+      <c r="G29" s="13" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
+      <c r="B30" s="7">
+        <v>20</v>
+      </c>
+      <c r="C30" s="7">
+        <v>34</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-14</v>
+      </c>
       <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="9"/>
+      <c r="F30" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
+      <c r="B31" s="11">
+        <v>94</v>
+      </c>
+      <c r="C31" s="11">
+        <v>263</v>
+      </c>
+      <c r="D31" s="11">
+        <v>-169</v>
+      </c>
       <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="13"/>
+      <c r="F31" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
+      <c r="B32" s="7">
+        <v>335</v>
+      </c>
+      <c r="C32" s="7">
+        <v>497</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-162</v>
+      </c>
       <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="9"/>
+      <c r="F32" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="12"/>
+      <c r="B33" s="11">
+        <v>348</v>
+      </c>
+      <c r="C33" s="11">
+        <v>271</v>
+      </c>
+      <c r="D33" s="11">
+        <v>77</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F33" s="12"/>
-      <c r="G33" s="13"/>
+      <c r="G33" s="13" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="8"/>
+      <c r="B34" s="7">
+        <v>147</v>
+      </c>
+      <c r="C34" s="7">
+        <v>121</v>
+      </c>
+      <c r="D34" s="7">
+        <v>26</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F34" s="8"/>
-      <c r="G34" s="9"/>
+      <c r="G34" s="9" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
+      <c r="B35" s="11">
+        <v>1031</v>
+      </c>
+      <c r="C35" s="11">
+        <v>1566</v>
+      </c>
+      <c r="D35" s="11">
+        <v>-535</v>
+      </c>
       <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="13"/>
+      <c r="F35" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
+      <c r="B36" s="7">
+        <v>176</v>
+      </c>
+      <c r="C36" s="7">
+        <v>567</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-391</v>
+      </c>
       <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="9"/>
+      <c r="F36" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="12"/>
+      <c r="B37" s="11">
+        <v>550</v>
+      </c>
+      <c r="C37" s="11">
+        <v>382</v>
+      </c>
+      <c r="D37" s="11">
+        <v>168</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="13"/>
+      <c r="G37" s="13" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
+      <c r="B38" s="7">
+        <v>78</v>
+      </c>
+      <c r="C38" s="7">
+        <v>228</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-150</v>
+      </c>
       <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="9"/>
+      <c r="F38" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
+      <c r="B39" s="11">
+        <v>0</v>
+      </c>
+      <c r="C39" s="11">
+        <v>10</v>
+      </c>
+      <c r="D39" s="11">
+        <v>-10</v>
+      </c>
       <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="13"/>
+      <c r="F39" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
+      <c r="B40" s="23">
+        <v>0</v>
+      </c>
+      <c r="C40" s="23">
+        <v>1</v>
+      </c>
+      <c r="D40" s="23">
+        <v>-1</v>
+      </c>
       <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="25"/>
+      <c r="F40" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="25" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
+      <c r="B41" s="27">
+        <v>1</v>
+      </c>
+      <c r="C41" s="27">
+        <v>6</v>
+      </c>
+      <c r="D41" s="27">
+        <v>-5</v>
+      </c>
       <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="29"/>
+      <c r="F41" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
+      <c r="B42" s="23">
+        <v>0</v>
+      </c>
+      <c r="C42" s="23">
+        <v>4</v>
+      </c>
+      <c r="D42" s="23">
+        <v>-4</v>
+      </c>
       <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="25"/>
+      <c r="F42" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="25" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
+      <c r="B43" s="27">
+        <v>40</v>
+      </c>
+      <c r="C43" s="27">
+        <v>113</v>
+      </c>
+      <c r="D43" s="27">
+        <v>-73</v>
+      </c>
       <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="29"/>
+      <c r="F43" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" s="29" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
+      <c r="B44" s="7">
+        <v>70</v>
+      </c>
+      <c r="C44" s="7">
+        <v>176</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-106</v>
+      </c>
       <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="9"/>
+      <c r="F44" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
+      <c r="B45" s="11">
+        <v>444</v>
+      </c>
+      <c r="C45" s="11">
+        <v>552</v>
+      </c>
+      <c r="D45" s="11">
+        <v>-108</v>
+      </c>
       <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="13"/>
+      <c r="F45" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="8"/>
+      <c r="B46" s="7">
+        <v>782</v>
+      </c>
+      <c r="C46" s="7">
+        <v>491</v>
+      </c>
+      <c r="D46" s="7">
+        <v>291</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F46" s="8"/>
-      <c r="G46" s="9"/>
+      <c r="G46" s="9" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
+      <c r="B47" s="11">
+        <v>233</v>
+      </c>
+      <c r="C47" s="11">
+        <v>494</v>
+      </c>
+      <c r="D47" s="11">
+        <v>-261</v>
+      </c>
       <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="13"/>
+      <c r="F47" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="8"/>
+      <c r="B48" s="7">
+        <v>251</v>
+      </c>
+      <c r="C48" s="7">
+        <v>187</v>
+      </c>
+      <c r="D48" s="7">
+        <v>64</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F48" s="8"/>
-      <c r="G48" s="9"/>
+      <c r="G48" s="9" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="12"/>
+      <c r="B49" s="11">
+        <v>985</v>
+      </c>
+      <c r="C49" s="11">
+        <v>462</v>
+      </c>
+      <c r="D49" s="11">
+        <v>523</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="13"/>
+      <c r="G49" s="13" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
+      <c r="B50" s="7">
+        <v>107</v>
+      </c>
+      <c r="C50" s="7">
+        <v>152</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-45</v>
+      </c>
       <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="9"/>
+      <c r="F50" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
+      <c r="B51" s="11">
+        <v>341</v>
+      </c>
+      <c r="C51" s="11">
+        <v>381</v>
+      </c>
+      <c r="D51" s="11">
+        <v>-40</v>
+      </c>
       <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="13"/>
+      <c r="F51" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
+      <c r="B52" s="7">
+        <v>55</v>
+      </c>
+      <c r="C52" s="7">
+        <v>222</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-167</v>
+      </c>
       <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="9"/>
+      <c r="F52" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
+      <c r="B53" s="11">
+        <v>27</v>
+      </c>
+      <c r="C53" s="11">
+        <v>263</v>
+      </c>
+      <c r="D53" s="11">
+        <v>-236</v>
+      </c>
       <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="13"/>
+      <c r="F53" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" s="13" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B54" s="31"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="32"/>
+      <c r="B54" s="31">
+        <v>399</v>
+      </c>
+      <c r="C54" s="31">
+        <v>223</v>
+      </c>
+      <c r="D54" s="31">
+        <v>176</v>
+      </c>
+      <c r="E54" s="32" t="s">
+        <v>8</v>
+      </c>
       <c r="F54" s="32"/>
-      <c r="G54" s="33"/>
+      <c r="G54" s="33" t="s">
+        <v>220</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-000005000000}"/>

--- a/statistics_files/2026/2026_99_ga_net_borrower_lender.xlsx
+++ b/statistics_files/2026/2026_99_ga_net_borrower_lender.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C143CEFD-28F2-4A59-98ED-2C6EEF1CAB1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C4212B4-9471-4A94-B6A5-2CA98EFA6BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="868" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1493" uniqueCount="233">
   <si>
     <t>Library</t>
   </si>
@@ -724,6 +724,42 @@
   </si>
   <si>
     <t>1.79 : 1</t>
+  </si>
+  <si>
+    <t>2.23 : 1</t>
+  </si>
+  <si>
+    <t>0.58 : 1</t>
+  </si>
+  <si>
+    <t>0.54 : 1</t>
+  </si>
+  <si>
+    <t>2.18 : 1</t>
+  </si>
+  <si>
+    <t>3.26 : 1</t>
+  </si>
+  <si>
+    <t>0.97 : 1</t>
+  </si>
+  <si>
+    <t>1.50 : 1</t>
+  </si>
+  <si>
+    <t>2.58 : 1</t>
+  </si>
+  <si>
+    <t>0.13 : 1</t>
+  </si>
+  <si>
+    <t>1.54 : 1</t>
+  </si>
+  <si>
+    <t>0.82 : 1</t>
+  </si>
+  <si>
+    <t>1.89 : 1</t>
   </si>
 </sst>
 </file>
@@ -5836,15 +5872,15 @@
       </c>
       <c r="B2" s="7">
         <f>January!B2+February!B2+March!B2+April!B2+May!B2+June!B2+July!B2+August!B2+September!B2+October!B2+November!B2+December!B2</f>
-        <v>8466</v>
+        <v>9925</v>
       </c>
       <c r="C2" s="7">
         <f>January!C2+February!C2+March!C2+April!C2+May!C2+June!C2+July!C2+August!C2+September!C2+October!C2+November!C2+December!C2</f>
-        <v>6879</v>
+        <v>8052</v>
       </c>
       <c r="D2" s="7">
         <f>January!D2+February!D2+March!D2+April!D2+May!D2+June!D2+July!D2+August!D2+September!D2+October!D2+November!D2+December!D2</f>
-        <v>1587</v>
+        <v>1873</v>
       </c>
       <c r="E2" s="8" t="str">
         <f>IF(D2 &gt; 0, "We borrowed more than we lent this year", "")</f>
@@ -5865,15 +5901,15 @@
       </c>
       <c r="B3" s="11">
         <f>January!B3+February!B3+March!B3+April!B3+May!B3+June!B3+July!B3+August!B3+September!B3+October!B3+November!B3+December!B3</f>
-        <v>3719</v>
+        <v>4490</v>
       </c>
       <c r="C3" s="11">
         <f>January!C3+February!C3+March!C3+April!C3+May!C3+June!C3+July!C3+August!C3+September!C3+October!C3+November!C3+December!C3</f>
-        <v>2447</v>
+        <v>2793</v>
       </c>
       <c r="D3" s="11">
         <f>January!D3+February!D3+March!D3+April!D3+May!D3+June!D3+July!D3+August!D3+September!D3+October!D3+November!D3+December!D3</f>
-        <v>1272</v>
+        <v>1697</v>
       </c>
       <c r="E3" s="12" t="str">
         <f t="shared" ref="E3:E54" si="0">IF(D3 &gt; 0, "We borrowed more than we lent this year", "")</f>
@@ -5885,7 +5921,7 @@
       </c>
       <c r="G3" s="13" t="str">
         <f t="shared" ref="G3:G54" si="2">IF(ISERROR(ROUND(B3/C3,2)&amp;" : 1"), "", ROUND(B3/C3,2)&amp;" : 1")</f>
-        <v>1.52 : 1</v>
+        <v>1.61 : 1</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5894,15 +5930,15 @@
       </c>
       <c r="B4" s="7">
         <f>January!B4+February!B4+March!B4+April!B4+May!B4+June!B4+July!B4+August!B4+September!B4+October!B4+November!B4+December!B4</f>
-        <v>7067</v>
+        <v>8337</v>
       </c>
       <c r="C4" s="7">
         <f>January!C4+February!C4+March!C4+April!C4+May!C4+June!C4+July!C4+August!C4+September!C4+October!C4+November!C4+December!C4</f>
-        <v>6754</v>
+        <v>7816</v>
       </c>
       <c r="D4" s="7">
         <f>January!D4+February!D4+March!D4+April!D4+May!D4+June!D4+July!D4+August!D4+September!D4+October!D4+November!D4+December!D4</f>
-        <v>313</v>
+        <v>521</v>
       </c>
       <c r="E4" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5914,7 +5950,7 @@
       </c>
       <c r="G4" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.05 : 1</v>
+        <v>1.07 : 1</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5923,15 +5959,15 @@
       </c>
       <c r="B5" s="11">
         <f>January!B5+February!B5+March!B5+April!B5+May!B5+June!B5+July!B5+August!B5+September!B5+October!B5+November!B5+December!B5</f>
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="C5" s="11">
         <f>January!C5+February!C5+March!C5+April!C5+May!C5+June!C5+July!C5+August!C5+September!C5+October!C5+November!C5+December!C5</f>
-        <v>701</v>
+        <v>806</v>
       </c>
       <c r="D5" s="11">
         <f>January!D5+February!D5+March!D5+April!D5+May!D5+June!D5+July!D5+August!D5+September!D5+October!D5+November!D5+December!D5</f>
-        <v>-568</v>
+        <v>-642</v>
       </c>
       <c r="E5" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5943,7 +5979,7 @@
       </c>
       <c r="G5" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.19 : 1</v>
+        <v>0.2 : 1</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5952,15 +5988,15 @@
       </c>
       <c r="B6" s="7">
         <f>January!B6+February!B6+March!B6+April!B6+May!B6+June!B6+July!B6+August!B6+September!B6+October!B6+November!B6+December!B6</f>
-        <v>5941</v>
+        <v>6861</v>
       </c>
       <c r="C6" s="7">
         <f>January!C6+February!C6+March!C6+April!C6+May!C6+June!C6+July!C6+August!C6+September!C6+October!C6+November!C6+December!C6</f>
-        <v>6613</v>
+        <v>7695</v>
       </c>
       <c r="D6" s="7">
         <f>January!D6+February!D6+March!D6+April!D6+May!D6+June!D6+July!D6+August!D6+September!D6+October!D6+November!D6+December!D6</f>
-        <v>-672</v>
+        <v>-834</v>
       </c>
       <c r="E6" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5972,7 +6008,7 @@
       </c>
       <c r="G6" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.9 : 1</v>
+        <v>0.89 : 1</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5981,15 +6017,15 @@
       </c>
       <c r="B7" s="11">
         <f>January!B7+February!B7+March!B7+April!B7+May!B7+June!B7+July!B7+August!B7+September!B7+October!B7+November!B7+December!B7</f>
-        <v>1499</v>
+        <v>1772</v>
       </c>
       <c r="C7" s="11">
         <f>January!C7+February!C7+March!C7+April!C7+May!C7+June!C7+July!C7+August!C7+September!C7+October!C7+November!C7+December!C7</f>
-        <v>1032</v>
+        <v>1201</v>
       </c>
       <c r="D7" s="11">
         <f>January!D7+February!D7+March!D7+April!D7+May!D7+June!D7+July!D7+August!D7+September!D7+October!D7+November!D7+December!D7</f>
-        <v>467</v>
+        <v>571</v>
       </c>
       <c r="E7" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6001,7 +6037,7 @@
       </c>
       <c r="G7" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.45 : 1</v>
+        <v>1.48 : 1</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6010,15 +6046,15 @@
       </c>
       <c r="B8" s="7">
         <f>January!B8+February!B8+March!B8+April!B8+May!B8+June!B8+July!B8+August!B8+September!B8+October!B8+November!B8+December!B8</f>
-        <v>636</v>
+        <v>801</v>
       </c>
       <c r="C8" s="7">
         <f>January!C8+February!C8+March!C8+April!C8+May!C8+June!C8+July!C8+August!C8+September!C8+October!C8+November!C8+December!C8</f>
-        <v>962</v>
+        <v>1100</v>
       </c>
       <c r="D8" s="7">
         <f>January!D8+February!D8+March!D8+April!D8+May!D8+June!D8+July!D8+August!D8+September!D8+October!D8+November!D8+December!D8</f>
-        <v>-326</v>
+        <v>-299</v>
       </c>
       <c r="E8" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6030,7 +6066,7 @@
       </c>
       <c r="G8" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.66 : 1</v>
+        <v>0.73 : 1</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6039,15 +6075,15 @@
       </c>
       <c r="B9" s="11">
         <f>January!B9+February!B9+March!B9+April!B9+May!B9+June!B9+July!B9+August!B9+September!B9+October!B9+November!B9+December!B9</f>
-        <v>344</v>
+        <v>420</v>
       </c>
       <c r="C9" s="11">
         <f>January!C9+February!C9+March!C9+April!C9+May!C9+June!C9+July!C9+August!C9+September!C9+October!C9+November!C9+December!C9</f>
-        <v>287</v>
+        <v>351</v>
       </c>
       <c r="D9" s="11">
         <f>January!D9+February!D9+March!D9+April!D9+May!D9+June!D9+July!D9+August!D9+September!D9+October!D9+November!D9+December!D9</f>
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E9" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6068,15 +6104,15 @@
       </c>
       <c r="B10" s="7">
         <f>January!B10+February!B10+March!B10+April!B10+May!B10+June!B10+July!B10+August!B10+September!B10+October!B10+November!B10+December!B10</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" s="7">
         <f>January!C10+February!C10+March!C10+April!C10+May!C10+June!C10+July!C10+August!C10+September!C10+October!C10+November!C10+December!C10</f>
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="D10" s="7">
         <f>January!D10+February!D10+March!D10+April!D10+May!D10+June!D10+July!D10+August!D10+September!D10+October!D10+November!D10+December!D10</f>
-        <v>-118</v>
+        <v>-138</v>
       </c>
       <c r="E10" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6088,7 +6124,7 @@
       </c>
       <c r="G10" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.02 : 1</v>
+        <v>0.03 : 1</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6126,15 +6162,15 @@
       </c>
       <c r="B12" s="15">
         <f>January!B12+February!B12+March!B12+April!B12+May!B12+June!B12+July!B12+August!B12+September!B12+October!B12+November!B12+December!B12</f>
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C12" s="15">
         <f>January!C12+February!C12+March!C12+April!C12+May!C12+June!C12+July!C12+August!C12+September!C12+October!C12+November!C12+December!C12</f>
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="D12" s="15">
         <f>January!D12+February!D12+March!D12+April!D12+May!D12+June!D12+July!D12+August!D12+September!D12+October!D12+November!D12+December!D12</f>
-        <v>-84</v>
+        <v>-98</v>
       </c>
       <c r="E12" s="16" t="str">
         <f t="shared" si="0"/>
@@ -6146,7 +6182,7 @@
       </c>
       <c r="G12" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>0.27 : 1</v>
+        <v>0.28 : 1</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6155,15 +6191,15 @@
       </c>
       <c r="B13" s="19">
         <f>January!B13+February!B13+March!B13+April!B13+May!B13+June!B13+July!B13+August!B13+September!B13+October!B13+November!B13+December!B13</f>
-        <v>289</v>
+        <v>323</v>
       </c>
       <c r="C13" s="19">
         <f>January!C13+February!C13+March!C13+April!C13+May!C13+June!C13+July!C13+August!C13+September!C13+October!C13+November!C13+December!C13</f>
-        <v>337</v>
+        <v>396</v>
       </c>
       <c r="D13" s="19">
         <f>January!D13+February!D13+March!D13+April!D13+May!D13+June!D13+July!D13+August!D13+September!D13+October!D13+November!D13+December!D13</f>
-        <v>-48</v>
+        <v>-73</v>
       </c>
       <c r="E13" s="20" t="str">
         <f t="shared" si="0"/>
@@ -6175,7 +6211,7 @@
       </c>
       <c r="G13" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>0.86 : 1</v>
+        <v>0.82 : 1</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6184,15 +6220,15 @@
       </c>
       <c r="B14" s="15">
         <f>January!B14+February!B14+March!B14+April!B14+May!B14+June!B14+July!B14+August!B14+September!B14+October!B14+November!B14+December!B14</f>
-        <v>751</v>
+        <v>867</v>
       </c>
       <c r="C14" s="15">
         <f>January!C14+February!C14+March!C14+April!C14+May!C14+June!C14+July!C14+August!C14+September!C14+October!C14+November!C14+December!C14</f>
-        <v>1716</v>
+        <v>2007</v>
       </c>
       <c r="D14" s="15">
         <f>January!D14+February!D14+March!D14+April!D14+May!D14+June!D14+July!D14+August!D14+September!D14+October!D14+November!D14+December!D14</f>
-        <v>-965</v>
+        <v>-1140</v>
       </c>
       <c r="E14" s="16" t="str">
         <f t="shared" si="0"/>
@@ -6204,7 +6240,7 @@
       </c>
       <c r="G14" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>0.44 : 1</v>
+        <v>0.43 : 1</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6213,15 +6249,15 @@
       </c>
       <c r="B15" s="19">
         <f>January!B15+February!B15+March!B15+April!B15+May!B15+June!B15+July!B15+August!B15+September!B15+October!B15+November!B15+December!B15</f>
-        <v>275</v>
+        <v>327</v>
       </c>
       <c r="C15" s="19">
         <f>January!C15+February!C15+March!C15+April!C15+May!C15+June!C15+July!C15+August!C15+September!C15+October!C15+November!C15+December!C15</f>
-        <v>828</v>
+        <v>961</v>
       </c>
       <c r="D15" s="19">
         <f>January!D15+February!D15+March!D15+April!D15+May!D15+June!D15+July!D15+August!D15+September!D15+October!D15+November!D15+December!D15</f>
-        <v>-553</v>
+        <v>-634</v>
       </c>
       <c r="E15" s="20" t="str">
         <f t="shared" si="0"/>
@@ -6233,7 +6269,7 @@
       </c>
       <c r="G15" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>0.33 : 1</v>
+        <v>0.34 : 1</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6242,15 +6278,15 @@
       </c>
       <c r="B16" s="7">
         <f>January!B16+February!B16+March!B16+April!B16+May!B16+June!B16+July!B16+August!B16+September!B16+October!B16+November!B16+December!B16</f>
-        <v>364</v>
+        <v>413</v>
       </c>
       <c r="C16" s="7">
         <f>January!C16+February!C16+March!C16+April!C16+May!C16+June!C16+July!C16+August!C16+September!C16+October!C16+November!C16+December!C16</f>
-        <v>1038</v>
+        <v>1179</v>
       </c>
       <c r="D16" s="7">
         <f>January!D16+February!D16+March!D16+April!D16+May!D16+June!D16+July!D16+August!D16+September!D16+October!D16+November!D16+December!D16</f>
-        <v>-674</v>
+        <v>-766</v>
       </c>
       <c r="E16" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6271,15 +6307,15 @@
       </c>
       <c r="B17" s="11">
         <f>January!B17+February!B17+March!B17+April!B17+May!B17+June!B17+July!B17+August!B17+September!B17+October!B17+November!B17+December!B17</f>
-        <v>3913</v>
+        <v>4526</v>
       </c>
       <c r="C17" s="11">
         <f>January!C17+February!C17+March!C17+April!C17+May!C17+June!C17+July!C17+August!C17+September!C17+October!C17+November!C17+December!C17</f>
-        <v>2510</v>
+        <v>2906</v>
       </c>
       <c r="D17" s="11">
         <f>January!D17+February!D17+March!D17+April!D17+May!D17+June!D17+July!D17+August!D17+September!D17+October!D17+November!D17+December!D17</f>
-        <v>1403</v>
+        <v>1620</v>
       </c>
       <c r="E17" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6300,15 +6336,15 @@
       </c>
       <c r="B18" s="7">
         <f>January!B18+February!B18+March!B18+April!B18+May!B18+June!B18+July!B18+August!B18+September!B18+October!B18+November!B18+December!B18</f>
-        <v>543</v>
+        <v>595</v>
       </c>
       <c r="C18" s="7">
         <f>January!C18+February!C18+March!C18+April!C18+May!C18+June!C18+July!C18+August!C18+September!C18+October!C18+November!C18+December!C18</f>
-        <v>482</v>
+        <v>578</v>
       </c>
       <c r="D18" s="7">
         <f>January!D18+February!D18+March!D18+April!D18+May!D18+June!D18+July!D18+August!D18+September!D18+October!D18+November!D18+December!D18</f>
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="E18" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6320,7 +6356,7 @@
       </c>
       <c r="G18" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.13 : 1</v>
+        <v>1.03 : 1</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6329,15 +6365,15 @@
       </c>
       <c r="B19" s="11">
         <f>January!B19+February!B19+March!B19+April!B19+May!B19+June!B19+July!B19+August!B19+September!B19+October!B19+November!B19+December!B19</f>
-        <v>2987</v>
+        <v>3550</v>
       </c>
       <c r="C19" s="11">
         <f>January!C19+February!C19+March!C19+April!C19+May!C19+June!C19+July!C19+August!C19+September!C19+October!C19+November!C19+December!C19</f>
-        <v>1959</v>
+        <v>2307</v>
       </c>
       <c r="D19" s="11">
         <f>January!D19+February!D19+March!D19+April!D19+May!D19+June!D19+July!D19+August!D19+September!D19+October!D19+November!D19+December!D19</f>
-        <v>1028</v>
+        <v>1243</v>
       </c>
       <c r="E19" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6349,7 +6385,7 @@
       </c>
       <c r="G19" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.52 : 1</v>
+        <v>1.54 : 1</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6362,11 +6398,11 @@
       </c>
       <c r="C20" s="7">
         <f>January!C20+February!C20+March!C20+April!C20+May!C20+June!C20+July!C20+August!C20+September!C20+October!C20+November!C20+December!C20</f>
-        <v>261</v>
+        <v>304</v>
       </c>
       <c r="D20" s="7">
         <f>January!D20+February!D20+March!D20+April!D20+May!D20+June!D20+July!D20+August!D20+September!D20+October!D20+November!D20+December!D20</f>
-        <v>-250</v>
+        <v>-293</v>
       </c>
       <c r="E20" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6387,15 +6423,15 @@
       </c>
       <c r="B21" s="11">
         <f>January!B21+February!B21+March!B21+April!B21+May!B21+June!B21+July!B21+August!B21+September!B21+October!B21+November!B21+December!B21</f>
-        <v>2932</v>
+        <v>3481</v>
       </c>
       <c r="C21" s="11">
         <f>January!C21+February!C21+March!C21+April!C21+May!C21+June!C21+July!C21+August!C21+September!C21+October!C21+November!C21+December!C21</f>
-        <v>2378</v>
+        <v>2751</v>
       </c>
       <c r="D21" s="11">
         <f>January!D21+February!D21+March!D21+April!D21+May!D21+June!D21+July!D21+August!D21+September!D21+October!D21+November!D21+December!D21</f>
-        <v>554</v>
+        <v>730</v>
       </c>
       <c r="E21" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6407,7 +6443,7 @@
       </c>
       <c r="G21" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.23 : 1</v>
+        <v>1.27 : 1</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6416,15 +6452,15 @@
       </c>
       <c r="B22" s="7">
         <f>January!B22+February!B22+March!B22+April!B22+May!B22+June!B22+July!B22+August!B22+September!B22+October!B22+November!B22+December!B22</f>
-        <v>524</v>
+        <v>586</v>
       </c>
       <c r="C22" s="7">
         <f>January!C22+February!C22+March!C22+April!C22+May!C22+June!C22+July!C22+August!C22+September!C22+October!C22+November!C22+December!C22</f>
-        <v>1341</v>
+        <v>1572</v>
       </c>
       <c r="D22" s="7">
         <f>January!D22+February!D22+March!D22+April!D22+May!D22+June!D22+July!D22+August!D22+September!D22+October!D22+November!D22+December!D22</f>
-        <v>-817</v>
+        <v>-986</v>
       </c>
       <c r="E22" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6436,7 +6472,7 @@
       </c>
       <c r="G22" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.39 : 1</v>
+        <v>0.37 : 1</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6445,15 +6481,15 @@
       </c>
       <c r="B23" s="11">
         <f>January!B23+February!B23+March!B23+April!B23+May!B23+June!B23+July!B23+August!B23+September!B23+October!B23+November!B23+December!B23</f>
-        <v>3751</v>
+        <v>4489</v>
       </c>
       <c r="C23" s="11">
         <f>January!C23+February!C23+March!C23+April!C23+May!C23+June!C23+July!C23+August!C23+September!C23+October!C23+November!C23+December!C23</f>
-        <v>3527</v>
+        <v>4117</v>
       </c>
       <c r="D23" s="11">
         <f>January!D23+February!D23+March!D23+April!D23+May!D23+June!D23+July!D23+August!D23+September!D23+October!D23+November!D23+December!D23</f>
-        <v>224</v>
+        <v>372</v>
       </c>
       <c r="E23" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6465,7 +6501,7 @@
       </c>
       <c r="G23" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.06 : 1</v>
+        <v>1.09 : 1</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6474,15 +6510,15 @@
       </c>
       <c r="B24" s="7">
         <f>January!B24+February!B24+March!B24+April!B24+May!B24+June!B24+July!B24+August!B24+September!B24+October!B24+November!B24+December!B24</f>
-        <v>10595</v>
+        <v>12206</v>
       </c>
       <c r="C24" s="7">
         <f>January!C24+February!C24+March!C24+April!C24+May!C24+June!C24+July!C24+August!C24+September!C24+October!C24+November!C24+December!C24</f>
-        <v>8302</v>
+        <v>9743</v>
       </c>
       <c r="D24" s="7">
         <f>January!D24+February!D24+March!D24+April!D24+May!D24+June!D24+July!D24+August!D24+September!D24+October!D24+November!D24+December!D24</f>
-        <v>2293</v>
+        <v>2463</v>
       </c>
       <c r="E24" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6494,7 +6530,7 @@
       </c>
       <c r="G24" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.28 : 1</v>
+        <v>1.25 : 1</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6503,15 +6539,15 @@
       </c>
       <c r="B25" s="11">
         <f>January!B25+February!B25+March!B25+April!B25+May!B25+June!B25+July!B25+August!B25+September!B25+October!B25+November!B25+December!B25</f>
-        <v>952</v>
+        <v>1055</v>
       </c>
       <c r="C25" s="11">
         <f>January!C25+February!C25+March!C25+April!C25+May!C25+June!C25+July!C25+August!C25+September!C25+October!C25+November!C25+December!C25</f>
-        <v>1962</v>
+        <v>2309</v>
       </c>
       <c r="D25" s="11">
         <f>January!D25+February!D25+March!D25+April!D25+May!D25+June!D25+July!D25+August!D25+September!D25+October!D25+November!D25+December!D25</f>
-        <v>-1010</v>
+        <v>-1254</v>
       </c>
       <c r="E25" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6523,7 +6559,7 @@
       </c>
       <c r="G25" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.49 : 1</v>
+        <v>0.46 : 1</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6561,15 +6597,15 @@
       </c>
       <c r="B27" s="11">
         <f>January!B27+February!B27+March!B27+April!B27+May!B27+June!B27+July!B27+August!B27+September!B27+October!B27+November!B27+December!B27</f>
-        <v>1213</v>
+        <v>1448</v>
       </c>
       <c r="C27" s="11">
         <f>January!C27+February!C27+March!C27+April!C27+May!C27+June!C27+July!C27+August!C27+September!C27+October!C27+November!C27+December!C27</f>
-        <v>944</v>
+        <v>1134</v>
       </c>
       <c r="D27" s="11">
         <f>January!D27+February!D27+March!D27+April!D27+May!D27+June!D27+July!D27+August!D27+September!D27+October!D27+November!D27+December!D27</f>
-        <v>269</v>
+        <v>314</v>
       </c>
       <c r="E27" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6590,15 +6626,15 @@
       </c>
       <c r="B28" s="7">
         <f>January!B28+February!B28+March!B28+April!B28+May!B28+June!B28+July!B28+August!B28+September!B28+October!B28+November!B28+December!B28</f>
-        <v>869</v>
+        <v>1052</v>
       </c>
       <c r="C28" s="7">
         <f>January!C28+February!C28+March!C28+April!C28+May!C28+June!C28+July!C28+August!C28+September!C28+October!C28+November!C28+December!C28</f>
-        <v>698</v>
+        <v>782</v>
       </c>
       <c r="D28" s="7">
         <f>January!D28+February!D28+March!D28+April!D28+May!D28+June!D28+July!D28+August!D28+September!D28+October!D28+November!D28+December!D28</f>
-        <v>171</v>
+        <v>270</v>
       </c>
       <c r="E28" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6610,7 +6646,7 @@
       </c>
       <c r="G28" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.24 : 1</v>
+        <v>1.35 : 1</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6619,15 +6655,15 @@
       </c>
       <c r="B29" s="11">
         <f>January!B29+February!B29+March!B29+April!B29+May!B29+June!B29+July!B29+August!B29+September!B29+October!B29+November!B29+December!B29</f>
-        <v>5009</v>
+        <v>5853</v>
       </c>
       <c r="C29" s="11">
         <f>January!C29+February!C29+March!C29+April!C29+May!C29+June!C29+July!C29+August!C29+September!C29+October!C29+November!C29+December!C29</f>
-        <v>2734</v>
+        <v>3205</v>
       </c>
       <c r="D29" s="11">
         <f>January!D29+February!D29+March!D29+April!D29+May!D29+June!D29+July!D29+August!D29+September!D29+October!D29+November!D29+December!D29</f>
-        <v>2275</v>
+        <v>2648</v>
       </c>
       <c r="E29" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6648,15 +6684,15 @@
       </c>
       <c r="B30" s="7">
         <f>January!B30+February!B30+March!B30+April!B30+May!B30+June!B30+July!B30+August!B30+September!B30+October!B30+November!B30+December!B30</f>
-        <v>175</v>
+        <v>263</v>
       </c>
       <c r="C30" s="7">
         <f>January!C30+February!C30+March!C30+April!C30+May!C30+June!C30+July!C30+August!C30+September!C30+October!C30+November!C30+December!C30</f>
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="D30" s="7">
         <f>January!D30+February!D30+March!D30+April!D30+May!D30+June!D30+July!D30+August!D30+September!D30+October!D30+November!D30+December!D30</f>
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="E30" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6668,7 +6704,7 @@
       </c>
       <c r="G30" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.02 : 1</v>
+        <v>1.33 : 1</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6677,15 +6713,15 @@
       </c>
       <c r="B31" s="11">
         <f>January!B31+February!B31+March!B31+April!B31+May!B31+June!B31+July!B31+August!B31+September!B31+October!B31+November!B31+December!B31</f>
-        <v>691</v>
+        <v>803</v>
       </c>
       <c r="C31" s="11">
         <f>January!C31+February!C31+March!C31+April!C31+May!C31+June!C31+July!C31+August!C31+September!C31+October!C31+November!C31+December!C31</f>
-        <v>1562</v>
+        <v>1899</v>
       </c>
       <c r="D31" s="11">
         <f>January!D31+February!D31+March!D31+April!D31+May!D31+June!D31+July!D31+August!D31+September!D31+October!D31+November!D31+December!D31</f>
-        <v>-871</v>
+        <v>-1096</v>
       </c>
       <c r="E31" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6697,7 +6733,7 @@
       </c>
       <c r="G31" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.44 : 1</v>
+        <v>0.42 : 1</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6706,15 +6742,15 @@
       </c>
       <c r="B32" s="7">
         <f>January!B32+February!B32+March!B32+April!B32+May!B32+June!B32+July!B32+August!B32+September!B32+October!B32+November!B32+December!B32</f>
-        <v>2376</v>
+        <v>2825</v>
       </c>
       <c r="C32" s="7">
         <f>January!C32+February!C32+March!C32+April!C32+May!C32+June!C32+July!C32+August!C32+September!C32+October!C32+November!C32+December!C32</f>
-        <v>3031</v>
+        <v>3494</v>
       </c>
       <c r="D32" s="7">
         <f>January!D32+February!D32+March!D32+April!D32+May!D32+June!D32+July!D32+August!D32+September!D32+October!D32+November!D32+December!D32</f>
-        <v>-655</v>
+        <v>-669</v>
       </c>
       <c r="E32" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6726,7 +6762,7 @@
       </c>
       <c r="G32" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.78 : 1</v>
+        <v>0.81 : 1</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6735,15 +6771,15 @@
       </c>
       <c r="B33" s="11">
         <f>January!B33+February!B33+March!B33+April!B33+May!B33+June!B33+July!B33+August!B33+September!B33+October!B33+November!B33+December!B33</f>
-        <v>2096</v>
+        <v>2419</v>
       </c>
       <c r="C33" s="11">
         <f>January!C33+February!C33+March!C33+April!C33+May!C33+June!C33+July!C33+August!C33+September!C33+October!C33+November!C33+December!C33</f>
-        <v>1893</v>
+        <v>2227</v>
       </c>
       <c r="D33" s="11">
         <f>January!D33+February!D33+March!D33+April!D33+May!D33+June!D33+July!D33+August!D33+September!D33+October!D33+November!D33+December!D33</f>
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="E33" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6755,7 +6791,7 @@
       </c>
       <c r="G33" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.11 : 1</v>
+        <v>1.09 : 1</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6764,15 +6800,15 @@
       </c>
       <c r="B34" s="7">
         <f>January!B34+February!B34+March!B34+April!B34+May!B34+June!B34+July!B34+August!B34+September!B34+October!B34+November!B34+December!B34</f>
-        <v>1014</v>
+        <v>1197</v>
       </c>
       <c r="C34" s="7">
         <f>January!C34+February!C34+March!C34+April!C34+May!C34+June!C34+July!C34+August!C34+September!C34+October!C34+November!C34+December!C34</f>
-        <v>702</v>
+        <v>824</v>
       </c>
       <c r="D34" s="7">
         <f>January!D34+February!D34+March!D34+April!D34+May!D34+June!D34+July!D34+August!D34+September!D34+October!D34+November!D34+December!D34</f>
-        <v>312</v>
+        <v>373</v>
       </c>
       <c r="E34" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6784,7 +6820,7 @@
       </c>
       <c r="G34" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.44 : 1</v>
+        <v>1.45 : 1</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6793,15 +6829,15 @@
       </c>
       <c r="B35" s="11">
         <f>January!B35+February!B35+March!B35+April!B35+May!B35+June!B35+July!B35+August!B35+September!B35+October!B35+November!B35+December!B35</f>
-        <v>5914</v>
+        <v>6946</v>
       </c>
       <c r="C35" s="11">
         <f>January!C35+February!C35+March!C35+April!C35+May!C35+June!C35+July!C35+August!C35+September!C35+October!C35+November!C35+December!C35</f>
-        <v>9026</v>
+        <v>10820</v>
       </c>
       <c r="D35" s="11">
         <f>January!D35+February!D35+March!D35+April!D35+May!D35+June!D35+July!D35+August!D35+September!D35+October!D35+November!D35+December!D35</f>
-        <v>-3112</v>
+        <v>-3874</v>
       </c>
       <c r="E35" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6813,7 +6849,7 @@
       </c>
       <c r="G35" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.66 : 1</v>
+        <v>0.64 : 1</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6822,15 +6858,15 @@
       </c>
       <c r="B36" s="7">
         <f>January!B36+February!B36+March!B36+April!B36+May!B36+June!B36+July!B36+August!B36+September!B36+October!B36+November!B36+December!B36</f>
-        <v>1026</v>
+        <v>1203</v>
       </c>
       <c r="C36" s="7">
         <f>January!C36+February!C36+March!C36+April!C36+May!C36+June!C36+July!C36+August!C36+September!C36+October!C36+November!C36+December!C36</f>
-        <v>3300</v>
+        <v>3804</v>
       </c>
       <c r="D36" s="7">
         <f>January!D36+February!D36+March!D36+April!D36+May!D36+June!D36+July!D36+August!D36+September!D36+October!D36+November!D36+December!D36</f>
-        <v>-2274</v>
+        <v>-2601</v>
       </c>
       <c r="E36" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6842,7 +6878,7 @@
       </c>
       <c r="G36" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.31 : 1</v>
+        <v>0.32 : 1</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6851,15 +6887,15 @@
       </c>
       <c r="B37" s="11">
         <f>January!B37+February!B37+March!B37+April!B37+May!B37+June!B37+July!B37+August!B37+September!B37+October!B37+November!B37+December!B37</f>
-        <v>3408</v>
+        <v>4054</v>
       </c>
       <c r="C37" s="11">
         <f>January!C37+February!C37+March!C37+April!C37+May!C37+June!C37+July!C37+August!C37+September!C37+October!C37+November!C37+December!C37</f>
-        <v>2312</v>
+        <v>2562</v>
       </c>
       <c r="D37" s="11">
         <f>January!D37+February!D37+March!D37+April!D37+May!D37+June!D37+July!D37+August!D37+September!D37+October!D37+November!D37+December!D37</f>
-        <v>1096</v>
+        <v>1492</v>
       </c>
       <c r="E37" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6871,7 +6907,7 @@
       </c>
       <c r="G37" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.47 : 1</v>
+        <v>1.58 : 1</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6880,15 +6916,15 @@
       </c>
       <c r="B38" s="7">
         <f>January!B38+February!B38+March!B38+April!B38+May!B38+June!B38+July!B38+August!B38+September!B38+October!B38+November!B38+December!B38</f>
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="C38" s="7">
         <f>January!C38+February!C38+March!C38+April!C38+May!C38+June!C38+July!C38+August!C38+September!C38+October!C38+November!C38+December!C38</f>
-        <v>1254</v>
+        <v>1481</v>
       </c>
       <c r="D38" s="7">
         <f>January!D38+February!D38+March!D38+April!D38+May!D38+June!D38+July!D38+August!D38+September!D38+October!D38+November!D38+December!D38</f>
-        <v>-1009</v>
+        <v>-1206</v>
       </c>
       <c r="E38" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6900,7 +6936,7 @@
       </c>
       <c r="G38" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.2 : 1</v>
+        <v>0.19 : 1</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6913,11 +6949,11 @@
       </c>
       <c r="C39" s="11">
         <f>January!C39+February!C39+March!C39+April!C39+May!C39+June!C39+July!C39+August!C39+September!C39+October!C39+November!C39+December!C39</f>
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D39" s="11">
         <f>January!D39+February!D39+March!D39+April!D39+May!D39+June!D39+July!D39+August!D39+September!D39+October!D39+November!D39+December!D39</f>
-        <v>-253</v>
+        <v>-254</v>
       </c>
       <c r="E39" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6942,11 +6978,11 @@
       </c>
       <c r="C40" s="23">
         <f>January!C40+February!C40+March!C40+April!C40+May!C40+June!C40+July!C40+August!C40+September!C40+October!C40+November!C40+December!C40</f>
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D40" s="23">
         <f>January!D40+February!D40+March!D40+April!D40+May!D40+June!D40+July!D40+August!D40+September!D40+October!D40+November!D40+December!D40</f>
-        <v>-116</v>
+        <v>-118</v>
       </c>
       <c r="E40" s="24" t="str">
         <f t="shared" si="0"/>
@@ -6971,11 +7007,11 @@
       </c>
       <c r="C41" s="27">
         <f>January!C41+February!C41+March!C41+April!C41+May!C41+June!C41+July!C41+August!C41+September!C41+October!C41+November!C41+December!C41</f>
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D41" s="27">
         <f>January!D41+February!D41+March!D41+April!D41+May!D41+June!D41+July!D41+August!D41+September!D41+October!D41+November!D41+December!D41</f>
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="E41" s="28" t="str">
         <f t="shared" si="0"/>
@@ -7000,11 +7036,11 @@
       </c>
       <c r="C42" s="23">
         <f>January!C42+February!C42+March!C42+April!C42+May!C42+June!C42+July!C42+August!C42+September!C42+October!C42+November!C42+December!C42</f>
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D42" s="23">
         <f>January!D42+February!D42+March!D42+April!D42+May!D42+June!D42+July!D42+August!D42+September!D42+October!D42+November!D42+December!D42</f>
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="E42" s="24" t="str">
         <f t="shared" si="0"/>
@@ -7025,15 +7061,15 @@
       </c>
       <c r="B43" s="27">
         <f>January!B43+February!B43+March!B43+April!B43+May!B43+June!B43+July!B43+August!B43+September!B43+October!B43+November!B43+December!B43</f>
-        <v>807</v>
+        <v>936</v>
       </c>
       <c r="C43" s="27">
         <f>January!C43+February!C43+March!C43+April!C43+May!C43+June!C43+July!C43+August!C43+September!C43+October!C43+November!C43+December!C43</f>
-        <v>593</v>
+        <v>677</v>
       </c>
       <c r="D43" s="27">
         <f>January!D43+February!D43+March!D43+April!D43+May!D43+June!D43+July!D43+August!D43+September!D43+October!D43+November!D43+December!D43</f>
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="E43" s="28" t="str">
         <f t="shared" si="0"/>
@@ -7045,7 +7081,7 @@
       </c>
       <c r="G43" s="29" t="str">
         <f t="shared" si="2"/>
-        <v>1.36 : 1</v>
+        <v>1.38 : 1</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7054,15 +7090,15 @@
       </c>
       <c r="B44" s="7">
         <f>January!B44+February!B44+March!B44+April!B44+May!B44+June!B44+July!B44+August!B44+September!B44+October!B44+November!B44+December!B44</f>
-        <v>381</v>
+        <v>436</v>
       </c>
       <c r="C44" s="7">
         <f>January!C44+February!C44+March!C44+April!C44+May!C44+June!C44+July!C44+August!C44+September!C44+October!C44+November!C44+December!C44</f>
-        <v>1064</v>
+        <v>1248</v>
       </c>
       <c r="D44" s="7">
         <f>January!D44+February!D44+March!D44+April!D44+May!D44+June!D44+July!D44+August!D44+September!D44+October!D44+November!D44+December!D44</f>
-        <v>-683</v>
+        <v>-812</v>
       </c>
       <c r="E44" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7074,7 +7110,7 @@
       </c>
       <c r="G44" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.36 : 1</v>
+        <v>0.35 : 1</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7083,15 +7119,15 @@
       </c>
       <c r="B45" s="11">
         <f>January!B45+February!B45+March!B45+April!B45+May!B45+June!B45+July!B45+August!B45+September!B45+October!B45+November!B45+December!B45</f>
-        <v>3093</v>
+        <v>3599</v>
       </c>
       <c r="C45" s="11">
         <f>January!C45+February!C45+March!C45+April!C45+May!C45+June!C45+July!C45+August!C45+September!C45+October!C45+November!C45+December!C45</f>
-        <v>3457</v>
+        <v>4073</v>
       </c>
       <c r="D45" s="11">
         <f>January!D45+February!D45+March!D45+April!D45+May!D45+June!D45+July!D45+August!D45+September!D45+October!D45+November!D45+December!D45</f>
-        <v>-364</v>
+        <v>-474</v>
       </c>
       <c r="E45" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7103,7 +7139,7 @@
       </c>
       <c r="G45" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.89 : 1</v>
+        <v>0.88 : 1</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7112,15 +7148,15 @@
       </c>
       <c r="B46" s="7">
         <f>January!B46+February!B46+March!B46+April!B46+May!B46+June!B46+July!B46+August!B46+September!B46+October!B46+November!B46+December!B46</f>
-        <v>5150</v>
+        <v>5887</v>
       </c>
       <c r="C46" s="7">
         <f>January!C46+February!C46+March!C46+April!C46+May!C46+June!C46+July!C46+August!C46+September!C46+October!C46+November!C46+December!C46</f>
-        <v>4041</v>
+        <v>4740</v>
       </c>
       <c r="D46" s="7">
         <f>January!D46+February!D46+March!D46+April!D46+May!D46+June!D46+July!D46+August!D46+September!D46+October!D46+November!D46+December!D46</f>
-        <v>1109</v>
+        <v>1147</v>
       </c>
       <c r="E46" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7132,7 +7168,7 @@
       </c>
       <c r="G46" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.27 : 1</v>
+        <v>1.24 : 1</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7141,15 +7177,15 @@
       </c>
       <c r="B47" s="11">
         <f>January!B47+February!B47+March!B47+April!B47+May!B47+June!B47+July!B47+August!B47+September!B47+October!B47+November!B47+December!B47</f>
-        <v>1357</v>
+        <v>1581</v>
       </c>
       <c r="C47" s="11">
         <f>January!C47+February!C47+March!C47+April!C47+May!C47+June!C47+July!C47+August!C47+September!C47+October!C47+November!C47+December!C47</f>
-        <v>3441</v>
+        <v>3989</v>
       </c>
       <c r="D47" s="11">
         <f>January!D47+February!D47+March!D47+April!D47+May!D47+June!D47+July!D47+August!D47+September!D47+October!D47+November!D47+December!D47</f>
-        <v>-2084</v>
+        <v>-2408</v>
       </c>
       <c r="E47" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7161,7 +7197,7 @@
       </c>
       <c r="G47" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>0.39 : 1</v>
+        <v>0.4 : 1</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7170,15 +7206,15 @@
       </c>
       <c r="B48" s="7">
         <f>January!B48+February!B48+March!B48+April!B48+May!B48+June!B48+July!B48+August!B48+September!B48+October!B48+November!B48+December!B48</f>
-        <v>2380</v>
+        <v>2673</v>
       </c>
       <c r="C48" s="7">
         <f>January!C48+February!C48+March!C48+April!C48+May!C48+June!C48+July!C48+August!C48+September!C48+October!C48+November!C48+December!C48</f>
-        <v>1487</v>
+        <v>1642</v>
       </c>
       <c r="D48" s="7">
         <f>January!D48+February!D48+March!D48+April!D48+May!D48+June!D48+July!D48+August!D48+September!D48+October!D48+November!D48+December!D48</f>
-        <v>893</v>
+        <v>1031</v>
       </c>
       <c r="E48" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7190,7 +7226,7 @@
       </c>
       <c r="G48" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>1.6 : 1</v>
+        <v>1.63 : 1</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7199,15 +7235,15 @@
       </c>
       <c r="B49" s="11">
         <f>January!B49+February!B49+March!B49+April!B49+May!B49+June!B49+July!B49+August!B49+September!B49+October!B49+November!B49+December!B49</f>
-        <v>5757</v>
+        <v>6699</v>
       </c>
       <c r="C49" s="11">
         <f>January!C49+February!C49+March!C49+April!C49+May!C49+June!C49+July!C49+August!C49+September!C49+October!C49+November!C49+December!C49</f>
-        <v>3276</v>
+        <v>3821</v>
       </c>
       <c r="D49" s="11">
         <f>January!D49+February!D49+March!D49+April!D49+May!D49+June!D49+July!D49+August!D49+September!D49+October!D49+November!D49+December!D49</f>
-        <v>2481</v>
+        <v>2878</v>
       </c>
       <c r="E49" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7219,7 +7255,7 @@
       </c>
       <c r="G49" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.76 : 1</v>
+        <v>1.75 : 1</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7228,15 +7264,15 @@
       </c>
       <c r="B50" s="7">
         <f>January!B50+February!B50+March!B50+April!B50+May!B50+June!B50+July!B50+August!B50+September!B50+October!B50+November!B50+December!B50</f>
-        <v>717</v>
+        <v>810</v>
       </c>
       <c r="C50" s="7">
         <f>January!C50+February!C50+March!C50+April!C50+May!C50+June!C50+July!C50+August!C50+September!C50+October!C50+November!C50+December!C50</f>
-        <v>987</v>
+        <v>1119</v>
       </c>
       <c r="D50" s="7">
         <f>January!D50+February!D50+March!D50+April!D50+May!D50+June!D50+July!D50+August!D50+September!D50+October!D50+November!D50+December!D50</f>
-        <v>-270</v>
+        <v>-309</v>
       </c>
       <c r="E50" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7248,7 +7284,7 @@
       </c>
       <c r="G50" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.73 : 1</v>
+        <v>0.72 : 1</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7257,15 +7293,15 @@
       </c>
       <c r="B51" s="11">
         <f>January!B51+February!B51+March!B51+April!B51+May!B51+June!B51+July!B51+August!B51+September!B51+October!B51+November!B51+December!B51</f>
-        <v>2675</v>
+        <v>2994</v>
       </c>
       <c r="C51" s="11">
         <f>January!C51+February!C51+March!C51+April!C51+May!C51+June!C51+July!C51+August!C51+September!C51+October!C51+November!C51+December!C51</f>
-        <v>2183</v>
+        <v>2538</v>
       </c>
       <c r="D51" s="11">
         <f>January!D51+February!D51+March!D51+April!D51+May!D51+June!D51+July!D51+August!D51+September!D51+October!D51+November!D51+December!D51</f>
-        <v>492</v>
+        <v>456</v>
       </c>
       <c r="E51" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7277,7 +7313,7 @@
       </c>
       <c r="G51" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>1.23 : 1</v>
+        <v>1.18 : 1</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7286,15 +7322,15 @@
       </c>
       <c r="B52" s="7">
         <f>January!B52+February!B52+March!B52+April!B52+May!B52+June!B52+July!B52+August!B52+September!B52+October!B52+November!B52+December!B52</f>
-        <v>671</v>
+        <v>697</v>
       </c>
       <c r="C52" s="7">
         <f>January!C52+February!C52+March!C52+April!C52+May!C52+June!C52+July!C52+August!C52+September!C52+October!C52+November!C52+December!C52</f>
-        <v>1327</v>
+        <v>1512</v>
       </c>
       <c r="D52" s="7">
         <f>January!D52+February!D52+March!D52+April!D52+May!D52+June!D52+July!D52+August!D52+September!D52+October!D52+November!D52+December!D52</f>
-        <v>-656</v>
+        <v>-815</v>
       </c>
       <c r="E52" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7306,7 +7342,7 @@
       </c>
       <c r="G52" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>0.51 : 1</v>
+        <v>0.46 : 1</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7315,15 +7351,15 @@
       </c>
       <c r="B53" s="11">
         <f>January!B53+February!B53+March!B53+April!B53+May!B53+June!B53+July!B53+August!B53+September!B53+October!B53+November!B53+December!B53</f>
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="C53" s="11">
         <f>January!C53+February!C53+March!C53+April!C53+May!C53+June!C53+July!C53+August!C53+September!C53+October!C53+November!C53+December!C53</f>
-        <v>1486</v>
+        <v>1751</v>
       </c>
       <c r="D53" s="11">
         <f>January!D53+February!D53+March!D53+April!D53+May!D53+June!D53+July!D53+August!D53+September!D53+October!D53+November!D53+December!D53</f>
-        <v>-1329</v>
+        <v>-1558</v>
       </c>
       <c r="E53" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7344,15 +7380,15 @@
       </c>
       <c r="B54" s="31">
         <f>January!B54+February!B54+March!B54+April!B54+May!B54+June!B54+July!B54+August!B54+September!B54+October!B54+November!B54+December!B54</f>
-        <v>2384</v>
+        <v>2688</v>
       </c>
       <c r="C54" s="31">
         <f>January!C54+February!C54+March!C54+April!C54+May!C54+June!C54+July!C54+August!C54+September!C54+October!C54+November!C54+December!C54</f>
-        <v>1241</v>
+        <v>1476</v>
       </c>
       <c r="D54" s="31">
         <f>January!D54+February!D54+March!D54+April!D54+May!D54+June!D54+July!D54+August!D54+September!D54+October!D54+November!D54+December!D54</f>
-        <v>1143</v>
+        <v>1212</v>
       </c>
       <c r="E54" s="32" t="str">
         <f t="shared" si="0"/>
@@ -7364,7 +7400,7 @@
       </c>
       <c r="G54" s="33" t="str">
         <f t="shared" si="2"/>
-        <v>1.92 : 1</v>
+        <v>1.82 : 1</v>
       </c>
     </row>
   </sheetData>
@@ -13346,108 +13382,204 @@
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8"/>
+      <c r="B2" s="7">
+        <v>1459</v>
+      </c>
+      <c r="C2" s="7">
+        <v>1173</v>
+      </c>
+      <c r="D2" s="7">
+        <v>286</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F2" s="8"/>
-      <c r="G2" s="9"/>
+      <c r="G2" s="9" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="12"/>
+      <c r="B3" s="11">
+        <v>771</v>
+      </c>
+      <c r="C3" s="11">
+        <v>346</v>
+      </c>
+      <c r="D3" s="11">
+        <v>425</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F3" s="12"/>
-      <c r="G3" s="13"/>
+      <c r="G3" s="13" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8"/>
+      <c r="B4" s="7">
+        <v>1270</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1062</v>
+      </c>
+      <c r="D4" s="7">
+        <v>208</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F4" s="8"/>
-      <c r="G4" s="9"/>
+      <c r="G4" s="9" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
+      <c r="B5" s="11">
+        <v>31</v>
+      </c>
+      <c r="C5" s="11">
+        <v>105</v>
+      </c>
+      <c r="D5" s="11">
+        <v>-74</v>
+      </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13"/>
+      <c r="F5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+      <c r="B6" s="7">
+        <v>920</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1082</v>
+      </c>
+      <c r="D6" s="7">
+        <v>-162</v>
+      </c>
       <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9"/>
+      <c r="F6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12"/>
+      <c r="B7" s="11">
+        <v>273</v>
+      </c>
+      <c r="C7" s="11">
+        <v>169</v>
+      </c>
+      <c r="D7" s="11">
+        <v>104</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="13"/>
+      <c r="G7" s="13" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8"/>
+      <c r="B8" s="7">
+        <v>165</v>
+      </c>
+      <c r="C8" s="7">
+        <v>138</v>
+      </c>
+      <c r="D8" s="7">
+        <v>27</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F8" s="8"/>
-      <c r="G8" s="9"/>
+      <c r="G8" s="9" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12"/>
+      <c r="B9" s="11">
+        <v>76</v>
+      </c>
+      <c r="C9" s="11">
+        <v>64</v>
+      </c>
+      <c r="D9" s="11">
+        <v>12</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="13"/>
+      <c r="G9" s="13" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="B10" s="7">
+        <v>2</v>
+      </c>
+      <c r="C10" s="7">
+        <v>22</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-20</v>
+      </c>
       <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9"/>
+      <c r="F10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
+      <c r="B11" s="11">
+        <v>0</v>
+      </c>
+      <c r="C11" s="11">
+        <v>0</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0</v>
+      </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
       <c r="G11" s="13"/>
@@ -13456,163 +13588,309 @@
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
+      <c r="B12" s="15">
+        <v>8</v>
+      </c>
+      <c r="C12" s="15">
+        <v>22</v>
+      </c>
+      <c r="D12" s="15">
+        <v>-14</v>
+      </c>
       <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17"/>
+      <c r="F12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
+      <c r="B13" s="19">
+        <v>34</v>
+      </c>
+      <c r="C13" s="19">
+        <v>59</v>
+      </c>
+      <c r="D13" s="19">
+        <v>-25</v>
+      </c>
       <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="21"/>
+      <c r="F13" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
+      <c r="B14" s="15">
+        <v>116</v>
+      </c>
+      <c r="C14" s="15">
+        <v>291</v>
+      </c>
+      <c r="D14" s="15">
+        <v>-175</v>
+      </c>
       <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="17"/>
+      <c r="F14" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
+      <c r="B15" s="19">
+        <v>52</v>
+      </c>
+      <c r="C15" s="19">
+        <v>133</v>
+      </c>
+      <c r="D15" s="19">
+        <v>-81</v>
+      </c>
       <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="21"/>
+      <c r="F15" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
+      <c r="B16" s="7">
+        <v>49</v>
+      </c>
+      <c r="C16" s="7">
+        <v>141</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-92</v>
+      </c>
       <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="9"/>
+      <c r="F16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="12"/>
+      <c r="B17" s="11">
+        <v>613</v>
+      </c>
+      <c r="C17" s="11">
+        <v>396</v>
+      </c>
+      <c r="D17" s="11">
+        <v>217</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F17" s="12"/>
-      <c r="G17" s="13"/>
+      <c r="G17" s="13" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
+      <c r="B18" s="7">
+        <v>52</v>
+      </c>
+      <c r="C18" s="7">
+        <v>96</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-44</v>
+      </c>
       <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="9"/>
+      <c r="F18" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="12"/>
+      <c r="B19" s="11">
+        <v>563</v>
+      </c>
+      <c r="C19" s="11">
+        <v>348</v>
+      </c>
+      <c r="D19" s="11">
+        <v>215</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="13"/>
+      <c r="G19" s="13" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
+      <c r="B20" s="7">
+        <v>0</v>
+      </c>
+      <c r="C20" s="7">
+        <v>43</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-43</v>
+      </c>
       <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="9"/>
+      <c r="F20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="12"/>
+      <c r="B21" s="11">
+        <v>549</v>
+      </c>
+      <c r="C21" s="11">
+        <v>373</v>
+      </c>
+      <c r="D21" s="11">
+        <v>176</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="13"/>
+      <c r="G21" s="13" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+      <c r="B22" s="7">
+        <v>62</v>
+      </c>
+      <c r="C22" s="7">
+        <v>231</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-169</v>
+      </c>
       <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="9"/>
+      <c r="F22" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="12"/>
+      <c r="B23" s="11">
+        <v>738</v>
+      </c>
+      <c r="C23" s="11">
+        <v>590</v>
+      </c>
+      <c r="D23" s="11">
+        <v>148</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="13"/>
+      <c r="G23" s="13" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8"/>
+      <c r="B24" s="7">
+        <v>1611</v>
+      </c>
+      <c r="C24" s="7">
+        <v>1441</v>
+      </c>
+      <c r="D24" s="7">
+        <v>170</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
+      <c r="G24" s="9" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="B25" s="11">
+        <v>103</v>
+      </c>
+      <c r="C25" s="11">
+        <v>347</v>
+      </c>
+      <c r="D25" s="11">
+        <v>-244</v>
+      </c>
       <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="13"/>
+      <c r="F25" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
+      <c r="B26" s="7">
+        <v>0</v>
+      </c>
+      <c r="C26" s="7">
+        <v>0</v>
+      </c>
+      <c r="D26" s="7">
+        <v>0</v>
+      </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
@@ -13621,309 +13899,589 @@
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="12"/>
+      <c r="B27" s="11">
+        <v>235</v>
+      </c>
+      <c r="C27" s="11">
+        <v>190</v>
+      </c>
+      <c r="D27" s="11">
+        <v>45</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F27" s="12"/>
-      <c r="G27" s="13"/>
+      <c r="G27" s="13" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="8"/>
+      <c r="B28" s="7">
+        <v>183</v>
+      </c>
+      <c r="C28" s="7">
+        <v>84</v>
+      </c>
+      <c r="D28" s="7">
+        <v>99</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F28" s="8"/>
-      <c r="G28" s="9"/>
+      <c r="G28" s="9" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="12"/>
+      <c r="B29" s="11">
+        <v>844</v>
+      </c>
+      <c r="C29" s="11">
+        <v>471</v>
+      </c>
+      <c r="D29" s="11">
+        <v>373</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F29" s="12"/>
-      <c r="G29" s="13"/>
+      <c r="G29" s="13" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="8"/>
+      <c r="B30" s="7">
+        <v>88</v>
+      </c>
+      <c r="C30" s="7">
+        <v>27</v>
+      </c>
+      <c r="D30" s="7">
+        <v>61</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F30" s="8"/>
-      <c r="G30" s="9"/>
+      <c r="G30" s="9" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
+      <c r="B31" s="11">
+        <v>112</v>
+      </c>
+      <c r="C31" s="11">
+        <v>337</v>
+      </c>
+      <c r="D31" s="11">
+        <v>-225</v>
+      </c>
       <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="13"/>
+      <c r="F31" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
+      <c r="B32" s="7">
+        <v>449</v>
+      </c>
+      <c r="C32" s="7">
+        <v>463</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-14</v>
+      </c>
       <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="9"/>
+      <c r="F32" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
+      <c r="B33" s="11">
+        <v>323</v>
+      </c>
+      <c r="C33" s="11">
+        <v>334</v>
+      </c>
+      <c r="D33" s="11">
+        <v>-11</v>
+      </c>
       <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="13"/>
+      <c r="F33" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="8"/>
+      <c r="B34" s="7">
+        <v>183</v>
+      </c>
+      <c r="C34" s="7">
+        <v>122</v>
+      </c>
+      <c r="D34" s="7">
+        <v>61</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F34" s="8"/>
-      <c r="G34" s="9"/>
+      <c r="G34" s="9" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
+      <c r="B35" s="11">
+        <v>1032</v>
+      </c>
+      <c r="C35" s="11">
+        <v>1794</v>
+      </c>
+      <c r="D35" s="11">
+        <v>-762</v>
+      </c>
       <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="13"/>
+      <c r="F35" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
+      <c r="B36" s="7">
+        <v>177</v>
+      </c>
+      <c r="C36" s="7">
+        <v>504</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-327</v>
+      </c>
       <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="9"/>
+      <c r="F36" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="12"/>
+      <c r="B37" s="11">
+        <v>646</v>
+      </c>
+      <c r="C37" s="11">
+        <v>250</v>
+      </c>
+      <c r="D37" s="11">
+        <v>396</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="13"/>
+      <c r="G37" s="13" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
+      <c r="B38" s="7">
+        <v>30</v>
+      </c>
+      <c r="C38" s="7">
+        <v>227</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-197</v>
+      </c>
       <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="9"/>
+      <c r="F38" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
+      <c r="B39" s="11">
+        <v>0</v>
+      </c>
+      <c r="C39" s="11">
+        <v>1</v>
+      </c>
+      <c r="D39" s="11">
+        <v>-1</v>
+      </c>
       <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="13"/>
+      <c r="F39" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
+      <c r="B40" s="23">
+        <v>0</v>
+      </c>
+      <c r="C40" s="23">
+        <v>2</v>
+      </c>
+      <c r="D40" s="23">
+        <v>-2</v>
+      </c>
       <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="25"/>
+      <c r="F40" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="25" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
+      <c r="B41" s="27">
+        <v>0</v>
+      </c>
+      <c r="C41" s="27">
+        <v>1</v>
+      </c>
+      <c r="D41" s="27">
+        <v>-1</v>
+      </c>
       <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="29"/>
+      <c r="F41" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
+      <c r="B42" s="23">
+        <v>0</v>
+      </c>
+      <c r="C42" s="23">
+        <v>1</v>
+      </c>
+      <c r="D42" s="23">
+        <v>-1</v>
+      </c>
       <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="25"/>
+      <c r="F42" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="25" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="28"/>
+      <c r="B43" s="27">
+        <v>129</v>
+      </c>
+      <c r="C43" s="27">
+        <v>84</v>
+      </c>
+      <c r="D43" s="27">
+        <v>45</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>8</v>
+      </c>
       <c r="F43" s="28"/>
-      <c r="G43" s="29"/>
+      <c r="G43" s="29" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
+      <c r="B44" s="7">
+        <v>55</v>
+      </c>
+      <c r="C44" s="7">
+        <v>184</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-129</v>
+      </c>
       <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="9"/>
+      <c r="F44" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
+      <c r="B45" s="11">
+        <v>506</v>
+      </c>
+      <c r="C45" s="11">
+        <v>616</v>
+      </c>
+      <c r="D45" s="11">
+        <v>-110</v>
+      </c>
       <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="13"/>
+      <c r="F45" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="8"/>
+      <c r="B46" s="7">
+        <v>737</v>
+      </c>
+      <c r="C46" s="7">
+        <v>699</v>
+      </c>
+      <c r="D46" s="7">
+        <v>38</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F46" s="8"/>
-      <c r="G46" s="9"/>
+      <c r="G46" s="9" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
+      <c r="B47" s="11">
+        <v>224</v>
+      </c>
+      <c r="C47" s="11">
+        <v>548</v>
+      </c>
+      <c r="D47" s="11">
+        <v>-324</v>
+      </c>
       <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="13"/>
+      <c r="F47" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="8"/>
+      <c r="B48" s="7">
+        <v>293</v>
+      </c>
+      <c r="C48" s="7">
+        <v>155</v>
+      </c>
+      <c r="D48" s="7">
+        <v>138</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F48" s="8"/>
-      <c r="G48" s="9"/>
+      <c r="G48" s="9" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="12"/>
+      <c r="B49" s="11">
+        <v>942</v>
+      </c>
+      <c r="C49" s="11">
+        <v>545</v>
+      </c>
+      <c r="D49" s="11">
+        <v>397</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="13"/>
+      <c r="G49" s="13" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
+      <c r="B50" s="7">
+        <v>93</v>
+      </c>
+      <c r="C50" s="7">
+        <v>132</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-39</v>
+      </c>
       <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="9"/>
+      <c r="F50" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
+      <c r="B51" s="11">
+        <v>319</v>
+      </c>
+      <c r="C51" s="11">
+        <v>355</v>
+      </c>
+      <c r="D51" s="11">
+        <v>-36</v>
+      </c>
       <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="13"/>
+      <c r="F51" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
+      <c r="B52" s="7">
+        <v>26</v>
+      </c>
+      <c r="C52" s="7">
+        <v>185</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-159</v>
+      </c>
       <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="9"/>
+      <c r="F52" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
+      <c r="B53" s="11">
+        <v>36</v>
+      </c>
+      <c r="C53" s="11">
+        <v>265</v>
+      </c>
+      <c r="D53" s="11">
+        <v>-229</v>
+      </c>
       <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="13"/>
+      <c r="F53" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" s="13" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B54" s="31"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="32"/>
+      <c r="B54" s="31">
+        <v>304</v>
+      </c>
+      <c r="C54" s="31">
+        <v>235</v>
+      </c>
+      <c r="D54" s="31">
+        <v>69</v>
+      </c>
+      <c r="E54" s="32" t="s">
+        <v>8</v>
+      </c>
       <c r="F54" s="32"/>
-      <c r="G54" s="33"/>
+      <c r="G54" s="33" t="s">
+        <v>193</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
